--- a/report-2026-06-04.xlsx
+++ b/report-2026-06-04.xlsx
@@ -21,7 +21,7 @@
     <t>PunMonitor Leader Election — Current State</t>
   </si>
   <si>
-    <t>Generated 2026-06-04T00:05:00+05:30</t>
+    <t>Generated 2026-06-04T00:05:01+05:30</t>
   </si>
   <si>
     <t>Election method</t>
@@ -72,7 +72,7 @@
     <t>Leader last update</t>
   </si>
   <si>
-    <t>2026-06-03T22:56:12+05:30 (1h8m47s ago)</t>
+    <t>2026-06-03T22:56:12+05:30 (1h8m48s ago)</t>
   </si>
   <si>
     <t>Leader stale?</t>
@@ -1204,7 +1204,7 @@
     <t>Generated</t>
   </si>
   <si>
-    <t>2026-06-04T00:05:00+05:30</t>
+    <t>2026-06-04T00:05:01+05:30</t>
   </si>
   <si>
     <t>Total events</t>
@@ -1799,7 +1799,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>1h 39m 19s</t>
+          <t>1h 39m 20s</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -1829,7 +1829,7 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>00:05:00</t>
+          <t>00:05:01</t>
         </is>
       </c>
     </row>
@@ -1936,7 +1936,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>00:05:00</t>
+          <t>00:05:01</t>
         </is>
       </c>
     </row>

--- a/report-2026-06-04.xlsx
+++ b/report-2026-06-04.xlsx
@@ -21,7 +21,7 @@
     <t>PunMonitor Leader Election — Current State</t>
   </si>
   <si>
-    <t>Generated 2026-06-04T00:05:01+05:30</t>
+    <t>Generated 2026-06-04T00:05:03+05:30</t>
   </si>
   <si>
     <t>Election method</t>
@@ -72,7 +72,7 @@
     <t>Leader last update</t>
   </si>
   <si>
-    <t>2026-06-03T22:56:12+05:30 (1h8m48s ago)</t>
+    <t>2026-06-03T22:56:12+05:30 (1h8m50s ago)</t>
   </si>
   <si>
     <t>Leader stale?</t>
@@ -1204,7 +1204,7 @@
     <t>Generated</t>
   </si>
   <si>
-    <t>2026-06-04T00:05:01+05:30</t>
+    <t>2026-06-04T00:05:03+05:30</t>
   </si>
   <si>
     <t>Total events</t>
@@ -1799,7 +1799,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>1h 39m 20s</t>
+          <t>1h 39m 22s</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -1829,7 +1829,7 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>00:05:01</t>
+          <t>00:05:03</t>
         </is>
       </c>
     </row>
@@ -1936,7 +1936,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>00:05:01</t>
+          <t>00:05:03</t>
         </is>
       </c>
     </row>

--- a/report-2026-06-04.xlsx
+++ b/report-2026-06-04.xlsx
@@ -21,7 +21,7 @@
     <t>PunMonitor Leader Election — Current State</t>
   </si>
   <si>
-    <t>Generated 2026-06-04T00:05:03+05:30</t>
+    <t>Generated 2026-06-04T00:05:04+05:30</t>
   </si>
   <si>
     <t>Election method</t>
@@ -72,7 +72,7 @@
     <t>Leader last update</t>
   </si>
   <si>
-    <t>2026-06-03T22:56:12+05:30 (1h8m50s ago)</t>
+    <t>2026-06-03T22:56:12+05:30 (1h8m51s ago)</t>
   </si>
   <si>
     <t>Leader stale?</t>
@@ -1204,7 +1204,7 @@
     <t>Generated</t>
   </si>
   <si>
-    <t>2026-06-04T00:05:03+05:30</t>
+    <t>2026-06-04T00:05:04+05:30</t>
   </si>
   <si>
     <t>Total events</t>
@@ -1799,7 +1799,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>1h 39m 22s</t>
+          <t>1h 39m 24s</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -1829,7 +1829,7 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>00:05:03</t>
+          <t>00:05:04</t>
         </is>
       </c>
     </row>
@@ -1936,7 +1936,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>00:05:03</t>
+          <t>00:05:04</t>
         </is>
       </c>
     </row>

--- a/report-2026-06-04.xlsx
+++ b/report-2026-06-04.xlsx
@@ -21,7 +21,7 @@
     <t>PunMonitor Leader Election — Current State</t>
   </si>
   <si>
-    <t>Generated 2026-06-04T00:05:04+05:30</t>
+    <t>Generated 2026-06-04T00:05:06+05:30</t>
   </si>
   <si>
     <t>Election method</t>
@@ -72,7 +72,7 @@
     <t>Leader last update</t>
   </si>
   <si>
-    <t>2026-06-03T22:56:12+05:30 (1h8m51s ago)</t>
+    <t>2026-06-03T22:56:12+05:30 (1h8m53s ago)</t>
   </si>
   <si>
     <t>Leader stale?</t>
@@ -1204,7 +1204,7 @@
     <t>Generated</t>
   </si>
   <si>
-    <t>2026-06-04T00:05:04+05:30</t>
+    <t>2026-06-04T00:05:06+05:30</t>
   </si>
   <si>
     <t>Total events</t>
@@ -1799,7 +1799,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>1h 39m 24s</t>
+          <t>1h 39m 25s</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -1819,7 +1819,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>8h 7m 0s</t>
+          <t>8h 7m 5s</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -1829,7 +1829,7 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>00:05:04</t>
+          <t>00:05:06</t>
         </is>
       </c>
     </row>
@@ -1936,7 +1936,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>00:05:04</t>
+          <t>00:05:06</t>
         </is>
       </c>
     </row>

--- a/report-2026-06-04.xlsx
+++ b/report-2026-06-04.xlsx
@@ -21,7 +21,7 @@
     <t>PunMonitor Leader Election — Current State</t>
   </si>
   <si>
-    <t>Generated 2026-06-04T00:05:06+05:30</t>
+    <t>Generated 2026-06-04T00:05:08+05:30</t>
   </si>
   <si>
     <t>Election method</t>
@@ -72,7 +72,7 @@
     <t>Leader last update</t>
   </si>
   <si>
-    <t>2026-06-03T22:56:12+05:30 (1h8m53s ago)</t>
+    <t>2026-06-03T22:56:12+05:30 (1h8m55s ago)</t>
   </si>
   <si>
     <t>Leader stale?</t>
@@ -1204,7 +1204,7 @@
     <t>Generated</t>
   </si>
   <si>
-    <t>2026-06-04T00:05:06+05:30</t>
+    <t>2026-06-04T00:05:08+05:30</t>
   </si>
   <si>
     <t>Total events</t>
@@ -1799,7 +1799,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>1h 39m 25s</t>
+          <t>1h 39m 27s</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -1829,7 +1829,7 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>00:05:06</t>
+          <t>00:05:08</t>
         </is>
       </c>
     </row>
@@ -1936,7 +1936,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>00:05:06</t>
+          <t>00:05:08</t>
         </is>
       </c>
     </row>

--- a/report-2026-06-04.xlsx
+++ b/report-2026-06-04.xlsx
@@ -21,7 +21,7 @@
     <t>PunMonitor Leader Election — Current State</t>
   </si>
   <si>
-    <t>Generated 2026-06-04T00:05:08+05:30</t>
+    <t>Generated 2026-06-04T00:05:09+05:30</t>
   </si>
   <si>
     <t>Election method</t>
@@ -72,7 +72,7 @@
     <t>Leader last update</t>
   </si>
   <si>
-    <t>2026-06-03T22:56:12+05:30 (1h8m55s ago)</t>
+    <t>2026-06-03T22:56:12+05:30 (1h8m56s ago)</t>
   </si>
   <si>
     <t>Leader stale?</t>
@@ -1204,7 +1204,7 @@
     <t>Generated</t>
   </si>
   <si>
-    <t>2026-06-04T00:05:08+05:30</t>
+    <t>2026-06-04T00:05:09+05:30</t>
   </si>
   <si>
     <t>Total events</t>
@@ -1799,7 +1799,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>1h 39m 27s</t>
+          <t>1h 39m 28s</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -1829,7 +1829,7 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>00:05:08</t>
+          <t>00:05:09</t>
         </is>
       </c>
     </row>
@@ -1936,7 +1936,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>00:05:08</t>
+          <t>00:05:09</t>
         </is>
       </c>
     </row>

--- a/report-2026-06-04.xlsx
+++ b/report-2026-06-04.xlsx
@@ -21,7 +21,7 @@
     <t>PunMonitor Leader Election — Current State</t>
   </si>
   <si>
-    <t>Generated 2026-06-04T00:05:09+05:30</t>
+    <t>Generated 2026-06-04T00:05:11+05:30</t>
   </si>
   <si>
     <t>Election method</t>
@@ -72,7 +72,7 @@
     <t>Leader last update</t>
   </si>
   <si>
-    <t>2026-06-03T22:56:12+05:30 (1h8m56s ago)</t>
+    <t>2026-06-03T22:56:12+05:30 (1h8m58s ago)</t>
   </si>
   <si>
     <t>Leader stale?</t>
@@ -1204,7 +1204,7 @@
     <t>Generated</t>
   </si>
   <si>
-    <t>2026-06-04T00:05:09+05:30</t>
+    <t>2026-06-04T00:05:11+05:30</t>
   </si>
   <si>
     <t>Total events</t>
@@ -1799,7 +1799,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>1h 39m 28s</t>
+          <t>1h 39m 30s</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -1819,7 +1819,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>8h 7m 5s</t>
+          <t>8h 7m 10s</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -1829,7 +1829,7 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>00:05:09</t>
+          <t>00:05:11</t>
         </is>
       </c>
     </row>
@@ -1936,7 +1936,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>00:05:09</t>
+          <t>00:05:11</t>
         </is>
       </c>
     </row>

--- a/report-2026-06-04.xlsx
+++ b/report-2026-06-04.xlsx
@@ -21,7 +21,7 @@
     <t>PunMonitor Leader Election — Current State</t>
   </si>
   <si>
-    <t>Generated 2026-06-04T00:05:11+05:30</t>
+    <t>Generated 2026-06-04T00:05:12+05:30</t>
   </si>
   <si>
     <t>Election method</t>
@@ -72,7 +72,7 @@
     <t>Leader last update</t>
   </si>
   <si>
-    <t>2026-06-03T22:56:12+05:30 (1h8m58s ago)</t>
+    <t>2026-06-03T22:56:12+05:30 (1h8m59s ago)</t>
   </si>
   <si>
     <t>Leader stale?</t>
@@ -1204,7 +1204,7 @@
     <t>Generated</t>
   </si>
   <si>
-    <t>2026-06-04T00:05:11+05:30</t>
+    <t>2026-06-04T00:05:12+05:30</t>
   </si>
   <si>
     <t>Total events</t>
@@ -1799,7 +1799,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>1h 39m 30s</t>
+          <t>1h 39m 32s</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -1829,7 +1829,7 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>00:05:11</t>
+          <t>00:05:12</t>
         </is>
       </c>
     </row>
@@ -1936,7 +1936,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>00:05:11</t>
+          <t>00:05:12</t>
         </is>
       </c>
     </row>

--- a/report-2026-06-04.xlsx
+++ b/report-2026-06-04.xlsx
@@ -21,7 +21,7 @@
     <t>PunMonitor Leader Election — Current State</t>
   </si>
   <si>
-    <t>Generated 2026-06-04T00:05:12+05:30</t>
+    <t>Generated 2026-06-04T00:05:14+05:30</t>
   </si>
   <si>
     <t>Election method</t>
@@ -72,7 +72,7 @@
     <t>Leader last update</t>
   </si>
   <si>
-    <t>2026-06-03T22:56:12+05:30 (1h8m59s ago)</t>
+    <t>2026-06-03T22:56:12+05:30 (1h9m1s ago)</t>
   </si>
   <si>
     <t>Leader stale?</t>
@@ -1204,7 +1204,7 @@
     <t>Generated</t>
   </si>
   <si>
-    <t>2026-06-04T00:05:12+05:30</t>
+    <t>2026-06-04T00:05:14+05:30</t>
   </si>
   <si>
     <t>Total events</t>
@@ -1799,7 +1799,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>1h 39m 32s</t>
+          <t>1h 39m 33s</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -1829,7 +1829,7 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>00:05:12</t>
+          <t>00:05:14</t>
         </is>
       </c>
     </row>
@@ -1891,12 +1891,12 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>164254.2</t>
+          <t>167367.2</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -1936,7 +1936,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>00:05:12</t>
+          <t>00:05:14</t>
         </is>
       </c>
     </row>

--- a/report-2026-06-04.xlsx
+++ b/report-2026-06-04.xlsx
@@ -21,7 +21,7 @@
     <t>PunMonitor Leader Election — Current State</t>
   </si>
   <si>
-    <t>Generated 2026-06-04T00:05:14+05:30</t>
+    <t>Generated 2026-06-04T00:05:16+05:30</t>
   </si>
   <si>
     <t>Election method</t>
@@ -72,7 +72,7 @@
     <t>Leader last update</t>
   </si>
   <si>
-    <t>2026-06-03T22:56:12+05:30 (1h9m1s ago)</t>
+    <t>2026-06-03T22:56:12+05:30 (1h9m3s ago)</t>
   </si>
   <si>
     <t>Leader stale?</t>
@@ -1204,7 +1204,7 @@
     <t>Generated</t>
   </si>
   <si>
-    <t>2026-06-04T00:05:14+05:30</t>
+    <t>2026-06-04T00:05:16+05:30</t>
   </si>
   <si>
     <t>Total events</t>
@@ -1799,7 +1799,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>1h 39m 33s</t>
+          <t>1h 39m 35s</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -1819,7 +1819,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>8h 7m 10s</t>
+          <t>8h 7m 15s</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -1829,7 +1829,7 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>00:05:14</t>
+          <t>00:05:16</t>
         </is>
       </c>
     </row>
@@ -1936,7 +1936,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>00:05:14</t>
+          <t>00:05:16</t>
         </is>
       </c>
     </row>

--- a/report-2026-06-04.xlsx
+++ b/report-2026-06-04.xlsx
@@ -16,12 +16,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="397" uniqueCount="397">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="400" uniqueCount="400">
   <si>
     <t>PunMonitor Leader Election — Current State</t>
   </si>
   <si>
-    <t>Generated 2026-06-04T00:05:16+05:30</t>
+    <t>Generated 2026-06-04T00:59:52+05:30</t>
   </si>
   <si>
     <t>Election method</t>
@@ -72,13 +72,13 @@
     <t>Leader last update</t>
   </si>
   <si>
-    <t>2026-06-03T22:56:12+05:30 (1h9m3s ago)</t>
+    <t>2026-06-04T00:57:52+05:30 (2m0s ago)</t>
   </si>
   <si>
     <t>Leader stale?</t>
   </si>
   <si>
-    <t>YES — leader hasn't renewed in 5m0s</t>
+    <t>No</t>
   </si>
   <si>
     <t>Last check</t>
@@ -87,7 +87,7 @@
     <t>Check count</t>
   </si>
   <si>
-    <t>21</t>
+    <t>1</t>
   </si>
   <si>
     <t>Last error</t>
@@ -1201,10 +1201,19 @@
     <t>22:56:12.981</t>
   </si>
   <si>
+    <t>2026-06-04T00:57:52.3430131+05:30</t>
+  </si>
+  <si>
+    <t>2026-06-04</t>
+  </si>
+  <si>
+    <t>00:57:52.343</t>
+  </si>
+  <si>
     <t>Generated</t>
   </si>
   <si>
-    <t>2026-06-04T00:05:16+05:30</t>
+    <t>2026-06-04T00:59:52+05:30</t>
   </si>
   <si>
     <t>Total events</t>
@@ -1759,12 +1768,12 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>10.0.38</t>
+          <t>10.0.40</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>agent</t>
+          <t>server+agent</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -1799,12 +1808,12 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>1h 39m 35s</t>
+          <t>0h 2m 17s</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>2026-06-03 22:25:40</t>
+          <t>2026-06-04 00:57:34</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
@@ -1814,12 +1823,12 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2026-06-03 22:25:40</t>
+          <t>2026-06-04 00:57:34</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>8h 7m 15s</t>
+          <t>8h 44m 15s</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -1829,7 +1838,7 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>00:05:16</t>
+          <t>00:59:52</t>
         </is>
       </c>
     </row>
@@ -1866,7 +1875,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>10.0.38</t>
+          <t>10.0.40</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -1876,7 +1885,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>websocket</t>
+          <t>self</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -1886,17 +1895,17 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>107.0</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>167367.2</t>
+          <t>112672.1</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>255</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -1906,12 +1915,12 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>5813</t>
+          <t>18</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>2026-06-03 22:25:40</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
@@ -1921,12 +1930,12 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-06-03 22:25:40</t>
+          <t>2026-06-04 00:57:34</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>8h 6m 25s</t>
+          <t>8h 42m 15s</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -1936,7 +1945,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>00:05:16</t>
+          <t>00:59:52</t>
         </is>
       </c>
     </row>
@@ -2055,17 +2064,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-06-03T22:56:12.9819715+05:30</t>
+          <t>2026-06-04T00:57:52.3430131+05:30</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>22:56:12.981</t>
+          <t>00:57:52.343</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -10635,18 +10644,56 @@
         <v>43</v>
       </c>
     </row>
-    <row r="192">
-      <c r="A192" t="s">
+    <row r="191">
+      <c r="A191" s="4">
+        <v>174</v>
+      </c>
+      <c r="B191" s="4" t="s">
         <v>394</v>
       </c>
-      <c r="B192" t="s">
+      <c r="C191" s="4" t="s">
         <v>395</v>
       </c>
-      <c r="D192" t="s">
+      <c r="D191" s="4" t="s">
         <v>396</v>
       </c>
-      <c r="E192">
-        <v>173</v>
+      <c r="E191" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F191" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G191" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H191" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I191" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J191" s="4">
+        <v>0</v>
+      </c>
+      <c r="K191" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L191" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="s">
+        <v>397</v>
+      </c>
+      <c r="B193" t="s">
+        <v>398</v>
+      </c>
+      <c r="D193" t="s">
+        <v>399</v>
+      </c>
+      <c r="E193">
+        <v>174</v>
       </c>
     </row>
   </sheetData>

--- a/report-2026-06-04.xlsx
+++ b/report-2026-06-04.xlsx
@@ -16,12 +16,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="400" uniqueCount="400">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="404" uniqueCount="404">
   <si>
     <t>PunMonitor Leader Election — Current State</t>
   </si>
   <si>
-    <t>Generated 2026-06-04T00:59:52+05:30</t>
+    <t>Generated 2026-06-04T01:05:07+05:30</t>
   </si>
   <si>
     <t>Election method</t>
@@ -72,7 +72,7 @@
     <t>Leader last update</t>
   </si>
   <si>
-    <t>2026-06-04T00:57:52+05:30 (2m0s ago)</t>
+    <t>2026-06-04T01:03:07+05:30 (2m0s ago)</t>
   </si>
   <si>
     <t>Leader stale?</t>
@@ -87,7 +87,7 @@
     <t>Check count</t>
   </si>
   <si>
-    <t>1</t>
+    <t>4</t>
   </si>
   <si>
     <t>Last error</t>
@@ -1210,10 +1210,22 @@
     <t>00:57:52.343</t>
   </si>
   <si>
+    <t>2026-06-04T01:00:23.8818216+05:30</t>
+  </si>
+  <si>
+    <t>01:00:23.881</t>
+  </si>
+  <si>
+    <t>2026-06-04T01:02:53.9479856+05:30</t>
+  </si>
+  <si>
+    <t>01:02:53.947</t>
+  </si>
+  <si>
     <t>Generated</t>
   </si>
   <si>
-    <t>2026-06-04T00:59:52+05:30</t>
+    <t>2026-06-04T01:05:07+05:30</t>
   </si>
   <si>
     <t>Total events</t>
@@ -1808,7 +1820,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>0h 2m 17s</t>
+          <t>0h 7m 32s</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -1828,7 +1840,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>8h 44m 15s</t>
+          <t>8h 48m 15s</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -1838,7 +1850,7 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>00:59:52</t>
+          <t>01:05:07</t>
         </is>
       </c>
     </row>
@@ -1895,17 +1907,17 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>107.0</t>
+          <t>98.0</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>112672.1</t>
+          <t>113233.9</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>255</t>
+          <t>969</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -1915,7 +1927,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>333</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -1935,7 +1947,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>8h 42m 15s</t>
+          <t>8h 46m 15s</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -1945,7 +1957,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>00:59:52</t>
+          <t>01:05:07</t>
         </is>
       </c>
     </row>
@@ -2064,7 +2076,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-06-04T00:57:52.3430131+05:30</t>
+          <t>2026-06-04T01:02:53.9479856+05:30</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -2074,7 +2086,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>00:57:52.343</t>
+          <t>01:02:53.947</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -10682,18 +10694,94 @@
         <v>43</v>
       </c>
     </row>
+    <row r="192">
+      <c r="A192" s="4">
+        <v>175</v>
+      </c>
+      <c r="B192" s="4" t="s">
+        <v>397</v>
+      </c>
+      <c r="C192" s="4" t="s">
+        <v>395</v>
+      </c>
+      <c r="D192" s="4" t="s">
+        <v>398</v>
+      </c>
+      <c r="E192" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F192" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G192" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H192" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I192" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J192" s="4">
+        <v>0</v>
+      </c>
+      <c r="K192" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L192" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
     <row r="193">
-      <c r="A193" t="s">
-        <v>397</v>
-      </c>
-      <c r="B193" t="s">
-        <v>398</v>
-      </c>
-      <c r="D193" t="s">
+      <c r="A193" s="4">
+        <v>176</v>
+      </c>
+      <c r="B193" s="4" t="s">
         <v>399</v>
       </c>
-      <c r="E193">
-        <v>174</v>
+      <c r="C193" s="4" t="s">
+        <v>395</v>
+      </c>
+      <c r="D193" s="4" t="s">
+        <v>400</v>
+      </c>
+      <c r="E193" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F193" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G193" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H193" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I193" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J193" s="4">
+        <v>0</v>
+      </c>
+      <c r="K193" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L193" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="s">
+        <v>401</v>
+      </c>
+      <c r="B195" t="s">
+        <v>402</v>
+      </c>
+      <c r="D195" t="s">
+        <v>403</v>
+      </c>
+      <c r="E195">
+        <v>176</v>
       </c>
     </row>
   </sheetData>

--- a/report-2026-06-04.xlsx
+++ b/report-2026-06-04.xlsx
@@ -16,12 +16,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="404" uniqueCount="404">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="408" uniqueCount="408">
   <si>
     <t>PunMonitor Leader Election — Current State</t>
   </si>
   <si>
-    <t>Generated 2026-06-04T01:05:07+05:30</t>
+    <t>Generated 2026-06-04T01:10:07+05:30</t>
   </si>
   <si>
     <t>Election method</t>
@@ -72,7 +72,7 @@
     <t>Leader last update</t>
   </si>
   <si>
-    <t>2026-06-04T01:03:07+05:30 (2m0s ago)</t>
+    <t>2026-06-04T01:08:29+05:30 (1m38s ago)</t>
   </si>
   <si>
     <t>Leader stale?</t>
@@ -87,7 +87,7 @@
     <t>Check count</t>
   </si>
   <si>
-    <t>4</t>
+    <t>9</t>
   </si>
   <si>
     <t>Last error</t>
@@ -1222,10 +1222,22 @@
     <t>01:02:53.947</t>
   </si>
   <si>
+    <t>2026-06-04T01:05:24.0380178+05:30</t>
+  </si>
+  <si>
+    <t>01:05:24.038</t>
+  </si>
+  <si>
+    <t>2026-06-04T01:07:54.042152+05:30</t>
+  </si>
+  <si>
+    <t>01:07:54.042</t>
+  </si>
+  <si>
     <t>Generated</t>
   </si>
   <si>
-    <t>2026-06-04T01:05:07+05:30</t>
+    <t>2026-06-04T01:10:07+05:30</t>
   </si>
   <si>
     <t>Total events</t>
@@ -1820,7 +1832,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>0h 7m 32s</t>
+          <t>0h 12m 32s</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -1840,7 +1852,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>8h 48m 15s</t>
+          <t>8h 52m 15s</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -1850,7 +1862,7 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>01:05:07</t>
+          <t>01:10:07</t>
         </is>
       </c>
     </row>
@@ -1907,17 +1919,17 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>98.0</t>
+          <t>120.0</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>113233.9</t>
+          <t>127816.7</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>969</t>
+          <t>2086</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -1927,7 +1939,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>333</t>
+          <t>655</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -1947,7 +1959,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>8h 46m 15s</t>
+          <t>8h 50m 55s</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -1957,7 +1969,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>01:05:07</t>
+          <t>01:10:07</t>
         </is>
       </c>
     </row>
@@ -2076,7 +2088,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-06-04T01:02:53.9479856+05:30</t>
+          <t>2026-06-04T01:07:54.042152+05:30</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -2086,7 +2098,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>01:02:53.947</t>
+          <t>01:07:54.042</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -10770,18 +10782,94 @@
         <v>43</v>
       </c>
     </row>
+    <row r="194">
+      <c r="A194" s="4">
+        <v>177</v>
+      </c>
+      <c r="B194" s="4" t="s">
+        <v>401</v>
+      </c>
+      <c r="C194" s="4" t="s">
+        <v>395</v>
+      </c>
+      <c r="D194" s="4" t="s">
+        <v>402</v>
+      </c>
+      <c r="E194" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F194" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G194" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H194" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I194" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J194" s="4">
+        <v>0</v>
+      </c>
+      <c r="K194" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L194" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
     <row r="195">
-      <c r="A195" t="s">
-        <v>401</v>
-      </c>
-      <c r="B195" t="s">
-        <v>402</v>
-      </c>
-      <c r="D195" t="s">
+      <c r="A195" s="4">
+        <v>178</v>
+      </c>
+      <c r="B195" s="4" t="s">
         <v>403</v>
       </c>
-      <c r="E195">
-        <v>176</v>
+      <c r="C195" s="4" t="s">
+        <v>395</v>
+      </c>
+      <c r="D195" s="4" t="s">
+        <v>404</v>
+      </c>
+      <c r="E195" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F195" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G195" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H195" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I195" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J195" s="4">
+        <v>0</v>
+      </c>
+      <c r="K195" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L195" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="s">
+        <v>405</v>
+      </c>
+      <c r="B197" t="s">
+        <v>406</v>
+      </c>
+      <c r="D197" t="s">
+        <v>407</v>
+      </c>
+      <c r="E197">
+        <v>178</v>
       </c>
     </row>
   </sheetData>

--- a/report-2026-06-04.xlsx
+++ b/report-2026-06-04.xlsx
@@ -16,12 +16,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="408" uniqueCount="408">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="410" uniqueCount="410">
   <si>
     <t>PunMonitor Leader Election — Current State</t>
   </si>
   <si>
-    <t>Generated 2026-06-04T01:10:07+05:30</t>
+    <t>Generated 2026-06-04T01:10:29+05:30</t>
   </si>
   <si>
     <t>Election method</t>
@@ -72,7 +72,7 @@
     <t>Leader last update</t>
   </si>
   <si>
-    <t>2026-06-04T01:08:29+05:30 (1m38s ago)</t>
+    <t>2026-06-04T01:10:23+05:30 (5s ago)</t>
   </si>
   <si>
     <t>Leader stale?</t>
@@ -87,7 +87,7 @@
     <t>Check count</t>
   </si>
   <si>
-    <t>9</t>
+    <t>10</t>
   </si>
   <si>
     <t>Last error</t>
@@ -1234,10 +1234,16 @@
     <t>01:07:54.042</t>
   </si>
   <si>
+    <t>2026-06-04T01:10:23.7615026+05:30</t>
+  </si>
+  <si>
+    <t>01:10:23.761</t>
+  </si>
+  <si>
     <t>Generated</t>
   </si>
   <si>
-    <t>2026-06-04T01:10:07+05:30</t>
+    <t>2026-06-04T01:10:29+05:30</t>
   </si>
   <si>
     <t>Total events</t>
@@ -1832,7 +1838,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>0h 12m 32s</t>
+          <t>0h 12m 54s</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -1852,7 +1858,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>8h 52m 15s</t>
+          <t>8h 52m 30s</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -1862,7 +1868,7 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>01:10:07</t>
+          <t>01:10:29</t>
         </is>
       </c>
     </row>
@@ -1919,17 +1925,17 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>120.0</t>
+          <t>119.0</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>127816.7</t>
+          <t>127955.3</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2086</t>
+          <t>2192</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -1969,7 +1975,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>01:10:07</t>
+          <t>01:10:29</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2094,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-06-04T01:07:54.042152+05:30</t>
+          <t>2026-06-04T01:10:23.7615026+05:30</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -2098,7 +2104,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>01:07:54.042</t>
+          <t>01:10:23.761</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -10858,18 +10864,56 @@
         <v>43</v>
       </c>
     </row>
-    <row r="197">
-      <c r="A197" t="s">
+    <row r="196">
+      <c r="A196" s="4">
+        <v>179</v>
+      </c>
+      <c r="B196" s="4" t="s">
         <v>405</v>
       </c>
-      <c r="B197" t="s">
+      <c r="C196" s="4" t="s">
+        <v>395</v>
+      </c>
+      <c r="D196" s="4" t="s">
         <v>406</v>
       </c>
-      <c r="D197" t="s">
+      <c r="E196" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F196" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G196" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H196" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I196" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J196" s="4">
+        <v>0</v>
+      </c>
+      <c r="K196" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L196" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="s">
         <v>407</v>
       </c>
-      <c r="E197">
-        <v>178</v>
+      <c r="B198" t="s">
+        <v>408</v>
+      </c>
+      <c r="D198" t="s">
+        <v>409</v>
+      </c>
+      <c r="E198">
+        <v>179</v>
       </c>
     </row>
   </sheetData>

--- a/report-2026-06-04.xlsx
+++ b/report-2026-06-04.xlsx
@@ -16,12 +16,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="410" uniqueCount="410">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="412" uniqueCount="412">
   <si>
     <t>PunMonitor Leader Election — Current State</t>
   </si>
   <si>
-    <t>Generated 2026-06-04T01:10:29+05:30</t>
+    <t>Generated 2026-06-04T01:15:03+05:30</t>
   </si>
   <si>
     <t>Election method</t>
@@ -72,7 +72,7 @@
     <t>Leader last update</t>
   </si>
   <si>
-    <t>2026-06-04T01:10:23+05:30 (5s ago)</t>
+    <t>2026-06-04T01:13:51+05:30 (1m12s ago)</t>
   </si>
   <si>
     <t>Leader stale?</t>
@@ -87,7 +87,7 @@
     <t>Check count</t>
   </si>
   <si>
-    <t>10</t>
+    <t>15</t>
   </si>
   <si>
     <t>Last error</t>
@@ -1240,10 +1240,16 @@
     <t>01:10:23.761</t>
   </si>
   <si>
+    <t>2026-06-04T01:12:53.9351089+05:30</t>
+  </si>
+  <si>
+    <t>01:12:53.935</t>
+  </si>
+  <si>
     <t>Generated</t>
   </si>
   <si>
-    <t>2026-06-04T01:10:29+05:30</t>
+    <t>2026-06-04T01:15:03+05:30</t>
   </si>
   <si>
     <t>Total events</t>
@@ -1838,7 +1844,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>0h 12m 54s</t>
+          <t>0h 17m 28s</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -1858,7 +1864,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>8h 52m 30s</t>
+          <t>8h 56m 5s</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -1868,7 +1874,7 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>01:10:29</t>
+          <t>01:15:03</t>
         </is>
       </c>
     </row>
@@ -1925,17 +1931,17 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>119.0</t>
+          <t>1105.0</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>127955.3</t>
+          <t>310145.5</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2192</t>
+          <t>3764</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -1945,7 +1951,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>655</t>
+          <t>976</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -1965,7 +1971,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>8h 50m 55s</t>
+          <t>8h 55m 0s</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -1975,7 +1981,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>01:10:29</t>
+          <t>01:15:03</t>
         </is>
       </c>
     </row>
@@ -2094,7 +2100,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-06-04T01:10:23.7615026+05:30</t>
+          <t>2026-06-04T01:12:53.9351089+05:30</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -2104,7 +2110,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>01:10:23.761</t>
+          <t>01:12:53.935</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -10902,18 +10908,56 @@
         <v>43</v>
       </c>
     </row>
-    <row r="198">
-      <c r="A198" t="s">
+    <row r="197">
+      <c r="A197" s="4">
+        <v>180</v>
+      </c>
+      <c r="B197" s="4" t="s">
         <v>407</v>
       </c>
-      <c r="B198" t="s">
+      <c r="C197" s="4" t="s">
+        <v>395</v>
+      </c>
+      <c r="D197" s="4" t="s">
         <v>408</v>
       </c>
-      <c r="D198" t="s">
+      <c r="E197" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F197" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G197" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H197" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I197" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J197" s="4">
+        <v>0</v>
+      </c>
+      <c r="K197" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L197" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="s">
         <v>409</v>
       </c>
-      <c r="E198">
-        <v>179</v>
+      <c r="B199" t="s">
+        <v>410</v>
+      </c>
+      <c r="D199" t="s">
+        <v>411</v>
+      </c>
+      <c r="E199">
+        <v>180</v>
       </c>
     </row>
   </sheetData>

--- a/report-2026-06-04.xlsx
+++ b/report-2026-06-04.xlsx
@@ -21,7 +21,7 @@
     <t>PunMonitor Leader Election — Current State</t>
   </si>
   <si>
-    <t>Generated 2026-06-04T01:15:03+05:30</t>
+    <t>Generated 2026-06-04T01:15:23+05:30</t>
   </si>
   <si>
     <t>Election method</t>
@@ -72,7 +72,7 @@
     <t>Leader last update</t>
   </si>
   <si>
-    <t>2026-06-04T01:13:51+05:30 (1m12s ago)</t>
+    <t>2026-06-04T01:13:51+05:30 (1m31s ago)</t>
   </si>
   <si>
     <t>Leader stale?</t>
@@ -1249,7 +1249,7 @@
     <t>Generated</t>
   </si>
   <si>
-    <t>2026-06-04T01:15:03+05:30</t>
+    <t>2026-06-04T01:15:23+05:30</t>
   </si>
   <si>
     <t>Total events</t>
@@ -1844,7 +1844,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>0h 17m 28s</t>
+          <t>0h 17m 48s</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -1864,7 +1864,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>8h 56m 5s</t>
+          <t>8h 56m 25s</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -1874,7 +1874,7 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>01:15:03</t>
+          <t>01:15:22</t>
         </is>
       </c>
     </row>
@@ -1931,7 +1931,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>1105.0</t>
+          <t>1241.0</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -1941,7 +1941,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>3764</t>
+          <t>3874</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -1981,7 +1981,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>01:15:03</t>
+          <t>01:15:22</t>
         </is>
       </c>
     </row>

--- a/report-2026-06-04.xlsx
+++ b/report-2026-06-04.xlsx
@@ -16,12 +16,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="412" uniqueCount="412">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="414" uniqueCount="414">
   <si>
     <t>PunMonitor Leader Election — Current State</t>
   </si>
   <si>
-    <t>Generated 2026-06-04T01:15:23+05:30</t>
+    <t>Generated 2026-06-04T01:15:51+05:30</t>
   </si>
   <si>
     <t>Election method</t>
@@ -72,7 +72,7 @@
     <t>Leader last update</t>
   </si>
   <si>
-    <t>2026-06-04T01:13:51+05:30 (1m31s ago)</t>
+    <t>2026-06-04T01:15:23+05:30 (27s ago)</t>
   </si>
   <si>
     <t>Leader stale?</t>
@@ -87,7 +87,7 @@
     <t>Check count</t>
   </si>
   <si>
-    <t>15</t>
+    <t>16</t>
   </si>
   <si>
     <t>Last error</t>
@@ -1246,10 +1246,16 @@
     <t>01:12:53.935</t>
   </si>
   <si>
+    <t>2026-06-04T01:15:23.803568+05:30</t>
+  </si>
+  <si>
+    <t>01:15:23.803</t>
+  </si>
+  <si>
     <t>Generated</t>
   </si>
   <si>
-    <t>2026-06-04T01:15:23+05:30</t>
+    <t>2026-06-04T01:15:51+05:30</t>
   </si>
   <si>
     <t>Total events</t>
@@ -1844,7 +1850,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>0h 17m 48s</t>
+          <t>0h 18m 16s</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -1864,7 +1870,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>8h 56m 25s</t>
+          <t>8h 56m 55s</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -1874,7 +1880,7 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>01:15:22</t>
+          <t>01:15:51</t>
         </is>
       </c>
     </row>
@@ -1931,7 +1937,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>1241.0</t>
+          <t>1089.0</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -1941,7 +1947,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>3874</t>
+          <t>4032</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -1981,7 +1987,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>01:15:22</t>
+          <t>01:15:51</t>
         </is>
       </c>
     </row>
@@ -2100,7 +2106,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-06-04T01:12:53.9351089+05:30</t>
+          <t>2026-06-04T01:15:23.803568+05:30</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -2110,7 +2116,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>01:12:53.935</t>
+          <t>01:15:23.803</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -10946,18 +10952,56 @@
         <v>43</v>
       </c>
     </row>
-    <row r="199">
-      <c r="A199" t="s">
+    <row r="198">
+      <c r="A198" s="4">
+        <v>181</v>
+      </c>
+      <c r="B198" s="4" t="s">
         <v>409</v>
       </c>
-      <c r="B199" t="s">
+      <c r="C198" s="4" t="s">
+        <v>395</v>
+      </c>
+      <c r="D198" s="4" t="s">
         <v>410</v>
       </c>
-      <c r="D199" t="s">
+      <c r="E198" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F198" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G198" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H198" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I198" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J198" s="4">
+        <v>0</v>
+      </c>
+      <c r="K198" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L198" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="s">
         <v>411</v>
       </c>
-      <c r="E199">
-        <v>180</v>
+      <c r="B200" t="s">
+        <v>412</v>
+      </c>
+      <c r="D200" t="s">
+        <v>413</v>
+      </c>
+      <c r="E200">
+        <v>181</v>
       </c>
     </row>
   </sheetData>

--- a/report-2026-06-04.xlsx
+++ b/report-2026-06-04.xlsx
@@ -16,12 +16,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="414" uniqueCount="414">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="418" uniqueCount="418">
   <si>
     <t>PunMonitor Leader Election — Current State</t>
   </si>
   <si>
-    <t>Generated 2026-06-04T01:15:51+05:30</t>
+    <t>Generated 2026-06-04T01:20:12+05:30</t>
   </si>
   <si>
     <t>Election method</t>
@@ -72,7 +72,7 @@
     <t>Leader last update</t>
   </si>
   <si>
-    <t>2026-06-04T01:15:23+05:30 (27s ago)</t>
+    <t>2026-06-04T01:19:09+05:30 (1m3s ago)</t>
   </si>
   <si>
     <t>Leader stale?</t>
@@ -87,7 +87,7 @@
     <t>Check count</t>
   </si>
   <si>
-    <t>16</t>
+    <t>21</t>
   </si>
   <si>
     <t>Last error</t>
@@ -1252,10 +1252,22 @@
     <t>01:15:23.803</t>
   </si>
   <si>
+    <t>2026-06-04T01:17:53.8723261+05:30</t>
+  </si>
+  <si>
+    <t>01:17:53.872</t>
+  </si>
+  <si>
+    <t>2026-06-04T01:19:09.2243347+05:30</t>
+  </si>
+  <si>
+    <t>01:19:09.224</t>
+  </si>
+  <si>
     <t>Generated</t>
   </si>
   <si>
-    <t>2026-06-04T01:15:51+05:30</t>
+    <t>2026-06-04T01:20:12+05:30</t>
   </si>
   <si>
     <t>Total events</t>
@@ -1850,7 +1862,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>0h 18m 16s</t>
+          <t>0h 22m 37s</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -1870,7 +1882,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>8h 56m 55s</t>
+          <t>9h 1m 15s</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -1880,7 +1892,7 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>01:15:51</t>
+          <t>01:20:12</t>
         </is>
       </c>
     </row>
@@ -1937,17 +1949,17 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>1089.0</t>
+          <t>1920.0</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>310145.5</t>
+          <t>310737.5</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>4032</t>
+          <t>5438</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -1957,7 +1969,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>976</t>
+          <t>1294</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -1977,7 +1989,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>8h 55m 0s</t>
+          <t>9h 0m 10s</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -1987,7 +1999,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>01:15:51</t>
+          <t>01:20:12</t>
         </is>
       </c>
     </row>
@@ -2106,7 +2118,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-06-04T01:15:23.803568+05:30</t>
+          <t>2026-06-04T01:19:09.2243347+05:30</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -2116,7 +2128,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>01:15:23.803</t>
+          <t>01:19:09.224</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -10990,18 +11002,94 @@
         <v>43</v>
       </c>
     </row>
+    <row r="199">
+      <c r="A199" s="4">
+        <v>182</v>
+      </c>
+      <c r="B199" s="4" t="s">
+        <v>411</v>
+      </c>
+      <c r="C199" s="4" t="s">
+        <v>395</v>
+      </c>
+      <c r="D199" s="4" t="s">
+        <v>412</v>
+      </c>
+      <c r="E199" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F199" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G199" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H199" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I199" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J199" s="4">
+        <v>0</v>
+      </c>
+      <c r="K199" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L199" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
     <row r="200">
-      <c r="A200" t="s">
-        <v>411</v>
-      </c>
-      <c r="B200" t="s">
-        <v>412</v>
-      </c>
-      <c r="D200" t="s">
+      <c r="A200" s="4">
+        <v>183</v>
+      </c>
+      <c r="B200" s="4" t="s">
         <v>413</v>
       </c>
-      <c r="E200">
-        <v>181</v>
+      <c r="C200" s="4" t="s">
+        <v>395</v>
+      </c>
+      <c r="D200" s="4" t="s">
+        <v>414</v>
+      </c>
+      <c r="E200" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F200" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G200" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H200" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I200" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J200" s="4">
+        <v>0</v>
+      </c>
+      <c r="K200" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L200" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="s">
+        <v>415</v>
+      </c>
+      <c r="B202" t="s">
+        <v>416</v>
+      </c>
+      <c r="D202" t="s">
+        <v>417</v>
+      </c>
+      <c r="E202">
+        <v>183</v>
       </c>
     </row>
   </sheetData>

--- a/report-2026-06-04.xlsx
+++ b/report-2026-06-04.xlsx
@@ -21,7 +21,7 @@
     <t>PunMonitor Leader Election — Current State</t>
   </si>
   <si>
-    <t>Generated 2026-06-04T01:20:12+05:30</t>
+    <t>Generated 2026-06-04T01:20:39+05:30</t>
   </si>
   <si>
     <t>Election method</t>
@@ -72,7 +72,7 @@
     <t>Leader last update</t>
   </si>
   <si>
-    <t>2026-06-04T01:19:09+05:30 (1m3s ago)</t>
+    <t>2026-06-04T01:19:09+05:30 (1m29s ago)</t>
   </si>
   <si>
     <t>Leader stale?</t>
@@ -1267,7 +1267,7 @@
     <t>Generated</t>
   </si>
   <si>
-    <t>2026-06-04T01:20:12+05:30</t>
+    <t>2026-06-04T01:20:39+05:30</t>
   </si>
   <si>
     <t>Total events</t>
@@ -1862,7 +1862,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>0h 22m 37s</t>
+          <t>0h 23m 4s</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -1882,7 +1882,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>9h 1m 15s</t>
+          <t>9h 1m 40s</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -1892,7 +1892,7 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>01:20:12</t>
+          <t>01:20:39</t>
         </is>
       </c>
     </row>
@@ -1949,7 +1949,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>1920.0</t>
+          <t>2221.0</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -1959,7 +1959,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>5438</t>
+          <t>5556</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -1999,7 +1999,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>01:20:12</t>
+          <t>01:20:39</t>
         </is>
       </c>
     </row>

--- a/report-2026-06-04.xlsx
+++ b/report-2026-06-04.xlsx
@@ -21,7 +21,7 @@
     <t>PunMonitor Leader Election — Current State</t>
   </si>
   <si>
-    <t>Generated 2026-06-04T01:20:39+05:30</t>
+    <t>Generated 2026-06-04T01:21:09+05:30</t>
   </si>
   <si>
     <t>Election method</t>
@@ -72,7 +72,7 @@
     <t>Leader last update</t>
   </si>
   <si>
-    <t>2026-06-04T01:19:09+05:30 (1m29s ago)</t>
+    <t>2026-06-04T01:19:09+05:30 (2m0s ago)</t>
   </si>
   <si>
     <t>Leader stale?</t>
@@ -1267,7 +1267,7 @@
     <t>Generated</t>
   </si>
   <si>
-    <t>2026-06-04T01:20:39+05:30</t>
+    <t>2026-06-04T01:21:09+05:30</t>
   </si>
   <si>
     <t>Total events</t>
@@ -1862,7 +1862,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>0h 23m 4s</t>
+          <t>0h 23m 34s</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -1882,7 +1882,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>9h 1m 40s</t>
+          <t>9h 2m 10s</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -1892,7 +1892,7 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>01:20:39</t>
+          <t>01:21:09</t>
         </is>
       </c>
     </row>
@@ -1949,17 +1949,17 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2221.0</t>
+          <t>1891.0</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>310737.5</t>
+          <t>310083.5</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>5556</t>
+          <t>5724</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -1999,7 +1999,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>01:20:39</t>
+          <t>01:21:09</t>
         </is>
       </c>
     </row>

--- a/report-2026-06-04.xlsx
+++ b/report-2026-06-04.xlsx
@@ -16,12 +16,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="418" uniqueCount="418">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="422" uniqueCount="422">
   <si>
     <t>PunMonitor Leader Election — Current State</t>
   </si>
   <si>
-    <t>Generated 2026-06-04T01:21:09+05:30</t>
+    <t>Generated 2026-06-04T01:25:07+05:30</t>
   </si>
   <si>
     <t>Election method</t>
@@ -72,7 +72,7 @@
     <t>Leader last update</t>
   </si>
   <si>
-    <t>2026-06-04T01:19:09+05:30 (2m0s ago)</t>
+    <t>2026-06-04T01:23:40+05:30 (1m27s ago)</t>
   </si>
   <si>
     <t>Leader stale?</t>
@@ -87,7 +87,7 @@
     <t>Check count</t>
   </si>
   <si>
-    <t>21</t>
+    <t>25</t>
   </si>
   <si>
     <t>Last error</t>
@@ -1264,10 +1264,22 @@
     <t>01:19:09.224</t>
   </si>
   <si>
+    <t>2026-06-04T01:21:40.4314298+05:30</t>
+  </si>
+  <si>
+    <t>01:21:40.431</t>
+  </si>
+  <si>
+    <t>2026-06-04T01:23:07.9690529+05:30</t>
+  </si>
+  <si>
+    <t>01:23:07.969</t>
+  </si>
+  <si>
     <t>Generated</t>
   </si>
   <si>
-    <t>2026-06-04T01:21:09+05:30</t>
+    <t>2026-06-04T01:25:07+05:30</t>
   </si>
   <si>
     <t>Total events</t>
@@ -1827,7 +1839,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>server+agent</t>
+          <t>agent</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -1862,7 +1874,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>0h 23m 34s</t>
+          <t>0h 27m 33s</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -1882,7 +1894,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>9h 2m 10s</t>
+          <t>9h 5m 35s</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -1892,7 +1904,7 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>01:21:09</t>
+          <t>01:25:07</t>
         </is>
       </c>
     </row>
@@ -1939,7 +1951,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>self</t>
+          <t>websocket</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -1949,17 +1961,17 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>1891.0</t>
+          <t>1433.0</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>310083.5</t>
+          <t>129842.7</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>5724</t>
+          <t>605</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -1969,7 +1981,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>1294</t>
+          <t>1566</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -1979,17 +1991,17 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>Jun 2 07:00 PM</t>
+          <t>—</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-06-04 00:57:34</t>
+          <t>—</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>9h 0m 10s</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -1999,7 +2011,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>01:21:09</t>
+          <t>01:25:07</t>
         </is>
       </c>
     </row>
@@ -2118,7 +2130,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-06-04T01:19:09.2243347+05:30</t>
+          <t>2026-06-04T01:23:07.9690529+05:30</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -2128,7 +2140,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>01:19:09.224</t>
+          <t>01:23:07.969</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -11078,18 +11090,94 @@
         <v>43</v>
       </c>
     </row>
+    <row r="201">
+      <c r="A201" s="4">
+        <v>184</v>
+      </c>
+      <c r="B201" s="4" t="s">
+        <v>415</v>
+      </c>
+      <c r="C201" s="4" t="s">
+        <v>395</v>
+      </c>
+      <c r="D201" s="4" t="s">
+        <v>416</v>
+      </c>
+      <c r="E201" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F201" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G201" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H201" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I201" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J201" s="4">
+        <v>0</v>
+      </c>
+      <c r="K201" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L201" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
     <row r="202">
-      <c r="A202" t="s">
-        <v>415</v>
-      </c>
-      <c r="B202" t="s">
-        <v>416</v>
-      </c>
-      <c r="D202" t="s">
+      <c r="A202" s="4">
+        <v>185</v>
+      </c>
+      <c r="B202" s="4" t="s">
         <v>417</v>
       </c>
-      <c r="E202">
-        <v>183</v>
+      <c r="C202" s="4" t="s">
+        <v>395</v>
+      </c>
+      <c r="D202" s="4" t="s">
+        <v>418</v>
+      </c>
+      <c r="E202" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F202" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G202" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H202" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I202" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J202" s="4">
+        <v>0</v>
+      </c>
+      <c r="K202" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L202" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="s">
+        <v>419</v>
+      </c>
+      <c r="B204" t="s">
+        <v>420</v>
+      </c>
+      <c r="D204" t="s">
+        <v>421</v>
+      </c>
+      <c r="E204">
+        <v>185</v>
       </c>
     </row>
   </sheetData>

--- a/report-2026-06-04.xlsx
+++ b/report-2026-06-04.xlsx
@@ -21,7 +21,7 @@
     <t>PunMonitor Leader Election — Current State</t>
   </si>
   <si>
-    <t>Generated 2026-06-04T01:25:07+05:30</t>
+    <t>Generated 2026-06-04T01:25:27+05:30</t>
   </si>
   <si>
     <t>Election method</t>
@@ -72,7 +72,7 @@
     <t>Leader last update</t>
   </si>
   <si>
-    <t>2026-06-04T01:23:40+05:30 (1m27s ago)</t>
+    <t>2026-06-04T01:23:40+05:30 (1m46s ago)</t>
   </si>
   <si>
     <t>Leader stale?</t>
@@ -1279,7 +1279,7 @@
     <t>Generated</t>
   </si>
   <si>
-    <t>2026-06-04T01:25:07+05:30</t>
+    <t>2026-06-04T01:25:27+05:30</t>
   </si>
   <si>
     <t>Total events</t>
@@ -1874,7 +1874,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>0h 27m 33s</t>
+          <t>0h 27m 52s</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>9h 5m 35s</t>
+          <t>9h 5m 45s</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -1904,7 +1904,7 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>01:25:07</t>
+          <t>01:25:27</t>
         </is>
       </c>
     </row>
@@ -1961,17 +1961,17 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>1433.0</t>
+          <t>1232.0</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>129842.7</t>
+          <t>105329.5</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>605</t>
+          <t>821</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -2011,7 +2011,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>01:25:07</t>
+          <t>01:25:27</t>
         </is>
       </c>
     </row>

--- a/report-2026-06-04.xlsx
+++ b/report-2026-06-04.xlsx
@@ -16,12 +16,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="422" uniqueCount="422">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="440" uniqueCount="440">
   <si>
     <t>PunMonitor Leader Election — Current State</t>
   </si>
   <si>
-    <t>Generated 2026-06-04T01:25:27+05:30</t>
+    <t>Generated 2026-06-04T03:25:53+05:30</t>
   </si>
   <si>
     <t>Election method</t>
@@ -72,7 +72,7 @@
     <t>Leader last update</t>
   </si>
   <si>
-    <t>2026-06-04T01:23:40+05:30 (1m46s ago)</t>
+    <t>2026-06-04T03:23:53+05:30 (2m0s ago)</t>
   </si>
   <si>
     <t>Leader stale?</t>
@@ -87,7 +87,7 @@
     <t>Check count</t>
   </si>
   <si>
-    <t>25</t>
+    <t>8</t>
   </si>
   <si>
     <t>Last error</t>
@@ -1276,10 +1276,64 @@
     <t>01:23:07.969</t>
   </si>
   <si>
+    <t>2026-06-04T03:04:27.0786558+05:30</t>
+  </si>
+  <si>
+    <t>03:04:27.078</t>
+  </si>
+  <si>
+    <t>2026-06-04T03:05:50.2551035+05:30</t>
+  </si>
+  <si>
+    <t>03:05:50.255</t>
+  </si>
+  <si>
+    <t>2026-06-04T03:08:34.2275175+05:30</t>
+  </si>
+  <si>
+    <t>03:08:34.227</t>
+  </si>
+  <si>
+    <t>2026-06-04T03:11:05.3422929+05:30</t>
+  </si>
+  <si>
+    <t>03:11:05.342</t>
+  </si>
+  <si>
+    <t>2026-06-04T03:13:35.5646936+05:30</t>
+  </si>
+  <si>
+    <t>03:13:35.564</t>
+  </si>
+  <si>
+    <t>2026-06-04T03:16:05.6354567+05:30</t>
+  </si>
+  <si>
+    <t>03:16:05.635</t>
+  </si>
+  <si>
+    <t>2026-06-04T03:18:35.4737447+05:30</t>
+  </si>
+  <si>
+    <t>03:18:35.473</t>
+  </si>
+  <si>
+    <t>2026-06-04T03:21:05.4759638+05:30</t>
+  </si>
+  <si>
+    <t>03:21:05.475</t>
+  </si>
+  <si>
+    <t>2026-06-04T03:23:35.3965904+05:30</t>
+  </si>
+  <si>
+    <t>03:23:35.396</t>
+  </si>
+  <si>
     <t>Generated</t>
   </si>
   <si>
-    <t>2026-06-04T01:25:27+05:30</t>
+    <t>2026-06-04T03:25:53+05:30</t>
   </si>
   <si>
     <t>Total events</t>
@@ -1834,12 +1888,12 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>10.0.40</t>
+          <t>10.0.41</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>agent</t>
+          <t>server+agent</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -1874,12 +1928,12 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>0h 27m 52s</t>
+          <t>0h 17m 35s</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>2026-06-04 00:57:34</t>
+          <t>2026-06-04 03:08:18</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
@@ -1889,12 +1943,12 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2026-06-04 00:57:34</t>
+          <t>2026-06-04 03:08:18</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>9h 5m 45s</t>
+          <t>10h 4m 35s</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -1904,7 +1958,7 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>01:25:27</t>
+          <t>03:25:53</t>
         </is>
       </c>
     </row>
@@ -1941,7 +1995,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>10.0.40</t>
+          <t>10.0.41</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -1951,7 +2005,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>websocket</t>
+          <t>self</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -1961,17 +2015,17 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>1232.0</t>
+          <t>113.0</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>105329.5</t>
+          <t>113835.9</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>821</t>
+          <t>2479</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -1981,7 +2035,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>1566</t>
+          <t>936</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -1991,17 +2045,17 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Jun 2 07:00 PM</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2026-06-04 03:08:18</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>10h 4m 15s</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -2011,7 +2065,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>01:25:27</t>
+          <t>03:25:53</t>
         </is>
       </c>
     </row>
@@ -2130,7 +2184,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-06-04T01:23:07.9690529+05:30</t>
+          <t>2026-06-04T03:23:35.3965904+05:30</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -2140,7 +2194,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>01:23:07.969</t>
+          <t>03:23:35.396</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -11166,18 +11220,360 @@
         <v>43</v>
       </c>
     </row>
+    <row r="203">
+      <c r="A203" s="4">
+        <v>186</v>
+      </c>
+      <c r="B203" s="4" t="s">
+        <v>419</v>
+      </c>
+      <c r="C203" s="4" t="s">
+        <v>395</v>
+      </c>
+      <c r="D203" s="4" t="s">
+        <v>420</v>
+      </c>
+      <c r="E203" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F203" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G203" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H203" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I203" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J203" s="4">
+        <v>0</v>
+      </c>
+      <c r="K203" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L203" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
     <row r="204">
-      <c r="A204" t="s">
-        <v>419</v>
-      </c>
-      <c r="B204" t="s">
-        <v>420</v>
-      </c>
-      <c r="D204" t="s">
+      <c r="A204" s="4">
+        <v>187</v>
+      </c>
+      <c r="B204" s="4" t="s">
         <v>421</v>
       </c>
-      <c r="E204">
-        <v>185</v>
+      <c r="C204" s="4" t="s">
+        <v>395</v>
+      </c>
+      <c r="D204" s="4" t="s">
+        <v>422</v>
+      </c>
+      <c r="E204" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F204" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G204" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H204" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I204" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J204" s="4">
+        <v>0</v>
+      </c>
+      <c r="K204" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L204" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" s="4">
+        <v>188</v>
+      </c>
+      <c r="B205" s="4" t="s">
+        <v>423</v>
+      </c>
+      <c r="C205" s="4" t="s">
+        <v>395</v>
+      </c>
+      <c r="D205" s="4" t="s">
+        <v>424</v>
+      </c>
+      <c r="E205" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F205" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G205" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H205" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I205" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J205" s="4">
+        <v>0</v>
+      </c>
+      <c r="K205" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L205" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" s="4">
+        <v>189</v>
+      </c>
+      <c r="B206" s="4" t="s">
+        <v>425</v>
+      </c>
+      <c r="C206" s="4" t="s">
+        <v>395</v>
+      </c>
+      <c r="D206" s="4" t="s">
+        <v>426</v>
+      </c>
+      <c r="E206" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F206" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G206" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H206" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I206" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J206" s="4">
+        <v>0</v>
+      </c>
+      <c r="K206" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L206" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" s="4">
+        <v>190</v>
+      </c>
+      <c r="B207" s="4" t="s">
+        <v>427</v>
+      </c>
+      <c r="C207" s="4" t="s">
+        <v>395</v>
+      </c>
+      <c r="D207" s="4" t="s">
+        <v>428</v>
+      </c>
+      <c r="E207" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F207" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G207" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H207" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I207" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J207" s="4">
+        <v>0</v>
+      </c>
+      <c r="K207" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L207" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" s="4">
+        <v>191</v>
+      </c>
+      <c r="B208" s="4" t="s">
+        <v>429</v>
+      </c>
+      <c r="C208" s="4" t="s">
+        <v>395</v>
+      </c>
+      <c r="D208" s="4" t="s">
+        <v>430</v>
+      </c>
+      <c r="E208" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F208" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G208" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H208" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I208" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J208" s="4">
+        <v>0</v>
+      </c>
+      <c r="K208" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L208" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" s="4">
+        <v>192</v>
+      </c>
+      <c r="B209" s="4" t="s">
+        <v>431</v>
+      </c>
+      <c r="C209" s="4" t="s">
+        <v>395</v>
+      </c>
+      <c r="D209" s="4" t="s">
+        <v>432</v>
+      </c>
+      <c r="E209" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F209" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G209" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H209" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I209" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J209" s="4">
+        <v>0</v>
+      </c>
+      <c r="K209" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L209" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" s="4">
+        <v>193</v>
+      </c>
+      <c r="B210" s="4" t="s">
+        <v>433</v>
+      </c>
+      <c r="C210" s="4" t="s">
+        <v>395</v>
+      </c>
+      <c r="D210" s="4" t="s">
+        <v>434</v>
+      </c>
+      <c r="E210" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F210" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G210" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H210" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I210" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J210" s="4">
+        <v>0</v>
+      </c>
+      <c r="K210" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L210" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" s="4">
+        <v>194</v>
+      </c>
+      <c r="B211" s="4" t="s">
+        <v>435</v>
+      </c>
+      <c r="C211" s="4" t="s">
+        <v>395</v>
+      </c>
+      <c r="D211" s="4" t="s">
+        <v>436</v>
+      </c>
+      <c r="E211" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F211" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G211" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H211" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I211" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J211" s="4">
+        <v>0</v>
+      </c>
+      <c r="K211" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L211" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="s">
+        <v>437</v>
+      </c>
+      <c r="B213" t="s">
+        <v>438</v>
+      </c>
+      <c r="D213" t="s">
+        <v>439</v>
+      </c>
+      <c r="E213">
+        <v>194</v>
       </c>
     </row>
   </sheetData>

--- a/report-2026-06-04.xlsx
+++ b/report-2026-06-04.xlsx
@@ -16,12 +16,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="440" uniqueCount="440">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="444" uniqueCount="444">
   <si>
     <t>PunMonitor Leader Election — Current State</t>
   </si>
   <si>
-    <t>Generated 2026-06-04T03:25:53+05:30</t>
+    <t>Generated 2026-06-04T03:30:47+05:30</t>
   </si>
   <si>
     <t>Election method</t>
@@ -72,7 +72,7 @@
     <t>Leader last update</t>
   </si>
   <si>
-    <t>2026-06-04T03:23:53+05:30 (2m0s ago)</t>
+    <t>2026-06-04T03:29:08+05:30 (1m38s ago)</t>
   </si>
   <si>
     <t>Leader stale?</t>
@@ -87,7 +87,7 @@
     <t>Check count</t>
   </si>
   <si>
-    <t>8</t>
+    <t>13</t>
   </si>
   <si>
     <t>Last error</t>
@@ -1330,10 +1330,22 @@
     <t>03:23:35.396</t>
   </si>
   <si>
+    <t>2026-06-04T03:26:05.4278634+05:30</t>
+  </si>
+  <si>
+    <t>03:26:05.427</t>
+  </si>
+  <si>
+    <t>2026-06-04T03:28:35.5426508+05:30</t>
+  </si>
+  <si>
+    <t>03:28:35.542</t>
+  </si>
+  <si>
     <t>Generated</t>
   </si>
   <si>
-    <t>2026-06-04T03:25:53+05:30</t>
+    <t>2026-06-04T03:30:47+05:30</t>
   </si>
   <si>
     <t>Total events</t>
@@ -1928,7 +1940,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>0h 17m 35s</t>
+          <t>0h 22m 28s</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -1948,7 +1960,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>10h 4m 35s</t>
+          <t>10h 6m 45s</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -1958,7 +1970,7 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>03:25:53</t>
+          <t>03:30:47</t>
         </is>
       </c>
     </row>
@@ -2015,17 +2027,17 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>113.0</t>
+          <t>202.0</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>113835.9</t>
+          <t>114775.5</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2479</t>
+          <t>5766</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -2035,7 +2047,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>936</t>
+          <t>1251</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -2055,7 +2067,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>10h 4m 15s</t>
+          <t>10h 6m 40s</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -2065,7 +2077,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>03:25:53</t>
+          <t>03:30:47</t>
         </is>
       </c>
     </row>
@@ -2184,7 +2196,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-06-04T03:23:35.3965904+05:30</t>
+          <t>2026-06-04T03:28:35.5426508+05:30</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -2194,7 +2206,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>03:23:35.396</t>
+          <t>03:28:35.542</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -11562,18 +11574,94 @@
         <v>43</v>
       </c>
     </row>
+    <row r="212">
+      <c r="A212" s="4">
+        <v>195</v>
+      </c>
+      <c r="B212" s="4" t="s">
+        <v>437</v>
+      </c>
+      <c r="C212" s="4" t="s">
+        <v>395</v>
+      </c>
+      <c r="D212" s="4" t="s">
+        <v>438</v>
+      </c>
+      <c r="E212" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F212" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G212" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H212" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I212" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J212" s="4">
+        <v>0</v>
+      </c>
+      <c r="K212" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L212" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
     <row r="213">
-      <c r="A213" t="s">
-        <v>437</v>
-      </c>
-      <c r="B213" t="s">
-        <v>438</v>
-      </c>
-      <c r="D213" t="s">
+      <c r="A213" s="4">
+        <v>196</v>
+      </c>
+      <c r="B213" s="4" t="s">
         <v>439</v>
       </c>
-      <c r="E213">
-        <v>194</v>
+      <c r="C213" s="4" t="s">
+        <v>395</v>
+      </c>
+      <c r="D213" s="4" t="s">
+        <v>440</v>
+      </c>
+      <c r="E213" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F213" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G213" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H213" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I213" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J213" s="4">
+        <v>0</v>
+      </c>
+      <c r="K213" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L213" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="s">
+        <v>441</v>
+      </c>
+      <c r="B215" t="s">
+        <v>442</v>
+      </c>
+      <c r="D215" t="s">
+        <v>443</v>
+      </c>
+      <c r="E215">
+        <v>196</v>
       </c>
     </row>
   </sheetData>

--- a/report-2026-06-04.xlsx
+++ b/report-2026-06-04.xlsx
@@ -16,12 +16,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="444" uniqueCount="444">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="446" uniqueCount="446">
   <si>
     <t>PunMonitor Leader Election — Current State</t>
   </si>
   <si>
-    <t>Generated 2026-06-04T03:30:47+05:30</t>
+    <t>Generated 2026-06-04T03:31:08+05:30</t>
   </si>
   <si>
     <t>Election method</t>
@@ -72,7 +72,7 @@
     <t>Leader last update</t>
   </si>
   <si>
-    <t>2026-06-04T03:29:08+05:30 (1m38s ago)</t>
+    <t>2026-06-04T03:31:05+05:30 (3s ago)</t>
   </si>
   <si>
     <t>Leader stale?</t>
@@ -87,7 +87,7 @@
     <t>Check count</t>
   </si>
   <si>
-    <t>13</t>
+    <t>14</t>
   </si>
   <si>
     <t>Last error</t>
@@ -1342,10 +1342,16 @@
     <t>03:28:35.542</t>
   </si>
   <si>
+    <t>2026-06-04T03:31:05.4614829+05:30</t>
+  </si>
+  <si>
+    <t>03:31:05.461</t>
+  </si>
+  <si>
     <t>Generated</t>
   </si>
   <si>
-    <t>2026-06-04T03:30:47+05:30</t>
+    <t>2026-06-04T03:31:08+05:30</t>
   </si>
   <si>
     <t>Total events</t>
@@ -1940,7 +1946,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>0h 22m 28s</t>
+          <t>0h 22m 50s</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -1960,7 +1966,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>10h 6m 45s</t>
+          <t>10h 6m 50s</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -1970,7 +1976,7 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>03:30:47</t>
+          <t>03:31:08</t>
         </is>
       </c>
     </row>
@@ -2027,17 +2033,17 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>202.0</t>
+          <t>454.0</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>114775.5</t>
+          <t>111972.9</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>5766</t>
+          <t>6024</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -2077,7 +2083,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>03:30:47</t>
+          <t>03:31:08</t>
         </is>
       </c>
     </row>
@@ -2196,7 +2202,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-06-04T03:28:35.5426508+05:30</t>
+          <t>2026-06-04T03:31:05.4614829+05:30</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -2206,7 +2212,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>03:28:35.542</t>
+          <t>03:31:05.461</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -11650,18 +11656,56 @@
         <v>43</v>
       </c>
     </row>
-    <row r="215">
-      <c r="A215" t="s">
+    <row r="214">
+      <c r="A214" s="4">
+        <v>197</v>
+      </c>
+      <c r="B214" s="4" t="s">
         <v>441</v>
       </c>
-      <c r="B215" t="s">
+      <c r="C214" s="4" t="s">
+        <v>395</v>
+      </c>
+      <c r="D214" s="4" t="s">
         <v>442</v>
       </c>
-      <c r="D215" t="s">
+      <c r="E214" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F214" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G214" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H214" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I214" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J214" s="4">
+        <v>0</v>
+      </c>
+      <c r="K214" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L214" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="s">
         <v>443</v>
       </c>
-      <c r="E215">
-        <v>196</v>
+      <c r="B216" t="s">
+        <v>444</v>
+      </c>
+      <c r="D216" t="s">
+        <v>445</v>
+      </c>
+      <c r="E216">
+        <v>197</v>
       </c>
     </row>
   </sheetData>

--- a/report-2026-06-04.xlsx
+++ b/report-2026-06-04.xlsx
@@ -16,12 +16,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="446" uniqueCount="446">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="448" uniqueCount="448">
   <si>
     <t>PunMonitor Leader Election — Current State</t>
   </si>
   <si>
-    <t>Generated 2026-06-04T03:31:08+05:30</t>
+    <t>Generated 2026-06-04T03:35:48+05:30</t>
   </si>
   <si>
     <t>Election method</t>
@@ -72,7 +72,7 @@
     <t>Leader last update</t>
   </si>
   <si>
-    <t>2026-06-04T03:31:05+05:30 (3s ago)</t>
+    <t>2026-06-04T03:34:24+05:30 (1m24s ago)</t>
   </si>
   <si>
     <t>Leader stale?</t>
@@ -87,7 +87,7 @@
     <t>Check count</t>
   </si>
   <si>
-    <t>14</t>
+    <t>19</t>
   </si>
   <si>
     <t>Last error</t>
@@ -1348,10 +1348,16 @@
     <t>03:31:05.461</t>
   </si>
   <si>
+    <t>2026-06-04T03:33:35.7238947+05:30</t>
+  </si>
+  <si>
+    <t>03:33:35.723</t>
+  </si>
+  <si>
     <t>Generated</t>
   </si>
   <si>
-    <t>2026-06-04T03:31:08+05:30</t>
+    <t>2026-06-04T03:35:48+05:30</t>
   </si>
   <si>
     <t>Total events</t>
@@ -1946,7 +1952,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>0h 22m 50s</t>
+          <t>0h 27m 30s</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -1966,7 +1972,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>10h 6m 50s</t>
+          <t>10h 10m 35s</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -1976,7 +1982,7 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>03:31:08</t>
+          <t>03:35:48</t>
         </is>
       </c>
     </row>
@@ -2033,17 +2039,17 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>454.0</t>
+          <t>1418.0</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>111972.9</t>
+          <t>311275.5</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>6024</t>
+          <t>7630</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -2053,7 +2059,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>1251</t>
+          <t>1566</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -2073,7 +2079,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>10h 6m 40s</t>
+          <t>10h 9m 10s</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -2083,7 +2089,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>03:31:08</t>
+          <t>03:35:48</t>
         </is>
       </c>
     </row>
@@ -2202,7 +2208,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-06-04T03:31:05.4614829+05:30</t>
+          <t>2026-06-04T03:33:35.7238947+05:30</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -2212,7 +2218,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>03:31:05.461</t>
+          <t>03:33:35.723</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -11694,18 +11700,56 @@
         <v>43</v>
       </c>
     </row>
-    <row r="216">
-      <c r="A216" t="s">
+    <row r="215">
+      <c r="A215" s="4">
+        <v>198</v>
+      </c>
+      <c r="B215" s="4" t="s">
         <v>443</v>
       </c>
-      <c r="B216" t="s">
+      <c r="C215" s="4" t="s">
+        <v>395</v>
+      </c>
+      <c r="D215" s="4" t="s">
         <v>444</v>
       </c>
-      <c r="D216" t="s">
+      <c r="E215" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F215" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G215" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H215" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I215" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J215" s="4">
+        <v>0</v>
+      </c>
+      <c r="K215" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L215" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="s">
         <v>445</v>
       </c>
-      <c r="E216">
-        <v>197</v>
+      <c r="B217" t="s">
+        <v>446</v>
+      </c>
+      <c r="D217" t="s">
+        <v>447</v>
+      </c>
+      <c r="E217">
+        <v>198</v>
       </c>
     </row>
   </sheetData>

--- a/report-2026-06-04.xlsx
+++ b/report-2026-06-04.xlsx
@@ -21,7 +21,7 @@
     <t>PunMonitor Leader Election — Current State</t>
   </si>
   <si>
-    <t>Generated 2026-06-04T03:35:48+05:30</t>
+    <t>Generated 2026-06-04T03:36:06+05:30</t>
   </si>
   <si>
     <t>Election method</t>
@@ -72,7 +72,7 @@
     <t>Leader last update</t>
   </si>
   <si>
-    <t>2026-06-04T03:34:24+05:30 (1m24s ago)</t>
+    <t>2026-06-04T03:34:24+05:30 (1m41s ago)</t>
   </si>
   <si>
     <t>Leader stale?</t>
@@ -1357,7 +1357,7 @@
     <t>Generated</t>
   </si>
   <si>
-    <t>2026-06-04T03:35:48+05:30</t>
+    <t>2026-06-04T03:36:06+05:30</t>
   </si>
   <si>
     <t>Total events</t>
@@ -1952,7 +1952,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>0h 27m 30s</t>
+          <t>0h 27m 48s</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -1972,7 +1972,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>10h 10m 35s</t>
+          <t>10h 10m 50s</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -1982,7 +1982,7 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>03:35:48</t>
+          <t>03:36:06</t>
         </is>
       </c>
     </row>
@@ -2039,17 +2039,17 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>1418.0</t>
+          <t>1397.0</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>311275.5</t>
+          <t>311487.5</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>7630</t>
+          <t>7717</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -2089,7 +2089,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>03:35:48</t>
+          <t>03:36:06</t>
         </is>
       </c>
     </row>

--- a/report-2026-06-04.xlsx
+++ b/report-2026-06-04.xlsx
@@ -21,7 +21,7 @@
     <t>PunMonitor Leader Election — Current State</t>
   </si>
   <si>
-    <t>Generated 2026-06-04T03:36:06+05:30</t>
+    <t>Generated 2026-06-04T03:36:24+05:30</t>
   </si>
   <si>
     <t>Election method</t>
@@ -72,7 +72,7 @@
     <t>Leader last update</t>
   </si>
   <si>
-    <t>2026-06-04T03:34:24+05:30 (1m41s ago)</t>
+    <t>2026-06-04T03:34:24+05:30 (2m0s ago)</t>
   </si>
   <si>
     <t>Leader stale?</t>
@@ -1357,7 +1357,7 @@
     <t>Generated</t>
   </si>
   <si>
-    <t>2026-06-04T03:36:06+05:30</t>
+    <t>2026-06-04T03:36:24+05:30</t>
   </si>
   <si>
     <t>Total events</t>
@@ -1952,7 +1952,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>0h 27m 48s</t>
+          <t>0h 28m 6s</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -1972,7 +1972,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>10h 10m 50s</t>
+          <t>10h 11m 10s</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -1982,7 +1982,7 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>03:36:06</t>
+          <t>03:36:24</t>
         </is>
       </c>
     </row>
@@ -2039,7 +2039,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>1397.0</t>
+          <t>1612.0</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -2049,7 +2049,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>7717</t>
+          <t>7813</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -2089,7 +2089,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>03:36:06</t>
+          <t>03:36:24</t>
         </is>
       </c>
     </row>

--- a/report-2026-06-04.xlsx
+++ b/report-2026-06-04.xlsx
@@ -16,12 +16,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="448" uniqueCount="448">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="452" uniqueCount="452">
   <si>
     <t>PunMonitor Leader Election — Current State</t>
   </si>
   <si>
-    <t>Generated 2026-06-04T03:36:24+05:30</t>
+    <t>Generated 2026-06-04T03:40:54+05:30</t>
   </si>
   <si>
     <t>Election method</t>
@@ -72,7 +72,7 @@
     <t>Leader last update</t>
   </si>
   <si>
-    <t>2026-06-04T03:34:24+05:30 (2m0s ago)</t>
+    <t>2026-06-04T03:39:35+05:30 (1m19s ago)</t>
   </si>
   <si>
     <t>Leader stale?</t>
@@ -87,7 +87,7 @@
     <t>Check count</t>
   </si>
   <si>
-    <t>19</t>
+    <t>23</t>
   </si>
   <si>
     <t>Last error</t>
@@ -1354,10 +1354,22 @@
     <t>03:33:35.723</t>
   </si>
   <si>
+    <t>2026-06-04T03:36:55.6977214+05:30</t>
+  </si>
+  <si>
+    <t>03:36:55.697</t>
+  </si>
+  <si>
+    <t>2026-06-04T03:38:54.6046181+05:30</t>
+  </si>
+  <si>
+    <t>03:38:54.604</t>
+  </si>
+  <si>
     <t>Generated</t>
   </si>
   <si>
-    <t>2026-06-04T03:36:24+05:30</t>
+    <t>2026-06-04T03:40:54+05:30</t>
   </si>
   <si>
     <t>Total events</t>
@@ -1952,7 +1964,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>0h 28m 6s</t>
+          <t>0h 32m 36s</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -1972,7 +1984,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>10h 11m 10s</t>
+          <t>10h 15m 40s</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -1982,7 +1994,7 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>03:36:24</t>
+          <t>03:40:54</t>
         </is>
       </c>
     </row>
@@ -2039,17 +2051,17 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>1612.0</t>
+          <t>1965.0</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>311487.5</t>
+          <t>311149.5</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>7813</t>
+          <t>9224</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -2059,7 +2071,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>1566</t>
+          <t>1877</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -2079,7 +2091,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>10h 9m 10s</t>
+          <t>10h 14m 20s</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -2089,7 +2101,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>03:36:24</t>
+          <t>03:40:54</t>
         </is>
       </c>
     </row>
@@ -2208,7 +2220,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-06-04T03:33:35.7238947+05:30</t>
+          <t>2026-06-04T03:38:54.6046181+05:30</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -2218,7 +2230,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>03:33:35.723</t>
+          <t>03:38:54.604</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -11738,18 +11750,94 @@
         <v>43</v>
       </c>
     </row>
+    <row r="216">
+      <c r="A216" s="4">
+        <v>199</v>
+      </c>
+      <c r="B216" s="4" t="s">
+        <v>445</v>
+      </c>
+      <c r="C216" s="4" t="s">
+        <v>395</v>
+      </c>
+      <c r="D216" s="4" t="s">
+        <v>446</v>
+      </c>
+      <c r="E216" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F216" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G216" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H216" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I216" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J216" s="4">
+        <v>0</v>
+      </c>
+      <c r="K216" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L216" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
     <row r="217">
-      <c r="A217" t="s">
-        <v>445</v>
-      </c>
-      <c r="B217" t="s">
-        <v>446</v>
-      </c>
-      <c r="D217" t="s">
+      <c r="A217" s="4">
+        <v>200</v>
+      </c>
+      <c r="B217" s="4" t="s">
         <v>447</v>
       </c>
-      <c r="E217">
-        <v>198</v>
+      <c r="C217" s="4" t="s">
+        <v>395</v>
+      </c>
+      <c r="D217" s="4" t="s">
+        <v>448</v>
+      </c>
+      <c r="E217" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F217" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G217" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H217" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I217" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J217" s="4">
+        <v>0</v>
+      </c>
+      <c r="K217" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L217" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="s">
+        <v>449</v>
+      </c>
+      <c r="B219" t="s">
+        <v>450</v>
+      </c>
+      <c r="D219" t="s">
+        <v>451</v>
+      </c>
+      <c r="E219">
+        <v>200</v>
       </c>
     </row>
   </sheetData>

--- a/report-2026-06-04.xlsx
+++ b/report-2026-06-04.xlsx
@@ -21,7 +21,7 @@
     <t>PunMonitor Leader Election — Current State</t>
   </si>
   <si>
-    <t>Generated 2026-06-04T03:40:54+05:30</t>
+    <t>Generated 2026-06-04T03:41:23+05:30</t>
   </si>
   <si>
     <t>Election method</t>
@@ -72,7 +72,7 @@
     <t>Leader last update</t>
   </si>
   <si>
-    <t>2026-06-04T03:39:35+05:30 (1m19s ago)</t>
+    <t>2026-06-04T03:39:35+05:30 (1m47s ago)</t>
   </si>
   <si>
     <t>Leader stale?</t>
@@ -1369,7 +1369,7 @@
     <t>Generated</t>
   </si>
   <si>
-    <t>2026-06-04T03:40:54+05:30</t>
+    <t>2026-06-04T03:41:23+05:30</t>
   </si>
   <si>
     <t>Total events</t>
@@ -1964,7 +1964,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>0h 32m 36s</t>
+          <t>0h 33m 5s</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -1984,7 +1984,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>10h 15m 40s</t>
+          <t>10h 16m 5s</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -1994,7 +1994,7 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>03:40:54</t>
+          <t>03:41:23</t>
         </is>
       </c>
     </row>
@@ -2051,17 +2051,17 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>1965.0</t>
+          <t>1388.0</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>311149.5</t>
+          <t>310717.5</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>9224</t>
+          <t>9382</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -2101,7 +2101,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>03:40:54</t>
+          <t>03:41:23</t>
         </is>
       </c>
     </row>

--- a/report-2026-06-04.xlsx
+++ b/report-2026-06-04.xlsx
@@ -21,7 +21,7 @@
     <t>PunMonitor Leader Election — Current State</t>
   </si>
   <si>
-    <t>Generated 2026-06-04T03:41:23+05:30</t>
+    <t>Generated 2026-06-04T03:41:35+05:30</t>
   </si>
   <si>
     <t>Election method</t>
@@ -72,7 +72,7 @@
     <t>Leader last update</t>
   </si>
   <si>
-    <t>2026-06-04T03:39:35+05:30 (1m47s ago)</t>
+    <t>2026-06-04T03:39:35+05:30 (2m0s ago)</t>
   </si>
   <si>
     <t>Leader stale?</t>
@@ -1369,7 +1369,7 @@
     <t>Generated</t>
   </si>
   <si>
-    <t>2026-06-04T03:41:23+05:30</t>
+    <t>2026-06-04T03:41:35+05:30</t>
   </si>
   <si>
     <t>Total events</t>
@@ -1964,7 +1964,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>0h 33m 5s</t>
+          <t>0h 33m 17s</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -1984,7 +1984,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>10h 16m 5s</t>
+          <t>10h 16m 20s</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -1994,7 +1994,7 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>03:41:23</t>
+          <t>03:41:35</t>
         </is>
       </c>
     </row>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>1388.0</t>
+          <t>2750.0</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>9382</t>
+          <t>9433</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -2101,7 +2101,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>03:41:23</t>
+          <t>03:41:35</t>
         </is>
       </c>
     </row>

--- a/report-2026-06-04.xlsx
+++ b/report-2026-06-04.xlsx
@@ -16,12 +16,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="452" uniqueCount="452">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="458" uniqueCount="458">
   <si>
     <t>PunMonitor Leader Election — Current State</t>
   </si>
   <si>
-    <t>Generated 2026-06-04T03:41:35+05:30</t>
+    <t>Generated 2026-06-04T03:45:49+05:30</t>
   </si>
   <si>
     <t>Election method</t>
@@ -72,7 +72,7 @@
     <t>Leader last update</t>
   </si>
   <si>
-    <t>2026-06-04T03:39:35+05:30 (2m0s ago)</t>
+    <t>2026-06-04T03:44:56+05:30 (53s ago)</t>
   </si>
   <si>
     <t>Leader stale?</t>
@@ -87,7 +87,7 @@
     <t>Check count</t>
   </si>
   <si>
-    <t>23</t>
+    <t>28</t>
   </si>
   <si>
     <t>Last error</t>
@@ -1366,10 +1366,28 @@
     <t>03:38:54.604</t>
   </si>
   <si>
+    <t>2026-06-04T03:42:06.6511509+05:30</t>
+  </si>
+  <si>
+    <t>03:42:06.651</t>
+  </si>
+  <si>
+    <t>2026-06-04T03:43:49.960574+05:30</t>
+  </si>
+  <si>
+    <t>03:43:49.960</t>
+  </si>
+  <si>
+    <t>2026-06-04T03:44:56.0968146+05:30</t>
+  </si>
+  <si>
+    <t>03:44:56.096</t>
+  </si>
+  <si>
     <t>Generated</t>
   </si>
   <si>
-    <t>2026-06-04T03:41:35+05:30</t>
+    <t>2026-06-04T03:45:49+05:30</t>
   </si>
   <si>
     <t>Total events</t>
@@ -1964,7 +1982,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>0h 33m 17s</t>
+          <t>0h 37m 31s</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -1984,7 +2002,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>10h 16m 20s</t>
+          <t>10h 20m 35s</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -1994,7 +2012,7 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>03:41:35</t>
+          <t>03:45:49</t>
         </is>
       </c>
     </row>
@@ -2051,17 +2069,17 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2750.0</t>
+          <t>3102.0</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>310717.5</t>
+          <t>311077.5</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>9433</t>
+          <t>10752</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -2071,7 +2089,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>1877</t>
+          <t>2198</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -2091,7 +2109,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>10h 14m 20s</t>
+          <t>10h 19m 40s</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -2101,7 +2119,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>03:41:35</t>
+          <t>03:45:49</t>
         </is>
       </c>
     </row>
@@ -2220,7 +2238,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-06-04T03:38:54.6046181+05:30</t>
+          <t>2026-06-04T03:44:56.0968146+05:30</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -2230,7 +2248,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>03:38:54.604</t>
+          <t>03:44:56.096</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -11826,18 +11844,132 @@
         <v>43</v>
       </c>
     </row>
+    <row r="218">
+      <c r="A218" s="4">
+        <v>201</v>
+      </c>
+      <c r="B218" s="4" t="s">
+        <v>449</v>
+      </c>
+      <c r="C218" s="4" t="s">
+        <v>395</v>
+      </c>
+      <c r="D218" s="4" t="s">
+        <v>450</v>
+      </c>
+      <c r="E218" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F218" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G218" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H218" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I218" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J218" s="4">
+        <v>0</v>
+      </c>
+      <c r="K218" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L218" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
     <row r="219">
-      <c r="A219" t="s">
-        <v>449</v>
-      </c>
-      <c r="B219" t="s">
-        <v>450</v>
-      </c>
-      <c r="D219" t="s">
+      <c r="A219" s="4">
+        <v>202</v>
+      </c>
+      <c r="B219" s="4" t="s">
         <v>451</v>
       </c>
-      <c r="E219">
-        <v>200</v>
+      <c r="C219" s="4" t="s">
+        <v>395</v>
+      </c>
+      <c r="D219" s="4" t="s">
+        <v>452</v>
+      </c>
+      <c r="E219" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F219" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G219" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H219" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I219" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J219" s="4">
+        <v>0</v>
+      </c>
+      <c r="K219" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L219" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" s="4">
+        <v>203</v>
+      </c>
+      <c r="B220" s="4" t="s">
+        <v>453</v>
+      </c>
+      <c r="C220" s="4" t="s">
+        <v>395</v>
+      </c>
+      <c r="D220" s="4" t="s">
+        <v>454</v>
+      </c>
+      <c r="E220" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F220" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G220" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H220" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I220" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J220" s="4">
+        <v>0</v>
+      </c>
+      <c r="K220" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L220" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="s">
+        <v>455</v>
+      </c>
+      <c r="B222" t="s">
+        <v>456</v>
+      </c>
+      <c r="D222" t="s">
+        <v>457</v>
+      </c>
+      <c r="E222">
+        <v>203</v>
       </c>
     </row>
   </sheetData>

--- a/report-2026-06-04.xlsx
+++ b/report-2026-06-04.xlsx
@@ -21,7 +21,7 @@
     <t>PunMonitor Leader Election — Current State</t>
   </si>
   <si>
-    <t>Generated 2026-06-04T03:45:49+05:30</t>
+    <t>Generated 2026-06-04T03:46:13+05:30</t>
   </si>
   <si>
     <t>Election method</t>
@@ -72,7 +72,7 @@
     <t>Leader last update</t>
   </si>
   <si>
-    <t>2026-06-04T03:44:56+05:30 (53s ago)</t>
+    <t>2026-06-04T03:44:56+05:30 (1m17s ago)</t>
   </si>
   <si>
     <t>Leader stale?</t>
@@ -1387,7 +1387,7 @@
     <t>Generated</t>
   </si>
   <si>
-    <t>2026-06-04T03:45:49+05:30</t>
+    <t>2026-06-04T03:46:13+05:30</t>
   </si>
   <si>
     <t>Total events</t>
@@ -1982,7 +1982,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>0h 37m 31s</t>
+          <t>0h 37m 55s</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -2002,7 +2002,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>10h 20m 35s</t>
+          <t>10h 21m 0s</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -2012,7 +2012,7 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>03:45:49</t>
+          <t>03:46:13</t>
         </is>
       </c>
     </row>
@@ -2069,17 +2069,17 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>3102.0</t>
+          <t>3495.0</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>311077.5</t>
+          <t>311213.5</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>10752</t>
+          <t>10865</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -2119,7 +2119,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>03:45:49</t>
+          <t>03:46:13</t>
         </is>
       </c>
     </row>

--- a/report-2026-06-04.xlsx
+++ b/report-2026-06-04.xlsx
@@ -21,7 +21,7 @@
     <t>PunMonitor Leader Election — Current State</t>
   </si>
   <si>
-    <t>Generated 2026-06-04T03:46:13+05:30</t>
+    <t>Generated 2026-06-04T03:46:34+05:30</t>
   </si>
   <si>
     <t>Election method</t>
@@ -72,7 +72,7 @@
     <t>Leader last update</t>
   </si>
   <si>
-    <t>2026-06-04T03:44:56+05:30 (1m17s ago)</t>
+    <t>2026-06-04T03:44:56+05:30 (1m38s ago)</t>
   </si>
   <si>
     <t>Leader stale?</t>
@@ -1387,7 +1387,7 @@
     <t>Generated</t>
   </si>
   <si>
-    <t>2026-06-04T03:46:13+05:30</t>
+    <t>2026-06-04T03:46:34+05:30</t>
   </si>
   <si>
     <t>Total events</t>
@@ -1982,7 +1982,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>0h 37m 55s</t>
+          <t>0h 38m 16s</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -2002,7 +2002,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>10h 21m 0s</t>
+          <t>10h 21m 20s</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -2012,7 +2012,7 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>03:46:13</t>
+          <t>03:46:34</t>
         </is>
       </c>
     </row>
@@ -2069,7 +2069,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>3495.0</t>
+          <t>2336.0</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -2079,7 +2079,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>10865</t>
+          <t>10976</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -2119,7 +2119,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>03:46:13</t>
+          <t>03:46:34</t>
         </is>
       </c>
     </row>

--- a/report-2026-06-04.xlsx
+++ b/report-2026-06-04.xlsx
@@ -21,7 +21,7 @@
     <t>PunMonitor Leader Election — Current State</t>
   </si>
   <si>
-    <t>Generated 2026-06-04T03:46:34+05:30</t>
+    <t>Generated 2026-06-04T03:46:56+05:30</t>
   </si>
   <si>
     <t>Election method</t>
@@ -72,7 +72,7 @@
     <t>Leader last update</t>
   </si>
   <si>
-    <t>2026-06-04T03:44:56+05:30 (1m38s ago)</t>
+    <t>2026-06-04T03:44:56+05:30 (2m0s ago)</t>
   </si>
   <si>
     <t>Leader stale?</t>
@@ -1387,7 +1387,7 @@
     <t>Generated</t>
   </si>
   <si>
-    <t>2026-06-04T03:46:34+05:30</t>
+    <t>2026-06-04T03:46:56+05:30</t>
   </si>
   <si>
     <t>Total events</t>
@@ -1982,7 +1982,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>0h 38m 16s</t>
+          <t>0h 38m 37s</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -2002,7 +2002,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>10h 21m 20s</t>
+          <t>10h 21m 40s</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -2012,7 +2012,7 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>03:46:34</t>
+          <t>03:46:56</t>
         </is>
       </c>
     </row>
@@ -2069,7 +2069,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2336.0</t>
+          <t>2496.0</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -2079,7 +2079,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>10976</t>
+          <t>11102</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -2119,7 +2119,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>03:46:34</t>
+          <t>03:46:56</t>
         </is>
       </c>
     </row>

--- a/report-2026-06-04.xlsx
+++ b/report-2026-06-04.xlsx
@@ -16,12 +16,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="458" uniqueCount="458">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="464" uniqueCount="464">
   <si>
     <t>PunMonitor Leader Election — Current State</t>
   </si>
   <si>
-    <t>Generated 2026-06-04T03:46:56+05:30</t>
+    <t>Generated 2026-06-04T03:50:48+05:30</t>
   </si>
   <si>
     <t>Election method</t>
@@ -72,7 +72,7 @@
     <t>Leader last update</t>
   </si>
   <si>
-    <t>2026-06-04T03:44:56+05:30 (2m0s ago)</t>
+    <t>2026-06-04T03:50:12+05:30 (36s ago)</t>
   </si>
   <si>
     <t>Leader stale?</t>
@@ -87,7 +87,7 @@
     <t>Check count</t>
   </si>
   <si>
-    <t>28</t>
+    <t>34</t>
   </si>
   <si>
     <t>Last error</t>
@@ -1384,10 +1384,28 @@
     <t>03:44:56.096</t>
   </si>
   <si>
+    <t>2026-06-04T03:47:27.2831596+05:30</t>
+  </si>
+  <si>
+    <t>03:47:27.283</t>
+  </si>
+  <si>
+    <t>2026-06-04T03:48:48.4540788+05:30</t>
+  </si>
+  <si>
+    <t>03:48:48.454</t>
+  </si>
+  <si>
+    <t>2026-06-04T03:49:50.8025575+05:30</t>
+  </si>
+  <si>
+    <t>03:49:50.802</t>
+  </si>
+  <si>
     <t>Generated</t>
   </si>
   <si>
-    <t>2026-06-04T03:46:56+05:30</t>
+    <t>2026-06-04T03:50:48+05:30</t>
   </si>
   <si>
     <t>Total events</t>
@@ -1982,7 +2000,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>0h 38m 37s</t>
+          <t>0h 42m 30s</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -2002,7 +2020,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>10h 21m 40s</t>
+          <t>10h 24m 25s</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -2012,7 +2030,7 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>03:46:56</t>
+          <t>03:50:48</t>
         </is>
       </c>
     </row>
@@ -2069,17 +2087,17 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2496.0</t>
+          <t>4916.0</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>311213.5</t>
+          <t>457477.5</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>11102</t>
+          <t>12664</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -2089,7 +2107,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>2198</t>
+          <t>2514</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -2109,7 +2127,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>10h 19m 40s</t>
+          <t>10h 24m 25s</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -2119,7 +2137,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>03:46:56</t>
+          <t>03:50:48</t>
         </is>
       </c>
     </row>
@@ -2238,7 +2256,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-06-04T03:44:56.0968146+05:30</t>
+          <t>2026-06-04T03:49:50.8025575+05:30</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -2248,7 +2266,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>03:44:56.096</t>
+          <t>03:49:50.802</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -11958,18 +11976,132 @@
         <v>43</v>
       </c>
     </row>
+    <row r="221">
+      <c r="A221" s="4">
+        <v>204</v>
+      </c>
+      <c r="B221" s="4" t="s">
+        <v>455</v>
+      </c>
+      <c r="C221" s="4" t="s">
+        <v>395</v>
+      </c>
+      <c r="D221" s="4" t="s">
+        <v>456</v>
+      </c>
+      <c r="E221" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F221" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G221" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H221" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I221" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J221" s="4">
+        <v>0</v>
+      </c>
+      <c r="K221" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L221" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
     <row r="222">
-      <c r="A222" t="s">
-        <v>455</v>
-      </c>
-      <c r="B222" t="s">
-        <v>456</v>
-      </c>
-      <c r="D222" t="s">
+      <c r="A222" s="4">
+        <v>205</v>
+      </c>
+      <c r="B222" s="4" t="s">
         <v>457</v>
       </c>
-      <c r="E222">
-        <v>203</v>
+      <c r="C222" s="4" t="s">
+        <v>395</v>
+      </c>
+      <c r="D222" s="4" t="s">
+        <v>458</v>
+      </c>
+      <c r="E222" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F222" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G222" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H222" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I222" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J222" s="4">
+        <v>0</v>
+      </c>
+      <c r="K222" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L222" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" s="4">
+        <v>206</v>
+      </c>
+      <c r="B223" s="4" t="s">
+        <v>459</v>
+      </c>
+      <c r="C223" s="4" t="s">
+        <v>395</v>
+      </c>
+      <c r="D223" s="4" t="s">
+        <v>460</v>
+      </c>
+      <c r="E223" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F223" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G223" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H223" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I223" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J223" s="4">
+        <v>0</v>
+      </c>
+      <c r="K223" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L223" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="s">
+        <v>461</v>
+      </c>
+      <c r="B225" t="s">
+        <v>462</v>
+      </c>
+      <c r="D225" t="s">
+        <v>463</v>
+      </c>
+      <c r="E225">
+        <v>206</v>
       </c>
     </row>
   </sheetData>

--- a/report-2026-06-04.xlsx
+++ b/report-2026-06-04.xlsx
@@ -21,7 +21,7 @@
     <t>PunMonitor Leader Election — Current State</t>
   </si>
   <si>
-    <t>Generated 2026-06-04T03:50:48+05:30</t>
+    <t>Generated 2026-06-04T03:51:07+05:30</t>
   </si>
   <si>
     <t>Election method</t>
@@ -72,7 +72,7 @@
     <t>Leader last update</t>
   </si>
   <si>
-    <t>2026-06-04T03:50:12+05:30 (36s ago)</t>
+    <t>2026-06-04T03:50:12+05:30 (54s ago)</t>
   </si>
   <si>
     <t>Leader stale?</t>
@@ -1405,7 +1405,7 @@
     <t>Generated</t>
   </si>
   <si>
-    <t>2026-06-04T03:50:48+05:30</t>
+    <t>2026-06-04T03:51:07+05:30</t>
   </si>
   <si>
     <t>Total events</t>
@@ -2000,7 +2000,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>0h 42m 30s</t>
+          <t>0h 42m 48s</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -2020,7 +2020,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>10h 24m 25s</t>
+          <t>10h 24m 35s</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -2030,7 +2030,7 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>03:50:48</t>
+          <t>03:51:07</t>
         </is>
       </c>
     </row>
@@ -2087,17 +2087,17 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>4916.0</t>
+          <t>6510.0</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>457477.5</t>
+          <t>344430.9</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>12664</t>
+          <t>12717</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -2137,7 +2137,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>03:50:48</t>
+          <t>03:51:07</t>
         </is>
       </c>
     </row>

--- a/report-2026-06-04.xlsx
+++ b/report-2026-06-04.xlsx
@@ -21,7 +21,7 @@
     <t>PunMonitor Leader Election — Current State</t>
   </si>
   <si>
-    <t>Generated 2026-06-04T03:51:07+05:30</t>
+    <t>Generated 2026-06-04T03:51:28+05:30</t>
   </si>
   <si>
     <t>Election method</t>
@@ -72,7 +72,7 @@
     <t>Leader last update</t>
   </si>
   <si>
-    <t>2026-06-04T03:50:12+05:30 (54s ago)</t>
+    <t>2026-06-04T03:50:12+05:30 (1m15s ago)</t>
   </si>
   <si>
     <t>Leader stale?</t>
@@ -1405,7 +1405,7 @@
     <t>Generated</t>
   </si>
   <si>
-    <t>2026-06-04T03:51:07+05:30</t>
+    <t>2026-06-04T03:51:28+05:30</t>
   </si>
   <si>
     <t>Total events</t>
@@ -2000,7 +2000,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>0h 42m 48s</t>
+          <t>0h 43m 10s</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -2030,7 +2030,7 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>03:51:07</t>
+          <t>03:51:28</t>
         </is>
       </c>
     </row>
@@ -2087,17 +2087,17 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>6510.0</t>
+          <t>6557.0</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>344430.9</t>
+          <t>389767.7</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>12717</t>
+          <t>12791</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -2137,7 +2137,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>03:51:07</t>
+          <t>03:51:28</t>
         </is>
       </c>
     </row>

--- a/report-2026-06-04.xlsx
+++ b/report-2026-06-04.xlsx
@@ -21,7 +21,7 @@
     <t>PunMonitor Leader Election — Current State</t>
   </si>
   <si>
-    <t>Generated 2026-06-04T03:51:28+05:30</t>
+    <t>Generated 2026-06-04T03:51:50+05:30</t>
   </si>
   <si>
     <t>Election method</t>
@@ -72,7 +72,7 @@
     <t>Leader last update</t>
   </si>
   <si>
-    <t>2026-06-04T03:50:12+05:30 (1m15s ago)</t>
+    <t>2026-06-04T03:50:12+05:30 (1m38s ago)</t>
   </si>
   <si>
     <t>Leader stale?</t>
@@ -1405,7 +1405,7 @@
     <t>Generated</t>
   </si>
   <si>
-    <t>2026-06-04T03:51:28+05:30</t>
+    <t>2026-06-04T03:51:50+05:30</t>
   </si>
   <si>
     <t>Total events</t>
@@ -2000,7 +2000,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>0h 43m 10s</t>
+          <t>0h 43m 32s</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -2030,7 +2030,7 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>03:51:28</t>
+          <t>03:51:50</t>
         </is>
       </c>
     </row>
@@ -2087,17 +2087,17 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>6557.0</t>
+          <t>1524.0</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>389767.7</t>
+          <t>169156.1</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>12791</t>
+          <t>12913</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -2137,7 +2137,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>03:51:28</t>
+          <t>03:51:50</t>
         </is>
       </c>
     </row>

--- a/report-2026-06-04.xlsx
+++ b/report-2026-06-04.xlsx
@@ -21,7 +21,7 @@
     <t>PunMonitor Leader Election — Current State</t>
   </si>
   <si>
-    <t>Generated 2026-06-04T03:51:50+05:30</t>
+    <t>Generated 2026-06-04T03:52:12+05:30</t>
   </si>
   <si>
     <t>Election method</t>
@@ -72,7 +72,7 @@
     <t>Leader last update</t>
   </si>
   <si>
-    <t>2026-06-04T03:50:12+05:30 (1m38s ago)</t>
+    <t>2026-06-04T03:50:12+05:30 (2m0s ago)</t>
   </si>
   <si>
     <t>Leader stale?</t>
@@ -1405,7 +1405,7 @@
     <t>Generated</t>
   </si>
   <si>
-    <t>2026-06-04T03:51:50+05:30</t>
+    <t>2026-06-04T03:52:12+05:30</t>
   </si>
   <si>
     <t>Total events</t>
@@ -2000,7 +2000,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>0h 43m 32s</t>
+          <t>0h 43m 54s</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -2030,7 +2030,7 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>03:51:50</t>
+          <t>03:52:12</t>
         </is>
       </c>
     </row>
@@ -2087,17 +2087,17 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>1524.0</t>
+          <t>4450.0</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>169156.1</t>
+          <t>381651.5</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>12913</t>
+          <t>13077</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -2137,7 +2137,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>03:51:50</t>
+          <t>03:52:12</t>
         </is>
       </c>
     </row>

--- a/report-2026-06-04.xlsx
+++ b/report-2026-06-04.xlsx
@@ -16,12 +16,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="464" uniqueCount="464">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="470" uniqueCount="470">
   <si>
     <t>PunMonitor Leader Election — Current State</t>
   </si>
   <si>
-    <t>Generated 2026-06-04T03:52:12+05:30</t>
+    <t>Generated 2026-06-04T03:55:48+05:30</t>
   </si>
   <si>
     <t>Election method</t>
@@ -72,7 +72,7 @@
     <t>Leader last update</t>
   </si>
   <si>
-    <t>2026-06-04T03:50:12+05:30 (2m0s ago)</t>
+    <t>2026-06-04T03:55:25+05:30 (23s ago)</t>
   </si>
   <si>
     <t>Leader stale?</t>
@@ -87,7 +87,7 @@
     <t>Check count</t>
   </si>
   <si>
-    <t>34</t>
+    <t>41</t>
   </si>
   <si>
     <t>Last error</t>
@@ -1402,10 +1402,28 @@
     <t>03:49:50.802</t>
   </si>
   <si>
+    <t>2026-06-04T03:52:43.6917746+05:30</t>
+  </si>
+  <si>
+    <t>03:52:43.691</t>
+  </si>
+  <si>
+    <t>2026-06-04T03:53:48.4217083+05:30</t>
+  </si>
+  <si>
+    <t>03:53:48.421</t>
+  </si>
+  <si>
+    <t>2026-06-04T03:55:06.8955829+05:30</t>
+  </si>
+  <si>
+    <t>03:55:06.895</t>
+  </si>
+  <si>
     <t>Generated</t>
   </si>
   <si>
-    <t>2026-06-04T03:52:12+05:30</t>
+    <t>2026-06-04T03:55:48+05:30</t>
   </si>
   <si>
     <t>Total events</t>
@@ -2000,7 +2018,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>0h 43m 54s</t>
+          <t>0h 47m 30s</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -2020,7 +2038,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>10h 24m 35s</t>
+          <t>10h 26m 0s</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -2030,7 +2048,7 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>03:52:12</t>
+          <t>03:55:48</t>
         </is>
       </c>
     </row>
@@ -2087,17 +2105,17 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>4450.0</t>
+          <t>2437.0</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>381651.5</t>
+          <t>143756.9</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>13077</t>
+          <t>14073</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -2107,7 +2125,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>2514</t>
+          <t>2827</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -2127,7 +2145,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>10h 24m 25s</t>
+          <t>10h 26m 0s</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -2137,7 +2155,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>03:52:12</t>
+          <t>03:55:48</t>
         </is>
       </c>
     </row>
@@ -2256,7 +2274,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-06-04T03:49:50.8025575+05:30</t>
+          <t>2026-06-04T03:55:06.8955829+05:30</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -2266,7 +2284,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>03:49:50.802</t>
+          <t>03:55:06.895</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -12090,18 +12108,132 @@
         <v>43</v>
       </c>
     </row>
+    <row r="224">
+      <c r="A224" s="4">
+        <v>207</v>
+      </c>
+      <c r="B224" s="4" t="s">
+        <v>461</v>
+      </c>
+      <c r="C224" s="4" t="s">
+        <v>395</v>
+      </c>
+      <c r="D224" s="4" t="s">
+        <v>462</v>
+      </c>
+      <c r="E224" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F224" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G224" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H224" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I224" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J224" s="4">
+        <v>0</v>
+      </c>
+      <c r="K224" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L224" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
     <row r="225">
-      <c r="A225" t="s">
-        <v>461</v>
-      </c>
-      <c r="B225" t="s">
-        <v>462</v>
-      </c>
-      <c r="D225" t="s">
+      <c r="A225" s="4">
+        <v>208</v>
+      </c>
+      <c r="B225" s="4" t="s">
         <v>463</v>
       </c>
-      <c r="E225">
-        <v>206</v>
+      <c r="C225" s="4" t="s">
+        <v>395</v>
+      </c>
+      <c r="D225" s="4" t="s">
+        <v>464</v>
+      </c>
+      <c r="E225" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F225" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G225" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H225" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I225" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J225" s="4">
+        <v>0</v>
+      </c>
+      <c r="K225" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L225" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" s="4">
+        <v>209</v>
+      </c>
+      <c r="B226" s="4" t="s">
+        <v>465</v>
+      </c>
+      <c r="C226" s="4" t="s">
+        <v>395</v>
+      </c>
+      <c r="D226" s="4" t="s">
+        <v>466</v>
+      </c>
+      <c r="E226" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F226" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G226" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H226" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I226" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J226" s="4">
+        <v>0</v>
+      </c>
+      <c r="K226" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L226" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="s">
+        <v>467</v>
+      </c>
+      <c r="B228" t="s">
+        <v>468</v>
+      </c>
+      <c r="D228" t="s">
+        <v>469</v>
+      </c>
+      <c r="E228">
+        <v>209</v>
       </c>
     </row>
   </sheetData>

--- a/report-2026-06-04.xlsx
+++ b/report-2026-06-04.xlsx
@@ -21,7 +21,7 @@
     <t>PunMonitor Leader Election — Current State</t>
   </si>
   <si>
-    <t>Generated 2026-06-04T03:55:48+05:30</t>
+    <t>Generated 2026-06-04T03:56:04+05:30</t>
   </si>
   <si>
     <t>Election method</t>
@@ -72,7 +72,7 @@
     <t>Leader last update</t>
   </si>
   <si>
-    <t>2026-06-04T03:55:25+05:30 (23s ago)</t>
+    <t>2026-06-04T03:55:25+05:30 (39s ago)</t>
   </si>
   <si>
     <t>Leader stale?</t>
@@ -1423,7 +1423,7 @@
     <t>Generated</t>
   </si>
   <si>
-    <t>2026-06-04T03:55:48+05:30</t>
+    <t>2026-06-04T03:56:04+05:30</t>
   </si>
   <si>
     <t>Total events</t>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>0h 47m 30s</t>
+          <t>0h 47m 46s</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>03:55:48</t>
+          <t>03:56:04</t>
         </is>
       </c>
     </row>
@@ -2105,17 +2105,17 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2437.0</t>
+          <t>3504.0</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>143756.9</t>
+          <t>148638.5</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>14073</t>
+          <t>14199</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -2155,7 +2155,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>03:55:48</t>
+          <t>03:56:04</t>
         </is>
       </c>
     </row>

--- a/report-2026-06-04.xlsx
+++ b/report-2026-06-04.xlsx
@@ -21,7 +21,7 @@
     <t>PunMonitor Leader Election — Current State</t>
   </si>
   <si>
-    <t>Generated 2026-06-04T03:56:04+05:30</t>
+    <t>Generated 2026-06-04T03:56:18+05:30</t>
   </si>
   <si>
     <t>Election method</t>
@@ -72,7 +72,7 @@
     <t>Leader last update</t>
   </si>
   <si>
-    <t>2026-06-04T03:55:25+05:30 (39s ago)</t>
+    <t>2026-06-04T03:55:25+05:30 (53s ago)</t>
   </si>
   <si>
     <t>Leader stale?</t>
@@ -1423,7 +1423,7 @@
     <t>Generated</t>
   </si>
   <si>
-    <t>2026-06-04T03:56:04+05:30</t>
+    <t>2026-06-04T03:56:18+05:30</t>
   </si>
   <si>
     <t>Total events</t>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>0h 47m 46s</t>
+          <t>0h 48m 0s</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>03:56:04</t>
+          <t>03:56:18</t>
         </is>
       </c>
     </row>
@@ -2105,17 +2105,17 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>3504.0</t>
+          <t>2811.0</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>148638.5</t>
+          <t>140933.1</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>14199</t>
+          <t>14323</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -2155,7 +2155,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>03:56:04</t>
+          <t>03:56:18</t>
         </is>
       </c>
     </row>

--- a/report-2026-06-04.xlsx
+++ b/report-2026-06-04.xlsx
@@ -21,7 +21,7 @@
     <t>PunMonitor Leader Election — Current State</t>
   </si>
   <si>
-    <t>Generated 2026-06-04T03:56:18+05:30</t>
+    <t>Generated 2026-06-04T03:56:35+05:30</t>
   </si>
   <si>
     <t>Election method</t>
@@ -72,7 +72,7 @@
     <t>Leader last update</t>
   </si>
   <si>
-    <t>2026-06-04T03:55:25+05:30 (53s ago)</t>
+    <t>2026-06-04T03:55:25+05:30 (1m10s ago)</t>
   </si>
   <si>
     <t>Leader stale?</t>
@@ -1423,7 +1423,7 @@
     <t>Generated</t>
   </si>
   <si>
-    <t>2026-06-04T03:56:18+05:30</t>
+    <t>2026-06-04T03:56:35+05:30</t>
   </si>
   <si>
     <t>Total events</t>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>0h 48m 0s</t>
+          <t>0h 48m 17s</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>03:56:18</t>
+          <t>03:56:35</t>
         </is>
       </c>
     </row>
@@ -2105,17 +2105,17 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2811.0</t>
+          <t>2286.0</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>140933.1</t>
+          <t>140127.1</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>14323</t>
+          <t>14487</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -2155,7 +2155,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>03:56:18</t>
+          <t>03:56:35</t>
         </is>
       </c>
     </row>

--- a/report-2026-06-04.xlsx
+++ b/report-2026-06-04.xlsx
@@ -21,7 +21,7 @@
     <t>PunMonitor Leader Election — Current State</t>
   </si>
   <si>
-    <t>Generated 2026-06-04T03:56:35+05:30</t>
+    <t>Generated 2026-06-04T03:57:06+05:30</t>
   </si>
   <si>
     <t>Election method</t>
@@ -72,7 +72,7 @@
     <t>Leader last update</t>
   </si>
   <si>
-    <t>2026-06-04T03:55:25+05:30 (1m10s ago)</t>
+    <t>2026-06-04T03:55:25+05:30 (1m41s ago)</t>
   </si>
   <si>
     <t>Leader stale?</t>
@@ -1423,7 +1423,7 @@
     <t>Generated</t>
   </si>
   <si>
-    <t>2026-06-04T03:56:35+05:30</t>
+    <t>2026-06-04T03:57:06+05:30</t>
   </si>
   <si>
     <t>Total events</t>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>0h 48m 17s</t>
+          <t>0h 48m 48s</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -2038,7 +2038,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>10h 26m 0s</t>
+          <t>10h 26m 15s</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>03:56:35</t>
+          <t>03:57:06</t>
         </is>
       </c>
     </row>
@@ -2105,17 +2105,17 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2286.0</t>
+          <t>8886.0</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>140127.1</t>
+          <t>310945.5</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>14487</t>
+          <t>14669</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -2155,7 +2155,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>03:56:35</t>
+          <t>03:57:06</t>
         </is>
       </c>
     </row>

--- a/report-2026-06-04.xlsx
+++ b/report-2026-06-04.xlsx
@@ -16,12 +16,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="470" uniqueCount="470">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="483" uniqueCount="483">
   <si>
     <t>PunMonitor Leader Election — Current State</t>
   </si>
   <si>
-    <t>Generated 2026-06-04T03:57:06+05:30</t>
+    <t>Generated 2026-06-04T04:16:02+05:30</t>
   </si>
   <si>
     <t>Election method</t>
@@ -72,7 +72,7 @@
     <t>Leader last update</t>
   </si>
   <si>
-    <t>2026-06-04T03:55:25+05:30 (1m41s ago)</t>
+    <t>2026-06-04T04:15:33+05:30 (29s ago)</t>
   </si>
   <si>
     <t>Leader stale?</t>
@@ -87,7 +87,7 @@
     <t>Check count</t>
   </si>
   <si>
-    <t>41</t>
+    <t>51</t>
   </si>
   <si>
     <t>Last error</t>
@@ -1420,10 +1420,49 @@
     <t>03:55:06.895</t>
   </si>
   <si>
+    <t>2026-06-04T03:58:01.1748151+05:30</t>
+  </si>
+  <si>
+    <t>03:58:01.174</t>
+  </si>
+  <si>
+    <t>Get "https://api.github.com/repos/puniteswra-spec/PU/contents/primary_server.json": read tcp 192.168.0.128:62274-&gt;20.207.73.85:443: wsarecv: A connection attempt failed because the connected party did not properly respond after a period of time, or established connection failed because connected host has failed to respond.</t>
+  </si>
+  <si>
+    <t>2026-06-04T04:00:25.4651354+05:30</t>
+  </si>
+  <si>
+    <t>04:00:25.465</t>
+  </si>
+  <si>
+    <t>2026-06-04T04:05:25.4820715+05:30</t>
+  </si>
+  <si>
+    <t>04:05:25.482</t>
+  </si>
+  <si>
+    <t>2026-06-04T04:10:25.4645832+05:30</t>
+  </si>
+  <si>
+    <t>04:10:25.464</t>
+  </si>
+  <si>
+    <t>2026-06-04T04:13:47.8879236+05:30</t>
+  </si>
+  <si>
+    <t>04:13:47.887</t>
+  </si>
+  <si>
+    <t>2026-06-04T04:15:11.0712181+05:30</t>
+  </si>
+  <si>
+    <t>04:15:11.071</t>
+  </si>
+  <si>
     <t>Generated</t>
   </si>
   <si>
-    <t>2026-06-04T03:57:06+05:30</t>
+    <t>2026-06-04T04:16:02+05:30</t>
   </si>
   <si>
     <t>Total events</t>
@@ -1958,7 +1997,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>192.168.0.128</t>
+          <t>192.168.0.164</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -2018,7 +2057,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>0h 48m 48s</t>
+          <t>1h 7m 44s</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -2038,7 +2077,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>10h 26m 15s</t>
+          <t>10h 45m 10s</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -2048,7 +2087,7 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>03:57:06</t>
+          <t>04:16:02</t>
         </is>
       </c>
     </row>
@@ -2065,7 +2104,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>192.168.0.128</t>
+          <t>192.168.0.164</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -2105,17 +2144,17 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>8886.0</t>
+          <t>5960.0</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>310945.5</t>
+          <t>295903.5</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>14669</t>
+          <t>16942</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -2125,7 +2164,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>2827</t>
+          <t>4036</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -2145,7 +2184,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>10h 26m 0s</t>
+          <t>10h 44m 45s</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -2155,7 +2194,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>03:57:06</t>
+          <t>04:16:02</t>
         </is>
       </c>
     </row>
@@ -2274,7 +2313,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-06-04T03:55:06.8955829+05:30</t>
+          <t>2026-06-04T04:15:11.0712181+05:30</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -2284,7 +2323,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>03:55:06.895</t>
+          <t>04:15:11.071</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -12222,18 +12261,246 @@
         <v>43</v>
       </c>
     </row>
+    <row r="227">
+      <c r="A227" s="3">
+        <v>210</v>
+      </c>
+      <c r="B227" s="3" t="s">
+        <v>467</v>
+      </c>
+      <c r="C227" s="3" t="s">
+        <v>395</v>
+      </c>
+      <c r="D227" s="3" t="s">
+        <v>468</v>
+      </c>
+      <c r="E227" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F227" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G227" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="H227" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="I227" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="J227" s="3">
+        <v>9223372036</v>
+      </c>
+      <c r="K227" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="L227" s="3" t="s">
+        <v>469</v>
+      </c>
+    </row>
     <row r="228">
-      <c r="A228" t="s">
-        <v>467</v>
-      </c>
-      <c r="B228" t="s">
-        <v>468</v>
-      </c>
-      <c r="D228" t="s">
-        <v>469</v>
-      </c>
-      <c r="E228">
-        <v>209</v>
+      <c r="A228" s="3">
+        <v>211</v>
+      </c>
+      <c r="B228" s="3" t="s">
+        <v>470</v>
+      </c>
+      <c r="C228" s="3" t="s">
+        <v>395</v>
+      </c>
+      <c r="D228" s="3" t="s">
+        <v>471</v>
+      </c>
+      <c r="E228" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F228" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G228" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="H228" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="I228" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="J228" s="3">
+        <v>9223372036</v>
+      </c>
+      <c r="K228" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="L228" s="3" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" s="3">
+        <v>212</v>
+      </c>
+      <c r="B229" s="3" t="s">
+        <v>472</v>
+      </c>
+      <c r="C229" s="3" t="s">
+        <v>395</v>
+      </c>
+      <c r="D229" s="3" t="s">
+        <v>473</v>
+      </c>
+      <c r="E229" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F229" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G229" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="H229" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="I229" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="J229" s="3">
+        <v>9223372036</v>
+      </c>
+      <c r="K229" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="L229" s="3" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" s="3">
+        <v>213</v>
+      </c>
+      <c r="B230" s="3" t="s">
+        <v>474</v>
+      </c>
+      <c r="C230" s="3" t="s">
+        <v>395</v>
+      </c>
+      <c r="D230" s="3" t="s">
+        <v>475</v>
+      </c>
+      <c r="E230" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F230" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G230" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="H230" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="I230" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="J230" s="3">
+        <v>9223372036</v>
+      </c>
+      <c r="K230" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="L230" s="3" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" s="4">
+        <v>214</v>
+      </c>
+      <c r="B231" s="4" t="s">
+        <v>476</v>
+      </c>
+      <c r="C231" s="4" t="s">
+        <v>395</v>
+      </c>
+      <c r="D231" s="4" t="s">
+        <v>477</v>
+      </c>
+      <c r="E231" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F231" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G231" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H231" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I231" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J231" s="4">
+        <v>0</v>
+      </c>
+      <c r="K231" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L231" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" s="4">
+        <v>215</v>
+      </c>
+      <c r="B232" s="4" t="s">
+        <v>478</v>
+      </c>
+      <c r="C232" s="4" t="s">
+        <v>395</v>
+      </c>
+      <c r="D232" s="4" t="s">
+        <v>479</v>
+      </c>
+      <c r="E232" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F232" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G232" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H232" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I232" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J232" s="4">
+        <v>0</v>
+      </c>
+      <c r="K232" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L232" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="s">
+        <v>480</v>
+      </c>
+      <c r="B234" t="s">
+        <v>481</v>
+      </c>
+      <c r="D234" t="s">
+        <v>482</v>
+      </c>
+      <c r="E234">
+        <v>215</v>
       </c>
     </row>
   </sheetData>

--- a/report-2026-06-04.xlsx
+++ b/report-2026-06-04.xlsx
@@ -21,7 +21,7 @@
     <t>PunMonitor Leader Election — Current State</t>
   </si>
   <si>
-    <t>Generated 2026-06-04T04:16:02+05:30</t>
+    <t>Generated 2026-06-04T04:16:23+05:30</t>
   </si>
   <si>
     <t>Election method</t>
@@ -72,7 +72,7 @@
     <t>Leader last update</t>
   </si>
   <si>
-    <t>2026-06-04T04:15:33+05:30 (29s ago)</t>
+    <t>2026-06-04T04:15:33+05:30 (50s ago)</t>
   </si>
   <si>
     <t>Leader stale?</t>
@@ -1462,7 +1462,7 @@
     <t>Generated</t>
   </si>
   <si>
-    <t>2026-06-04T04:16:02+05:30</t>
+    <t>2026-06-04T04:16:23+05:30</t>
   </si>
   <si>
     <t>Total events</t>
@@ -2057,7 +2057,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>1h 7m 44s</t>
+          <t>1h 8m 5s</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>10h 45m 10s</t>
+          <t>10h 45m 35s</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -2087,7 +2087,7 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>04:16:02</t>
+          <t>04:16:23</t>
         </is>
       </c>
     </row>
@@ -2144,7 +2144,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>5960.0</t>
+          <t>16472.0</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -2154,7 +2154,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>16942</t>
+          <t>16983</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -2194,7 +2194,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>04:16:02</t>
+          <t>04:16:23</t>
         </is>
       </c>
     </row>

--- a/report-2026-06-04.xlsx
+++ b/report-2026-06-04.xlsx
@@ -21,7 +21,7 @@
     <t>PunMonitor Leader Election — Current State</t>
   </si>
   <si>
-    <t>Generated 2026-06-04T04:16:23+05:30</t>
+    <t>Generated 2026-06-04T04:16:38+05:30</t>
   </si>
   <si>
     <t>Election method</t>
@@ -72,7 +72,7 @@
     <t>Leader last update</t>
   </si>
   <si>
-    <t>2026-06-04T04:15:33+05:30 (50s ago)</t>
+    <t>2026-06-04T04:15:33+05:30 (1m5s ago)</t>
   </si>
   <si>
     <t>Leader stale?</t>
@@ -1462,7 +1462,7 @@
     <t>Generated</t>
   </si>
   <si>
-    <t>2026-06-04T04:16:23+05:30</t>
+    <t>2026-06-04T04:16:38+05:30</t>
   </si>
   <si>
     <t>Total events</t>
@@ -2057,7 +2057,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>1h 8m 5s</t>
+          <t>1h 8m 20s</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>10h 45m 35s</t>
+          <t>10h 45m 50s</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -2087,7 +2087,7 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>04:16:23</t>
+          <t>04:16:38</t>
         </is>
       </c>
     </row>
@@ -2144,7 +2144,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>16472.0</t>
+          <t>16037.0</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -2154,7 +2154,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>16983</t>
+          <t>17011</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -2194,7 +2194,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>04:16:23</t>
+          <t>04:16:38</t>
         </is>
       </c>
     </row>

--- a/report-2026-06-04.xlsx
+++ b/report-2026-06-04.xlsx
@@ -16,12 +16,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="483" uniqueCount="483">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="487" uniqueCount="487">
   <si>
     <t>PunMonitor Leader Election — Current State</t>
   </si>
   <si>
-    <t>Generated 2026-06-04T04:16:38+05:30</t>
+    <t>Generated 2026-06-04T19:06:30+05:30</t>
   </si>
   <si>
     <t>Election method</t>
@@ -57,43 +57,46 @@
     <t>Mode / Role</t>
   </si>
   <si>
-    <t>SERVER+LEADER (this instance is the GitHub primary)</t>
+    <t>SERVER (primary)</t>
   </si>
   <si>
     <t>Self is leader</t>
   </si>
   <si>
-    <t>YES — this instance is the primary server</t>
+    <t>No</t>
   </si>
   <si>
     <t>Current leader</t>
   </si>
   <si>
+    <t>(no leader recorded)</t>
+  </si>
+  <si>
     <t>Leader last update</t>
   </si>
   <si>
-    <t>2026-06-04T04:15:33+05:30 (1m5s ago)</t>
+    <t>(never)</t>
   </si>
   <si>
     <t>Leader stale?</t>
   </si>
   <si>
-    <t>No</t>
-  </si>
-  <si>
     <t>Last check</t>
   </si>
   <si>
+    <t>2026-06-04T19:06:16+05:30 (14s ago)</t>
+  </si>
+  <si>
     <t>Check count</t>
   </si>
   <si>
-    <t>51</t>
+    <t>53</t>
   </si>
   <si>
     <t>Last error</t>
   </si>
   <si>
-    <t>(none)</t>
+    <t>Get "https://api.github.com/repos/puniteswra-spec/PU/contents/primary_server.json": dial tcp: lookup api.github.com: no such host</t>
   </si>
   <si>
     <t>Election History (row-wise — latest first)</t>
@@ -886,9 +889,6 @@
     <t>04:02:38.142</t>
   </si>
   <si>
-    <t>Get "https://api.github.com/repos/puniteswra-spec/PU/contents/primary_server.json": dial tcp: lookup api.github.com: no such host</t>
-  </si>
-  <si>
     <t>2026-06-03T04:05:08.1306949+05:30</t>
   </si>
   <si>
@@ -1459,10 +1459,22 @@
     <t>04:15:11.071</t>
   </si>
   <si>
+    <t>2026-06-04T19:06:15.5965806+05:30</t>
+  </si>
+  <si>
+    <t>19:06:15.596</t>
+  </si>
+  <si>
+    <t>2026-06-04T19:06:16.6865666+05:30</t>
+  </si>
+  <si>
+    <t>19:06:16.686</t>
+  </si>
+  <si>
     <t>Generated</t>
   </si>
   <si>
-    <t>2026-06-04T04:16:38+05:30</t>
+    <t>2026-06-04T19:06:31+05:30</t>
   </si>
   <si>
     <t>Total events</t>
@@ -1997,7 +2009,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>192.168.0.164</t>
+          <t>192.168.0.128</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -2057,7 +2069,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>1h 8m 20s</t>
+          <t>15h 58m 12s</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -2077,7 +2089,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>10h 45m 50s</t>
+          <t>10h 46m 30s</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -2087,7 +2099,7 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>04:16:38</t>
+          <t>19:06:30</t>
         </is>
       </c>
     </row>
@@ -2144,17 +2156,17 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>16037.0</t>
+          <t>2000.0</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>295903.5</t>
+          <t>300453.5</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>17011</t>
+          <t>17110</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -2194,7 +2206,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>04:16:38</t>
+          <t>19:06:30</t>
         </is>
       </c>
     </row>
@@ -2308,12 +2320,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>[renewed]</t>
+          <t>[error]</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-06-04T04:15:11.0712181+05:30</t>
+          <t>2026-06-04T19:06:16.6865666+05:30</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -2323,12 +2335,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>04:15:11.071</t>
+          <t>19:06:16.686</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>renewed</t>
+          <t>error</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -2348,20 +2360,20 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>PuneetU-EB6LMJD-cf4a9ce5</t>
+          <t/>
         </is>
       </c>
       <c r="J5">
-        <v>0</v>
+        <v>9223372036</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>renewed</t>
+          <t>error</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t/>
+          <t>Get "https://api.github.com/repos/puniteswra-spec/PU/contents/primary_server.json": dial tcp: lookup api.github.com: no such host</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -4222,23 +4234,23 @@
         <v>16</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>9</v>
+        <v>17</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="6" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="6" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
     </row>
     <row r="12">
@@ -4246,28 +4258,28 @@
         <v>21</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="6" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B16" s="5"/>
       <c r="C16" s="5"/>
@@ -4283,40 +4295,40 @@
     </row>
     <row r="17">
       <c r="A17" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="I17" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J17" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K17" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="L17" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="18">
@@ -4324,16 +4336,16 @@
         <v>1</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F18" s="3" t="s">
         <v>3</v>
@@ -4345,16 +4357,16 @@
         <v>11</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="J18" s="3">
         <v>9223372036</v>
       </c>
       <c r="K18" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="L18" s="3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="19">
@@ -4362,16 +4374,16 @@
         <v>2</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F19" s="3" t="s">
         <v>3</v>
@@ -4383,16 +4395,16 @@
         <v>11</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="J19" s="3">
         <v>9223372036</v>
       </c>
       <c r="K19" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="L19" s="3" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="20">
@@ -4400,16 +4412,16 @@
         <v>3</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F20" s="3" t="s">
         <v>3</v>
@@ -4421,16 +4433,16 @@
         <v>11</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="J20" s="3">
         <v>9223372036</v>
       </c>
       <c r="K20" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="L20" s="3" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="21">
@@ -4438,16 +4450,16 @@
         <v>4</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F21" s="3" t="s">
         <v>3</v>
@@ -4459,16 +4471,16 @@
         <v>11</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="J21" s="3">
         <v>9223372036</v>
       </c>
       <c r="K21" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="L21" s="3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="22">
@@ -4476,16 +4488,16 @@
         <v>5</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F22" s="3" t="s">
         <v>3</v>
@@ -4497,16 +4509,16 @@
         <v>11</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="J22" s="3">
         <v>9223372036</v>
       </c>
       <c r="K22" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="L22" s="3" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="23">
@@ -4514,16 +4526,16 @@
         <v>6</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F23" s="3" t="s">
         <v>3</v>
@@ -4535,16 +4547,16 @@
         <v>11</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="J23" s="3">
         <v>9223372036</v>
       </c>
       <c r="K23" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="L23" s="3" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="24">
@@ -4552,16 +4564,16 @@
         <v>7</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F24" s="3" t="s">
         <v>3</v>
@@ -4573,16 +4585,16 @@
         <v>11</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="J24" s="3">
         <v>9223372036</v>
       </c>
       <c r="K24" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="L24" s="3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="25">
@@ -4590,16 +4602,16 @@
         <v>8</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F25" s="3" t="s">
         <v>3</v>
@@ -4611,16 +4623,16 @@
         <v>11</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="J25" s="3">
         <v>9223372036</v>
       </c>
       <c r="K25" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="L25" s="3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="26">
@@ -4628,16 +4640,16 @@
         <v>9</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F26" s="3" t="s">
         <v>3</v>
@@ -4649,16 +4661,16 @@
         <v>11</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="J26" s="3">
         <v>9223372036</v>
       </c>
       <c r="K26" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="L26" s="3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="27">
@@ -4666,16 +4678,16 @@
         <v>10</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F27" s="3" t="s">
         <v>3</v>
@@ -4687,16 +4699,16 @@
         <v>11</v>
       </c>
       <c r="I27" s="3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="J27" s="3">
         <v>9223372036</v>
       </c>
       <c r="K27" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="L27" s="3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="28">
@@ -4704,16 +4716,16 @@
         <v>11</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F28" s="3" t="s">
         <v>3</v>
@@ -4725,16 +4737,16 @@
         <v>11</v>
       </c>
       <c r="I28" s="3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="J28" s="3">
         <v>9223372036</v>
       </c>
       <c r="K28" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="L28" s="3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="29">
@@ -4742,16 +4754,16 @@
         <v>12</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F29" s="3" t="s">
         <v>3</v>
@@ -4763,16 +4775,16 @@
         <v>11</v>
       </c>
       <c r="I29" s="3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="J29" s="3">
         <v>9223372036</v>
       </c>
       <c r="K29" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="L29" s="3" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="30">
@@ -4780,16 +4792,16 @@
         <v>13</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F30" s="3" t="s">
         <v>3</v>
@@ -4801,16 +4813,16 @@
         <v>11</v>
       </c>
       <c r="I30" s="3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="J30" s="3">
         <v>9223372036</v>
       </c>
       <c r="K30" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="L30" s="3" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="31">
@@ -4818,16 +4830,16 @@
         <v>14</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F31" s="3" t="s">
         <v>3</v>
@@ -4839,16 +4851,16 @@
         <v>11</v>
       </c>
       <c r="I31" s="3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="J31" s="3">
         <v>9223372036</v>
       </c>
       <c r="K31" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="L31" s="3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="32">
@@ -4856,16 +4868,16 @@
         <v>15</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F32" s="3" t="s">
         <v>3</v>
@@ -4877,16 +4889,16 @@
         <v>11</v>
       </c>
       <c r="I32" s="3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="J32" s="3">
         <v>9223372036</v>
       </c>
       <c r="K32" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="L32" s="3" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="33">
@@ -4894,16 +4906,16 @@
         <v>16</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E33" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F33" s="3" t="s">
         <v>3</v>
@@ -4915,16 +4927,16 @@
         <v>11</v>
       </c>
       <c r="I33" s="3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="J33" s="3">
         <v>9223372036</v>
       </c>
       <c r="K33" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="L33" s="3" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="34">
@@ -4932,16 +4944,16 @@
         <v>17</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C34" s="4" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D34" s="4" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E34" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F34" s="4" t="s">
         <v>3</v>
@@ -4959,10 +4971,10 @@
         <v>0</v>
       </c>
       <c r="K34" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="L34" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="35">
@@ -4970,16 +4982,16 @@
         <v>18</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C35" s="4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D35" s="4" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E35" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F35" s="4" t="s">
         <v>3</v>
@@ -4997,10 +5009,10 @@
         <v>0</v>
       </c>
       <c r="K35" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="L35" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="36">
@@ -5008,16 +5020,16 @@
         <v>19</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C36" s="4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D36" s="4" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E36" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F36" s="4" t="s">
         <v>3</v>
@@ -5035,10 +5047,10 @@
         <v>0</v>
       </c>
       <c r="K36" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="L36" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="37">
@@ -5046,16 +5058,16 @@
         <v>20</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C37" s="4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D37" s="4" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E37" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F37" s="4" t="s">
         <v>3</v>
@@ -5073,10 +5085,10 @@
         <v>0</v>
       </c>
       <c r="K37" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="L37" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="38">
@@ -5084,16 +5096,16 @@
         <v>21</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C38" s="4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D38" s="4" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E38" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F38" s="4" t="s">
         <v>3</v>
@@ -5111,10 +5123,10 @@
         <v>0</v>
       </c>
       <c r="K38" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="L38" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="39">
@@ -5122,16 +5134,16 @@
         <v>22</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C39" s="4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D39" s="4" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E39" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F39" s="4" t="s">
         <v>3</v>
@@ -5149,10 +5161,10 @@
         <v>0</v>
       </c>
       <c r="K39" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="L39" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="40">
@@ -5160,16 +5172,16 @@
         <v>23</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C40" s="4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D40" s="4" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E40" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F40" s="4" t="s">
         <v>3</v>
@@ -5187,10 +5199,10 @@
         <v>0</v>
       </c>
       <c r="K40" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="L40" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="41">
@@ -5198,16 +5210,16 @@
         <v>24</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C41" s="4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D41" s="4" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="E41" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F41" s="4" t="s">
         <v>3</v>
@@ -5225,10 +5237,10 @@
         <v>0</v>
       </c>
       <c r="K41" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="L41" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="42">
@@ -5236,16 +5248,16 @@
         <v>25</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C42" s="4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D42" s="4" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E42" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F42" s="4" t="s">
         <v>3</v>
@@ -5263,10 +5275,10 @@
         <v>0</v>
       </c>
       <c r="K42" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="L42" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="43">
@@ -5274,16 +5286,16 @@
         <v>26</v>
       </c>
       <c r="B43" s="4" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C43" s="4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D43" s="4" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E43" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F43" s="4" t="s">
         <v>3</v>
@@ -5301,10 +5313,10 @@
         <v>0</v>
       </c>
       <c r="K43" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="L43" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="44">
@@ -5312,16 +5324,16 @@
         <v>27</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C44" s="4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D44" s="4" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E44" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F44" s="4" t="s">
         <v>3</v>
@@ -5339,10 +5351,10 @@
         <v>0</v>
       </c>
       <c r="K44" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="L44" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="45">
@@ -5350,16 +5362,16 @@
         <v>28</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C45" s="4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D45" s="4" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E45" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F45" s="4" t="s">
         <v>3</v>
@@ -5377,10 +5389,10 @@
         <v>0</v>
       </c>
       <c r="K45" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="L45" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="46">
@@ -5388,16 +5400,16 @@
         <v>29</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C46" s="4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D46" s="4" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="E46" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F46" s="4" t="s">
         <v>3</v>
@@ -5415,10 +5427,10 @@
         <v>0</v>
       </c>
       <c r="K46" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="L46" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="47">
@@ -5426,16 +5438,16 @@
         <v>30</v>
       </c>
       <c r="B47" s="4" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C47" s="4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D47" s="4" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E47" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F47" s="4" t="s">
         <v>3</v>
@@ -5453,10 +5465,10 @@
         <v>0</v>
       </c>
       <c r="K47" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="L47" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="48">
@@ -5464,16 +5476,16 @@
         <v>31</v>
       </c>
       <c r="B48" s="4" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C48" s="4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D48" s="4" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E48" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F48" s="4" t="s">
         <v>3</v>
@@ -5491,10 +5503,10 @@
         <v>0</v>
       </c>
       <c r="K48" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="L48" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="49">
@@ -5502,16 +5514,16 @@
         <v>32</v>
       </c>
       <c r="B49" s="4" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C49" s="4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D49" s="4" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="E49" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F49" s="4" t="s">
         <v>3</v>
@@ -5529,10 +5541,10 @@
         <v>0</v>
       </c>
       <c r="K49" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="L49" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="50">
@@ -5540,16 +5552,16 @@
         <v>33</v>
       </c>
       <c r="B50" s="4" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C50" s="4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D50" s="4" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="E50" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F50" s="4" t="s">
         <v>3</v>
@@ -5567,10 +5579,10 @@
         <v>0</v>
       </c>
       <c r="K50" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="L50" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="51">
@@ -5578,16 +5590,16 @@
         <v>34</v>
       </c>
       <c r="B51" s="4" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C51" s="4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D51" s="4" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="E51" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F51" s="4" t="s">
         <v>3</v>
@@ -5605,10 +5617,10 @@
         <v>0</v>
       </c>
       <c r="K51" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="L51" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="52">
@@ -5616,16 +5628,16 @@
         <v>35</v>
       </c>
       <c r="B52" s="4" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C52" s="4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D52" s="4" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="E52" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F52" s="4" t="s">
         <v>3</v>
@@ -5643,10 +5655,10 @@
         <v>0</v>
       </c>
       <c r="K52" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="L52" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="53">
@@ -5654,16 +5666,16 @@
         <v>36</v>
       </c>
       <c r="B53" s="4" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C53" s="4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D53" s="4" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="E53" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F53" s="4" t="s">
         <v>3</v>
@@ -5681,10 +5693,10 @@
         <v>0</v>
       </c>
       <c r="K53" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="L53" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="54">
@@ -5692,16 +5704,16 @@
         <v>37</v>
       </c>
       <c r="B54" s="4" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C54" s="4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D54" s="4" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="E54" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F54" s="4" t="s">
         <v>3</v>
@@ -5719,10 +5731,10 @@
         <v>0</v>
       </c>
       <c r="K54" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="L54" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="55">
@@ -5730,16 +5742,16 @@
         <v>38</v>
       </c>
       <c r="B55" s="4" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C55" s="4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D55" s="4" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="E55" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F55" s="4" t="s">
         <v>3</v>
@@ -5757,10 +5769,10 @@
         <v>0</v>
       </c>
       <c r="K55" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="L55" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="56">
@@ -5768,16 +5780,16 @@
         <v>39</v>
       </c>
       <c r="B56" s="4" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C56" s="4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D56" s="4" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E56" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F56" s="4" t="s">
         <v>3</v>
@@ -5795,10 +5807,10 @@
         <v>0</v>
       </c>
       <c r="K56" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="L56" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="57">
@@ -5806,16 +5818,16 @@
         <v>40</v>
       </c>
       <c r="B57" s="4" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C57" s="4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D57" s="4" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E57" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F57" s="4" t="s">
         <v>3</v>
@@ -5833,10 +5845,10 @@
         <v>0</v>
       </c>
       <c r="K57" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="L57" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="58">
@@ -5844,16 +5856,16 @@
         <v>41</v>
       </c>
       <c r="B58" s="4" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C58" s="4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D58" s="4" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="E58" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F58" s="4" t="s">
         <v>3</v>
@@ -5871,10 +5883,10 @@
         <v>0</v>
       </c>
       <c r="K58" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="L58" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="59">
@@ -5882,16 +5894,16 @@
         <v>42</v>
       </c>
       <c r="B59" s="4" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C59" s="4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D59" s="4" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E59" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F59" s="4" t="s">
         <v>3</v>
@@ -5909,10 +5921,10 @@
         <v>0</v>
       </c>
       <c r="K59" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="L59" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="60">
@@ -5920,16 +5932,16 @@
         <v>43</v>
       </c>
       <c r="B60" s="4" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C60" s="4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D60" s="4" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="E60" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F60" s="4" t="s">
         <v>3</v>
@@ -5947,10 +5959,10 @@
         <v>0</v>
       </c>
       <c r="K60" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="L60" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="61">
@@ -5958,16 +5970,16 @@
         <v>44</v>
       </c>
       <c r="B61" s="4" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C61" s="4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D61" s="4" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E61" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F61" s="4" t="s">
         <v>3</v>
@@ -5985,10 +5997,10 @@
         <v>0</v>
       </c>
       <c r="K61" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="L61" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="62">
@@ -5996,16 +6008,16 @@
         <v>45</v>
       </c>
       <c r="B62" s="4" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C62" s="4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D62" s="4" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E62" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F62" s="4" t="s">
         <v>3</v>
@@ -6023,10 +6035,10 @@
         <v>0</v>
       </c>
       <c r="K62" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="L62" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="63">
@@ -6034,16 +6046,16 @@
         <v>46</v>
       </c>
       <c r="B63" s="4" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C63" s="4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D63" s="4" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="E63" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F63" s="4" t="s">
         <v>3</v>
@@ -6061,10 +6073,10 @@
         <v>0</v>
       </c>
       <c r="K63" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="L63" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="64">
@@ -6072,16 +6084,16 @@
         <v>47</v>
       </c>
       <c r="B64" s="4" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C64" s="4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D64" s="4" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E64" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F64" s="4" t="s">
         <v>3</v>
@@ -6099,10 +6111,10 @@
         <v>0</v>
       </c>
       <c r="K64" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="L64" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="65">
@@ -6110,16 +6122,16 @@
         <v>48</v>
       </c>
       <c r="B65" s="4" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C65" s="4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D65" s="4" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="E65" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F65" s="4" t="s">
         <v>3</v>
@@ -6137,10 +6149,10 @@
         <v>0</v>
       </c>
       <c r="K65" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="L65" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="66">
@@ -6148,16 +6160,16 @@
         <v>49</v>
       </c>
       <c r="B66" s="4" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C66" s="4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D66" s="4" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="E66" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F66" s="4" t="s">
         <v>3</v>
@@ -6175,10 +6187,10 @@
         <v>0</v>
       </c>
       <c r="K66" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="L66" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="67">
@@ -6186,16 +6198,16 @@
         <v>50</v>
       </c>
       <c r="B67" s="4" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C67" s="4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D67" s="4" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E67" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F67" s="4" t="s">
         <v>3</v>
@@ -6213,10 +6225,10 @@
         <v>0</v>
       </c>
       <c r="K67" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="L67" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="68">
@@ -6224,16 +6236,16 @@
         <v>51</v>
       </c>
       <c r="B68" s="4" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C68" s="4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D68" s="4" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E68" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F68" s="4" t="s">
         <v>3</v>
@@ -6251,10 +6263,10 @@
         <v>0</v>
       </c>
       <c r="K68" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="L68" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="69">
@@ -6262,16 +6274,16 @@
         <v>52</v>
       </c>
       <c r="B69" s="4" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C69" s="4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D69" s="4" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="E69" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F69" s="4" t="s">
         <v>3</v>
@@ -6289,10 +6301,10 @@
         <v>0</v>
       </c>
       <c r="K69" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="L69" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="70">
@@ -6300,16 +6312,16 @@
         <v>53</v>
       </c>
       <c r="B70" s="4" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C70" s="4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D70" s="4" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="E70" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F70" s="4" t="s">
         <v>3</v>
@@ -6327,10 +6339,10 @@
         <v>0</v>
       </c>
       <c r="K70" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="L70" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="71">
@@ -6338,16 +6350,16 @@
         <v>54</v>
       </c>
       <c r="B71" s="4" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C71" s="4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D71" s="4" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="E71" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F71" s="4" t="s">
         <v>3</v>
@@ -6365,10 +6377,10 @@
         <v>0</v>
       </c>
       <c r="K71" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="L71" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="72">
@@ -6376,16 +6388,16 @@
         <v>55</v>
       </c>
       <c r="B72" s="4" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C72" s="4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D72" s="4" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E72" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F72" s="4" t="s">
         <v>3</v>
@@ -6403,10 +6415,10 @@
         <v>0</v>
       </c>
       <c r="K72" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="L72" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="73">
@@ -6414,16 +6426,16 @@
         <v>56</v>
       </c>
       <c r="B73" s="4" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C73" s="4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D73" s="4" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E73" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F73" s="4" t="s">
         <v>3</v>
@@ -6441,10 +6453,10 @@
         <v>0</v>
       </c>
       <c r="K73" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="L73" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="74">
@@ -6452,16 +6464,16 @@
         <v>57</v>
       </c>
       <c r="B74" s="4" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C74" s="4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D74" s="4" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="E74" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F74" s="4" t="s">
         <v>3</v>
@@ -6479,10 +6491,10 @@
         <v>0</v>
       </c>
       <c r="K74" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="L74" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="75">
@@ -6490,16 +6502,16 @@
         <v>58</v>
       </c>
       <c r="B75" s="4" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C75" s="4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D75" s="4" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="E75" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F75" s="4" t="s">
         <v>3</v>
@@ -6517,10 +6529,10 @@
         <v>0</v>
       </c>
       <c r="K75" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="L75" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="76">
@@ -6528,16 +6540,16 @@
         <v>59</v>
       </c>
       <c r="B76" s="4" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C76" s="4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D76" s="4" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="E76" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F76" s="4" t="s">
         <v>3</v>
@@ -6555,10 +6567,10 @@
         <v>0</v>
       </c>
       <c r="K76" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="L76" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="77">
@@ -6566,16 +6578,16 @@
         <v>60</v>
       </c>
       <c r="B77" s="4" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C77" s="4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D77" s="4" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="E77" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F77" s="4" t="s">
         <v>3</v>
@@ -6593,10 +6605,10 @@
         <v>0</v>
       </c>
       <c r="K77" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="L77" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="78">
@@ -6604,16 +6616,16 @@
         <v>61</v>
       </c>
       <c r="B78" s="4" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C78" s="4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D78" s="4" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="E78" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F78" s="4" t="s">
         <v>3</v>
@@ -6631,10 +6643,10 @@
         <v>0</v>
       </c>
       <c r="K78" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="L78" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="79">
@@ -6642,16 +6654,16 @@
         <v>62</v>
       </c>
       <c r="B79" s="4" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C79" s="4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D79" s="4" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="E79" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F79" s="4" t="s">
         <v>3</v>
@@ -6669,10 +6681,10 @@
         <v>0</v>
       </c>
       <c r="K79" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="L79" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="80">
@@ -6680,16 +6692,16 @@
         <v>63</v>
       </c>
       <c r="B80" s="4" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C80" s="4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D80" s="4" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E80" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F80" s="4" t="s">
         <v>3</v>
@@ -6707,10 +6719,10 @@
         <v>0</v>
       </c>
       <c r="K80" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="L80" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="81">
@@ -6718,16 +6730,16 @@
         <v>64</v>
       </c>
       <c r="B81" s="4" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C81" s="4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D81" s="4" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="E81" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F81" s="4" t="s">
         <v>3</v>
@@ -6745,10 +6757,10 @@
         <v>0</v>
       </c>
       <c r="K81" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="L81" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="82">
@@ -6756,16 +6768,16 @@
         <v>65</v>
       </c>
       <c r="B82" s="4" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C82" s="4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D82" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="E82" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F82" s="4" t="s">
         <v>3</v>
@@ -6783,10 +6795,10 @@
         <v>0</v>
       </c>
       <c r="K82" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="L82" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="83">
@@ -6794,16 +6806,16 @@
         <v>66</v>
       </c>
       <c r="B83" s="4" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C83" s="4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D83" s="4" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="E83" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F83" s="4" t="s">
         <v>3</v>
@@ -6821,10 +6833,10 @@
         <v>0</v>
       </c>
       <c r="K83" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="L83" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="84">
@@ -6832,16 +6844,16 @@
         <v>67</v>
       </c>
       <c r="B84" s="4" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C84" s="4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D84" s="4" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="E84" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F84" s="4" t="s">
         <v>3</v>
@@ -6859,10 +6871,10 @@
         <v>0</v>
       </c>
       <c r="K84" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="L84" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="85">
@@ -6870,16 +6882,16 @@
         <v>68</v>
       </c>
       <c r="B85" s="4" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C85" s="4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D85" s="4" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E85" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F85" s="4" t="s">
         <v>3</v>
@@ -6897,10 +6909,10 @@
         <v>0</v>
       </c>
       <c r="K85" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="L85" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="86">
@@ -6908,16 +6920,16 @@
         <v>69</v>
       </c>
       <c r="B86" s="4" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C86" s="4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D86" s="4" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="E86" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F86" s="4" t="s">
         <v>3</v>
@@ -6935,10 +6947,10 @@
         <v>0</v>
       </c>
       <c r="K86" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="L86" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="87">
@@ -6946,16 +6958,16 @@
         <v>70</v>
       </c>
       <c r="B87" s="4" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C87" s="4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D87" s="4" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="E87" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F87" s="4" t="s">
         <v>3</v>
@@ -6973,10 +6985,10 @@
         <v>0</v>
       </c>
       <c r="K87" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="L87" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="88">
@@ -6984,16 +6996,16 @@
         <v>71</v>
       </c>
       <c r="B88" s="4" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C88" s="4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D88" s="4" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="E88" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F88" s="4" t="s">
         <v>3</v>
@@ -7011,10 +7023,10 @@
         <v>0</v>
       </c>
       <c r="K88" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="L88" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="89">
@@ -7022,16 +7034,16 @@
         <v>72</v>
       </c>
       <c r="B89" s="4" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C89" s="4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D89" s="4" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="E89" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F89" s="4" t="s">
         <v>3</v>
@@ -7049,10 +7061,10 @@
         <v>0</v>
       </c>
       <c r="K89" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="L89" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="90">
@@ -7060,16 +7072,16 @@
         <v>73</v>
       </c>
       <c r="B90" s="4" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C90" s="4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D90" s="4" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="E90" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F90" s="4" t="s">
         <v>3</v>
@@ -7087,10 +7099,10 @@
         <v>0</v>
       </c>
       <c r="K90" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="L90" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="91">
@@ -7098,16 +7110,16 @@
         <v>74</v>
       </c>
       <c r="B91" s="4" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C91" s="4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D91" s="4" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="E91" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F91" s="4" t="s">
         <v>3</v>
@@ -7125,10 +7137,10 @@
         <v>0</v>
       </c>
       <c r="K91" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="L91" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="92">
@@ -7136,16 +7148,16 @@
         <v>75</v>
       </c>
       <c r="B92" s="4" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C92" s="4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D92" s="4" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="E92" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F92" s="4" t="s">
         <v>3</v>
@@ -7163,10 +7175,10 @@
         <v>0</v>
       </c>
       <c r="K92" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="L92" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="93">
@@ -7174,16 +7186,16 @@
         <v>76</v>
       </c>
       <c r="B93" s="4" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C93" s="4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D93" s="4" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="E93" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F93" s="4" t="s">
         <v>3</v>
@@ -7201,10 +7213,10 @@
         <v>0</v>
       </c>
       <c r="K93" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="L93" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="94">
@@ -7212,16 +7224,16 @@
         <v>77</v>
       </c>
       <c r="B94" s="4" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C94" s="4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D94" s="4" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="E94" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F94" s="4" t="s">
         <v>3</v>
@@ -7239,10 +7251,10 @@
         <v>0</v>
       </c>
       <c r="K94" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="L94" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="95">
@@ -7250,16 +7262,16 @@
         <v>78</v>
       </c>
       <c r="B95" s="4" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C95" s="4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D95" s="4" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E95" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F95" s="4" t="s">
         <v>3</v>
@@ -7277,10 +7289,10 @@
         <v>0</v>
       </c>
       <c r="K95" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="L95" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="96">
@@ -7288,16 +7300,16 @@
         <v>79</v>
       </c>
       <c r="B96" s="4" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="C96" s="4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D96" s="4" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="E96" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F96" s="4" t="s">
         <v>3</v>
@@ -7315,10 +7327,10 @@
         <v>0</v>
       </c>
       <c r="K96" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="L96" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="97">
@@ -7326,16 +7338,16 @@
         <v>80</v>
       </c>
       <c r="B97" s="4" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="C97" s="4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D97" s="4" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E97" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F97" s="4" t="s">
         <v>3</v>
@@ -7353,10 +7365,10 @@
         <v>0</v>
       </c>
       <c r="K97" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="L97" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="98">
@@ -7364,16 +7376,16 @@
         <v>81</v>
       </c>
       <c r="B98" s="4" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="C98" s="4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D98" s="4" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E98" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F98" s="4" t="s">
         <v>3</v>
@@ -7391,10 +7403,10 @@
         <v>0</v>
       </c>
       <c r="K98" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="L98" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="99">
@@ -7402,16 +7414,16 @@
         <v>82</v>
       </c>
       <c r="B99" s="4" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="C99" s="4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D99" s="4" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="E99" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F99" s="4" t="s">
         <v>3</v>
@@ -7429,10 +7441,10 @@
         <v>0</v>
       </c>
       <c r="K99" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="L99" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="100">
@@ -7440,16 +7452,16 @@
         <v>83</v>
       </c>
       <c r="B100" s="4" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C100" s="4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D100" s="4" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="E100" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F100" s="4" t="s">
         <v>3</v>
@@ -7467,10 +7479,10 @@
         <v>0</v>
       </c>
       <c r="K100" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="L100" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="101">
@@ -7478,16 +7490,16 @@
         <v>84</v>
       </c>
       <c r="B101" s="4" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C101" s="4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D101" s="4" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="E101" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F101" s="4" t="s">
         <v>3</v>
@@ -7505,10 +7517,10 @@
         <v>0</v>
       </c>
       <c r="K101" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="L101" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="102">
@@ -7516,16 +7528,16 @@
         <v>85</v>
       </c>
       <c r="B102" s="4" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="C102" s="4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D102" s="4" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="E102" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F102" s="4" t="s">
         <v>3</v>
@@ -7543,10 +7555,10 @@
         <v>0</v>
       </c>
       <c r="K102" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="L102" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="103">
@@ -7554,16 +7566,16 @@
         <v>86</v>
       </c>
       <c r="B103" s="4" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="C103" s="4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D103" s="4" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="E103" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F103" s="4" t="s">
         <v>3</v>
@@ -7581,10 +7593,10 @@
         <v>0</v>
       </c>
       <c r="K103" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="L103" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="104">
@@ -7592,16 +7604,16 @@
         <v>87</v>
       </c>
       <c r="B104" s="4" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C104" s="4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D104" s="4" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="E104" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F104" s="4" t="s">
         <v>3</v>
@@ -7619,10 +7631,10 @@
         <v>0</v>
       </c>
       <c r="K104" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="L104" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="105">
@@ -7630,16 +7642,16 @@
         <v>88</v>
       </c>
       <c r="B105" s="4" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="C105" s="4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D105" s="4" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="E105" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F105" s="4" t="s">
         <v>3</v>
@@ -7657,10 +7669,10 @@
         <v>0</v>
       </c>
       <c r="K105" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="L105" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="106">
@@ -7668,16 +7680,16 @@
         <v>89</v>
       </c>
       <c r="B106" s="4" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="C106" s="4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D106" s="4" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="E106" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F106" s="4" t="s">
         <v>3</v>
@@ -7695,10 +7707,10 @@
         <v>0</v>
       </c>
       <c r="K106" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="L106" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="107">
@@ -7706,16 +7718,16 @@
         <v>90</v>
       </c>
       <c r="B107" s="4" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C107" s="4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D107" s="4" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="E107" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F107" s="4" t="s">
         <v>3</v>
@@ -7733,10 +7745,10 @@
         <v>0</v>
       </c>
       <c r="K107" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="L107" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="108">
@@ -7744,16 +7756,16 @@
         <v>91</v>
       </c>
       <c r="B108" s="4" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C108" s="4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D108" s="4" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="E108" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F108" s="4" t="s">
         <v>3</v>
@@ -7771,10 +7783,10 @@
         <v>0</v>
       </c>
       <c r="K108" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="L108" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="109">
@@ -7782,16 +7794,16 @@
         <v>92</v>
       </c>
       <c r="B109" s="4" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="C109" s="4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D109" s="4" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="E109" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F109" s="4" t="s">
         <v>3</v>
@@ -7809,10 +7821,10 @@
         <v>0</v>
       </c>
       <c r="K109" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="L109" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="110">
@@ -7820,16 +7832,16 @@
         <v>93</v>
       </c>
       <c r="B110" s="4" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C110" s="4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D110" s="4" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="E110" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F110" s="4" t="s">
         <v>3</v>
@@ -7847,10 +7859,10 @@
         <v>0</v>
       </c>
       <c r="K110" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="L110" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="111">
@@ -7858,16 +7870,16 @@
         <v>94</v>
       </c>
       <c r="B111" s="4" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="C111" s="4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D111" s="4" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="E111" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F111" s="4" t="s">
         <v>3</v>
@@ -7885,10 +7897,10 @@
         <v>0</v>
       </c>
       <c r="K111" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="L111" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="112">
@@ -7896,16 +7908,16 @@
         <v>95</v>
       </c>
       <c r="B112" s="4" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="C112" s="4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D112" s="4" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="E112" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F112" s="4" t="s">
         <v>3</v>
@@ -7923,10 +7935,10 @@
         <v>0</v>
       </c>
       <c r="K112" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="L112" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="113">
@@ -7934,16 +7946,16 @@
         <v>96</v>
       </c>
       <c r="B113" s="4" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="C113" s="4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D113" s="4" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="E113" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F113" s="4" t="s">
         <v>3</v>
@@ -7961,10 +7973,10 @@
         <v>0</v>
       </c>
       <c r="K113" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="L113" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="114">
@@ -7972,16 +7984,16 @@
         <v>97</v>
       </c>
       <c r="B114" s="4" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="C114" s="4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D114" s="4" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="E114" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F114" s="4" t="s">
         <v>3</v>
@@ -7999,10 +8011,10 @@
         <v>0</v>
       </c>
       <c r="K114" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="L114" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="115">
@@ -8010,16 +8022,16 @@
         <v>98</v>
       </c>
       <c r="B115" s="4" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="C115" s="4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D115" s="4" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="E115" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F115" s="4" t="s">
         <v>3</v>
@@ -8037,10 +8049,10 @@
         <v>0</v>
       </c>
       <c r="K115" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="L115" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="116">
@@ -8048,16 +8060,16 @@
         <v>99</v>
       </c>
       <c r="B116" s="4" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="C116" s="4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D116" s="4" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="E116" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F116" s="4" t="s">
         <v>3</v>
@@ -8075,10 +8087,10 @@
         <v>0</v>
       </c>
       <c r="K116" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="L116" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="117">
@@ -8086,16 +8098,16 @@
         <v>100</v>
       </c>
       <c r="B117" s="4" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="C117" s="4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D117" s="4" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="E117" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F117" s="4" t="s">
         <v>3</v>
@@ -8113,10 +8125,10 @@
         <v>0</v>
       </c>
       <c r="K117" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="L117" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="118">
@@ -8124,16 +8136,16 @@
         <v>101</v>
       </c>
       <c r="B118" s="4" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="C118" s="4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D118" s="4" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="E118" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F118" s="4" t="s">
         <v>3</v>
@@ -8151,10 +8163,10 @@
         <v>0</v>
       </c>
       <c r="K118" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="L118" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="119">
@@ -8162,16 +8174,16 @@
         <v>102</v>
       </c>
       <c r="B119" s="4" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="C119" s="4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D119" s="4" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="E119" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F119" s="4" t="s">
         <v>3</v>
@@ -8189,10 +8201,10 @@
         <v>0</v>
       </c>
       <c r="K119" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="L119" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="120">
@@ -8200,16 +8212,16 @@
         <v>103</v>
       </c>
       <c r="B120" s="4" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="C120" s="4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D120" s="4" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E120" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F120" s="4" t="s">
         <v>3</v>
@@ -8227,10 +8239,10 @@
         <v>0</v>
       </c>
       <c r="K120" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="L120" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="121">
@@ -8238,16 +8250,16 @@
         <v>104</v>
       </c>
       <c r="B121" s="4" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C121" s="4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D121" s="4" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E121" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F121" s="4" t="s">
         <v>3</v>
@@ -8265,10 +8277,10 @@
         <v>0</v>
       </c>
       <c r="K121" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="L121" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="122">
@@ -8276,16 +8288,16 @@
         <v>105</v>
       </c>
       <c r="B122" s="4" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="C122" s="4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D122" s="4" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E122" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F122" s="4" t="s">
         <v>3</v>
@@ -8303,10 +8315,10 @@
         <v>0</v>
       </c>
       <c r="K122" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="L122" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="123">
@@ -8314,16 +8326,16 @@
         <v>106</v>
       </c>
       <c r="B123" s="4" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="C123" s="4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D123" s="4" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E123" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F123" s="4" t="s">
         <v>3</v>
@@ -8341,10 +8353,10 @@
         <v>0</v>
       </c>
       <c r="K123" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="L123" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="124">
@@ -8352,16 +8364,16 @@
         <v>107</v>
       </c>
       <c r="B124" s="4" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="C124" s="4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D124" s="4" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E124" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F124" s="4" t="s">
         <v>3</v>
@@ -8379,10 +8391,10 @@
         <v>0</v>
       </c>
       <c r="K124" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="L124" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="125">
@@ -8390,16 +8402,16 @@
         <v>108</v>
       </c>
       <c r="B125" s="4" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="C125" s="4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D125" s="4" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="E125" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F125" s="4" t="s">
         <v>3</v>
@@ -8417,10 +8429,10 @@
         <v>0</v>
       </c>
       <c r="K125" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="L125" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="126">
@@ -8428,16 +8440,16 @@
         <v>109</v>
       </c>
       <c r="B126" s="4" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="C126" s="4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D126" s="4" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="E126" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F126" s="4" t="s">
         <v>3</v>
@@ -8455,10 +8467,10 @@
         <v>0</v>
       </c>
       <c r="K126" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="L126" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="127">
@@ -8466,16 +8478,16 @@
         <v>110</v>
       </c>
       <c r="B127" s="4" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="C127" s="4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D127" s="4" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="E127" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F127" s="4" t="s">
         <v>3</v>
@@ -8493,10 +8505,10 @@
         <v>0</v>
       </c>
       <c r="K127" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="L127" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="128">
@@ -8504,16 +8516,16 @@
         <v>111</v>
       </c>
       <c r="B128" s="4" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="C128" s="4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D128" s="4" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="E128" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F128" s="4" t="s">
         <v>3</v>
@@ -8531,10 +8543,10 @@
         <v>0</v>
       </c>
       <c r="K128" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="L128" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="129">
@@ -8542,16 +8554,16 @@
         <v>112</v>
       </c>
       <c r="B129" s="4" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="C129" s="4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D129" s="4" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="E129" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F129" s="4" t="s">
         <v>3</v>
@@ -8569,10 +8581,10 @@
         <v>0</v>
       </c>
       <c r="K129" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="L129" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="130">
@@ -8580,16 +8592,16 @@
         <v>113</v>
       </c>
       <c r="B130" s="4" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="C130" s="4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D130" s="4" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="E130" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F130" s="4" t="s">
         <v>3</v>
@@ -8607,10 +8619,10 @@
         <v>0</v>
       </c>
       <c r="K130" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="L130" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="131">
@@ -8618,16 +8630,16 @@
         <v>114</v>
       </c>
       <c r="B131" s="4" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="C131" s="4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D131" s="4" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="E131" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F131" s="4" t="s">
         <v>3</v>
@@ -8645,10 +8657,10 @@
         <v>0</v>
       </c>
       <c r="K131" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="L131" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="132">
@@ -8656,16 +8668,16 @@
         <v>115</v>
       </c>
       <c r="B132" s="4" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="C132" s="4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D132" s="4" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="E132" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F132" s="4" t="s">
         <v>3</v>
@@ -8683,10 +8695,10 @@
         <v>0</v>
       </c>
       <c r="K132" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="L132" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="133">
@@ -8694,16 +8706,16 @@
         <v>116</v>
       </c>
       <c r="B133" s="4" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="C133" s="4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D133" s="4" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="E133" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F133" s="4" t="s">
         <v>3</v>
@@ -8721,10 +8733,10 @@
         <v>0</v>
       </c>
       <c r="K133" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="L133" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="134">
@@ -8732,16 +8744,16 @@
         <v>117</v>
       </c>
       <c r="B134" s="4" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="C134" s="4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D134" s="4" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="E134" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F134" s="4" t="s">
         <v>3</v>
@@ -8759,10 +8771,10 @@
         <v>0</v>
       </c>
       <c r="K134" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="L134" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="135">
@@ -8770,16 +8782,16 @@
         <v>118</v>
       </c>
       <c r="B135" s="4" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="C135" s="4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D135" s="4" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="E135" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F135" s="4" t="s">
         <v>3</v>
@@ -8797,10 +8809,10 @@
         <v>0</v>
       </c>
       <c r="K135" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="L135" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="136">
@@ -8808,16 +8820,16 @@
         <v>119</v>
       </c>
       <c r="B136" s="4" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="C136" s="4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D136" s="4" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="E136" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F136" s="4" t="s">
         <v>3</v>
@@ -8835,10 +8847,10 @@
         <v>0</v>
       </c>
       <c r="K136" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="L136" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="137">
@@ -8846,16 +8858,16 @@
         <v>120</v>
       </c>
       <c r="B137" s="4" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="C137" s="4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D137" s="4" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="E137" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F137" s="4" t="s">
         <v>3</v>
@@ -8873,10 +8885,10 @@
         <v>0</v>
       </c>
       <c r="K137" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="L137" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="138">
@@ -8884,16 +8896,16 @@
         <v>121</v>
       </c>
       <c r="B138" s="3" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="C138" s="3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D138" s="3" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="E138" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F138" s="3" t="s">
         <v>3</v>
@@ -8905,16 +8917,16 @@
         <v>11</v>
       </c>
       <c r="I138" s="3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="J138" s="3">
         <v>9223372036</v>
       </c>
       <c r="K138" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="L138" s="3" t="s">
-        <v>289</v>
+        <v>26</v>
       </c>
     </row>
     <row r="139">
@@ -8925,13 +8937,13 @@
         <v>290</v>
       </c>
       <c r="C139" s="3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D139" s="3" t="s">
         <v>291</v>
       </c>
       <c r="E139" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F139" s="3" t="s">
         <v>3</v>
@@ -8943,16 +8955,16 @@
         <v>11</v>
       </c>
       <c r="I139" s="3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="J139" s="3">
         <v>9223372036</v>
       </c>
       <c r="K139" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="L139" s="3" t="s">
-        <v>289</v>
+        <v>26</v>
       </c>
     </row>
     <row r="140">
@@ -8963,13 +8975,13 @@
         <v>292</v>
       </c>
       <c r="C140" s="3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D140" s="3" t="s">
         <v>293</v>
       </c>
       <c r="E140" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F140" s="3" t="s">
         <v>3</v>
@@ -8981,16 +8993,16 @@
         <v>11</v>
       </c>
       <c r="I140" s="3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="J140" s="3">
         <v>9223372036</v>
       </c>
       <c r="K140" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="L140" s="3" t="s">
-        <v>289</v>
+        <v>26</v>
       </c>
     </row>
     <row r="141">
@@ -9001,13 +9013,13 @@
         <v>294</v>
       </c>
       <c r="C141" s="3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D141" s="3" t="s">
         <v>295</v>
       </c>
       <c r="E141" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F141" s="3" t="s">
         <v>3</v>
@@ -9019,16 +9031,16 @@
         <v>11</v>
       </c>
       <c r="I141" s="3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="J141" s="3">
         <v>9223372036</v>
       </c>
       <c r="K141" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="L141" s="3" t="s">
-        <v>289</v>
+        <v>26</v>
       </c>
     </row>
     <row r="142">
@@ -9039,13 +9051,13 @@
         <v>296</v>
       </c>
       <c r="C142" s="3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D142" s="3" t="s">
         <v>297</v>
       </c>
       <c r="E142" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F142" s="3" t="s">
         <v>3</v>
@@ -9057,16 +9069,16 @@
         <v>11</v>
       </c>
       <c r="I142" s="3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="J142" s="3">
         <v>9223372036</v>
       </c>
       <c r="K142" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="L142" s="3" t="s">
-        <v>289</v>
+        <v>26</v>
       </c>
     </row>
     <row r="143">
@@ -9077,13 +9089,13 @@
         <v>298</v>
       </c>
       <c r="C143" s="4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D143" s="4" t="s">
         <v>299</v>
       </c>
       <c r="E143" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F143" s="4" t="s">
         <v>3</v>
@@ -9101,10 +9113,10 @@
         <v>0</v>
       </c>
       <c r="K143" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="L143" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="144">
@@ -9115,13 +9127,13 @@
         <v>300</v>
       </c>
       <c r="C144" s="4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D144" s="4" t="s">
         <v>301</v>
       </c>
       <c r="E144" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F144" s="4" t="s">
         <v>3</v>
@@ -9139,10 +9151,10 @@
         <v>0</v>
       </c>
       <c r="K144" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="L144" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="145">
@@ -9153,13 +9165,13 @@
         <v>302</v>
       </c>
       <c r="C145" s="4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D145" s="4" t="s">
         <v>303</v>
       </c>
       <c r="E145" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F145" s="4" t="s">
         <v>3</v>
@@ -9177,10 +9189,10 @@
         <v>0</v>
       </c>
       <c r="K145" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="L145" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="146">
@@ -9191,13 +9203,13 @@
         <v>304</v>
       </c>
       <c r="C146" s="4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D146" s="4" t="s">
         <v>305</v>
       </c>
       <c r="E146" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F146" s="4" t="s">
         <v>3</v>
@@ -9215,10 +9227,10 @@
         <v>0</v>
       </c>
       <c r="K146" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="L146" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="147">
@@ -9229,13 +9241,13 @@
         <v>306</v>
       </c>
       <c r="C147" s="4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D147" s="4" t="s">
         <v>307</v>
       </c>
       <c r="E147" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F147" s="4" t="s">
         <v>3</v>
@@ -9253,10 +9265,10 @@
         <v>0</v>
       </c>
       <c r="K147" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="L147" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="148">
@@ -9267,13 +9279,13 @@
         <v>308</v>
       </c>
       <c r="C148" s="4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D148" s="4" t="s">
         <v>309</v>
       </c>
       <c r="E148" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F148" s="4" t="s">
         <v>3</v>
@@ -9291,10 +9303,10 @@
         <v>0</v>
       </c>
       <c r="K148" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="L148" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="149">
@@ -9305,13 +9317,13 @@
         <v>310</v>
       </c>
       <c r="C149" s="4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D149" s="4" t="s">
         <v>311</v>
       </c>
       <c r="E149" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F149" s="4" t="s">
         <v>3</v>
@@ -9329,10 +9341,10 @@
         <v>0</v>
       </c>
       <c r="K149" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="L149" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="150">
@@ -9343,13 +9355,13 @@
         <v>312</v>
       </c>
       <c r="C150" s="4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D150" s="4" t="s">
         <v>313</v>
       </c>
       <c r="E150" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F150" s="4" t="s">
         <v>3</v>
@@ -9367,10 +9379,10 @@
         <v>0</v>
       </c>
       <c r="K150" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="L150" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="151">
@@ -9381,13 +9393,13 @@
         <v>314</v>
       </c>
       <c r="C151" s="4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D151" s="4" t="s">
         <v>315</v>
       </c>
       <c r="E151" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F151" s="4" t="s">
         <v>3</v>
@@ -9405,10 +9417,10 @@
         <v>0</v>
       </c>
       <c r="K151" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="L151" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="152">
@@ -9419,13 +9431,13 @@
         <v>316</v>
       </c>
       <c r="C152" s="4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D152" s="4" t="s">
         <v>317</v>
       </c>
       <c r="E152" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F152" s="4" t="s">
         <v>3</v>
@@ -9443,10 +9455,10 @@
         <v>0</v>
       </c>
       <c r="K152" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="L152" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="153">
@@ -9457,13 +9469,13 @@
         <v>318</v>
       </c>
       <c r="C153" s="4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D153" s="4" t="s">
         <v>319</v>
       </c>
       <c r="E153" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F153" s="4" t="s">
         <v>3</v>
@@ -9481,10 +9493,10 @@
         <v>0</v>
       </c>
       <c r="K153" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="L153" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="154">
@@ -9495,13 +9507,13 @@
         <v>320</v>
       </c>
       <c r="C154" s="4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D154" s="4" t="s">
         <v>321</v>
       </c>
       <c r="E154" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F154" s="4" t="s">
         <v>3</v>
@@ -9519,10 +9531,10 @@
         <v>0</v>
       </c>
       <c r="K154" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="L154" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="155">
@@ -9533,13 +9545,13 @@
         <v>322</v>
       </c>
       <c r="C155" s="4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D155" s="4" t="s">
         <v>323</v>
       </c>
       <c r="E155" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F155" s="4" t="s">
         <v>3</v>
@@ -9557,10 +9569,10 @@
         <v>0</v>
       </c>
       <c r="K155" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="L155" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="156">
@@ -9571,13 +9583,13 @@
         <v>324</v>
       </c>
       <c r="C156" s="4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D156" s="4" t="s">
         <v>325</v>
       </c>
       <c r="E156" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F156" s="4" t="s">
         <v>3</v>
@@ -9595,10 +9607,10 @@
         <v>0</v>
       </c>
       <c r="K156" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="L156" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="157">
@@ -9609,13 +9621,13 @@
         <v>326</v>
       </c>
       <c r="C157" s="4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D157" s="4" t="s">
         <v>327</v>
       </c>
       <c r="E157" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F157" s="4" t="s">
         <v>3</v>
@@ -9633,10 +9645,10 @@
         <v>0</v>
       </c>
       <c r="K157" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="L157" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="158">
@@ -9647,13 +9659,13 @@
         <v>328</v>
       </c>
       <c r="C158" s="4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D158" s="4" t="s">
         <v>329</v>
       </c>
       <c r="E158" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F158" s="4" t="s">
         <v>3</v>
@@ -9671,10 +9683,10 @@
         <v>0</v>
       </c>
       <c r="K158" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="L158" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="159">
@@ -9685,13 +9697,13 @@
         <v>330</v>
       </c>
       <c r="C159" s="4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D159" s="4" t="s">
         <v>331</v>
       </c>
       <c r="E159" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F159" s="4" t="s">
         <v>3</v>
@@ -9709,10 +9721,10 @@
         <v>0</v>
       </c>
       <c r="K159" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="L159" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="160">
@@ -9723,13 +9735,13 @@
         <v>332</v>
       </c>
       <c r="C160" s="4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D160" s="4" t="s">
         <v>333</v>
       </c>
       <c r="E160" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F160" s="4" t="s">
         <v>3</v>
@@ -9747,10 +9759,10 @@
         <v>0</v>
       </c>
       <c r="K160" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="L160" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="161">
@@ -9761,13 +9773,13 @@
         <v>334</v>
       </c>
       <c r="C161" s="4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D161" s="4" t="s">
         <v>335</v>
       </c>
       <c r="E161" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F161" s="4" t="s">
         <v>3</v>
@@ -9785,10 +9797,10 @@
         <v>0</v>
       </c>
       <c r="K161" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="L161" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="162">
@@ -9799,13 +9811,13 @@
         <v>336</v>
       </c>
       <c r="C162" s="4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D162" s="4" t="s">
         <v>337</v>
       </c>
       <c r="E162" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F162" s="4" t="s">
         <v>3</v>
@@ -9823,10 +9835,10 @@
         <v>0</v>
       </c>
       <c r="K162" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="L162" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="163">
@@ -9837,13 +9849,13 @@
         <v>338</v>
       </c>
       <c r="C163" s="4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D163" s="4" t="s">
         <v>339</v>
       </c>
       <c r="E163" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F163" s="4" t="s">
         <v>3</v>
@@ -9861,10 +9873,10 @@
         <v>0</v>
       </c>
       <c r="K163" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="L163" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="164">
@@ -9875,13 +9887,13 @@
         <v>340</v>
       </c>
       <c r="C164" s="4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D164" s="4" t="s">
         <v>341</v>
       </c>
       <c r="E164" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F164" s="4" t="s">
         <v>3</v>
@@ -9899,10 +9911,10 @@
         <v>0</v>
       </c>
       <c r="K164" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="L164" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="165">
@@ -9913,13 +9925,13 @@
         <v>342</v>
       </c>
       <c r="C165" s="4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D165" s="4" t="s">
         <v>343</v>
       </c>
       <c r="E165" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F165" s="4" t="s">
         <v>3</v>
@@ -9937,10 +9949,10 @@
         <v>0</v>
       </c>
       <c r="K165" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="L165" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="166">
@@ -9951,13 +9963,13 @@
         <v>344</v>
       </c>
       <c r="C166" s="4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D166" s="4" t="s">
         <v>345</v>
       </c>
       <c r="E166" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F166" s="4" t="s">
         <v>3</v>
@@ -9975,10 +9987,10 @@
         <v>0</v>
       </c>
       <c r="K166" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="L166" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="167">
@@ -9989,13 +10001,13 @@
         <v>346</v>
       </c>
       <c r="C167" s="4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D167" s="4" t="s">
         <v>347</v>
       </c>
       <c r="E167" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F167" s="4" t="s">
         <v>3</v>
@@ -10013,10 +10025,10 @@
         <v>0</v>
       </c>
       <c r="K167" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="L167" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="168">
@@ -10027,13 +10039,13 @@
         <v>348</v>
       </c>
       <c r="C168" s="4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D168" s="4" t="s">
         <v>349</v>
       </c>
       <c r="E168" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F168" s="4" t="s">
         <v>3</v>
@@ -10051,10 +10063,10 @@
         <v>0</v>
       </c>
       <c r="K168" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="L168" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="169">
@@ -10065,13 +10077,13 @@
         <v>350</v>
       </c>
       <c r="C169" s="4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D169" s="4" t="s">
         <v>351</v>
       </c>
       <c r="E169" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F169" s="4" t="s">
         <v>3</v>
@@ -10089,10 +10101,10 @@
         <v>0</v>
       </c>
       <c r="K169" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="L169" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="170">
@@ -10103,13 +10115,13 @@
         <v>352</v>
       </c>
       <c r="C170" s="4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D170" s="4" t="s">
         <v>353</v>
       </c>
       <c r="E170" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F170" s="4" t="s">
         <v>3</v>
@@ -10127,10 +10139,10 @@
         <v>0</v>
       </c>
       <c r="K170" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="L170" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="171">
@@ -10141,13 +10153,13 @@
         <v>354</v>
       </c>
       <c r="C171" s="4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D171" s="4" t="s">
         <v>355</v>
       </c>
       <c r="E171" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F171" s="4" t="s">
         <v>3</v>
@@ -10165,10 +10177,10 @@
         <v>0</v>
       </c>
       <c r="K171" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="L171" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="172">
@@ -10179,13 +10191,13 @@
         <v>356</v>
       </c>
       <c r="C172" s="4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D172" s="4" t="s">
         <v>357</v>
       </c>
       <c r="E172" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F172" s="4" t="s">
         <v>3</v>
@@ -10203,10 +10215,10 @@
         <v>0</v>
       </c>
       <c r="K172" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="L172" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="173">
@@ -10217,13 +10229,13 @@
         <v>358</v>
       </c>
       <c r="C173" s="4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D173" s="4" t="s">
         <v>359</v>
       </c>
       <c r="E173" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F173" s="4" t="s">
         <v>3</v>
@@ -10241,10 +10253,10 @@
         <v>0</v>
       </c>
       <c r="K173" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="L173" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="174">
@@ -10255,13 +10267,13 @@
         <v>360</v>
       </c>
       <c r="C174" s="4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D174" s="4" t="s">
         <v>361</v>
       </c>
       <c r="E174" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F174" s="4" t="s">
         <v>3</v>
@@ -10279,10 +10291,10 @@
         <v>0</v>
       </c>
       <c r="K174" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="L174" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="175">
@@ -10293,13 +10305,13 @@
         <v>362</v>
       </c>
       <c r="C175" s="4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D175" s="4" t="s">
         <v>363</v>
       </c>
       <c r="E175" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F175" s="4" t="s">
         <v>3</v>
@@ -10317,10 +10329,10 @@
         <v>0</v>
       </c>
       <c r="K175" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="L175" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="176">
@@ -10331,13 +10343,13 @@
         <v>364</v>
       </c>
       <c r="C176" s="4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D176" s="4" t="s">
         <v>365</v>
       </c>
       <c r="E176" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F176" s="4" t="s">
         <v>3</v>
@@ -10355,10 +10367,10 @@
         <v>0</v>
       </c>
       <c r="K176" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="L176" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="177">
@@ -10369,13 +10381,13 @@
         <v>366</v>
       </c>
       <c r="C177" s="4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D177" s="4" t="s">
         <v>367</v>
       </c>
       <c r="E177" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F177" s="4" t="s">
         <v>3</v>
@@ -10393,10 +10405,10 @@
         <v>0</v>
       </c>
       <c r="K177" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="L177" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="178">
@@ -10407,13 +10419,13 @@
         <v>368</v>
       </c>
       <c r="C178" s="4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D178" s="4" t="s">
         <v>369</v>
       </c>
       <c r="E178" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F178" s="4" t="s">
         <v>3</v>
@@ -10431,10 +10443,10 @@
         <v>0</v>
       </c>
       <c r="K178" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="L178" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="179">
@@ -10445,13 +10457,13 @@
         <v>370</v>
       </c>
       <c r="C179" s="4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D179" s="4" t="s">
         <v>371</v>
       </c>
       <c r="E179" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F179" s="4" t="s">
         <v>3</v>
@@ -10469,10 +10481,10 @@
         <v>0</v>
       </c>
       <c r="K179" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="L179" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="180">
@@ -10483,13 +10495,13 @@
         <v>372</v>
       </c>
       <c r="C180" s="4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D180" s="4" t="s">
         <v>373</v>
       </c>
       <c r="E180" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F180" s="4" t="s">
         <v>3</v>
@@ -10507,10 +10519,10 @@
         <v>0</v>
       </c>
       <c r="K180" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="L180" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="181">
@@ -10521,13 +10533,13 @@
         <v>374</v>
       </c>
       <c r="C181" s="4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D181" s="4" t="s">
         <v>375</v>
       </c>
       <c r="E181" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F181" s="4" t="s">
         <v>3</v>
@@ -10545,10 +10557,10 @@
         <v>0</v>
       </c>
       <c r="K181" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="L181" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="182">
@@ -10559,13 +10571,13 @@
         <v>376</v>
       </c>
       <c r="C182" s="4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D182" s="4" t="s">
         <v>377</v>
       </c>
       <c r="E182" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F182" s="4" t="s">
         <v>3</v>
@@ -10583,10 +10595,10 @@
         <v>0</v>
       </c>
       <c r="K182" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="L182" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="183">
@@ -10597,13 +10609,13 @@
         <v>378</v>
       </c>
       <c r="C183" s="4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D183" s="4" t="s">
         <v>379</v>
       </c>
       <c r="E183" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F183" s="4" t="s">
         <v>3</v>
@@ -10621,10 +10633,10 @@
         <v>0</v>
       </c>
       <c r="K183" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="L183" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="184">
@@ -10635,13 +10647,13 @@
         <v>380</v>
       </c>
       <c r="C184" s="4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D184" s="4" t="s">
         <v>381</v>
       </c>
       <c r="E184" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F184" s="4" t="s">
         <v>3</v>
@@ -10659,10 +10671,10 @@
         <v>0</v>
       </c>
       <c r="K184" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="L184" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="185">
@@ -10673,13 +10685,13 @@
         <v>382</v>
       </c>
       <c r="C185" s="4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D185" s="4" t="s">
         <v>383</v>
       </c>
       <c r="E185" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F185" s="4" t="s">
         <v>3</v>
@@ -10697,10 +10709,10 @@
         <v>0</v>
       </c>
       <c r="K185" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="L185" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="186">
@@ -10711,13 +10723,13 @@
         <v>384</v>
       </c>
       <c r="C186" s="4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D186" s="4" t="s">
         <v>385</v>
       </c>
       <c r="E186" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F186" s="4" t="s">
         <v>3</v>
@@ -10735,10 +10747,10 @@
         <v>0</v>
       </c>
       <c r="K186" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="L186" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="187">
@@ -10749,13 +10761,13 @@
         <v>386</v>
       </c>
       <c r="C187" s="4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D187" s="4" t="s">
         <v>387</v>
       </c>
       <c r="E187" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F187" s="4" t="s">
         <v>3</v>
@@ -10773,10 +10785,10 @@
         <v>0</v>
       </c>
       <c r="K187" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="L187" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="188">
@@ -10787,13 +10799,13 @@
         <v>388</v>
       </c>
       <c r="C188" s="4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D188" s="4" t="s">
         <v>389</v>
       </c>
       <c r="E188" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F188" s="4" t="s">
         <v>3</v>
@@ -10811,10 +10823,10 @@
         <v>0</v>
       </c>
       <c r="K188" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="L188" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="189">
@@ -10825,13 +10837,13 @@
         <v>390</v>
       </c>
       <c r="C189" s="4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D189" s="4" t="s">
         <v>391</v>
       </c>
       <c r="E189" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F189" s="4" t="s">
         <v>3</v>
@@ -10849,10 +10861,10 @@
         <v>0</v>
       </c>
       <c r="K189" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="L189" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="190">
@@ -10863,13 +10875,13 @@
         <v>392</v>
       </c>
       <c r="C190" s="4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D190" s="4" t="s">
         <v>393</v>
       </c>
       <c r="E190" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F190" s="4" t="s">
         <v>3</v>
@@ -10887,10 +10899,10 @@
         <v>0</v>
       </c>
       <c r="K190" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="L190" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="191">
@@ -10907,7 +10919,7 @@
         <v>396</v>
       </c>
       <c r="E191" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F191" s="4" t="s">
         <v>3</v>
@@ -10925,10 +10937,10 @@
         <v>0</v>
       </c>
       <c r="K191" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="L191" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="192">
@@ -10945,7 +10957,7 @@
         <v>398</v>
       </c>
       <c r="E192" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F192" s="4" t="s">
         <v>3</v>
@@ -10963,10 +10975,10 @@
         <v>0</v>
       </c>
       <c r="K192" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="L192" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="193">
@@ -10983,7 +10995,7 @@
         <v>400</v>
       </c>
       <c r="E193" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F193" s="4" t="s">
         <v>3</v>
@@ -11001,10 +11013,10 @@
         <v>0</v>
       </c>
       <c r="K193" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="L193" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="194">
@@ -11021,7 +11033,7 @@
         <v>402</v>
       </c>
       <c r="E194" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F194" s="4" t="s">
         <v>3</v>
@@ -11039,10 +11051,10 @@
         <v>0</v>
       </c>
       <c r="K194" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="L194" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="195">
@@ -11059,7 +11071,7 @@
         <v>404</v>
       </c>
       <c r="E195" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F195" s="4" t="s">
         <v>3</v>
@@ -11077,10 +11089,10 @@
         <v>0</v>
       </c>
       <c r="K195" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="L195" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="196">
@@ -11097,7 +11109,7 @@
         <v>406</v>
       </c>
       <c r="E196" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F196" s="4" t="s">
         <v>3</v>
@@ -11115,10 +11127,10 @@
         <v>0</v>
       </c>
       <c r="K196" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="L196" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="197">
@@ -11135,7 +11147,7 @@
         <v>408</v>
       </c>
       <c r="E197" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F197" s="4" t="s">
         <v>3</v>
@@ -11153,10 +11165,10 @@
         <v>0</v>
       </c>
       <c r="K197" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="L197" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="198">
@@ -11173,7 +11185,7 @@
         <v>410</v>
       </c>
       <c r="E198" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F198" s="4" t="s">
         <v>3</v>
@@ -11191,10 +11203,10 @@
         <v>0</v>
       </c>
       <c r="K198" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="L198" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="199">
@@ -11211,7 +11223,7 @@
         <v>412</v>
       </c>
       <c r="E199" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F199" s="4" t="s">
         <v>3</v>
@@ -11229,10 +11241,10 @@
         <v>0</v>
       </c>
       <c r="K199" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="L199" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="200">
@@ -11249,7 +11261,7 @@
         <v>414</v>
       </c>
       <c r="E200" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F200" s="4" t="s">
         <v>3</v>
@@ -11267,10 +11279,10 @@
         <v>0</v>
       </c>
       <c r="K200" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="L200" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="201">
@@ -11287,7 +11299,7 @@
         <v>416</v>
       </c>
       <c r="E201" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F201" s="4" t="s">
         <v>3</v>
@@ -11305,10 +11317,10 @@
         <v>0</v>
       </c>
       <c r="K201" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="L201" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="202">
@@ -11325,7 +11337,7 @@
         <v>418</v>
       </c>
       <c r="E202" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F202" s="4" t="s">
         <v>3</v>
@@ -11343,10 +11355,10 @@
         <v>0</v>
       </c>
       <c r="K202" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="L202" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="203">
@@ -11363,7 +11375,7 @@
         <v>420</v>
       </c>
       <c r="E203" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F203" s="4" t="s">
         <v>3</v>
@@ -11381,10 +11393,10 @@
         <v>0</v>
       </c>
       <c r="K203" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="L203" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="204">
@@ -11401,7 +11413,7 @@
         <v>422</v>
       </c>
       <c r="E204" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F204" s="4" t="s">
         <v>3</v>
@@ -11419,10 +11431,10 @@
         <v>0</v>
       </c>
       <c r="K204" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="L204" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="205">
@@ -11439,7 +11451,7 @@
         <v>424</v>
       </c>
       <c r="E205" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F205" s="4" t="s">
         <v>3</v>
@@ -11457,10 +11469,10 @@
         <v>0</v>
       </c>
       <c r="K205" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="L205" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="206">
@@ -11477,7 +11489,7 @@
         <v>426</v>
       </c>
       <c r="E206" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F206" s="4" t="s">
         <v>3</v>
@@ -11495,10 +11507,10 @@
         <v>0</v>
       </c>
       <c r="K206" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="L206" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="207">
@@ -11515,7 +11527,7 @@
         <v>428</v>
       </c>
       <c r="E207" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F207" s="4" t="s">
         <v>3</v>
@@ -11533,10 +11545,10 @@
         <v>0</v>
       </c>
       <c r="K207" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="L207" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="208">
@@ -11553,7 +11565,7 @@
         <v>430</v>
       </c>
       <c r="E208" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F208" s="4" t="s">
         <v>3</v>
@@ -11571,10 +11583,10 @@
         <v>0</v>
       </c>
       <c r="K208" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="L208" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="209">
@@ -11591,7 +11603,7 @@
         <v>432</v>
       </c>
       <c r="E209" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F209" s="4" t="s">
         <v>3</v>
@@ -11609,10 +11621,10 @@
         <v>0</v>
       </c>
       <c r="K209" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="L209" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="210">
@@ -11629,7 +11641,7 @@
         <v>434</v>
       </c>
       <c r="E210" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F210" s="4" t="s">
         <v>3</v>
@@ -11647,10 +11659,10 @@
         <v>0</v>
       </c>
       <c r="K210" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="L210" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="211">
@@ -11667,7 +11679,7 @@
         <v>436</v>
       </c>
       <c r="E211" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F211" s="4" t="s">
         <v>3</v>
@@ -11685,10 +11697,10 @@
         <v>0</v>
       </c>
       <c r="K211" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="L211" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="212">
@@ -11705,7 +11717,7 @@
         <v>438</v>
       </c>
       <c r="E212" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F212" s="4" t="s">
         <v>3</v>
@@ -11723,10 +11735,10 @@
         <v>0</v>
       </c>
       <c r="K212" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="L212" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="213">
@@ -11743,7 +11755,7 @@
         <v>440</v>
       </c>
       <c r="E213" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F213" s="4" t="s">
         <v>3</v>
@@ -11761,10 +11773,10 @@
         <v>0</v>
       </c>
       <c r="K213" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="L213" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="214">
@@ -11781,7 +11793,7 @@
         <v>442</v>
       </c>
       <c r="E214" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F214" s="4" t="s">
         <v>3</v>
@@ -11799,10 +11811,10 @@
         <v>0</v>
       </c>
       <c r="K214" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="L214" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="215">
@@ -11819,7 +11831,7 @@
         <v>444</v>
       </c>
       <c r="E215" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F215" s="4" t="s">
         <v>3</v>
@@ -11837,10 +11849,10 @@
         <v>0</v>
       </c>
       <c r="K215" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="L215" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="216">
@@ -11857,7 +11869,7 @@
         <v>446</v>
       </c>
       <c r="E216" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F216" s="4" t="s">
         <v>3</v>
@@ -11875,10 +11887,10 @@
         <v>0</v>
       </c>
       <c r="K216" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="L216" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="217">
@@ -11895,7 +11907,7 @@
         <v>448</v>
       </c>
       <c r="E217" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F217" s="4" t="s">
         <v>3</v>
@@ -11913,10 +11925,10 @@
         <v>0</v>
       </c>
       <c r="K217" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="L217" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="218">
@@ -11933,7 +11945,7 @@
         <v>450</v>
       </c>
       <c r="E218" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F218" s="4" t="s">
         <v>3</v>
@@ -11951,10 +11963,10 @@
         <v>0</v>
       </c>
       <c r="K218" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="L218" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="219">
@@ -11971,7 +11983,7 @@
         <v>452</v>
       </c>
       <c r="E219" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F219" s="4" t="s">
         <v>3</v>
@@ -11989,10 +12001,10 @@
         <v>0</v>
       </c>
       <c r="K219" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="L219" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="220">
@@ -12009,7 +12021,7 @@
         <v>454</v>
       </c>
       <c r="E220" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F220" s="4" t="s">
         <v>3</v>
@@ -12027,10 +12039,10 @@
         <v>0</v>
       </c>
       <c r="K220" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="L220" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="221">
@@ -12047,7 +12059,7 @@
         <v>456</v>
       </c>
       <c r="E221" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F221" s="4" t="s">
         <v>3</v>
@@ -12065,10 +12077,10 @@
         <v>0</v>
       </c>
       <c r="K221" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="L221" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="222">
@@ -12085,7 +12097,7 @@
         <v>458</v>
       </c>
       <c r="E222" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F222" s="4" t="s">
         <v>3</v>
@@ -12103,10 +12115,10 @@
         <v>0</v>
       </c>
       <c r="K222" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="L222" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="223">
@@ -12123,7 +12135,7 @@
         <v>460</v>
       </c>
       <c r="E223" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F223" s="4" t="s">
         <v>3</v>
@@ -12141,10 +12153,10 @@
         <v>0</v>
       </c>
       <c r="K223" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="L223" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="224">
@@ -12161,7 +12173,7 @@
         <v>462</v>
       </c>
       <c r="E224" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F224" s="4" t="s">
         <v>3</v>
@@ -12179,10 +12191,10 @@
         <v>0</v>
       </c>
       <c r="K224" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="L224" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="225">
@@ -12199,7 +12211,7 @@
         <v>464</v>
       </c>
       <c r="E225" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F225" s="4" t="s">
         <v>3</v>
@@ -12217,10 +12229,10 @@
         <v>0</v>
       </c>
       <c r="K225" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="L225" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="226">
@@ -12237,7 +12249,7 @@
         <v>466</v>
       </c>
       <c r="E226" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F226" s="4" t="s">
         <v>3</v>
@@ -12255,10 +12267,10 @@
         <v>0</v>
       </c>
       <c r="K226" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="L226" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="227">
@@ -12275,7 +12287,7 @@
         <v>468</v>
       </c>
       <c r="E227" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F227" s="3" t="s">
         <v>3</v>
@@ -12287,13 +12299,13 @@
         <v>11</v>
       </c>
       <c r="I227" s="3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="J227" s="3">
         <v>9223372036</v>
       </c>
       <c r="K227" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="L227" s="3" t="s">
         <v>469</v>
@@ -12313,7 +12325,7 @@
         <v>471</v>
       </c>
       <c r="E228" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F228" s="3" t="s">
         <v>3</v>
@@ -12325,16 +12337,16 @@
         <v>11</v>
       </c>
       <c r="I228" s="3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="J228" s="3">
         <v>9223372036</v>
       </c>
       <c r="K228" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="L228" s="3" t="s">
-        <v>289</v>
+        <v>26</v>
       </c>
     </row>
     <row r="229">
@@ -12351,7 +12363,7 @@
         <v>473</v>
       </c>
       <c r="E229" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F229" s="3" t="s">
         <v>3</v>
@@ -12363,16 +12375,16 @@
         <v>11</v>
       </c>
       <c r="I229" s="3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="J229" s="3">
         <v>9223372036</v>
       </c>
       <c r="K229" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="L229" s="3" t="s">
-        <v>289</v>
+        <v>26</v>
       </c>
     </row>
     <row r="230">
@@ -12389,7 +12401,7 @@
         <v>475</v>
       </c>
       <c r="E230" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F230" s="3" t="s">
         <v>3</v>
@@ -12401,16 +12413,16 @@
         <v>11</v>
       </c>
       <c r="I230" s="3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="J230" s="3">
         <v>9223372036</v>
       </c>
       <c r="K230" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="L230" s="3" t="s">
-        <v>289</v>
+        <v>26</v>
       </c>
     </row>
     <row r="231">
@@ -12427,7 +12439,7 @@
         <v>477</v>
       </c>
       <c r="E231" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F231" s="4" t="s">
         <v>3</v>
@@ -12445,10 +12457,10 @@
         <v>0</v>
       </c>
       <c r="K231" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="L231" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="232">
@@ -12465,7 +12477,7 @@
         <v>479</v>
       </c>
       <c r="E232" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F232" s="4" t="s">
         <v>3</v>
@@ -12483,24 +12495,100 @@
         <v>0</v>
       </c>
       <c r="K232" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="L232" s="4" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" s="3">
+        <v>216</v>
+      </c>
+      <c r="B233" s="3" t="s">
+        <v>480</v>
+      </c>
+      <c r="C233" s="3" t="s">
+        <v>395</v>
+      </c>
+      <c r="D233" s="3" t="s">
+        <v>481</v>
+      </c>
+      <c r="E233" s="3" t="s">
         <v>43</v>
       </c>
+      <c r="F233" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G233" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="H233" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="I233" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="J233" s="3">
+        <v>9223372036</v>
+      </c>
+      <c r="K233" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="L233" s="3" t="s">
+        <v>26</v>
+      </c>
     </row>
     <row r="234">
-      <c r="A234" t="s">
-        <v>480</v>
-      </c>
-      <c r="B234" t="s">
-        <v>481</v>
-      </c>
-      <c r="D234" t="s">
+      <c r="A234" s="3">
+        <v>217</v>
+      </c>
+      <c r="B234" s="3" t="s">
         <v>482</v>
       </c>
-      <c r="E234">
-        <v>215</v>
+      <c r="C234" s="3" t="s">
+        <v>395</v>
+      </c>
+      <c r="D234" s="3" t="s">
+        <v>483</v>
+      </c>
+      <c r="E234" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="F234" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G234" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="H234" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="I234" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="J234" s="3">
+        <v>9223372036</v>
+      </c>
+      <c r="K234" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="L234" s="3" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="s">
+        <v>484</v>
+      </c>
+      <c r="B236" t="s">
+        <v>485</v>
+      </c>
+      <c r="D236" t="s">
+        <v>486</v>
+      </c>
+      <c r="E236">
+        <v>217</v>
       </c>
     </row>
   </sheetData>

--- a/report-2026-06-04.xlsx
+++ b/report-2026-06-04.xlsx
@@ -16,12 +16,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="487" uniqueCount="487">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="489" uniqueCount="489">
   <si>
     <t>PunMonitor Leader Election — Current State</t>
   </si>
   <si>
-    <t>Generated 2026-06-04T19:06:30+05:30</t>
+    <t>Generated 2026-06-04T19:18:43+05:30</t>
   </si>
   <si>
     <t>Election method</t>
@@ -57,46 +57,43 @@
     <t>Mode / Role</t>
   </si>
   <si>
-    <t>SERVER (primary)</t>
+    <t>SERVER+LEADER (this instance is the GitHub primary)</t>
   </si>
   <si>
     <t>Self is leader</t>
   </si>
   <si>
+    <t>YES — this instance is the primary server</t>
+  </si>
+  <si>
+    <t>Current leader</t>
+  </si>
+  <si>
+    <t>Leader last update</t>
+  </si>
+  <si>
+    <t>2026-06-04T19:16:42+05:30 (2m0s ago)</t>
+  </si>
+  <si>
+    <t>Leader stale?</t>
+  </si>
+  <si>
     <t>No</t>
   </si>
   <si>
-    <t>Current leader</t>
-  </si>
-  <si>
-    <t>(no leader recorded)</t>
-  </si>
-  <si>
-    <t>Leader last update</t>
-  </si>
-  <si>
-    <t>(never)</t>
-  </si>
-  <si>
-    <t>Leader stale?</t>
-  </si>
-  <si>
     <t>Last check</t>
   </si>
   <si>
-    <t>2026-06-04T19:06:16+05:30 (14s ago)</t>
-  </si>
-  <si>
     <t>Check count</t>
   </si>
   <si>
-    <t>53</t>
+    <t>1</t>
   </si>
   <si>
     <t>Last error</t>
   </si>
   <si>
-    <t>Get "https://api.github.com/repos/puniteswra-spec/PU/contents/primary_server.json": dial tcp: lookup api.github.com: no such host</t>
+    <t>(none)</t>
   </si>
   <si>
     <t>Election History (row-wise — latest first)</t>
@@ -889,6 +886,9 @@
     <t>04:02:38.142</t>
   </si>
   <si>
+    <t>Get "https://api.github.com/repos/puniteswra-spec/PU/contents/primary_server.json": dial tcp: lookup api.github.com: no such host</t>
+  </si>
+  <si>
     <t>2026-06-03T04:05:08.1306949+05:30</t>
   </si>
   <si>
@@ -1471,10 +1471,16 @@
     <t>19:06:16.686</t>
   </si>
   <si>
+    <t>2026-06-04T19:16:42.9746537+05:30</t>
+  </si>
+  <si>
+    <t>19:16:42.974</t>
+  </si>
+  <si>
     <t>Generated</t>
   </si>
   <si>
-    <t>2026-06-04T19:06:31+05:30</t>
+    <t>2026-06-04T19:18:43+05:30</t>
   </si>
   <si>
     <t>Total events</t>
@@ -2029,7 +2035,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>10.0.41</t>
+          <t>10.0.44</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -2069,27 +2075,27 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>15h 58m 12s</t>
+          <t>0h 2m 19s</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>2026-06-04 03:08:18</t>
+          <t>2026-06-04 19:16:23</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>Jun 2 07:00 PM</t>
+          <t>Jun 4 07:08 PM</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2026-06-04 03:08:18</t>
+          <t>2026-06-04 19:16:23</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>10h 46m 30s</t>
+          <t>10h 47m 0s</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -2099,7 +2105,7 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>19:06:30</t>
+          <t>19:18:43</t>
         </is>
       </c>
     </row>
@@ -2116,7 +2122,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>192.168.0.164</t>
+          <t>192.168.0.128</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -2136,7 +2142,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>10.0.41</t>
+          <t>10.0.44</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -2156,17 +2162,17 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2000.0</t>
+          <t>108.0</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>300453.5</t>
+          <t>111812.1</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>17110</t>
+          <t>2104</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -2176,7 +2182,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>4036</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -2186,17 +2192,17 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>Jun 2 07:00 PM</t>
+          <t>Jun 4 07:08 PM</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-06-04 03:08:18</t>
+          <t>2026-06-04 19:16:23</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>10h 44m 45s</t>
+          <t>10h 47m 0s</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -2206,7 +2212,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>19:06:30</t>
+          <t>19:18:43</t>
         </is>
       </c>
     </row>
@@ -2320,12 +2326,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>[error]</t>
+          <t>[renewed]</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-06-04T19:06:16.6865666+05:30</t>
+          <t>2026-06-04T19:16:42.9746537+05:30</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -2335,12 +2341,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>19:06:16.686</t>
+          <t>19:16:42.974</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>renewed</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -2360,20 +2366,20 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
+          <t>PuneetU-EB6LMJD-cf4a9ce5</t>
+        </is>
+      </c>
+      <c r="J5">
+        <v>0</v>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>renewed</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
           <t/>
-        </is>
-      </c>
-      <c r="J5">
-        <v>9223372036</v>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>error</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>Get "https://api.github.com/repos/puniteswra-spec/PU/contents/primary_server.json": dial tcp: lookup api.github.com: no such host</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -4234,23 +4240,23 @@
         <v>16</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="B10" s="2" t="s">
         <v>18</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>19</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="B11" s="2" t="s">
         <v>20</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>15</v>
       </c>
     </row>
     <row r="12">
@@ -4258,28 +4264,28 @@
         <v>21</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B13" s="2" t="s">
         <v>23</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>24</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="B14" s="2" t="s">
         <v>25</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>26</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B16" s="5"/>
       <c r="C16" s="5"/>
@@ -4295,40 +4301,40 @@
     </row>
     <row r="17">
       <c r="A17" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B17" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="B17" s="1" t="s">
+      <c r="C17" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="C17" s="1" t="s">
+      <c r="D17" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D17" s="1" t="s">
+      <c r="E17" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="E17" s="1" t="s">
+      <c r="F17" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="F17" s="1" t="s">
+      <c r="G17" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="G17" s="1" t="s">
+      <c r="H17" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="H17" s="1" t="s">
+      <c r="I17" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="I17" s="1" t="s">
+      <c r="J17" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="J17" s="1" t="s">
+      <c r="K17" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="K17" s="1" t="s">
+      <c r="L17" s="1" t="s">
         <v>38</v>
-      </c>
-      <c r="L17" s="1" t="s">
-        <v>39</v>
       </c>
     </row>
     <row r="18">
@@ -4336,17 +4342,17 @@
         <v>1</v>
       </c>
       <c r="B18" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="C18" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="C18" s="3" t="s">
+      <c r="D18" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="D18" s="3" t="s">
+      <c r="E18" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="E18" s="3" t="s">
-        <v>43</v>
-      </c>
       <c r="F18" s="3" t="s">
         <v>3</v>
       </c>
@@ -4357,16 +4363,16 @@
         <v>11</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="J18" s="3">
         <v>9223372036</v>
       </c>
       <c r="K18" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="L18" s="3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="19">
@@ -4374,16 +4380,16 @@
         <v>2</v>
       </c>
       <c r="B19" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="D19" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="C19" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="D19" s="3" t="s">
-        <v>47</v>
-      </c>
       <c r="E19" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F19" s="3" t="s">
         <v>3</v>
@@ -4395,16 +4401,16 @@
         <v>11</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="J19" s="3">
         <v>9223372036</v>
       </c>
       <c r="K19" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="L19" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="20">
@@ -4412,16 +4418,16 @@
         <v>3</v>
       </c>
       <c r="B20" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="D20" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="C20" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="D20" s="3" t="s">
-        <v>50</v>
-      </c>
       <c r="E20" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F20" s="3" t="s">
         <v>3</v>
@@ -4433,16 +4439,16 @@
         <v>11</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="J20" s="3">
         <v>9223372036</v>
       </c>
       <c r="K20" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="L20" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="21">
@@ -4450,16 +4456,16 @@
         <v>4</v>
       </c>
       <c r="B21" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="D21" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="C21" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="D21" s="3" t="s">
-        <v>52</v>
-      </c>
       <c r="E21" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F21" s="3" t="s">
         <v>3</v>
@@ -4471,16 +4477,16 @@
         <v>11</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="J21" s="3">
         <v>9223372036</v>
       </c>
       <c r="K21" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="L21" s="3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="22">
@@ -4488,16 +4494,16 @@
         <v>5</v>
       </c>
       <c r="B22" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="D22" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="C22" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="D22" s="3" t="s">
-        <v>54</v>
-      </c>
       <c r="E22" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F22" s="3" t="s">
         <v>3</v>
@@ -4509,16 +4515,16 @@
         <v>11</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="J22" s="3">
         <v>9223372036</v>
       </c>
       <c r="K22" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="L22" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="23">
@@ -4526,16 +4532,16 @@
         <v>6</v>
       </c>
       <c r="B23" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="D23" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="C23" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="D23" s="3" t="s">
-        <v>56</v>
-      </c>
       <c r="E23" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F23" s="3" t="s">
         <v>3</v>
@@ -4547,16 +4553,16 @@
         <v>11</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="J23" s="3">
         <v>9223372036</v>
       </c>
       <c r="K23" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="L23" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="24">
@@ -4564,16 +4570,16 @@
         <v>7</v>
       </c>
       <c r="B24" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="D24" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="C24" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="D24" s="3" t="s">
-        <v>58</v>
-      </c>
       <c r="E24" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F24" s="3" t="s">
         <v>3</v>
@@ -4585,16 +4591,16 @@
         <v>11</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="J24" s="3">
         <v>9223372036</v>
       </c>
       <c r="K24" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="L24" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="25">
@@ -4602,16 +4608,16 @@
         <v>8</v>
       </c>
       <c r="B25" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="D25" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="C25" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="D25" s="3" t="s">
-        <v>61</v>
-      </c>
       <c r="E25" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F25" s="3" t="s">
         <v>3</v>
@@ -4623,16 +4629,16 @@
         <v>11</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="J25" s="3">
         <v>9223372036</v>
       </c>
       <c r="K25" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="L25" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="26">
@@ -4640,16 +4646,16 @@
         <v>9</v>
       </c>
       <c r="B26" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="D26" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="C26" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="D26" s="3" t="s">
-        <v>63</v>
-      </c>
       <c r="E26" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F26" s="3" t="s">
         <v>3</v>
@@ -4661,16 +4667,16 @@
         <v>11</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="J26" s="3">
         <v>9223372036</v>
       </c>
       <c r="K26" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="L26" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="27">
@@ -4678,16 +4684,16 @@
         <v>10</v>
       </c>
       <c r="B27" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="D27" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="C27" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="D27" s="3" t="s">
-        <v>65</v>
-      </c>
       <c r="E27" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F27" s="3" t="s">
         <v>3</v>
@@ -4699,16 +4705,16 @@
         <v>11</v>
       </c>
       <c r="I27" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="J27" s="3">
         <v>9223372036</v>
       </c>
       <c r="K27" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="L27" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="28">
@@ -4716,16 +4722,16 @@
         <v>11</v>
       </c>
       <c r="B28" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="D28" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="C28" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="D28" s="3" t="s">
-        <v>67</v>
-      </c>
       <c r="E28" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F28" s="3" t="s">
         <v>3</v>
@@ -4737,16 +4743,16 @@
         <v>11</v>
       </c>
       <c r="I28" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="J28" s="3">
         <v>9223372036</v>
       </c>
       <c r="K28" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="L28" s="3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="29">
@@ -4754,16 +4760,16 @@
         <v>12</v>
       </c>
       <c r="B29" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="D29" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="C29" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="D29" s="3" t="s">
-        <v>69</v>
-      </c>
       <c r="E29" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F29" s="3" t="s">
         <v>3</v>
@@ -4775,16 +4781,16 @@
         <v>11</v>
       </c>
       <c r="I29" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="J29" s="3">
         <v>9223372036</v>
       </c>
       <c r="K29" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="L29" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="30">
@@ -4792,16 +4798,16 @@
         <v>13</v>
       </c>
       <c r="B30" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="C30" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="D30" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="C30" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="D30" s="3" t="s">
-        <v>71</v>
-      </c>
       <c r="E30" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F30" s="3" t="s">
         <v>3</v>
@@ -4813,16 +4819,16 @@
         <v>11</v>
       </c>
       <c r="I30" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="J30" s="3">
         <v>9223372036</v>
       </c>
       <c r="K30" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="L30" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="31">
@@ -4830,16 +4836,16 @@
         <v>14</v>
       </c>
       <c r="B31" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="C31" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="D31" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="C31" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="D31" s="3" t="s">
-        <v>73</v>
-      </c>
       <c r="E31" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F31" s="3" t="s">
         <v>3</v>
@@ -4851,16 +4857,16 @@
         <v>11</v>
       </c>
       <c r="I31" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="J31" s="3">
         <v>9223372036</v>
       </c>
       <c r="K31" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="L31" s="3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="32">
@@ -4868,16 +4874,16 @@
         <v>15</v>
       </c>
       <c r="B32" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="C32" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="D32" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="C32" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="D32" s="3" t="s">
-        <v>75</v>
-      </c>
       <c r="E32" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F32" s="3" t="s">
         <v>3</v>
@@ -4889,16 +4895,16 @@
         <v>11</v>
       </c>
       <c r="I32" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="J32" s="3">
         <v>9223372036</v>
       </c>
       <c r="K32" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="L32" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="33">
@@ -4906,16 +4912,16 @@
         <v>16</v>
       </c>
       <c r="B33" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="C33" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="D33" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="C33" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="D33" s="3" t="s">
-        <v>77</v>
-      </c>
       <c r="E33" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F33" s="3" t="s">
         <v>3</v>
@@ -4927,16 +4933,16 @@
         <v>11</v>
       </c>
       <c r="I33" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="J33" s="3">
         <v>9223372036</v>
       </c>
       <c r="K33" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="L33" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="34">
@@ -4944,16 +4950,16 @@
         <v>17</v>
       </c>
       <c r="B34" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="C34" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="D34" s="4" t="s">
         <v>78</v>
       </c>
-      <c r="C34" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="D34" s="4" t="s">
-        <v>79</v>
-      </c>
       <c r="E34" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F34" s="4" t="s">
         <v>3</v>
@@ -4971,10 +4977,10 @@
         <v>0</v>
       </c>
       <c r="K34" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="L34" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="35">
@@ -4982,16 +4988,16 @@
         <v>18</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C35" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="D35" s="4" t="s">
         <v>82</v>
       </c>
-      <c r="D35" s="4" t="s">
-        <v>83</v>
-      </c>
       <c r="E35" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F35" s="4" t="s">
         <v>3</v>
@@ -5009,10 +5015,10 @@
         <v>0</v>
       </c>
       <c r="K35" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="L35" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="36">
@@ -5020,16 +5026,16 @@
         <v>19</v>
       </c>
       <c r="B36" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="C36" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="D36" s="4" t="s">
         <v>84</v>
       </c>
-      <c r="C36" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="D36" s="4" t="s">
-        <v>85</v>
-      </c>
       <c r="E36" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F36" s="4" t="s">
         <v>3</v>
@@ -5047,10 +5053,10 @@
         <v>0</v>
       </c>
       <c r="K36" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="L36" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="37">
@@ -5058,16 +5064,16 @@
         <v>20</v>
       </c>
       <c r="B37" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="C37" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="D37" s="4" t="s">
         <v>86</v>
       </c>
-      <c r="C37" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="D37" s="4" t="s">
-        <v>87</v>
-      </c>
       <c r="E37" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F37" s="4" t="s">
         <v>3</v>
@@ -5085,10 +5091,10 @@
         <v>0</v>
       </c>
       <c r="K37" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="L37" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="38">
@@ -5096,16 +5102,16 @@
         <v>21</v>
       </c>
       <c r="B38" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="C38" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="D38" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="C38" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="D38" s="4" t="s">
-        <v>89</v>
-      </c>
       <c r="E38" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F38" s="4" t="s">
         <v>3</v>
@@ -5123,10 +5129,10 @@
         <v>0</v>
       </c>
       <c r="K38" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="L38" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="39">
@@ -5134,16 +5140,16 @@
         <v>22</v>
       </c>
       <c r="B39" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="C39" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="D39" s="4" t="s">
         <v>90</v>
       </c>
-      <c r="C39" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="D39" s="4" t="s">
-        <v>91</v>
-      </c>
       <c r="E39" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F39" s="4" t="s">
         <v>3</v>
@@ -5161,10 +5167,10 @@
         <v>0</v>
       </c>
       <c r="K39" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="L39" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="40">
@@ -5172,16 +5178,16 @@
         <v>23</v>
       </c>
       <c r="B40" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="C40" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="D40" s="4" t="s">
         <v>92</v>
       </c>
-      <c r="C40" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="D40" s="4" t="s">
-        <v>93</v>
-      </c>
       <c r="E40" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F40" s="4" t="s">
         <v>3</v>
@@ -5199,10 +5205,10 @@
         <v>0</v>
       </c>
       <c r="K40" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="L40" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="41">
@@ -5210,16 +5216,16 @@
         <v>24</v>
       </c>
       <c r="B41" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="C41" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="D41" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="C41" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="D41" s="4" t="s">
-        <v>95</v>
-      </c>
       <c r="E41" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F41" s="4" t="s">
         <v>3</v>
@@ -5237,10 +5243,10 @@
         <v>0</v>
       </c>
       <c r="K41" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="L41" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="42">
@@ -5248,16 +5254,16 @@
         <v>25</v>
       </c>
       <c r="B42" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="C42" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="D42" s="4" t="s">
         <v>96</v>
       </c>
-      <c r="C42" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="D42" s="4" t="s">
-        <v>97</v>
-      </c>
       <c r="E42" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F42" s="4" t="s">
         <v>3</v>
@@ -5275,10 +5281,10 @@
         <v>0</v>
       </c>
       <c r="K42" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="L42" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="43">
@@ -5286,16 +5292,16 @@
         <v>26</v>
       </c>
       <c r="B43" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="C43" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="D43" s="4" t="s">
         <v>98</v>
       </c>
-      <c r="C43" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="D43" s="4" t="s">
-        <v>99</v>
-      </c>
       <c r="E43" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F43" s="4" t="s">
         <v>3</v>
@@ -5313,10 +5319,10 @@
         <v>0</v>
       </c>
       <c r="K43" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="L43" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="44">
@@ -5324,16 +5330,16 @@
         <v>27</v>
       </c>
       <c r="B44" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="C44" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="D44" s="4" t="s">
         <v>100</v>
       </c>
-      <c r="C44" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="D44" s="4" t="s">
-        <v>101</v>
-      </c>
       <c r="E44" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F44" s="4" t="s">
         <v>3</v>
@@ -5351,10 +5357,10 @@
         <v>0</v>
       </c>
       <c r="K44" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="L44" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="45">
@@ -5362,16 +5368,16 @@
         <v>28</v>
       </c>
       <c r="B45" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="C45" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="D45" s="4" t="s">
         <v>102</v>
       </c>
-      <c r="C45" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="D45" s="4" t="s">
-        <v>103</v>
-      </c>
       <c r="E45" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F45" s="4" t="s">
         <v>3</v>
@@ -5389,10 +5395,10 @@
         <v>0</v>
       </c>
       <c r="K45" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="L45" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="46">
@@ -5400,16 +5406,16 @@
         <v>29</v>
       </c>
       <c r="B46" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="C46" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="D46" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="C46" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="D46" s="4" t="s">
-        <v>105</v>
-      </c>
       <c r="E46" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F46" s="4" t="s">
         <v>3</v>
@@ -5427,10 +5433,10 @@
         <v>0</v>
       </c>
       <c r="K46" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="L46" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="47">
@@ -5438,16 +5444,16 @@
         <v>30</v>
       </c>
       <c r="B47" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="C47" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="D47" s="4" t="s">
         <v>106</v>
       </c>
-      <c r="C47" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="D47" s="4" t="s">
-        <v>107</v>
-      </c>
       <c r="E47" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F47" s="4" t="s">
         <v>3</v>
@@ -5465,10 +5471,10 @@
         <v>0</v>
       </c>
       <c r="K47" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="L47" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="48">
@@ -5476,16 +5482,16 @@
         <v>31</v>
       </c>
       <c r="B48" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="C48" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="D48" s="4" t="s">
         <v>108</v>
       </c>
-      <c r="C48" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="D48" s="4" t="s">
-        <v>109</v>
-      </c>
       <c r="E48" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F48" s="4" t="s">
         <v>3</v>
@@ -5503,10 +5509,10 @@
         <v>0</v>
       </c>
       <c r="K48" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="L48" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="49">
@@ -5514,16 +5520,16 @@
         <v>32</v>
       </c>
       <c r="B49" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="C49" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="D49" s="4" t="s">
         <v>110</v>
       </c>
-      <c r="C49" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="D49" s="4" t="s">
-        <v>111</v>
-      </c>
       <c r="E49" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F49" s="4" t="s">
         <v>3</v>
@@ -5541,10 +5547,10 @@
         <v>0</v>
       </c>
       <c r="K49" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="L49" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="50">
@@ -5552,16 +5558,16 @@
         <v>33</v>
       </c>
       <c r="B50" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="C50" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="D50" s="4" t="s">
         <v>112</v>
       </c>
-      <c r="C50" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="D50" s="4" t="s">
-        <v>113</v>
-      </c>
       <c r="E50" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F50" s="4" t="s">
         <v>3</v>
@@ -5579,10 +5585,10 @@
         <v>0</v>
       </c>
       <c r="K50" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="L50" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="51">
@@ -5590,16 +5596,16 @@
         <v>34</v>
       </c>
       <c r="B51" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="C51" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="D51" s="4" t="s">
         <v>114</v>
       </c>
-      <c r="C51" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="D51" s="4" t="s">
-        <v>115</v>
-      </c>
       <c r="E51" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F51" s="4" t="s">
         <v>3</v>
@@ -5617,10 +5623,10 @@
         <v>0</v>
       </c>
       <c r="K51" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="L51" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="52">
@@ -5628,16 +5634,16 @@
         <v>35</v>
       </c>
       <c r="B52" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="C52" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="D52" s="4" t="s">
         <v>116</v>
       </c>
-      <c r="C52" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="D52" s="4" t="s">
-        <v>117</v>
-      </c>
       <c r="E52" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F52" s="4" t="s">
         <v>3</v>
@@ -5655,10 +5661,10 @@
         <v>0</v>
       </c>
       <c r="K52" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="L52" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="53">
@@ -5666,16 +5672,16 @@
         <v>36</v>
       </c>
       <c r="B53" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="C53" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="D53" s="4" t="s">
         <v>118</v>
       </c>
-      <c r="C53" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="D53" s="4" t="s">
-        <v>119</v>
-      </c>
       <c r="E53" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F53" s="4" t="s">
         <v>3</v>
@@ -5693,10 +5699,10 @@
         <v>0</v>
       </c>
       <c r="K53" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="L53" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="54">
@@ -5704,16 +5710,16 @@
         <v>37</v>
       </c>
       <c r="B54" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="C54" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="D54" s="4" t="s">
         <v>120</v>
       </c>
-      <c r="C54" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="D54" s="4" t="s">
-        <v>121</v>
-      </c>
       <c r="E54" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F54" s="4" t="s">
         <v>3</v>
@@ -5731,10 +5737,10 @@
         <v>0</v>
       </c>
       <c r="K54" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="L54" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="55">
@@ -5742,16 +5748,16 @@
         <v>38</v>
       </c>
       <c r="B55" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="C55" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="D55" s="4" t="s">
         <v>122</v>
       </c>
-      <c r="C55" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="D55" s="4" t="s">
-        <v>123</v>
-      </c>
       <c r="E55" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F55" s="4" t="s">
         <v>3</v>
@@ -5769,10 +5775,10 @@
         <v>0</v>
       </c>
       <c r="K55" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="L55" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="56">
@@ -5780,16 +5786,16 @@
         <v>39</v>
       </c>
       <c r="B56" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="C56" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="D56" s="4" t="s">
         <v>124</v>
       </c>
-      <c r="C56" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="D56" s="4" t="s">
-        <v>125</v>
-      </c>
       <c r="E56" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F56" s="4" t="s">
         <v>3</v>
@@ -5807,10 +5813,10 @@
         <v>0</v>
       </c>
       <c r="K56" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="L56" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="57">
@@ -5818,16 +5824,16 @@
         <v>40</v>
       </c>
       <c r="B57" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="C57" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="D57" s="4" t="s">
         <v>126</v>
       </c>
-      <c r="C57" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="D57" s="4" t="s">
-        <v>127</v>
-      </c>
       <c r="E57" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F57" s="4" t="s">
         <v>3</v>
@@ -5845,10 +5851,10 @@
         <v>0</v>
       </c>
       <c r="K57" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="L57" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="58">
@@ -5856,16 +5862,16 @@
         <v>41</v>
       </c>
       <c r="B58" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="C58" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="D58" s="4" t="s">
         <v>128</v>
       </c>
-      <c r="C58" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="D58" s="4" t="s">
-        <v>129</v>
-      </c>
       <c r="E58" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F58" s="4" t="s">
         <v>3</v>
@@ -5883,10 +5889,10 @@
         <v>0</v>
       </c>
       <c r="K58" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="L58" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="59">
@@ -5894,16 +5900,16 @@
         <v>42</v>
       </c>
       <c r="B59" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="C59" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="D59" s="4" t="s">
         <v>130</v>
       </c>
-      <c r="C59" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="D59" s="4" t="s">
-        <v>131</v>
-      </c>
       <c r="E59" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F59" s="4" t="s">
         <v>3</v>
@@ -5921,10 +5927,10 @@
         <v>0</v>
       </c>
       <c r="K59" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="L59" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="60">
@@ -5932,16 +5938,16 @@
         <v>43</v>
       </c>
       <c r="B60" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="C60" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="D60" s="4" t="s">
         <v>132</v>
       </c>
-      <c r="C60" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="D60" s="4" t="s">
-        <v>133</v>
-      </c>
       <c r="E60" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F60" s="4" t="s">
         <v>3</v>
@@ -5959,10 +5965,10 @@
         <v>0</v>
       </c>
       <c r="K60" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="L60" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="61">
@@ -5970,16 +5976,16 @@
         <v>44</v>
       </c>
       <c r="B61" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="C61" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="D61" s="4" t="s">
         <v>134</v>
       </c>
-      <c r="C61" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="D61" s="4" t="s">
-        <v>135</v>
-      </c>
       <c r="E61" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F61" s="4" t="s">
         <v>3</v>
@@ -5997,10 +6003,10 @@
         <v>0</v>
       </c>
       <c r="K61" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="L61" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="62">
@@ -6008,16 +6014,16 @@
         <v>45</v>
       </c>
       <c r="B62" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="C62" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="D62" s="4" t="s">
         <v>136</v>
       </c>
-      <c r="C62" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="D62" s="4" t="s">
-        <v>137</v>
-      </c>
       <c r="E62" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F62" s="4" t="s">
         <v>3</v>
@@ -6035,10 +6041,10 @@
         <v>0</v>
       </c>
       <c r="K62" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="L62" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="63">
@@ -6046,16 +6052,16 @@
         <v>46</v>
       </c>
       <c r="B63" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="C63" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="D63" s="4" t="s">
         <v>138</v>
       </c>
-      <c r="C63" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="D63" s="4" t="s">
-        <v>139</v>
-      </c>
       <c r="E63" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F63" s="4" t="s">
         <v>3</v>
@@ -6073,10 +6079,10 @@
         <v>0</v>
       </c>
       <c r="K63" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="L63" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="64">
@@ -6084,16 +6090,16 @@
         <v>47</v>
       </c>
       <c r="B64" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="C64" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="D64" s="4" t="s">
         <v>140</v>
       </c>
-      <c r="C64" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="D64" s="4" t="s">
-        <v>141</v>
-      </c>
       <c r="E64" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F64" s="4" t="s">
         <v>3</v>
@@ -6111,10 +6117,10 @@
         <v>0</v>
       </c>
       <c r="K64" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="L64" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="65">
@@ -6122,16 +6128,16 @@
         <v>48</v>
       </c>
       <c r="B65" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="C65" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="D65" s="4" t="s">
         <v>142</v>
       </c>
-      <c r="C65" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="D65" s="4" t="s">
-        <v>143</v>
-      </c>
       <c r="E65" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F65" s="4" t="s">
         <v>3</v>
@@ -6149,10 +6155,10 @@
         <v>0</v>
       </c>
       <c r="K65" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="L65" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="66">
@@ -6160,16 +6166,16 @@
         <v>49</v>
       </c>
       <c r="B66" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="C66" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="D66" s="4" t="s">
         <v>144</v>
       </c>
-      <c r="C66" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="D66" s="4" t="s">
-        <v>145</v>
-      </c>
       <c r="E66" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F66" s="4" t="s">
         <v>3</v>
@@ -6187,10 +6193,10 @@
         <v>0</v>
       </c>
       <c r="K66" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="L66" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="67">
@@ -6198,16 +6204,16 @@
         <v>50</v>
       </c>
       <c r="B67" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="C67" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="D67" s="4" t="s">
         <v>146</v>
       </c>
-      <c r="C67" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="D67" s="4" t="s">
-        <v>147</v>
-      </c>
       <c r="E67" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F67" s="4" t="s">
         <v>3</v>
@@ -6225,10 +6231,10 @@
         <v>0</v>
       </c>
       <c r="K67" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="L67" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="68">
@@ -6236,16 +6242,16 @@
         <v>51</v>
       </c>
       <c r="B68" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="C68" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="D68" s="4" t="s">
         <v>148</v>
       </c>
-      <c r="C68" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="D68" s="4" t="s">
-        <v>149</v>
-      </c>
       <c r="E68" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F68" s="4" t="s">
         <v>3</v>
@@ -6263,10 +6269,10 @@
         <v>0</v>
       </c>
       <c r="K68" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="L68" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="69">
@@ -6274,16 +6280,16 @@
         <v>52</v>
       </c>
       <c r="B69" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="C69" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="D69" s="4" t="s">
         <v>150</v>
       </c>
-      <c r="C69" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="D69" s="4" t="s">
-        <v>151</v>
-      </c>
       <c r="E69" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F69" s="4" t="s">
         <v>3</v>
@@ -6301,10 +6307,10 @@
         <v>0</v>
       </c>
       <c r="K69" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="L69" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="70">
@@ -6312,16 +6318,16 @@
         <v>53</v>
       </c>
       <c r="B70" s="4" t="s">
+        <v>151</v>
+      </c>
+      <c r="C70" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="D70" s="4" t="s">
         <v>152</v>
       </c>
-      <c r="C70" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="D70" s="4" t="s">
-        <v>153</v>
-      </c>
       <c r="E70" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F70" s="4" t="s">
         <v>3</v>
@@ -6339,10 +6345,10 @@
         <v>0</v>
       </c>
       <c r="K70" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="L70" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="71">
@@ -6350,16 +6356,16 @@
         <v>54</v>
       </c>
       <c r="B71" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="C71" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="D71" s="4" t="s">
         <v>154</v>
       </c>
-      <c r="C71" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="D71" s="4" t="s">
-        <v>155</v>
-      </c>
       <c r="E71" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F71" s="4" t="s">
         <v>3</v>
@@ -6377,10 +6383,10 @@
         <v>0</v>
       </c>
       <c r="K71" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="L71" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="72">
@@ -6388,16 +6394,16 @@
         <v>55</v>
       </c>
       <c r="B72" s="4" t="s">
+        <v>155</v>
+      </c>
+      <c r="C72" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="D72" s="4" t="s">
         <v>156</v>
       </c>
-      <c r="C72" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="D72" s="4" t="s">
-        <v>157</v>
-      </c>
       <c r="E72" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F72" s="4" t="s">
         <v>3</v>
@@ -6415,10 +6421,10 @@
         <v>0</v>
       </c>
       <c r="K72" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="L72" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="73">
@@ -6426,16 +6432,16 @@
         <v>56</v>
       </c>
       <c r="B73" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="C73" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="D73" s="4" t="s">
         <v>158</v>
       </c>
-      <c r="C73" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="D73" s="4" t="s">
-        <v>159</v>
-      </c>
       <c r="E73" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F73" s="4" t="s">
         <v>3</v>
@@ -6453,10 +6459,10 @@
         <v>0</v>
       </c>
       <c r="K73" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="L73" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="74">
@@ -6464,16 +6470,16 @@
         <v>57</v>
       </c>
       <c r="B74" s="4" t="s">
+        <v>159</v>
+      </c>
+      <c r="C74" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="D74" s="4" t="s">
         <v>160</v>
       </c>
-      <c r="C74" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="D74" s="4" t="s">
-        <v>161</v>
-      </c>
       <c r="E74" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F74" s="4" t="s">
         <v>3</v>
@@ -6491,10 +6497,10 @@
         <v>0</v>
       </c>
       <c r="K74" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="L74" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="75">
@@ -6502,16 +6508,16 @@
         <v>58</v>
       </c>
       <c r="B75" s="4" t="s">
+        <v>161</v>
+      </c>
+      <c r="C75" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="D75" s="4" t="s">
         <v>162</v>
       </c>
-      <c r="C75" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="D75" s="4" t="s">
-        <v>163</v>
-      </c>
       <c r="E75" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F75" s="4" t="s">
         <v>3</v>
@@ -6529,10 +6535,10 @@
         <v>0</v>
       </c>
       <c r="K75" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="L75" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="76">
@@ -6540,16 +6546,16 @@
         <v>59</v>
       </c>
       <c r="B76" s="4" t="s">
+        <v>163</v>
+      </c>
+      <c r="C76" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="D76" s="4" t="s">
         <v>164</v>
       </c>
-      <c r="C76" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="D76" s="4" t="s">
-        <v>165</v>
-      </c>
       <c r="E76" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F76" s="4" t="s">
         <v>3</v>
@@ -6567,10 +6573,10 @@
         <v>0</v>
       </c>
       <c r="K76" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="L76" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="77">
@@ -6578,16 +6584,16 @@
         <v>60</v>
       </c>
       <c r="B77" s="4" t="s">
+        <v>165</v>
+      </c>
+      <c r="C77" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="D77" s="4" t="s">
         <v>166</v>
       </c>
-      <c r="C77" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="D77" s="4" t="s">
-        <v>167</v>
-      </c>
       <c r="E77" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F77" s="4" t="s">
         <v>3</v>
@@ -6605,10 +6611,10 @@
         <v>0</v>
       </c>
       <c r="K77" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="L77" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="78">
@@ -6616,16 +6622,16 @@
         <v>61</v>
       </c>
       <c r="B78" s="4" t="s">
+        <v>167</v>
+      </c>
+      <c r="C78" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="D78" s="4" t="s">
         <v>168</v>
       </c>
-      <c r="C78" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="D78" s="4" t="s">
-        <v>169</v>
-      </c>
       <c r="E78" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F78" s="4" t="s">
         <v>3</v>
@@ -6643,10 +6649,10 @@
         <v>0</v>
       </c>
       <c r="K78" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="L78" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="79">
@@ -6654,16 +6660,16 @@
         <v>62</v>
       </c>
       <c r="B79" s="4" t="s">
+        <v>169</v>
+      </c>
+      <c r="C79" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="D79" s="4" t="s">
         <v>170</v>
       </c>
-      <c r="C79" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="D79" s="4" t="s">
-        <v>171</v>
-      </c>
       <c r="E79" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F79" s="4" t="s">
         <v>3</v>
@@ -6681,10 +6687,10 @@
         <v>0</v>
       </c>
       <c r="K79" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="L79" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="80">
@@ -6692,16 +6698,16 @@
         <v>63</v>
       </c>
       <c r="B80" s="4" t="s">
+        <v>171</v>
+      </c>
+      <c r="C80" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="D80" s="4" t="s">
         <v>172</v>
       </c>
-      <c r="C80" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="D80" s="4" t="s">
-        <v>173</v>
-      </c>
       <c r="E80" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F80" s="4" t="s">
         <v>3</v>
@@ -6719,10 +6725,10 @@
         <v>0</v>
       </c>
       <c r="K80" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="L80" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="81">
@@ -6730,16 +6736,16 @@
         <v>64</v>
       </c>
       <c r="B81" s="4" t="s">
+        <v>173</v>
+      </c>
+      <c r="C81" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="D81" s="4" t="s">
         <v>174</v>
       </c>
-      <c r="C81" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="D81" s="4" t="s">
-        <v>175</v>
-      </c>
       <c r="E81" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F81" s="4" t="s">
         <v>3</v>
@@ -6757,10 +6763,10 @@
         <v>0</v>
       </c>
       <c r="K81" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="L81" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="82">
@@ -6768,16 +6774,16 @@
         <v>65</v>
       </c>
       <c r="B82" s="4" t="s">
+        <v>175</v>
+      </c>
+      <c r="C82" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="D82" s="4" t="s">
         <v>176</v>
       </c>
-      <c r="C82" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="D82" s="4" t="s">
-        <v>177</v>
-      </c>
       <c r="E82" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F82" s="4" t="s">
         <v>3</v>
@@ -6795,10 +6801,10 @@
         <v>0</v>
       </c>
       <c r="K82" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="L82" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="83">
@@ -6806,16 +6812,16 @@
         <v>66</v>
       </c>
       <c r="B83" s="4" t="s">
+        <v>177</v>
+      </c>
+      <c r="C83" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="D83" s="4" t="s">
         <v>178</v>
       </c>
-      <c r="C83" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="D83" s="4" t="s">
-        <v>179</v>
-      </c>
       <c r="E83" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F83" s="4" t="s">
         <v>3</v>
@@ -6833,10 +6839,10 @@
         <v>0</v>
       </c>
       <c r="K83" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="L83" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="84">
@@ -6844,16 +6850,16 @@
         <v>67</v>
       </c>
       <c r="B84" s="4" t="s">
+        <v>179</v>
+      </c>
+      <c r="C84" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="D84" s="4" t="s">
         <v>180</v>
       </c>
-      <c r="C84" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="D84" s="4" t="s">
-        <v>181</v>
-      </c>
       <c r="E84" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F84" s="4" t="s">
         <v>3</v>
@@ -6871,10 +6877,10 @@
         <v>0</v>
       </c>
       <c r="K84" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="L84" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="85">
@@ -6882,16 +6888,16 @@
         <v>68</v>
       </c>
       <c r="B85" s="4" t="s">
+        <v>181</v>
+      </c>
+      <c r="C85" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="D85" s="4" t="s">
         <v>182</v>
       </c>
-      <c r="C85" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="D85" s="4" t="s">
-        <v>183</v>
-      </c>
       <c r="E85" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F85" s="4" t="s">
         <v>3</v>
@@ -6909,10 +6915,10 @@
         <v>0</v>
       </c>
       <c r="K85" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="L85" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="86">
@@ -6920,16 +6926,16 @@
         <v>69</v>
       </c>
       <c r="B86" s="4" t="s">
+        <v>183</v>
+      </c>
+      <c r="C86" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="D86" s="4" t="s">
         <v>184</v>
       </c>
-      <c r="C86" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="D86" s="4" t="s">
-        <v>185</v>
-      </c>
       <c r="E86" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F86" s="4" t="s">
         <v>3</v>
@@ -6947,10 +6953,10 @@
         <v>0</v>
       </c>
       <c r="K86" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="L86" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="87">
@@ -6958,16 +6964,16 @@
         <v>70</v>
       </c>
       <c r="B87" s="4" t="s">
+        <v>185</v>
+      </c>
+      <c r="C87" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="D87" s="4" t="s">
         <v>186</v>
       </c>
-      <c r="C87" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="D87" s="4" t="s">
-        <v>187</v>
-      </c>
       <c r="E87" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F87" s="4" t="s">
         <v>3</v>
@@ -6985,10 +6991,10 @@
         <v>0</v>
       </c>
       <c r="K87" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="L87" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="88">
@@ -6996,16 +7002,16 @@
         <v>71</v>
       </c>
       <c r="B88" s="4" t="s">
+        <v>187</v>
+      </c>
+      <c r="C88" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="D88" s="4" t="s">
         <v>188</v>
       </c>
-      <c r="C88" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="D88" s="4" t="s">
-        <v>189</v>
-      </c>
       <c r="E88" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F88" s="4" t="s">
         <v>3</v>
@@ -7023,10 +7029,10 @@
         <v>0</v>
       </c>
       <c r="K88" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="L88" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="89">
@@ -7034,16 +7040,16 @@
         <v>72</v>
       </c>
       <c r="B89" s="4" t="s">
+        <v>189</v>
+      </c>
+      <c r="C89" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="D89" s="4" t="s">
         <v>190</v>
       </c>
-      <c r="C89" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="D89" s="4" t="s">
-        <v>191</v>
-      </c>
       <c r="E89" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F89" s="4" t="s">
         <v>3</v>
@@ -7061,10 +7067,10 @@
         <v>0</v>
       </c>
       <c r="K89" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="L89" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="90">
@@ -7072,16 +7078,16 @@
         <v>73</v>
       </c>
       <c r="B90" s="4" t="s">
+        <v>191</v>
+      </c>
+      <c r="C90" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="D90" s="4" t="s">
         <v>192</v>
       </c>
-      <c r="C90" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="D90" s="4" t="s">
-        <v>193</v>
-      </c>
       <c r="E90" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F90" s="4" t="s">
         <v>3</v>
@@ -7099,10 +7105,10 @@
         <v>0</v>
       </c>
       <c r="K90" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="L90" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="91">
@@ -7110,16 +7116,16 @@
         <v>74</v>
       </c>
       <c r="B91" s="4" t="s">
+        <v>193</v>
+      </c>
+      <c r="C91" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="D91" s="4" t="s">
         <v>194</v>
       </c>
-      <c r="C91" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="D91" s="4" t="s">
-        <v>195</v>
-      </c>
       <c r="E91" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F91" s="4" t="s">
         <v>3</v>
@@ -7137,10 +7143,10 @@
         <v>0</v>
       </c>
       <c r="K91" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="L91" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="92">
@@ -7148,16 +7154,16 @@
         <v>75</v>
       </c>
       <c r="B92" s="4" t="s">
+        <v>195</v>
+      </c>
+      <c r="C92" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="D92" s="4" t="s">
         <v>196</v>
       </c>
-      <c r="C92" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="D92" s="4" t="s">
-        <v>197</v>
-      </c>
       <c r="E92" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F92" s="4" t="s">
         <v>3</v>
@@ -7175,10 +7181,10 @@
         <v>0</v>
       </c>
       <c r="K92" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="L92" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="93">
@@ -7186,16 +7192,16 @@
         <v>76</v>
       </c>
       <c r="B93" s="4" t="s">
+        <v>197</v>
+      </c>
+      <c r="C93" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="D93" s="4" t="s">
         <v>198</v>
       </c>
-      <c r="C93" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="D93" s="4" t="s">
-        <v>199</v>
-      </c>
       <c r="E93" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F93" s="4" t="s">
         <v>3</v>
@@ -7213,10 +7219,10 @@
         <v>0</v>
       </c>
       <c r="K93" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="L93" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="94">
@@ -7224,16 +7230,16 @@
         <v>77</v>
       </c>
       <c r="B94" s="4" t="s">
+        <v>199</v>
+      </c>
+      <c r="C94" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="D94" s="4" t="s">
         <v>200</v>
       </c>
-      <c r="C94" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="D94" s="4" t="s">
-        <v>201</v>
-      </c>
       <c r="E94" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F94" s="4" t="s">
         <v>3</v>
@@ -7251,10 +7257,10 @@
         <v>0</v>
       </c>
       <c r="K94" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="L94" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="95">
@@ -7262,16 +7268,16 @@
         <v>78</v>
       </c>
       <c r="B95" s="4" t="s">
+        <v>201</v>
+      </c>
+      <c r="C95" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="D95" s="4" t="s">
         <v>202</v>
       </c>
-      <c r="C95" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="D95" s="4" t="s">
-        <v>203</v>
-      </c>
       <c r="E95" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F95" s="4" t="s">
         <v>3</v>
@@ -7289,10 +7295,10 @@
         <v>0</v>
       </c>
       <c r="K95" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="L95" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="96">
@@ -7300,16 +7306,16 @@
         <v>79</v>
       </c>
       <c r="B96" s="4" t="s">
+        <v>203</v>
+      </c>
+      <c r="C96" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="D96" s="4" t="s">
         <v>204</v>
       </c>
-      <c r="C96" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="D96" s="4" t="s">
-        <v>205</v>
-      </c>
       <c r="E96" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F96" s="4" t="s">
         <v>3</v>
@@ -7327,10 +7333,10 @@
         <v>0</v>
       </c>
       <c r="K96" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="L96" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="97">
@@ -7338,16 +7344,16 @@
         <v>80</v>
       </c>
       <c r="B97" s="4" t="s">
+        <v>205</v>
+      </c>
+      <c r="C97" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="D97" s="4" t="s">
         <v>206</v>
       </c>
-      <c r="C97" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="D97" s="4" t="s">
-        <v>207</v>
-      </c>
       <c r="E97" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F97" s="4" t="s">
         <v>3</v>
@@ -7365,10 +7371,10 @@
         <v>0</v>
       </c>
       <c r="K97" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="L97" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="98">
@@ -7376,16 +7382,16 @@
         <v>81</v>
       </c>
       <c r="B98" s="4" t="s">
+        <v>207</v>
+      </c>
+      <c r="C98" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="D98" s="4" t="s">
         <v>208</v>
       </c>
-      <c r="C98" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="D98" s="4" t="s">
-        <v>209</v>
-      </c>
       <c r="E98" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F98" s="4" t="s">
         <v>3</v>
@@ -7403,10 +7409,10 @@
         <v>0</v>
       </c>
       <c r="K98" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="L98" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="99">
@@ -7414,16 +7420,16 @@
         <v>82</v>
       </c>
       <c r="B99" s="4" t="s">
+        <v>209</v>
+      </c>
+      <c r="C99" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="D99" s="4" t="s">
         <v>210</v>
       </c>
-      <c r="C99" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="D99" s="4" t="s">
-        <v>211</v>
-      </c>
       <c r="E99" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F99" s="4" t="s">
         <v>3</v>
@@ -7441,10 +7447,10 @@
         <v>0</v>
       </c>
       <c r="K99" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="L99" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="100">
@@ -7452,16 +7458,16 @@
         <v>83</v>
       </c>
       <c r="B100" s="4" t="s">
+        <v>211</v>
+      </c>
+      <c r="C100" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="D100" s="4" t="s">
         <v>212</v>
       </c>
-      <c r="C100" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="D100" s="4" t="s">
-        <v>213</v>
-      </c>
       <c r="E100" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F100" s="4" t="s">
         <v>3</v>
@@ -7479,10 +7485,10 @@
         <v>0</v>
       </c>
       <c r="K100" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="L100" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="101">
@@ -7490,16 +7496,16 @@
         <v>84</v>
       </c>
       <c r="B101" s="4" t="s">
+        <v>213</v>
+      </c>
+      <c r="C101" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="D101" s="4" t="s">
         <v>214</v>
       </c>
-      <c r="C101" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="D101" s="4" t="s">
-        <v>215</v>
-      </c>
       <c r="E101" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F101" s="4" t="s">
         <v>3</v>
@@ -7517,10 +7523,10 @@
         <v>0</v>
       </c>
       <c r="K101" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="L101" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="102">
@@ -7528,16 +7534,16 @@
         <v>85</v>
       </c>
       <c r="B102" s="4" t="s">
+        <v>215</v>
+      </c>
+      <c r="C102" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="D102" s="4" t="s">
         <v>216</v>
       </c>
-      <c r="C102" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="D102" s="4" t="s">
-        <v>217</v>
-      </c>
       <c r="E102" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F102" s="4" t="s">
         <v>3</v>
@@ -7555,10 +7561,10 @@
         <v>0</v>
       </c>
       <c r="K102" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="L102" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="103">
@@ -7566,16 +7572,16 @@
         <v>86</v>
       </c>
       <c r="B103" s="4" t="s">
+        <v>217</v>
+      </c>
+      <c r="C103" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="D103" s="4" t="s">
         <v>218</v>
       </c>
-      <c r="C103" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="D103" s="4" t="s">
-        <v>219</v>
-      </c>
       <c r="E103" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F103" s="4" t="s">
         <v>3</v>
@@ -7593,10 +7599,10 @@
         <v>0</v>
       </c>
       <c r="K103" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="L103" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="104">
@@ -7604,16 +7610,16 @@
         <v>87</v>
       </c>
       <c r="B104" s="4" t="s">
+        <v>219</v>
+      </c>
+      <c r="C104" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="D104" s="4" t="s">
         <v>220</v>
       </c>
-      <c r="C104" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="D104" s="4" t="s">
-        <v>221</v>
-      </c>
       <c r="E104" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F104" s="4" t="s">
         <v>3</v>
@@ -7631,10 +7637,10 @@
         <v>0</v>
       </c>
       <c r="K104" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="L104" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="105">
@@ -7642,16 +7648,16 @@
         <v>88</v>
       </c>
       <c r="B105" s="4" t="s">
+        <v>221</v>
+      </c>
+      <c r="C105" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="D105" s="4" t="s">
         <v>222</v>
       </c>
-      <c r="C105" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="D105" s="4" t="s">
-        <v>223</v>
-      </c>
       <c r="E105" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F105" s="4" t="s">
         <v>3</v>
@@ -7669,10 +7675,10 @@
         <v>0</v>
       </c>
       <c r="K105" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="L105" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="106">
@@ -7680,16 +7686,16 @@
         <v>89</v>
       </c>
       <c r="B106" s="4" t="s">
+        <v>223</v>
+      </c>
+      <c r="C106" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="D106" s="4" t="s">
         <v>224</v>
       </c>
-      <c r="C106" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="D106" s="4" t="s">
-        <v>225</v>
-      </c>
       <c r="E106" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F106" s="4" t="s">
         <v>3</v>
@@ -7707,10 +7713,10 @@
         <v>0</v>
       </c>
       <c r="K106" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="L106" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="107">
@@ -7718,16 +7724,16 @@
         <v>90</v>
       </c>
       <c r="B107" s="4" t="s">
+        <v>225</v>
+      </c>
+      <c r="C107" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="D107" s="4" t="s">
         <v>226</v>
       </c>
-      <c r="C107" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="D107" s="4" t="s">
-        <v>227</v>
-      </c>
       <c r="E107" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F107" s="4" t="s">
         <v>3</v>
@@ -7745,10 +7751,10 @@
         <v>0</v>
       </c>
       <c r="K107" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="L107" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="108">
@@ -7756,16 +7762,16 @@
         <v>91</v>
       </c>
       <c r="B108" s="4" t="s">
+        <v>227</v>
+      </c>
+      <c r="C108" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="D108" s="4" t="s">
         <v>228</v>
       </c>
-      <c r="C108" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="D108" s="4" t="s">
-        <v>229</v>
-      </c>
       <c r="E108" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F108" s="4" t="s">
         <v>3</v>
@@ -7783,10 +7789,10 @@
         <v>0</v>
       </c>
       <c r="K108" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="L108" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="109">
@@ -7794,16 +7800,16 @@
         <v>92</v>
       </c>
       <c r="B109" s="4" t="s">
+        <v>229</v>
+      </c>
+      <c r="C109" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="D109" s="4" t="s">
         <v>230</v>
       </c>
-      <c r="C109" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="D109" s="4" t="s">
-        <v>231</v>
-      </c>
       <c r="E109" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F109" s="4" t="s">
         <v>3</v>
@@ -7821,10 +7827,10 @@
         <v>0</v>
       </c>
       <c r="K109" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="L109" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="110">
@@ -7832,16 +7838,16 @@
         <v>93</v>
       </c>
       <c r="B110" s="4" t="s">
+        <v>231</v>
+      </c>
+      <c r="C110" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="D110" s="4" t="s">
         <v>232</v>
       </c>
-      <c r="C110" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="D110" s="4" t="s">
-        <v>233</v>
-      </c>
       <c r="E110" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F110" s="4" t="s">
         <v>3</v>
@@ -7859,10 +7865,10 @@
         <v>0</v>
       </c>
       <c r="K110" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="L110" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="111">
@@ -7870,16 +7876,16 @@
         <v>94</v>
       </c>
       <c r="B111" s="4" t="s">
+        <v>233</v>
+      </c>
+      <c r="C111" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="D111" s="4" t="s">
         <v>234</v>
       </c>
-      <c r="C111" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="D111" s="4" t="s">
-        <v>235</v>
-      </c>
       <c r="E111" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F111" s="4" t="s">
         <v>3</v>
@@ -7897,10 +7903,10 @@
         <v>0</v>
       </c>
       <c r="K111" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="L111" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="112">
@@ -7908,16 +7914,16 @@
         <v>95</v>
       </c>
       <c r="B112" s="4" t="s">
+        <v>235</v>
+      </c>
+      <c r="C112" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="D112" s="4" t="s">
         <v>236</v>
       </c>
-      <c r="C112" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="D112" s="4" t="s">
-        <v>237</v>
-      </c>
       <c r="E112" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F112" s="4" t="s">
         <v>3</v>
@@ -7935,10 +7941,10 @@
         <v>0</v>
       </c>
       <c r="K112" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="L112" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="113">
@@ -7946,16 +7952,16 @@
         <v>96</v>
       </c>
       <c r="B113" s="4" t="s">
+        <v>237</v>
+      </c>
+      <c r="C113" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="D113" s="4" t="s">
         <v>238</v>
       </c>
-      <c r="C113" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="D113" s="4" t="s">
-        <v>239</v>
-      </c>
       <c r="E113" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F113" s="4" t="s">
         <v>3</v>
@@ -7973,10 +7979,10 @@
         <v>0</v>
       </c>
       <c r="K113" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="L113" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="114">
@@ -7984,16 +7990,16 @@
         <v>97</v>
       </c>
       <c r="B114" s="4" t="s">
+        <v>239</v>
+      </c>
+      <c r="C114" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="D114" s="4" t="s">
         <v>240</v>
       </c>
-      <c r="C114" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="D114" s="4" t="s">
-        <v>241</v>
-      </c>
       <c r="E114" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F114" s="4" t="s">
         <v>3</v>
@@ -8011,10 +8017,10 @@
         <v>0</v>
       </c>
       <c r="K114" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="L114" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="115">
@@ -8022,16 +8028,16 @@
         <v>98</v>
       </c>
       <c r="B115" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="C115" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="D115" s="4" t="s">
         <v>242</v>
       </c>
-      <c r="C115" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="D115" s="4" t="s">
-        <v>243</v>
-      </c>
       <c r="E115" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F115" s="4" t="s">
         <v>3</v>
@@ -8049,10 +8055,10 @@
         <v>0</v>
       </c>
       <c r="K115" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="L115" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="116">
@@ -8060,16 +8066,16 @@
         <v>99</v>
       </c>
       <c r="B116" s="4" t="s">
+        <v>243</v>
+      </c>
+      <c r="C116" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="D116" s="4" t="s">
         <v>244</v>
       </c>
-      <c r="C116" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="D116" s="4" t="s">
-        <v>245</v>
-      </c>
       <c r="E116" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F116" s="4" t="s">
         <v>3</v>
@@ -8087,10 +8093,10 @@
         <v>0</v>
       </c>
       <c r="K116" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="L116" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="117">
@@ -8098,16 +8104,16 @@
         <v>100</v>
       </c>
       <c r="B117" s="4" t="s">
+        <v>245</v>
+      </c>
+      <c r="C117" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="D117" s="4" t="s">
         <v>246</v>
       </c>
-      <c r="C117" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="D117" s="4" t="s">
-        <v>247</v>
-      </c>
       <c r="E117" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F117" s="4" t="s">
         <v>3</v>
@@ -8125,10 +8131,10 @@
         <v>0</v>
       </c>
       <c r="K117" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="L117" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="118">
@@ -8136,16 +8142,16 @@
         <v>101</v>
       </c>
       <c r="B118" s="4" t="s">
+        <v>247</v>
+      </c>
+      <c r="C118" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="D118" s="4" t="s">
         <v>248</v>
       </c>
-      <c r="C118" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="D118" s="4" t="s">
-        <v>249</v>
-      </c>
       <c r="E118" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F118" s="4" t="s">
         <v>3</v>
@@ -8163,10 +8169,10 @@
         <v>0</v>
       </c>
       <c r="K118" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="L118" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="119">
@@ -8174,16 +8180,16 @@
         <v>102</v>
       </c>
       <c r="B119" s="4" t="s">
+        <v>249</v>
+      </c>
+      <c r="C119" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="D119" s="4" t="s">
         <v>250</v>
       </c>
-      <c r="C119" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="D119" s="4" t="s">
-        <v>251</v>
-      </c>
       <c r="E119" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F119" s="4" t="s">
         <v>3</v>
@@ -8201,10 +8207,10 @@
         <v>0</v>
       </c>
       <c r="K119" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="L119" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="120">
@@ -8212,16 +8218,16 @@
         <v>103</v>
       </c>
       <c r="B120" s="4" t="s">
+        <v>251</v>
+      </c>
+      <c r="C120" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="D120" s="4" t="s">
         <v>252</v>
       </c>
-      <c r="C120" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="D120" s="4" t="s">
-        <v>253</v>
-      </c>
       <c r="E120" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F120" s="4" t="s">
         <v>3</v>
@@ -8239,10 +8245,10 @@
         <v>0</v>
       </c>
       <c r="K120" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="L120" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="121">
@@ -8250,16 +8256,16 @@
         <v>104</v>
       </c>
       <c r="B121" s="4" t="s">
+        <v>253</v>
+      </c>
+      <c r="C121" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="D121" s="4" t="s">
         <v>254</v>
       </c>
-      <c r="C121" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="D121" s="4" t="s">
-        <v>255</v>
-      </c>
       <c r="E121" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F121" s="4" t="s">
         <v>3</v>
@@ -8277,10 +8283,10 @@
         <v>0</v>
       </c>
       <c r="K121" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="L121" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="122">
@@ -8288,16 +8294,16 @@
         <v>105</v>
       </c>
       <c r="B122" s="4" t="s">
+        <v>255</v>
+      </c>
+      <c r="C122" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="D122" s="4" t="s">
         <v>256</v>
       </c>
-      <c r="C122" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="D122" s="4" t="s">
-        <v>257</v>
-      </c>
       <c r="E122" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F122" s="4" t="s">
         <v>3</v>
@@ -8315,10 +8321,10 @@
         <v>0</v>
       </c>
       <c r="K122" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="L122" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="123">
@@ -8326,16 +8332,16 @@
         <v>106</v>
       </c>
       <c r="B123" s="4" t="s">
+        <v>257</v>
+      </c>
+      <c r="C123" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="D123" s="4" t="s">
         <v>258</v>
       </c>
-      <c r="C123" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="D123" s="4" t="s">
-        <v>259</v>
-      </c>
       <c r="E123" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F123" s="4" t="s">
         <v>3</v>
@@ -8353,10 +8359,10 @@
         <v>0</v>
       </c>
       <c r="K123" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="L123" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="124">
@@ -8364,16 +8370,16 @@
         <v>107</v>
       </c>
       <c r="B124" s="4" t="s">
+        <v>259</v>
+      </c>
+      <c r="C124" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="D124" s="4" t="s">
         <v>260</v>
       </c>
-      <c r="C124" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="D124" s="4" t="s">
-        <v>261</v>
-      </c>
       <c r="E124" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F124" s="4" t="s">
         <v>3</v>
@@ -8391,10 +8397,10 @@
         <v>0</v>
       </c>
       <c r="K124" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="L124" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="125">
@@ -8402,16 +8408,16 @@
         <v>108</v>
       </c>
       <c r="B125" s="4" t="s">
+        <v>261</v>
+      </c>
+      <c r="C125" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="D125" s="4" t="s">
         <v>262</v>
       </c>
-      <c r="C125" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="D125" s="4" t="s">
-        <v>263</v>
-      </c>
       <c r="E125" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F125" s="4" t="s">
         <v>3</v>
@@ -8429,10 +8435,10 @@
         <v>0</v>
       </c>
       <c r="K125" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="L125" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="126">
@@ -8440,16 +8446,16 @@
         <v>109</v>
       </c>
       <c r="B126" s="4" t="s">
+        <v>263</v>
+      </c>
+      <c r="C126" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="D126" s="4" t="s">
         <v>264</v>
       </c>
-      <c r="C126" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="D126" s="4" t="s">
-        <v>265</v>
-      </c>
       <c r="E126" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F126" s="4" t="s">
         <v>3</v>
@@ -8467,10 +8473,10 @@
         <v>0</v>
       </c>
       <c r="K126" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="L126" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="127">
@@ -8478,16 +8484,16 @@
         <v>110</v>
       </c>
       <c r="B127" s="4" t="s">
+        <v>265</v>
+      </c>
+      <c r="C127" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="D127" s="4" t="s">
         <v>266</v>
       </c>
-      <c r="C127" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="D127" s="4" t="s">
-        <v>267</v>
-      </c>
       <c r="E127" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F127" s="4" t="s">
         <v>3</v>
@@ -8505,10 +8511,10 @@
         <v>0</v>
       </c>
       <c r="K127" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="L127" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="128">
@@ -8516,16 +8522,16 @@
         <v>111</v>
       </c>
       <c r="B128" s="4" t="s">
+        <v>267</v>
+      </c>
+      <c r="C128" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="D128" s="4" t="s">
         <v>268</v>
       </c>
-      <c r="C128" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="D128" s="4" t="s">
-        <v>269</v>
-      </c>
       <c r="E128" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F128" s="4" t="s">
         <v>3</v>
@@ -8543,10 +8549,10 @@
         <v>0</v>
       </c>
       <c r="K128" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="L128" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="129">
@@ -8554,16 +8560,16 @@
         <v>112</v>
       </c>
       <c r="B129" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="C129" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="D129" s="4" t="s">
         <v>270</v>
       </c>
-      <c r="C129" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="D129" s="4" t="s">
-        <v>271</v>
-      </c>
       <c r="E129" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F129" s="4" t="s">
         <v>3</v>
@@ -8581,10 +8587,10 @@
         <v>0</v>
       </c>
       <c r="K129" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="L129" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="130">
@@ -8592,16 +8598,16 @@
         <v>113</v>
       </c>
       <c r="B130" s="4" t="s">
+        <v>271</v>
+      </c>
+      <c r="C130" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="D130" s="4" t="s">
         <v>272</v>
       </c>
-      <c r="C130" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="D130" s="4" t="s">
-        <v>273</v>
-      </c>
       <c r="E130" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F130" s="4" t="s">
         <v>3</v>
@@ -8619,10 +8625,10 @@
         <v>0</v>
       </c>
       <c r="K130" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="L130" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="131">
@@ -8630,16 +8636,16 @@
         <v>114</v>
       </c>
       <c r="B131" s="4" t="s">
+        <v>273</v>
+      </c>
+      <c r="C131" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="D131" s="4" t="s">
         <v>274</v>
       </c>
-      <c r="C131" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="D131" s="4" t="s">
-        <v>275</v>
-      </c>
       <c r="E131" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F131" s="4" t="s">
         <v>3</v>
@@ -8657,10 +8663,10 @@
         <v>0</v>
       </c>
       <c r="K131" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="L131" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="132">
@@ -8668,16 +8674,16 @@
         <v>115</v>
       </c>
       <c r="B132" s="4" t="s">
+        <v>275</v>
+      </c>
+      <c r="C132" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="D132" s="4" t="s">
         <v>276</v>
       </c>
-      <c r="C132" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="D132" s="4" t="s">
-        <v>277</v>
-      </c>
       <c r="E132" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F132" s="4" t="s">
         <v>3</v>
@@ -8695,10 +8701,10 @@
         <v>0</v>
       </c>
       <c r="K132" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="L132" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="133">
@@ -8706,16 +8712,16 @@
         <v>116</v>
       </c>
       <c r="B133" s="4" t="s">
+        <v>277</v>
+      </c>
+      <c r="C133" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="D133" s="4" t="s">
         <v>278</v>
       </c>
-      <c r="C133" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="D133" s="4" t="s">
-        <v>279</v>
-      </c>
       <c r="E133" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F133" s="4" t="s">
         <v>3</v>
@@ -8733,10 +8739,10 @@
         <v>0</v>
       </c>
       <c r="K133" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="L133" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="134">
@@ -8744,16 +8750,16 @@
         <v>117</v>
       </c>
       <c r="B134" s="4" t="s">
+        <v>279</v>
+      </c>
+      <c r="C134" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="D134" s="4" t="s">
         <v>280</v>
       </c>
-      <c r="C134" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="D134" s="4" t="s">
-        <v>281</v>
-      </c>
       <c r="E134" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F134" s="4" t="s">
         <v>3</v>
@@ -8771,10 +8777,10 @@
         <v>0</v>
       </c>
       <c r="K134" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="L134" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="135">
@@ -8782,16 +8788,16 @@
         <v>118</v>
       </c>
       <c r="B135" s="4" t="s">
+        <v>281</v>
+      </c>
+      <c r="C135" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="D135" s="4" t="s">
         <v>282</v>
       </c>
-      <c r="C135" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="D135" s="4" t="s">
-        <v>283</v>
-      </c>
       <c r="E135" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F135" s="4" t="s">
         <v>3</v>
@@ -8809,10 +8815,10 @@
         <v>0</v>
       </c>
       <c r="K135" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="L135" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="136">
@@ -8820,16 +8826,16 @@
         <v>119</v>
       </c>
       <c r="B136" s="4" t="s">
+        <v>283</v>
+      </c>
+      <c r="C136" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="D136" s="4" t="s">
         <v>284</v>
       </c>
-      <c r="C136" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="D136" s="4" t="s">
-        <v>285</v>
-      </c>
       <c r="E136" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F136" s="4" t="s">
         <v>3</v>
@@ -8847,10 +8853,10 @@
         <v>0</v>
       </c>
       <c r="K136" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="L136" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="137">
@@ -8858,16 +8864,16 @@
         <v>120</v>
       </c>
       <c r="B137" s="4" t="s">
+        <v>285</v>
+      </c>
+      <c r="C137" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="D137" s="4" t="s">
         <v>286</v>
       </c>
-      <c r="C137" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="D137" s="4" t="s">
-        <v>287</v>
-      </c>
       <c r="E137" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F137" s="4" t="s">
         <v>3</v>
@@ -8885,10 +8891,10 @@
         <v>0</v>
       </c>
       <c r="K137" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="L137" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="138">
@@ -8896,16 +8902,16 @@
         <v>121</v>
       </c>
       <c r="B138" s="3" t="s">
+        <v>287</v>
+      </c>
+      <c r="C138" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="D138" s="3" t="s">
         <v>288</v>
       </c>
-      <c r="C138" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="D138" s="3" t="s">
-        <v>289</v>
-      </c>
       <c r="E138" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F138" s="3" t="s">
         <v>3</v>
@@ -8917,16 +8923,16 @@
         <v>11</v>
       </c>
       <c r="I138" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="J138" s="3">
         <v>9223372036</v>
       </c>
       <c r="K138" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="L138" s="3" t="s">
-        <v>26</v>
+        <v>289</v>
       </c>
     </row>
     <row r="139">
@@ -8937,13 +8943,13 @@
         <v>290</v>
       </c>
       <c r="C139" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D139" s="3" t="s">
         <v>291</v>
       </c>
       <c r="E139" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F139" s="3" t="s">
         <v>3</v>
@@ -8955,16 +8961,16 @@
         <v>11</v>
       </c>
       <c r="I139" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="J139" s="3">
         <v>9223372036</v>
       </c>
       <c r="K139" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="L139" s="3" t="s">
-        <v>26</v>
+        <v>289</v>
       </c>
     </row>
     <row r="140">
@@ -8975,13 +8981,13 @@
         <v>292</v>
       </c>
       <c r="C140" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D140" s="3" t="s">
         <v>293</v>
       </c>
       <c r="E140" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F140" s="3" t="s">
         <v>3</v>
@@ -8993,16 +8999,16 @@
         <v>11</v>
       </c>
       <c r="I140" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="J140" s="3">
         <v>9223372036</v>
       </c>
       <c r="K140" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="L140" s="3" t="s">
-        <v>26</v>
+        <v>289</v>
       </c>
     </row>
     <row r="141">
@@ -9013,13 +9019,13 @@
         <v>294</v>
       </c>
       <c r="C141" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D141" s="3" t="s">
         <v>295</v>
       </c>
       <c r="E141" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F141" s="3" t="s">
         <v>3</v>
@@ -9031,16 +9037,16 @@
         <v>11</v>
       </c>
       <c r="I141" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="J141" s="3">
         <v>9223372036</v>
       </c>
       <c r="K141" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="L141" s="3" t="s">
-        <v>26</v>
+        <v>289</v>
       </c>
     </row>
     <row r="142">
@@ -9051,13 +9057,13 @@
         <v>296</v>
       </c>
       <c r="C142" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D142" s="3" t="s">
         <v>297</v>
       </c>
       <c r="E142" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F142" s="3" t="s">
         <v>3</v>
@@ -9069,16 +9075,16 @@
         <v>11</v>
       </c>
       <c r="I142" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="J142" s="3">
         <v>9223372036</v>
       </c>
       <c r="K142" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="L142" s="3" t="s">
-        <v>26</v>
+        <v>289</v>
       </c>
     </row>
     <row r="143">
@@ -9089,13 +9095,13 @@
         <v>298</v>
       </c>
       <c r="C143" s="4" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D143" s="4" t="s">
         <v>299</v>
       </c>
       <c r="E143" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F143" s="4" t="s">
         <v>3</v>
@@ -9113,10 +9119,10 @@
         <v>0</v>
       </c>
       <c r="K143" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="L143" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="144">
@@ -9127,13 +9133,13 @@
         <v>300</v>
       </c>
       <c r="C144" s="4" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D144" s="4" t="s">
         <v>301</v>
       </c>
       <c r="E144" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F144" s="4" t="s">
         <v>3</v>
@@ -9151,10 +9157,10 @@
         <v>0</v>
       </c>
       <c r="K144" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="L144" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="145">
@@ -9165,13 +9171,13 @@
         <v>302</v>
       </c>
       <c r="C145" s="4" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D145" s="4" t="s">
         <v>303</v>
       </c>
       <c r="E145" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F145" s="4" t="s">
         <v>3</v>
@@ -9189,10 +9195,10 @@
         <v>0</v>
       </c>
       <c r="K145" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="L145" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="146">
@@ -9203,13 +9209,13 @@
         <v>304</v>
       </c>
       <c r="C146" s="4" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D146" s="4" t="s">
         <v>305</v>
       </c>
       <c r="E146" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F146" s="4" t="s">
         <v>3</v>
@@ -9227,10 +9233,10 @@
         <v>0</v>
       </c>
       <c r="K146" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="L146" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="147">
@@ -9241,13 +9247,13 @@
         <v>306</v>
       </c>
       <c r="C147" s="4" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D147" s="4" t="s">
         <v>307</v>
       </c>
       <c r="E147" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F147" s="4" t="s">
         <v>3</v>
@@ -9265,10 +9271,10 @@
         <v>0</v>
       </c>
       <c r="K147" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="L147" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="148">
@@ -9279,13 +9285,13 @@
         <v>308</v>
       </c>
       <c r="C148" s="4" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D148" s="4" t="s">
         <v>309</v>
       </c>
       <c r="E148" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F148" s="4" t="s">
         <v>3</v>
@@ -9303,10 +9309,10 @@
         <v>0</v>
       </c>
       <c r="K148" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="L148" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="149">
@@ -9317,13 +9323,13 @@
         <v>310</v>
       </c>
       <c r="C149" s="4" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D149" s="4" t="s">
         <v>311</v>
       </c>
       <c r="E149" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F149" s="4" t="s">
         <v>3</v>
@@ -9341,10 +9347,10 @@
         <v>0</v>
       </c>
       <c r="K149" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="L149" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="150">
@@ -9355,13 +9361,13 @@
         <v>312</v>
       </c>
       <c r="C150" s="4" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D150" s="4" t="s">
         <v>313</v>
       </c>
       <c r="E150" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F150" s="4" t="s">
         <v>3</v>
@@ -9379,10 +9385,10 @@
         <v>0</v>
       </c>
       <c r="K150" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="L150" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="151">
@@ -9393,13 +9399,13 @@
         <v>314</v>
       </c>
       <c r="C151" s="4" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D151" s="4" t="s">
         <v>315</v>
       </c>
       <c r="E151" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F151" s="4" t="s">
         <v>3</v>
@@ -9417,10 +9423,10 @@
         <v>0</v>
       </c>
       <c r="K151" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="L151" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="152">
@@ -9431,13 +9437,13 @@
         <v>316</v>
       </c>
       <c r="C152" s="4" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D152" s="4" t="s">
         <v>317</v>
       </c>
       <c r="E152" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F152" s="4" t="s">
         <v>3</v>
@@ -9455,10 +9461,10 @@
         <v>0</v>
       </c>
       <c r="K152" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="L152" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="153">
@@ -9469,13 +9475,13 @@
         <v>318</v>
       </c>
       <c r="C153" s="4" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D153" s="4" t="s">
         <v>319</v>
       </c>
       <c r="E153" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F153" s="4" t="s">
         <v>3</v>
@@ -9493,10 +9499,10 @@
         <v>0</v>
       </c>
       <c r="K153" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="L153" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="154">
@@ -9507,13 +9513,13 @@
         <v>320</v>
       </c>
       <c r="C154" s="4" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D154" s="4" t="s">
         <v>321</v>
       </c>
       <c r="E154" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F154" s="4" t="s">
         <v>3</v>
@@ -9531,10 +9537,10 @@
         <v>0</v>
       </c>
       <c r="K154" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="L154" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="155">
@@ -9545,13 +9551,13 @@
         <v>322</v>
       </c>
       <c r="C155" s="4" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D155" s="4" t="s">
         <v>323</v>
       </c>
       <c r="E155" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F155" s="4" t="s">
         <v>3</v>
@@ -9569,10 +9575,10 @@
         <v>0</v>
       </c>
       <c r="K155" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="L155" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="156">
@@ -9583,13 +9589,13 @@
         <v>324</v>
       </c>
       <c r="C156" s="4" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D156" s="4" t="s">
         <v>325</v>
       </c>
       <c r="E156" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F156" s="4" t="s">
         <v>3</v>
@@ -9607,10 +9613,10 @@
         <v>0</v>
       </c>
       <c r="K156" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="L156" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="157">
@@ -9621,13 +9627,13 @@
         <v>326</v>
       </c>
       <c r="C157" s="4" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D157" s="4" t="s">
         <v>327</v>
       </c>
       <c r="E157" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F157" s="4" t="s">
         <v>3</v>
@@ -9645,10 +9651,10 @@
         <v>0</v>
       </c>
       <c r="K157" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="L157" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="158">
@@ -9659,13 +9665,13 @@
         <v>328</v>
       </c>
       <c r="C158" s="4" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D158" s="4" t="s">
         <v>329</v>
       </c>
       <c r="E158" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F158" s="4" t="s">
         <v>3</v>
@@ -9683,10 +9689,10 @@
         <v>0</v>
       </c>
       <c r="K158" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="L158" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="159">
@@ -9697,13 +9703,13 @@
         <v>330</v>
       </c>
       <c r="C159" s="4" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D159" s="4" t="s">
         <v>331</v>
       </c>
       <c r="E159" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F159" s="4" t="s">
         <v>3</v>
@@ -9721,10 +9727,10 @@
         <v>0</v>
       </c>
       <c r="K159" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="L159" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="160">
@@ -9735,13 +9741,13 @@
         <v>332</v>
       </c>
       <c r="C160" s="4" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D160" s="4" t="s">
         <v>333</v>
       </c>
       <c r="E160" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F160" s="4" t="s">
         <v>3</v>
@@ -9759,10 +9765,10 @@
         <v>0</v>
       </c>
       <c r="K160" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="L160" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="161">
@@ -9773,13 +9779,13 @@
         <v>334</v>
       </c>
       <c r="C161" s="4" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D161" s="4" t="s">
         <v>335</v>
       </c>
       <c r="E161" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F161" s="4" t="s">
         <v>3</v>
@@ -9797,10 +9803,10 @@
         <v>0</v>
       </c>
       <c r="K161" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="L161" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="162">
@@ -9811,13 +9817,13 @@
         <v>336</v>
       </c>
       <c r="C162" s="4" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D162" s="4" t="s">
         <v>337</v>
       </c>
       <c r="E162" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F162" s="4" t="s">
         <v>3</v>
@@ -9835,10 +9841,10 @@
         <v>0</v>
       </c>
       <c r="K162" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="L162" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="163">
@@ -9849,13 +9855,13 @@
         <v>338</v>
       </c>
       <c r="C163" s="4" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D163" s="4" t="s">
         <v>339</v>
       </c>
       <c r="E163" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F163" s="4" t="s">
         <v>3</v>
@@ -9873,10 +9879,10 @@
         <v>0</v>
       </c>
       <c r="K163" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="L163" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="164">
@@ -9887,13 +9893,13 @@
         <v>340</v>
       </c>
       <c r="C164" s="4" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D164" s="4" t="s">
         <v>341</v>
       </c>
       <c r="E164" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F164" s="4" t="s">
         <v>3</v>
@@ -9911,10 +9917,10 @@
         <v>0</v>
       </c>
       <c r="K164" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="L164" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="165">
@@ -9925,13 +9931,13 @@
         <v>342</v>
       </c>
       <c r="C165" s="4" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D165" s="4" t="s">
         <v>343</v>
       </c>
       <c r="E165" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F165" s="4" t="s">
         <v>3</v>
@@ -9949,10 +9955,10 @@
         <v>0</v>
       </c>
       <c r="K165" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="L165" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="166">
@@ -9963,13 +9969,13 @@
         <v>344</v>
       </c>
       <c r="C166" s="4" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D166" s="4" t="s">
         <v>345</v>
       </c>
       <c r="E166" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F166" s="4" t="s">
         <v>3</v>
@@ -9987,10 +9993,10 @@
         <v>0</v>
       </c>
       <c r="K166" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="L166" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="167">
@@ -10001,13 +10007,13 @@
         <v>346</v>
       </c>
       <c r="C167" s="4" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D167" s="4" t="s">
         <v>347</v>
       </c>
       <c r="E167" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F167" s="4" t="s">
         <v>3</v>
@@ -10025,10 +10031,10 @@
         <v>0</v>
       </c>
       <c r="K167" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="L167" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="168">
@@ -10039,13 +10045,13 @@
         <v>348</v>
       </c>
       <c r="C168" s="4" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D168" s="4" t="s">
         <v>349</v>
       </c>
       <c r="E168" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F168" s="4" t="s">
         <v>3</v>
@@ -10063,10 +10069,10 @@
         <v>0</v>
       </c>
       <c r="K168" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="L168" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="169">
@@ -10077,13 +10083,13 @@
         <v>350</v>
       </c>
       <c r="C169" s="4" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D169" s="4" t="s">
         <v>351</v>
       </c>
       <c r="E169" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F169" s="4" t="s">
         <v>3</v>
@@ -10101,10 +10107,10 @@
         <v>0</v>
       </c>
       <c r="K169" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="L169" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="170">
@@ -10115,13 +10121,13 @@
         <v>352</v>
       </c>
       <c r="C170" s="4" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D170" s="4" t="s">
         <v>353</v>
       </c>
       <c r="E170" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F170" s="4" t="s">
         <v>3</v>
@@ -10139,10 +10145,10 @@
         <v>0</v>
       </c>
       <c r="K170" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="L170" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="171">
@@ -10153,13 +10159,13 @@
         <v>354</v>
       </c>
       <c r="C171" s="4" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D171" s="4" t="s">
         <v>355</v>
       </c>
       <c r="E171" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F171" s="4" t="s">
         <v>3</v>
@@ -10177,10 +10183,10 @@
         <v>0</v>
       </c>
       <c r="K171" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="L171" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="172">
@@ -10191,13 +10197,13 @@
         <v>356</v>
       </c>
       <c r="C172" s="4" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D172" s="4" t="s">
         <v>357</v>
       </c>
       <c r="E172" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F172" s="4" t="s">
         <v>3</v>
@@ -10215,10 +10221,10 @@
         <v>0</v>
       </c>
       <c r="K172" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="L172" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="173">
@@ -10229,13 +10235,13 @@
         <v>358</v>
       </c>
       <c r="C173" s="4" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D173" s="4" t="s">
         <v>359</v>
       </c>
       <c r="E173" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F173" s="4" t="s">
         <v>3</v>
@@ -10253,10 +10259,10 @@
         <v>0</v>
       </c>
       <c r="K173" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="L173" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="174">
@@ -10267,13 +10273,13 @@
         <v>360</v>
       </c>
       <c r="C174" s="4" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D174" s="4" t="s">
         <v>361</v>
       </c>
       <c r="E174" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F174" s="4" t="s">
         <v>3</v>
@@ -10291,10 +10297,10 @@
         <v>0</v>
       </c>
       <c r="K174" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="L174" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="175">
@@ -10305,13 +10311,13 @@
         <v>362</v>
       </c>
       <c r="C175" s="4" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D175" s="4" t="s">
         <v>363</v>
       </c>
       <c r="E175" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F175" s="4" t="s">
         <v>3</v>
@@ -10329,10 +10335,10 @@
         <v>0</v>
       </c>
       <c r="K175" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="L175" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="176">
@@ -10343,13 +10349,13 @@
         <v>364</v>
       </c>
       <c r="C176" s="4" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D176" s="4" t="s">
         <v>365</v>
       </c>
       <c r="E176" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F176" s="4" t="s">
         <v>3</v>
@@ -10367,10 +10373,10 @@
         <v>0</v>
       </c>
       <c r="K176" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="L176" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="177">
@@ -10381,13 +10387,13 @@
         <v>366</v>
       </c>
       <c r="C177" s="4" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D177" s="4" t="s">
         <v>367</v>
       </c>
       <c r="E177" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F177" s="4" t="s">
         <v>3</v>
@@ -10405,10 +10411,10 @@
         <v>0</v>
       </c>
       <c r="K177" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="L177" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="178">
@@ -10419,13 +10425,13 @@
         <v>368</v>
       </c>
       <c r="C178" s="4" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D178" s="4" t="s">
         <v>369</v>
       </c>
       <c r="E178" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F178" s="4" t="s">
         <v>3</v>
@@ -10443,10 +10449,10 @@
         <v>0</v>
       </c>
       <c r="K178" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="L178" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="179">
@@ -10457,13 +10463,13 @@
         <v>370</v>
       </c>
       <c r="C179" s="4" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D179" s="4" t="s">
         <v>371</v>
       </c>
       <c r="E179" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F179" s="4" t="s">
         <v>3</v>
@@ -10481,10 +10487,10 @@
         <v>0</v>
       </c>
       <c r="K179" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="L179" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="180">
@@ -10495,13 +10501,13 @@
         <v>372</v>
       </c>
       <c r="C180" s="4" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D180" s="4" t="s">
         <v>373</v>
       </c>
       <c r="E180" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F180" s="4" t="s">
         <v>3</v>
@@ -10519,10 +10525,10 @@
         <v>0</v>
       </c>
       <c r="K180" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="L180" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="181">
@@ -10533,13 +10539,13 @@
         <v>374</v>
       </c>
       <c r="C181" s="4" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D181" s="4" t="s">
         <v>375</v>
       </c>
       <c r="E181" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F181" s="4" t="s">
         <v>3</v>
@@ -10557,10 +10563,10 @@
         <v>0</v>
       </c>
       <c r="K181" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="L181" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="182">
@@ -10571,13 +10577,13 @@
         <v>376</v>
       </c>
       <c r="C182" s="4" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D182" s="4" t="s">
         <v>377</v>
       </c>
       <c r="E182" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F182" s="4" t="s">
         <v>3</v>
@@ -10595,10 +10601,10 @@
         <v>0</v>
       </c>
       <c r="K182" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="L182" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="183">
@@ -10609,13 +10615,13 @@
         <v>378</v>
       </c>
       <c r="C183" s="4" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D183" s="4" t="s">
         <v>379</v>
       </c>
       <c r="E183" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F183" s="4" t="s">
         <v>3</v>
@@ -10633,10 +10639,10 @@
         <v>0</v>
       </c>
       <c r="K183" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="L183" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="184">
@@ -10647,13 +10653,13 @@
         <v>380</v>
       </c>
       <c r="C184" s="4" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D184" s="4" t="s">
         <v>381</v>
       </c>
       <c r="E184" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F184" s="4" t="s">
         <v>3</v>
@@ -10671,10 +10677,10 @@
         <v>0</v>
       </c>
       <c r="K184" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="L184" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="185">
@@ -10685,13 +10691,13 @@
         <v>382</v>
       </c>
       <c r="C185" s="4" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D185" s="4" t="s">
         <v>383</v>
       </c>
       <c r="E185" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F185" s="4" t="s">
         <v>3</v>
@@ -10709,10 +10715,10 @@
         <v>0</v>
       </c>
       <c r="K185" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="L185" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="186">
@@ -10723,13 +10729,13 @@
         <v>384</v>
       </c>
       <c r="C186" s="4" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D186" s="4" t="s">
         <v>385</v>
       </c>
       <c r="E186" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F186" s="4" t="s">
         <v>3</v>
@@ -10747,10 +10753,10 @@
         <v>0</v>
       </c>
       <c r="K186" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="L186" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="187">
@@ -10761,13 +10767,13 @@
         <v>386</v>
       </c>
       <c r="C187" s="4" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D187" s="4" t="s">
         <v>387</v>
       </c>
       <c r="E187" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F187" s="4" t="s">
         <v>3</v>
@@ -10785,10 +10791,10 @@
         <v>0</v>
       </c>
       <c r="K187" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="L187" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="188">
@@ -10799,13 +10805,13 @@
         <v>388</v>
       </c>
       <c r="C188" s="4" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D188" s="4" t="s">
         <v>389</v>
       </c>
       <c r="E188" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F188" s="4" t="s">
         <v>3</v>
@@ -10823,10 +10829,10 @@
         <v>0</v>
       </c>
       <c r="K188" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="L188" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="189">
@@ -10837,13 +10843,13 @@
         <v>390</v>
       </c>
       <c r="C189" s="4" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D189" s="4" t="s">
         <v>391</v>
       </c>
       <c r="E189" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F189" s="4" t="s">
         <v>3</v>
@@ -10861,10 +10867,10 @@
         <v>0</v>
       </c>
       <c r="K189" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="L189" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="190">
@@ -10875,13 +10881,13 @@
         <v>392</v>
       </c>
       <c r="C190" s="4" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D190" s="4" t="s">
         <v>393</v>
       </c>
       <c r="E190" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F190" s="4" t="s">
         <v>3</v>
@@ -10899,10 +10905,10 @@
         <v>0</v>
       </c>
       <c r="K190" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="L190" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="191">
@@ -10919,7 +10925,7 @@
         <v>396</v>
       </c>
       <c r="E191" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F191" s="4" t="s">
         <v>3</v>
@@ -10937,10 +10943,10 @@
         <v>0</v>
       </c>
       <c r="K191" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="L191" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="192">
@@ -10957,7 +10963,7 @@
         <v>398</v>
       </c>
       <c r="E192" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F192" s="4" t="s">
         <v>3</v>
@@ -10975,10 +10981,10 @@
         <v>0</v>
       </c>
       <c r="K192" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="L192" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="193">
@@ -10995,7 +11001,7 @@
         <v>400</v>
       </c>
       <c r="E193" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F193" s="4" t="s">
         <v>3</v>
@@ -11013,10 +11019,10 @@
         <v>0</v>
       </c>
       <c r="K193" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="L193" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="194">
@@ -11033,7 +11039,7 @@
         <v>402</v>
       </c>
       <c r="E194" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F194" s="4" t="s">
         <v>3</v>
@@ -11051,10 +11057,10 @@
         <v>0</v>
       </c>
       <c r="K194" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="L194" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="195">
@@ -11071,7 +11077,7 @@
         <v>404</v>
       </c>
       <c r="E195" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F195" s="4" t="s">
         <v>3</v>
@@ -11089,10 +11095,10 @@
         <v>0</v>
       </c>
       <c r="K195" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="L195" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="196">
@@ -11109,7 +11115,7 @@
         <v>406</v>
       </c>
       <c r="E196" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F196" s="4" t="s">
         <v>3</v>
@@ -11127,10 +11133,10 @@
         <v>0</v>
       </c>
       <c r="K196" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="L196" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="197">
@@ -11147,7 +11153,7 @@
         <v>408</v>
       </c>
       <c r="E197" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F197" s="4" t="s">
         <v>3</v>
@@ -11165,10 +11171,10 @@
         <v>0</v>
       </c>
       <c r="K197" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="L197" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="198">
@@ -11185,7 +11191,7 @@
         <v>410</v>
       </c>
       <c r="E198" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F198" s="4" t="s">
         <v>3</v>
@@ -11203,10 +11209,10 @@
         <v>0</v>
       </c>
       <c r="K198" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="L198" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="199">
@@ -11223,7 +11229,7 @@
         <v>412</v>
       </c>
       <c r="E199" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F199" s="4" t="s">
         <v>3</v>
@@ -11241,10 +11247,10 @@
         <v>0</v>
       </c>
       <c r="K199" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="L199" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="200">
@@ -11261,7 +11267,7 @@
         <v>414</v>
       </c>
       <c r="E200" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F200" s="4" t="s">
         <v>3</v>
@@ -11279,10 +11285,10 @@
         <v>0</v>
       </c>
       <c r="K200" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="L200" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="201">
@@ -11299,7 +11305,7 @@
         <v>416</v>
       </c>
       <c r="E201" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F201" s="4" t="s">
         <v>3</v>
@@ -11317,10 +11323,10 @@
         <v>0</v>
       </c>
       <c r="K201" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="L201" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="202">
@@ -11337,7 +11343,7 @@
         <v>418</v>
       </c>
       <c r="E202" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F202" s="4" t="s">
         <v>3</v>
@@ -11355,10 +11361,10 @@
         <v>0</v>
       </c>
       <c r="K202" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="L202" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="203">
@@ -11375,7 +11381,7 @@
         <v>420</v>
       </c>
       <c r="E203" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F203" s="4" t="s">
         <v>3</v>
@@ -11393,10 +11399,10 @@
         <v>0</v>
       </c>
       <c r="K203" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="L203" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="204">
@@ -11413,7 +11419,7 @@
         <v>422</v>
       </c>
       <c r="E204" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F204" s="4" t="s">
         <v>3</v>
@@ -11431,10 +11437,10 @@
         <v>0</v>
       </c>
       <c r="K204" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="L204" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="205">
@@ -11451,7 +11457,7 @@
         <v>424</v>
       </c>
       <c r="E205" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F205" s="4" t="s">
         <v>3</v>
@@ -11469,10 +11475,10 @@
         <v>0</v>
       </c>
       <c r="K205" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="L205" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="206">
@@ -11489,7 +11495,7 @@
         <v>426</v>
       </c>
       <c r="E206" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F206" s="4" t="s">
         <v>3</v>
@@ -11507,10 +11513,10 @@
         <v>0</v>
       </c>
       <c r="K206" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="L206" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="207">
@@ -11527,7 +11533,7 @@
         <v>428</v>
       </c>
       <c r="E207" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F207" s="4" t="s">
         <v>3</v>
@@ -11545,10 +11551,10 @@
         <v>0</v>
       </c>
       <c r="K207" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="L207" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="208">
@@ -11565,7 +11571,7 @@
         <v>430</v>
       </c>
       <c r="E208" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F208" s="4" t="s">
         <v>3</v>
@@ -11583,10 +11589,10 @@
         <v>0</v>
       </c>
       <c r="K208" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="L208" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="209">
@@ -11603,7 +11609,7 @@
         <v>432</v>
       </c>
       <c r="E209" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F209" s="4" t="s">
         <v>3</v>
@@ -11621,10 +11627,10 @@
         <v>0</v>
       </c>
       <c r="K209" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="L209" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="210">
@@ -11641,7 +11647,7 @@
         <v>434</v>
       </c>
       <c r="E210" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F210" s="4" t="s">
         <v>3</v>
@@ -11659,10 +11665,10 @@
         <v>0</v>
       </c>
       <c r="K210" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="L210" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="211">
@@ -11679,7 +11685,7 @@
         <v>436</v>
       </c>
       <c r="E211" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F211" s="4" t="s">
         <v>3</v>
@@ -11697,10 +11703,10 @@
         <v>0</v>
       </c>
       <c r="K211" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="L211" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="212">
@@ -11717,7 +11723,7 @@
         <v>438</v>
       </c>
       <c r="E212" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F212" s="4" t="s">
         <v>3</v>
@@ -11735,10 +11741,10 @@
         <v>0</v>
       </c>
       <c r="K212" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="L212" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="213">
@@ -11755,7 +11761,7 @@
         <v>440</v>
       </c>
       <c r="E213" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F213" s="4" t="s">
         <v>3</v>
@@ -11773,10 +11779,10 @@
         <v>0</v>
       </c>
       <c r="K213" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="L213" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="214">
@@ -11793,7 +11799,7 @@
         <v>442</v>
       </c>
       <c r="E214" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F214" s="4" t="s">
         <v>3</v>
@@ -11811,10 +11817,10 @@
         <v>0</v>
       </c>
       <c r="K214" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="L214" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="215">
@@ -11831,7 +11837,7 @@
         <v>444</v>
       </c>
       <c r="E215" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F215" s="4" t="s">
         <v>3</v>
@@ -11849,10 +11855,10 @@
         <v>0</v>
       </c>
       <c r="K215" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="L215" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="216">
@@ -11869,7 +11875,7 @@
         <v>446</v>
       </c>
       <c r="E216" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F216" s="4" t="s">
         <v>3</v>
@@ -11887,10 +11893,10 @@
         <v>0</v>
       </c>
       <c r="K216" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="L216" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="217">
@@ -11907,7 +11913,7 @@
         <v>448</v>
       </c>
       <c r="E217" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F217" s="4" t="s">
         <v>3</v>
@@ -11925,10 +11931,10 @@
         <v>0</v>
       </c>
       <c r="K217" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="L217" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="218">
@@ -11945,7 +11951,7 @@
         <v>450</v>
       </c>
       <c r="E218" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F218" s="4" t="s">
         <v>3</v>
@@ -11963,10 +11969,10 @@
         <v>0</v>
       </c>
       <c r="K218" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="L218" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="219">
@@ -11983,7 +11989,7 @@
         <v>452</v>
       </c>
       <c r="E219" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F219" s="4" t="s">
         <v>3</v>
@@ -12001,10 +12007,10 @@
         <v>0</v>
       </c>
       <c r="K219" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="L219" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="220">
@@ -12021,7 +12027,7 @@
         <v>454</v>
       </c>
       <c r="E220" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F220" s="4" t="s">
         <v>3</v>
@@ -12039,10 +12045,10 @@
         <v>0</v>
       </c>
       <c r="K220" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="L220" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="221">
@@ -12059,7 +12065,7 @@
         <v>456</v>
       </c>
       <c r="E221" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F221" s="4" t="s">
         <v>3</v>
@@ -12077,10 +12083,10 @@
         <v>0</v>
       </c>
       <c r="K221" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="L221" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="222">
@@ -12097,7 +12103,7 @@
         <v>458</v>
       </c>
       <c r="E222" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F222" s="4" t="s">
         <v>3</v>
@@ -12115,10 +12121,10 @@
         <v>0</v>
       </c>
       <c r="K222" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="L222" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="223">
@@ -12135,7 +12141,7 @@
         <v>460</v>
       </c>
       <c r="E223" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F223" s="4" t="s">
         <v>3</v>
@@ -12153,10 +12159,10 @@
         <v>0</v>
       </c>
       <c r="K223" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="L223" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="224">
@@ -12173,7 +12179,7 @@
         <v>462</v>
       </c>
       <c r="E224" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F224" s="4" t="s">
         <v>3</v>
@@ -12191,10 +12197,10 @@
         <v>0</v>
       </c>
       <c r="K224" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="L224" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="225">
@@ -12211,7 +12217,7 @@
         <v>464</v>
       </c>
       <c r="E225" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F225" s="4" t="s">
         <v>3</v>
@@ -12229,10 +12235,10 @@
         <v>0</v>
       </c>
       <c r="K225" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="L225" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="226">
@@ -12249,7 +12255,7 @@
         <v>466</v>
       </c>
       <c r="E226" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F226" s="4" t="s">
         <v>3</v>
@@ -12267,10 +12273,10 @@
         <v>0</v>
       </c>
       <c r="K226" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="L226" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="227">
@@ -12287,7 +12293,7 @@
         <v>468</v>
       </c>
       <c r="E227" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F227" s="3" t="s">
         <v>3</v>
@@ -12299,13 +12305,13 @@
         <v>11</v>
       </c>
       <c r="I227" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="J227" s="3">
         <v>9223372036</v>
       </c>
       <c r="K227" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="L227" s="3" t="s">
         <v>469</v>
@@ -12325,7 +12331,7 @@
         <v>471</v>
       </c>
       <c r="E228" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F228" s="3" t="s">
         <v>3</v>
@@ -12337,16 +12343,16 @@
         <v>11</v>
       </c>
       <c r="I228" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="J228" s="3">
         <v>9223372036</v>
       </c>
       <c r="K228" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="L228" s="3" t="s">
-        <v>26</v>
+        <v>289</v>
       </c>
     </row>
     <row r="229">
@@ -12363,7 +12369,7 @@
         <v>473</v>
       </c>
       <c r="E229" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F229" s="3" t="s">
         <v>3</v>
@@ -12375,16 +12381,16 @@
         <v>11</v>
       </c>
       <c r="I229" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="J229" s="3">
         <v>9223372036</v>
       </c>
       <c r="K229" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="L229" s="3" t="s">
-        <v>26</v>
+        <v>289</v>
       </c>
     </row>
     <row r="230">
@@ -12401,7 +12407,7 @@
         <v>475</v>
       </c>
       <c r="E230" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F230" s="3" t="s">
         <v>3</v>
@@ -12413,16 +12419,16 @@
         <v>11</v>
       </c>
       <c r="I230" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="J230" s="3">
         <v>9223372036</v>
       </c>
       <c r="K230" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="L230" s="3" t="s">
-        <v>26</v>
+        <v>289</v>
       </c>
     </row>
     <row r="231">
@@ -12439,7 +12445,7 @@
         <v>477</v>
       </c>
       <c r="E231" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F231" s="4" t="s">
         <v>3</v>
@@ -12457,10 +12463,10 @@
         <v>0</v>
       </c>
       <c r="K231" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="L231" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="232">
@@ -12477,7 +12483,7 @@
         <v>479</v>
       </c>
       <c r="E232" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F232" s="4" t="s">
         <v>3</v>
@@ -12495,10 +12501,10 @@
         <v>0</v>
       </c>
       <c r="K232" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="L232" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="233">
@@ -12515,7 +12521,7 @@
         <v>481</v>
       </c>
       <c r="E233" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F233" s="3" t="s">
         <v>3</v>
@@ -12527,16 +12533,16 @@
         <v>11</v>
       </c>
       <c r="I233" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="J233" s="3">
         <v>9223372036</v>
       </c>
       <c r="K233" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="L233" s="3" t="s">
-        <v>26</v>
+        <v>289</v>
       </c>
     </row>
     <row r="234">
@@ -12553,7 +12559,7 @@
         <v>483</v>
       </c>
       <c r="E234" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F234" s="3" t="s">
         <v>3</v>
@@ -12565,30 +12571,68 @@
         <v>11</v>
       </c>
       <c r="I234" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="J234" s="3">
         <v>9223372036</v>
       </c>
       <c r="K234" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="L234" s="3" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="236">
-      <c r="A236" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" s="4">
+        <v>218</v>
+      </c>
+      <c r="B235" s="4" t="s">
         <v>484</v>
       </c>
-      <c r="B236" t="s">
+      <c r="C235" s="4" t="s">
+        <v>395</v>
+      </c>
+      <c r="D235" s="4" t="s">
         <v>485</v>
       </c>
-      <c r="D236" t="s">
+      <c r="E235" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F235" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G235" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H235" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I235" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J235" s="4">
+        <v>0</v>
+      </c>
+      <c r="K235" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L235" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="s">
         <v>486</v>
       </c>
-      <c r="E236">
-        <v>217</v>
+      <c r="B237" t="s">
+        <v>487</v>
+      </c>
+      <c r="D237" t="s">
+        <v>488</v>
+      </c>
+      <c r="E237">
+        <v>218</v>
       </c>
     </row>
   </sheetData>

--- a/report-2026-06-04.xlsx
+++ b/report-2026-06-04.xlsx
@@ -16,12 +16,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="489" uniqueCount="489">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="495" uniqueCount="495">
   <si>
     <t>PunMonitor Leader Election — Current State</t>
   </si>
   <si>
-    <t>Generated 2026-06-04T19:18:43+05:30</t>
+    <t>Generated 2026-06-04T19:26:05+05:30</t>
   </si>
   <si>
     <t>Election method</t>
@@ -72,7 +72,7 @@
     <t>Leader last update</t>
   </si>
   <si>
-    <t>2026-06-04T19:16:42+05:30 (2m0s ago)</t>
+    <t>2026-06-04T19:24:05+05:30 (2m0s ago)</t>
   </si>
   <si>
     <t>Leader stale?</t>
@@ -1477,10 +1477,28 @@
     <t>19:16:42.974</t>
   </si>
   <si>
+    <t>2026-06-04T19:19:14.5624078+05:30</t>
+  </si>
+  <si>
+    <t>19:19:14.562</t>
+  </si>
+  <si>
+    <t>2026-06-04T19:21:44.7288645+05:30</t>
+  </si>
+  <si>
+    <t>19:21:44.728</t>
+  </si>
+  <si>
+    <t>2026-06-04T19:24:05.3164993+05:30</t>
+  </si>
+  <si>
+    <t>19:24:05.316</t>
+  </si>
+  <si>
     <t>Generated</t>
   </si>
   <si>
-    <t>2026-06-04T19:18:43+05:30</t>
+    <t>2026-06-04T19:26:05+05:30</t>
   </si>
   <si>
     <t>Total events</t>
@@ -2035,7 +2053,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>10.0.44</t>
+          <t>10.0.45</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -2075,12 +2093,12 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>0h 2m 19s</t>
+          <t>0h 2m 17s</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>2026-06-04 19:16:23</t>
+          <t>2026-06-04 19:23:48</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
@@ -2090,12 +2108,12 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2026-06-04 19:16:23</t>
+          <t>2026-06-04 19:23:48</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>10h 47m 0s</t>
+          <t>10h 49m 10s</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -2105,7 +2123,7 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>19:18:43</t>
+          <t>19:26:05</t>
         </is>
       </c>
     </row>
@@ -2142,7 +2160,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>10.0.44</t>
+          <t>10.0.45</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -2162,17 +2180,17 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>108.0</t>
+          <t>147.0</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>111812.1</t>
+          <t>183988.9</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2104</t>
+          <t>1247</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -2182,7 +2200,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>17</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -2197,12 +2215,12 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-06-04 19:16:23</t>
+          <t>2026-06-04 19:23:48</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>10h 47m 0s</t>
+          <t>10h 49m 0s</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -2212,7 +2230,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>19:18:43</t>
+          <t>19:26:05</t>
         </is>
       </c>
     </row>
@@ -2331,7 +2349,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-06-04T19:16:42.9746537+05:30</t>
+          <t>2026-06-04T19:24:05.3164993+05:30</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -2341,7 +2359,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>19:16:42.974</t>
+          <t>19:24:05.316</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -12621,18 +12639,132 @@
         <v>43</v>
       </c>
     </row>
+    <row r="236">
+      <c r="A236" s="4">
+        <v>219</v>
+      </c>
+      <c r="B236" s="4" t="s">
+        <v>486</v>
+      </c>
+      <c r="C236" s="4" t="s">
+        <v>395</v>
+      </c>
+      <c r="D236" s="4" t="s">
+        <v>487</v>
+      </c>
+      <c r="E236" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F236" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G236" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H236" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I236" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J236" s="4">
+        <v>0</v>
+      </c>
+      <c r="K236" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L236" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
     <row r="237">
-      <c r="A237" t="s">
-        <v>486</v>
-      </c>
-      <c r="B237" t="s">
-        <v>487</v>
-      </c>
-      <c r="D237" t="s">
+      <c r="A237" s="4">
+        <v>220</v>
+      </c>
+      <c r="B237" s="4" t="s">
         <v>488</v>
       </c>
-      <c r="E237">
-        <v>218</v>
+      <c r="C237" s="4" t="s">
+        <v>395</v>
+      </c>
+      <c r="D237" s="4" t="s">
+        <v>489</v>
+      </c>
+      <c r="E237" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F237" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G237" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H237" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I237" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J237" s="4">
+        <v>0</v>
+      </c>
+      <c r="K237" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L237" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" s="4">
+        <v>221</v>
+      </c>
+      <c r="B238" s="4" t="s">
+        <v>490</v>
+      </c>
+      <c r="C238" s="4" t="s">
+        <v>395</v>
+      </c>
+      <c r="D238" s="4" t="s">
+        <v>491</v>
+      </c>
+      <c r="E238" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F238" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G238" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H238" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I238" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J238" s="4">
+        <v>0</v>
+      </c>
+      <c r="K238" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L238" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="s">
+        <v>492</v>
+      </c>
+      <c r="B240" t="s">
+        <v>493</v>
+      </c>
+      <c r="D240" t="s">
+        <v>494</v>
+      </c>
+      <c r="E240">
+        <v>221</v>
       </c>
     </row>
   </sheetData>

--- a/report-2026-06-04.xlsx
+++ b/report-2026-06-04.xlsx
@@ -16,12 +16,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="495" uniqueCount="495">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="499" uniqueCount="499">
   <si>
     <t>PunMonitor Leader Election — Current State</t>
   </si>
   <si>
-    <t>Generated 2026-06-04T19:26:05+05:30</t>
+    <t>Generated 2026-06-04T19:31:17+05:30</t>
   </si>
   <si>
     <t>Election method</t>
@@ -72,7 +72,7 @@
     <t>Leader last update</t>
   </si>
   <si>
-    <t>2026-06-04T19:24:05+05:30 (2m0s ago)</t>
+    <t>2026-06-04T19:29:17+05:30 (2m0s ago)</t>
   </si>
   <si>
     <t>Leader stale?</t>
@@ -87,7 +87,7 @@
     <t>Check count</t>
   </si>
   <si>
-    <t>1</t>
+    <t>4</t>
   </si>
   <si>
     <t>Last error</t>
@@ -1495,10 +1495,22 @@
     <t>19:24:05.316</t>
   </si>
   <si>
+    <t>2026-06-04T19:26:36.8608856+05:30</t>
+  </si>
+  <si>
+    <t>19:26:36.860</t>
+  </si>
+  <si>
+    <t>2026-06-04T19:29:06.8637433+05:30</t>
+  </si>
+  <si>
+    <t>19:29:06.863</t>
+  </si>
+  <si>
     <t>Generated</t>
   </si>
   <si>
-    <t>2026-06-04T19:26:05+05:30</t>
+    <t>2026-06-04T19:31:17+05:30</t>
   </si>
   <si>
     <t>Total events</t>
@@ -2093,7 +2105,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>0h 2m 17s</t>
+          <t>0h 7m 29s</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -2113,7 +2125,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>10h 49m 10s</t>
+          <t>10h 49m 25s</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -2123,44 +2135,44 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>19:26:05</t>
+          <t>19:31:17</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>PuneetU-EB6LMJD-cf4a9ce5</t>
+          <t>Puneets-MacBook-Air.local-esHl</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>PuneetU-EB6LMJD</t>
+          <t>Puneets-MacBook-Air.local</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>192.168.0.128</t>
+          <t>192.168.0.156</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>103.117.15.39</t>
+          <t>43.247.40.101</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>windows</t>
+          <t>darwin</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>amd64</t>
+          <t>arm64</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>10.0.45</t>
+          <t>10.0.0</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -2170,37 +2182,37 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>self</t>
+          <t>websocket</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>good</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>147.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>183988.9</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>1247</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>19011</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -2210,17 +2222,17 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>Jun 4 07:08 PM</t>
+          <t>—</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-06-04 19:23:48</t>
+          <t>—</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>10h 49m 0s</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -2230,217 +2242,324 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>19:26:05</t>
+          <t>19:31:17</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>── LATEST GITHUB ELECTION EVENT ──</t>
+          <t>PuneetU-EB6LMJD-cf4a9ce5</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t/>
+          <t>PuneetU-EB6LMJD</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t/>
+          <t>192.168.0.128</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t/>
+          <t>103.117.15.39</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t/>
+          <t>windows</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t/>
+          <t>amd64</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t/>
+          <t>10.0.45</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t/>
+          <t>agent</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t/>
+          <t>self</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t/>
+          <t>good</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t/>
+          <t>146.0</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t/>
+          <t>114068.7</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t/>
+          <t>5595</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t/>
+          <t>0.5</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t/>
+          <t>329</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t/>
+          <t>—</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t/>
+          <t>Jun 4 07:08 PM</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-06-04 19:23:48</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t/>
+          <t>10h 49m 25s</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t/>
+          <t>19:31:17</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>── LATEST GITHUB ELECTION EVENT ──</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
           <t>[renewed]</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>2026-06-04T19:24:05.3164993+05:30</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2026-06-04T19:29:06.8637433+05:30</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
         <is>
           <t>2026-06-04</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>19:24:05.316</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>19:29:06.863</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
         <is>
           <t>renewed</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>github</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>PuneetU-EB6LMJD-cf4a9ce5</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t>PuneetU-EB6LMJD</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="I6" t="inlineStr">
         <is>
           <t>PuneetU-EB6LMJD-cf4a9ce5</t>
         </is>
       </c>
-      <c r="J5">
-        <v>0</v>
-      </c>
-      <c r="K5" t="inlineStr">
+      <c r="J6">
+        <v>0</v>
+      </c>
+      <c r="K6" t="inlineStr">
         <is>
           <t>renewed</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="N6" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="O5" t="inlineStr">
+      <c r="O6" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="Q5" t="inlineStr">
+      <c r="Q6" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="R5" t="inlineStr">
+      <c r="R6" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="T5" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="U5" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -12753,18 +12872,94 @@
         <v>43</v>
       </c>
     </row>
+    <row r="239">
+      <c r="A239" s="4">
+        <v>222</v>
+      </c>
+      <c r="B239" s="4" t="s">
+        <v>492</v>
+      </c>
+      <c r="C239" s="4" t="s">
+        <v>395</v>
+      </c>
+      <c r="D239" s="4" t="s">
+        <v>493</v>
+      </c>
+      <c r="E239" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F239" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G239" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H239" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I239" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J239" s="4">
+        <v>0</v>
+      </c>
+      <c r="K239" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L239" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
     <row r="240">
-      <c r="A240" t="s">
-        <v>492</v>
-      </c>
-      <c r="B240" t="s">
-        <v>493</v>
-      </c>
-      <c r="D240" t="s">
+      <c r="A240" s="4">
+        <v>223</v>
+      </c>
+      <c r="B240" s="4" t="s">
         <v>494</v>
       </c>
-      <c r="E240">
-        <v>221</v>
+      <c r="C240" s="4" t="s">
+        <v>395</v>
+      </c>
+      <c r="D240" s="4" t="s">
+        <v>495</v>
+      </c>
+      <c r="E240" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F240" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G240" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H240" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I240" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J240" s="4">
+        <v>0</v>
+      </c>
+      <c r="K240" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L240" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="s">
+        <v>496</v>
+      </c>
+      <c r="B242" t="s">
+        <v>497</v>
+      </c>
+      <c r="D242" t="s">
+        <v>498</v>
+      </c>
+      <c r="E242">
+        <v>223</v>
       </c>
     </row>
   </sheetData>

--- a/report-2026-06-04.xlsx
+++ b/report-2026-06-04.xlsx
@@ -16,12 +16,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="499" uniqueCount="499">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="503" uniqueCount="503">
   <si>
     <t>PunMonitor Leader Election — Current State</t>
   </si>
   <si>
-    <t>Generated 2026-06-04T19:31:17+05:30</t>
+    <t>Generated 2026-06-04T19:36:17+05:30</t>
   </si>
   <si>
     <t>Election method</t>
@@ -72,7 +72,7 @@
     <t>Leader last update</t>
   </si>
   <si>
-    <t>2026-06-04T19:29:17+05:30 (2m0s ago)</t>
+    <t>2026-06-04T19:34:29+05:30 (1m47s ago)</t>
   </si>
   <si>
     <t>Leader stale?</t>
@@ -87,7 +87,7 @@
     <t>Check count</t>
   </si>
   <si>
-    <t>4</t>
+    <t>9</t>
   </si>
   <si>
     <t>Last error</t>
@@ -1507,10 +1507,22 @@
     <t>19:29:06.863</t>
   </si>
   <si>
+    <t>2026-06-04T19:31:36.7190916+05:30</t>
+  </si>
+  <si>
+    <t>19:31:36.719</t>
+  </si>
+  <si>
+    <t>2026-06-04T19:34:06.8059877+05:30</t>
+  </si>
+  <si>
+    <t>19:34:06.805</t>
+  </si>
+  <si>
     <t>Generated</t>
   </si>
   <si>
-    <t>2026-06-04T19:31:17+05:30</t>
+    <t>2026-06-04T19:36:17+05:30</t>
   </si>
   <si>
     <t>Total events</t>
@@ -2105,7 +2117,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>0h 7m 29s</t>
+          <t>0h 12m 29s</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -2125,7 +2137,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>10h 49m 25s</t>
+          <t>10h 49m 35s</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -2135,7 +2147,7 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>19:31:17</t>
+          <t>19:36:17</t>
         </is>
       </c>
     </row>
@@ -2187,27 +2199,27 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>degraded</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>491.0</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>15150.5</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>6</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -2242,7 +2254,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>19:31:17</t>
+          <t>19:36:17</t>
         </is>
       </c>
     </row>
@@ -2299,17 +2311,17 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>146.0</t>
+          <t>494.0</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>114068.7</t>
+          <t>131963.1</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>5595</t>
+          <t>9195</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -2319,7 +2331,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>329</t>
+          <t>642</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -2339,7 +2351,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>10h 49m 25s</t>
+          <t>10h 49m 35s</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -2349,7 +2361,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>19:31:17</t>
+          <t>19:36:17</t>
         </is>
       </c>
     </row>
@@ -2468,7 +2480,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-06-04T19:29:06.8637433+05:30</t>
+          <t>2026-06-04T19:34:06.8059877+05:30</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -2478,7 +2490,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>19:29:06.863</t>
+          <t>19:34:06.805</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -12948,18 +12960,94 @@
         <v>43</v>
       </c>
     </row>
+    <row r="241">
+      <c r="A241" s="4">
+        <v>224</v>
+      </c>
+      <c r="B241" s="4" t="s">
+        <v>496</v>
+      </c>
+      <c r="C241" s="4" t="s">
+        <v>395</v>
+      </c>
+      <c r="D241" s="4" t="s">
+        <v>497</v>
+      </c>
+      <c r="E241" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F241" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G241" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H241" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I241" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J241" s="4">
+        <v>0</v>
+      </c>
+      <c r="K241" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L241" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
     <row r="242">
-      <c r="A242" t="s">
-        <v>496</v>
-      </c>
-      <c r="B242" t="s">
-        <v>497</v>
-      </c>
-      <c r="D242" t="s">
+      <c r="A242" s="4">
+        <v>225</v>
+      </c>
+      <c r="B242" s="4" t="s">
         <v>498</v>
       </c>
-      <c r="E242">
-        <v>223</v>
+      <c r="C242" s="4" t="s">
+        <v>395</v>
+      </c>
+      <c r="D242" s="4" t="s">
+        <v>499</v>
+      </c>
+      <c r="E242" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F242" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G242" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H242" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I242" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J242" s="4">
+        <v>0</v>
+      </c>
+      <c r="K242" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L242" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="s">
+        <v>500</v>
+      </c>
+      <c r="B244" t="s">
+        <v>501</v>
+      </c>
+      <c r="D244" t="s">
+        <v>502</v>
+      </c>
+      <c r="E244">
+        <v>225</v>
       </c>
     </row>
   </sheetData>

--- a/report-2026-06-04.xlsx
+++ b/report-2026-06-04.xlsx
@@ -21,7 +21,7 @@
     <t>PunMonitor Leader Election — Current State</t>
   </si>
   <si>
-    <t>Generated 2026-06-04T19:36:17+05:30</t>
+    <t>Generated 2026-06-04T19:36:30+05:30</t>
   </si>
   <si>
     <t>Election method</t>
@@ -72,7 +72,7 @@
     <t>Leader last update</t>
   </si>
   <si>
-    <t>2026-06-04T19:34:29+05:30 (1m47s ago)</t>
+    <t>2026-06-04T19:34:29+05:30 (2m0s ago)</t>
   </si>
   <si>
     <t>Leader stale?</t>
@@ -1522,7 +1522,7 @@
     <t>Generated</t>
   </si>
   <si>
-    <t>2026-06-04T19:36:17+05:30</t>
+    <t>2026-06-04T19:36:30+05:30</t>
   </si>
   <si>
     <t>Total events</t>
@@ -2117,7 +2117,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>0h 12m 29s</t>
+          <t>0h 12m 41s</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -2147,7 +2147,7 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>19:36:17</t>
+          <t>19:36:30</t>
         </is>
       </c>
     </row>
@@ -2254,7 +2254,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>19:36:17</t>
+          <t>19:36:30</t>
         </is>
       </c>
     </row>
@@ -2311,17 +2311,17 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>494.0</t>
+          <t>470.0</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>131963.1</t>
+          <t>111553.5</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>9195</t>
+          <t>9330</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -2361,7 +2361,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>19:36:17</t>
+          <t>19:36:30</t>
         </is>
       </c>
     </row>

--- a/report-2026-06-04.xlsx
+++ b/report-2026-06-04.xlsx
@@ -16,12 +16,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="503" uniqueCount="503">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="507" uniqueCount="507">
   <si>
     <t>PunMonitor Leader Election — Current State</t>
   </si>
   <si>
-    <t>Generated 2026-06-04T19:36:30+05:30</t>
+    <t>Generated 2026-06-04T19:41:17+05:30</t>
   </si>
   <si>
     <t>Election method</t>
@@ -72,7 +72,7 @@
     <t>Leader last update</t>
   </si>
   <si>
-    <t>2026-06-04T19:34:29+05:30 (2m0s ago)</t>
+    <t>2026-06-04T19:39:52+05:30 (1m25s ago)</t>
   </si>
   <si>
     <t>Leader stale?</t>
@@ -87,7 +87,7 @@
     <t>Check count</t>
   </si>
   <si>
-    <t>9</t>
+    <t>15</t>
   </si>
   <si>
     <t>Last error</t>
@@ -1519,10 +1519,22 @@
     <t>19:34:06.805</t>
   </si>
   <si>
+    <t>2026-06-04T19:36:36.6396852+05:30</t>
+  </si>
+  <si>
+    <t>19:36:36.639</t>
+  </si>
+  <si>
+    <t>2026-06-04T19:39:06.7587225+05:30</t>
+  </si>
+  <si>
+    <t>19:39:06.758</t>
+  </si>
+  <si>
     <t>Generated</t>
   </si>
   <si>
-    <t>2026-06-04T19:36:30+05:30</t>
+    <t>2026-06-04T19:41:17+05:30</t>
   </si>
   <si>
     <t>Total events</t>
@@ -2117,7 +2129,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>0h 12m 41s</t>
+          <t>0h 17m 29s</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -2137,7 +2149,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>10h 49m 35s</t>
+          <t>10h 50m 35s</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -2147,7 +2159,7 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>19:36:30</t>
+          <t>19:41:17</t>
         </is>
       </c>
     </row>
@@ -2254,7 +2266,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>19:36:30</t>
+          <t>19:41:17</t>
         </is>
       </c>
     </row>
@@ -2311,17 +2323,17 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>470.0</t>
+          <t>736.0</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>111553.5</t>
+          <t>154913.5</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>9330</t>
+          <t>12202</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -2331,7 +2343,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>642</t>
+          <t>964</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -2351,7 +2363,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>10h 49m 35s</t>
+          <t>10h 50m 20s</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -2361,7 +2373,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>19:36:30</t>
+          <t>19:41:17</t>
         </is>
       </c>
     </row>
@@ -2480,7 +2492,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-06-04T19:34:06.8059877+05:30</t>
+          <t>2026-06-04T19:39:06.7587225+05:30</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -2490,7 +2502,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>19:34:06.805</t>
+          <t>19:39:06.758</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -13036,18 +13048,94 @@
         <v>43</v>
       </c>
     </row>
+    <row r="243">
+      <c r="A243" s="4">
+        <v>226</v>
+      </c>
+      <c r="B243" s="4" t="s">
+        <v>500</v>
+      </c>
+      <c r="C243" s="4" t="s">
+        <v>395</v>
+      </c>
+      <c r="D243" s="4" t="s">
+        <v>501</v>
+      </c>
+      <c r="E243" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F243" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G243" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H243" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I243" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J243" s="4">
+        <v>0</v>
+      </c>
+      <c r="K243" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L243" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
     <row r="244">
-      <c r="A244" t="s">
-        <v>500</v>
-      </c>
-      <c r="B244" t="s">
-        <v>501</v>
-      </c>
-      <c r="D244" t="s">
+      <c r="A244" s="4">
+        <v>227</v>
+      </c>
+      <c r="B244" s="4" t="s">
         <v>502</v>
       </c>
-      <c r="E244">
-        <v>225</v>
+      <c r="C244" s="4" t="s">
+        <v>395</v>
+      </c>
+      <c r="D244" s="4" t="s">
+        <v>503</v>
+      </c>
+      <c r="E244" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F244" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G244" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H244" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I244" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J244" s="4">
+        <v>0</v>
+      </c>
+      <c r="K244" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L244" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="s">
+        <v>504</v>
+      </c>
+      <c r="B246" t="s">
+        <v>505</v>
+      </c>
+      <c r="D246" t="s">
+        <v>506</v>
+      </c>
+      <c r="E246">
+        <v>227</v>
       </c>
     </row>
   </sheetData>

--- a/report-2026-06-04.xlsx
+++ b/report-2026-06-04.xlsx
@@ -21,7 +21,7 @@
     <t>PunMonitor Leader Election — Current State</t>
   </si>
   <si>
-    <t>Generated 2026-06-04T19:41:17+05:30</t>
+    <t>Generated 2026-06-04T19:41:30+05:30</t>
   </si>
   <si>
     <t>Election method</t>
@@ -72,7 +72,7 @@
     <t>Leader last update</t>
   </si>
   <si>
-    <t>2026-06-04T19:39:52+05:30 (1m25s ago)</t>
+    <t>2026-06-04T19:39:52+05:30 (1m37s ago)</t>
   </si>
   <si>
     <t>Leader stale?</t>
@@ -1534,7 +1534,7 @@
     <t>Generated</t>
   </si>
   <si>
-    <t>2026-06-04T19:41:17+05:30</t>
+    <t>2026-06-04T19:41:30+05:30</t>
   </si>
   <si>
     <t>Total events</t>
@@ -2129,7 +2129,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>0h 17m 29s</t>
+          <t>0h 17m 42s</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -2149,7 +2149,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>10h 50m 35s</t>
+          <t>10h 50m 50s</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -2159,7 +2159,7 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>19:41:17</t>
+          <t>19:41:30</t>
         </is>
       </c>
     </row>
@@ -2266,7 +2266,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>19:41:17</t>
+          <t>19:41:30</t>
         </is>
       </c>
     </row>
@@ -2323,7 +2323,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>736.0</t>
+          <t>703.0</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -2333,7 +2333,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>12202</t>
+          <t>12321</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -2373,7 +2373,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>19:41:17</t>
+          <t>19:41:30</t>
         </is>
       </c>
     </row>

--- a/report-2026-06-04.xlsx
+++ b/report-2026-06-04.xlsx
@@ -21,7 +21,7 @@
     <t>PunMonitor Leader Election — Current State</t>
   </si>
   <si>
-    <t>Generated 2026-06-04T19:41:30+05:30</t>
+    <t>Generated 2026-06-04T19:41:52+05:30</t>
   </si>
   <si>
     <t>Election method</t>
@@ -72,7 +72,7 @@
     <t>Leader last update</t>
   </si>
   <si>
-    <t>2026-06-04T19:39:52+05:30 (1m37s ago)</t>
+    <t>2026-06-04T19:39:52+05:30 (2m0s ago)</t>
   </si>
   <si>
     <t>Leader stale?</t>
@@ -1534,7 +1534,7 @@
     <t>Generated</t>
   </si>
   <si>
-    <t>2026-06-04T19:41:30+05:30</t>
+    <t>2026-06-04T19:41:52+05:30</t>
   </si>
   <si>
     <t>Total events</t>
@@ -2129,7 +2129,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>0h 17m 42s</t>
+          <t>0h 18m 4s</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -2149,7 +2149,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>10h 50m 50s</t>
+          <t>10h 50m 55s</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -2159,7 +2159,7 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>19:41:30</t>
+          <t>19:41:52</t>
         </is>
       </c>
     </row>
@@ -2211,7 +2211,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>degraded</t>
+          <t>stale</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -2266,7 +2266,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>19:41:30</t>
+          <t>19:41:52</t>
         </is>
       </c>
     </row>
@@ -2323,17 +2323,17 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>703.0</t>
+          <t>660.0</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>154913.5</t>
+          <t>73533.1</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>12321</t>
+          <t>12588</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -2373,7 +2373,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>19:41:30</t>
+          <t>19:41:52</t>
         </is>
       </c>
     </row>

--- a/report-2026-06-04.xlsx
+++ b/report-2026-06-04.xlsx
@@ -16,12 +16,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="507" uniqueCount="507">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="511" uniqueCount="511">
   <si>
     <t>PunMonitor Leader Election — Current State</t>
   </si>
   <si>
-    <t>Generated 2026-06-04T19:41:52+05:30</t>
+    <t>Generated 2026-06-04T19:46:22+05:30</t>
   </si>
   <si>
     <t>Election method</t>
@@ -72,7 +72,7 @@
     <t>Leader last update</t>
   </si>
   <si>
-    <t>2026-06-04T19:39:52+05:30 (2m0s ago)</t>
+    <t>2026-06-04T19:45:14+05:30 (1m8s ago)</t>
   </si>
   <si>
     <t>Leader stale?</t>
@@ -87,7 +87,7 @@
     <t>Check count</t>
   </si>
   <si>
-    <t>15</t>
+    <t>19</t>
   </si>
   <si>
     <t>Last error</t>
@@ -1531,10 +1531,22 @@
     <t>19:39:06.758</t>
   </si>
   <si>
+    <t>2026-06-04T19:42:23.6239534+05:30</t>
+  </si>
+  <si>
+    <t>19:42:23.623</t>
+  </si>
+  <si>
+    <t>2026-06-04T19:44:22.7685031+05:30</t>
+  </si>
+  <si>
+    <t>19:44:22.768</t>
+  </si>
+  <si>
     <t>Generated</t>
   </si>
   <si>
-    <t>2026-06-04T19:41:52+05:30</t>
+    <t>2026-06-04T19:46:22+05:30</t>
   </si>
   <si>
     <t>Total events</t>
@@ -2129,7 +2141,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>0h 18m 4s</t>
+          <t>0h 22m 34s</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -2149,7 +2161,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>10h 50m 55s</t>
+          <t>10h 51m 25s</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -2159,7 +2171,7 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>19:41:52</t>
+          <t>19:46:22</t>
         </is>
       </c>
     </row>
@@ -2266,7 +2278,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>19:41:52</t>
+          <t>19:46:22</t>
         </is>
       </c>
     </row>
@@ -2323,17 +2335,17 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>660.0</t>
+          <t>1066.0</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>73533.1</t>
+          <t>124179.9</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>12588</t>
+          <t>15030</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -2343,7 +2355,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>964</t>
+          <t>1287</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -2363,7 +2375,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>10h 50m 20s</t>
+          <t>10h 51m 25s</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -2373,7 +2385,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>19:41:52</t>
+          <t>19:46:22</t>
         </is>
       </c>
     </row>
@@ -2492,7 +2504,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-06-04T19:39:06.7587225+05:30</t>
+          <t>2026-06-04T19:44:22.7685031+05:30</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -2502,7 +2514,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>19:39:06.758</t>
+          <t>19:44:22.768</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -13124,18 +13136,94 @@
         <v>43</v>
       </c>
     </row>
+    <row r="245">
+      <c r="A245" s="4">
+        <v>228</v>
+      </c>
+      <c r="B245" s="4" t="s">
+        <v>504</v>
+      </c>
+      <c r="C245" s="4" t="s">
+        <v>395</v>
+      </c>
+      <c r="D245" s="4" t="s">
+        <v>505</v>
+      </c>
+      <c r="E245" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F245" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G245" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H245" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I245" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J245" s="4">
+        <v>0</v>
+      </c>
+      <c r="K245" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L245" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
     <row r="246">
-      <c r="A246" t="s">
-        <v>504</v>
-      </c>
-      <c r="B246" t="s">
-        <v>505</v>
-      </c>
-      <c r="D246" t="s">
+      <c r="A246" s="4">
+        <v>229</v>
+      </c>
+      <c r="B246" s="4" t="s">
         <v>506</v>
       </c>
-      <c r="E246">
-        <v>227</v>
+      <c r="C246" s="4" t="s">
+        <v>395</v>
+      </c>
+      <c r="D246" s="4" t="s">
+        <v>507</v>
+      </c>
+      <c r="E246" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F246" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G246" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H246" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I246" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J246" s="4">
+        <v>0</v>
+      </c>
+      <c r="K246" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L246" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="s">
+        <v>508</v>
+      </c>
+      <c r="B248" t="s">
+        <v>509</v>
+      </c>
+      <c r="D248" t="s">
+        <v>510</v>
+      </c>
+      <c r="E248">
+        <v>229</v>
       </c>
     </row>
   </sheetData>

--- a/report-2026-06-04.xlsx
+++ b/report-2026-06-04.xlsx
@@ -21,7 +21,7 @@
     <t>PunMonitor Leader Election — Current State</t>
   </si>
   <si>
-    <t>Generated 2026-06-04T19:46:22+05:30</t>
+    <t>Generated 2026-06-04T19:46:50+05:30</t>
   </si>
   <si>
     <t>Election method</t>
@@ -72,7 +72,7 @@
     <t>Leader last update</t>
   </si>
   <si>
-    <t>2026-06-04T19:45:14+05:30 (1m8s ago)</t>
+    <t>2026-06-04T19:45:14+05:30 (1m35s ago)</t>
   </si>
   <si>
     <t>Leader stale?</t>
@@ -1546,7 +1546,7 @@
     <t>Generated</t>
   </si>
   <si>
-    <t>2026-06-04T19:46:22+05:30</t>
+    <t>2026-06-04T19:46:50+05:30</t>
   </si>
   <si>
     <t>Total events</t>
@@ -2141,7 +2141,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>0h 22m 34s</t>
+          <t>0h 23m 2s</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -2161,7 +2161,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>10h 51m 25s</t>
+          <t>10h 51m 35s</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -2171,7 +2171,7 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>19:46:22</t>
+          <t>19:46:50</t>
         </is>
       </c>
     </row>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>19:46:22</t>
+          <t>19:46:50</t>
         </is>
       </c>
     </row>
@@ -2335,17 +2335,17 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>1066.0</t>
+          <t>1200.0</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>124179.9</t>
+          <t>112104.1</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>15030</t>
+          <t>15242</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -2385,7 +2385,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>19:46:22</t>
+          <t>19:46:50</t>
         </is>
       </c>
     </row>

--- a/report-2026-06-04.xlsx
+++ b/report-2026-06-04.xlsx
@@ -21,7 +21,7 @@
     <t>PunMonitor Leader Election — Current State</t>
   </si>
   <si>
-    <t>Generated 2026-06-04T19:46:50+05:30</t>
+    <t>Generated 2026-06-04T19:47:14+05:30</t>
   </si>
   <si>
     <t>Election method</t>
@@ -72,7 +72,7 @@
     <t>Leader last update</t>
   </si>
   <si>
-    <t>2026-06-04T19:45:14+05:30 (1m35s ago)</t>
+    <t>2026-06-04T19:45:14+05:30 (2m0s ago)</t>
   </si>
   <si>
     <t>Leader stale?</t>
@@ -1546,7 +1546,7 @@
     <t>Generated</t>
   </si>
   <si>
-    <t>2026-06-04T19:46:50+05:30</t>
+    <t>2026-06-04T19:47:14+05:30</t>
   </si>
   <si>
     <t>Total events</t>
@@ -2141,7 +2141,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>0h 23m 2s</t>
+          <t>0h 23m 26s</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -2161,7 +2161,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>10h 51m 35s</t>
+          <t>10h 51m 45s</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -2171,44 +2171,44 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>19:46:50</t>
+          <t>19:47:14</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Puneets-MacBook-Air.local-esHl</t>
+          <t>PuneetU-EB6LMJD-cf4a9ce5</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Puneets-MacBook-Air.local</t>
+          <t>PuneetU-EB6LMJD</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>192.168.0.156</t>
+          <t>192.168.0.128</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>43.247.40.101</t>
+          <t>103.117.15.39</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>darwin</t>
+          <t>windows</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>arm64</t>
+          <t>amd64</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>10.0.0</t>
+          <t>10.0.45</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -2218,27 +2218,27 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>websocket</t>
+          <t>self</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>stale</t>
+          <t>good</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>491.0</t>
+          <t>1927.0</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>15150.5</t>
+          <t>129293.5</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>15466</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -2248,7 +2248,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>19011</t>
+          <t>1287</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -2258,17 +2258,17 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Jun 4 07:08 PM</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2026-06-04 19:23:48</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>10h 51m 25s</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -2278,84 +2278,84 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>19:46:50</t>
+          <t>19:47:14</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>PuneetU-EB6LMJD-cf4a9ce5</t>
+          <t>Puneets-MacBook-Air.local-esHl</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>PuneetU-EB6LMJD</t>
+          <t>Puneets-MacBook-Air.local</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>192.168.0.128</t>
+          <t>192.168.0.156</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>103.117.15.39</t>
+          <t>43.247.40.101</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>windows</t>
+          <t>darwin</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>amd64</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>10.0.45</t>
+          <t>10.0.0</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>agent</t>
+          <t>disconnected</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>self</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>good</t>
+          <t>offline</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>1200.0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>112104.1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>15242</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>1287</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -2365,17 +2365,17 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>Jun 4 07:08 PM</t>
+          <t>—</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>2026-06-04 19:23:48</t>
+          <t>—</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>10h 51m 25s</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -2385,7 +2385,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>19:46:50</t>
+          <t>19:47:14</t>
         </is>
       </c>
     </row>

--- a/report-2026-06-04.xlsx
+++ b/report-2026-06-04.xlsx
@@ -16,12 +16,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="511" uniqueCount="511">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="517" uniqueCount="517">
   <si>
     <t>PunMonitor Leader Election — Current State</t>
   </si>
   <si>
-    <t>Generated 2026-06-04T19:47:14+05:30</t>
+    <t>Generated 2026-06-04T19:51:23+05:30</t>
   </si>
   <si>
     <t>Election method</t>
@@ -72,7 +72,7 @@
     <t>Leader last update</t>
   </si>
   <si>
-    <t>2026-06-04T19:45:14+05:30 (2m0s ago)</t>
+    <t>2026-06-04T19:50:33+05:30 (50s ago)</t>
   </si>
   <si>
     <t>Leader stale?</t>
@@ -87,7 +87,7 @@
     <t>Check count</t>
   </si>
   <si>
-    <t>19</t>
+    <t>24</t>
   </si>
   <si>
     <t>Last error</t>
@@ -1543,10 +1543,28 @@
     <t>19:44:22.768</t>
   </si>
   <si>
+    <t>2026-06-04T19:47:46.3462848+05:30</t>
+  </si>
+  <si>
+    <t>19:47:46.346</t>
+  </si>
+  <si>
+    <t>2026-06-04T19:49:22.9988654+05:30</t>
+  </si>
+  <si>
+    <t>19:49:22.998</t>
+  </si>
+  <si>
+    <t>2026-06-04T19:50:33.0134877+05:30</t>
+  </si>
+  <si>
+    <t>19:50:33.013</t>
+  </si>
+  <si>
     <t>Generated</t>
   </si>
   <si>
-    <t>2026-06-04T19:47:14+05:30</t>
+    <t>2026-06-04T19:51:23+05:30</t>
   </si>
   <si>
     <t>Total events</t>
@@ -2141,7 +2159,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>0h 23m 26s</t>
+          <t>0h 27m 35s</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -2161,7 +2179,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>10h 51m 45s</t>
+          <t>10h 52m 35s</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -2171,44 +2189,44 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>19:47:14</t>
+          <t>19:51:23</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>PuneetU-EB6LMJD-cf4a9ce5</t>
+          <t>Puneets-MacBook-Air.local-esHl</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>PuneetU-EB6LMJD</t>
+          <t>Puneets-MacBook-Air.local</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>192.168.0.128</t>
+          <t>192.168.0.156</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>103.117.15.39</t>
+          <t>43.247.40.101</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>windows</t>
+          <t>darwin</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>amd64</t>
+          <t>arm64</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>10.0.45</t>
+          <t>10.0.0</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -2218,27 +2236,27 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>self</t>
+          <t>websocket</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>good</t>
+          <t>degraded</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>1927.0</t>
+          <t>1304.0</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>129293.5</t>
+          <t>15150.5</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>15466</t>
+          <t>11</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -2248,27 +2266,27 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>1287</t>
+          <t>19065</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2026-06-03 10:39:05</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>Jun 4 07:08 PM</t>
+          <t>Jun 2 05:41 PM</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-06-04 19:23:48</t>
+          <t>2026-06-03 10:39:05</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>10h 51m 25s</t>
+          <t>13h 47m 45s</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -2278,104 +2296,104 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>19:47:14</t>
+          <t>19:51:23</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Puneets-MacBook-Air.local-esHl</t>
+          <t>PuneetU-EB6LMJD-cf4a9ce5</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Puneets-MacBook-Air.local</t>
+          <t>PuneetU-EB6LMJD</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>192.168.0.156</t>
+          <t>192.168.0.128</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>43.247.40.101</t>
+          <t>103.117.15.39</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>darwin</t>
+          <t>windows</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
+          <t>amd64</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>10.0.45</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>agent</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>self</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>1317.0</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>107420.3</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>17518</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>1605</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>10.0.0</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>disconnected</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>offline</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Jun 4 07:08 PM</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2026-06-04 19:23:48</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>10h 52m 35s</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -2385,7 +2403,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>19:47:14</t>
+          <t>19:51:23</t>
         </is>
       </c>
     </row>
@@ -2504,7 +2522,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-06-04T19:44:22.7685031+05:30</t>
+          <t>2026-06-04T19:50:33.0134877+05:30</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -2514,7 +2532,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>19:44:22.768</t>
+          <t>19:50:33.013</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -13212,18 +13230,132 @@
         <v>43</v>
       </c>
     </row>
+    <row r="247">
+      <c r="A247" s="4">
+        <v>230</v>
+      </c>
+      <c r="B247" s="4" t="s">
+        <v>508</v>
+      </c>
+      <c r="C247" s="4" t="s">
+        <v>395</v>
+      </c>
+      <c r="D247" s="4" t="s">
+        <v>509</v>
+      </c>
+      <c r="E247" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F247" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G247" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H247" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I247" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J247" s="4">
+        <v>0</v>
+      </c>
+      <c r="K247" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L247" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
     <row r="248">
-      <c r="A248" t="s">
-        <v>508</v>
-      </c>
-      <c r="B248" t="s">
-        <v>509</v>
-      </c>
-      <c r="D248" t="s">
+      <c r="A248" s="4">
+        <v>231</v>
+      </c>
+      <c r="B248" s="4" t="s">
         <v>510</v>
       </c>
-      <c r="E248">
-        <v>229</v>
+      <c r="C248" s="4" t="s">
+        <v>395</v>
+      </c>
+      <c r="D248" s="4" t="s">
+        <v>511</v>
+      </c>
+      <c r="E248" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F248" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G248" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H248" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I248" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J248" s="4">
+        <v>0</v>
+      </c>
+      <c r="K248" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L248" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" s="4">
+        <v>232</v>
+      </c>
+      <c r="B249" s="4" t="s">
+        <v>512</v>
+      </c>
+      <c r="C249" s="4" t="s">
+        <v>395</v>
+      </c>
+      <c r="D249" s="4" t="s">
+        <v>513</v>
+      </c>
+      <c r="E249" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F249" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G249" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H249" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I249" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J249" s="4">
+        <v>0</v>
+      </c>
+      <c r="K249" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L249" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="s">
+        <v>514</v>
+      </c>
+      <c r="B251" t="s">
+        <v>515</v>
+      </c>
+      <c r="D251" t="s">
+        <v>516</v>
+      </c>
+      <c r="E251">
+        <v>232</v>
       </c>
     </row>
   </sheetData>

--- a/report-2026-06-04.xlsx
+++ b/report-2026-06-04.xlsx
@@ -21,7 +21,7 @@
     <t>PunMonitor Leader Election — Current State</t>
   </si>
   <si>
-    <t>Generated 2026-06-04T19:51:23+05:30</t>
+    <t>Generated 2026-06-04T19:51:45+05:30</t>
   </si>
   <si>
     <t>Election method</t>
@@ -72,7 +72,7 @@
     <t>Leader last update</t>
   </si>
   <si>
-    <t>2026-06-04T19:50:33+05:30 (50s ago)</t>
+    <t>2026-06-04T19:50:33+05:30 (1m12s ago)</t>
   </si>
   <si>
     <t>Leader stale?</t>
@@ -1564,7 +1564,7 @@
     <t>Generated</t>
   </si>
   <si>
-    <t>2026-06-04T19:51:23+05:30</t>
+    <t>2026-06-04T19:51:45+05:30</t>
   </si>
   <si>
     <t>Total events</t>
@@ -2159,7 +2159,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>0h 27m 35s</t>
+          <t>0h 27m 57s</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -2179,7 +2179,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>10h 52m 35s</t>
+          <t>10h 52m 40s</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -2189,7 +2189,7 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>19:51:23</t>
+          <t>19:51:45</t>
         </is>
       </c>
     </row>
@@ -2296,7 +2296,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>19:51:23</t>
+          <t>19:51:45</t>
         </is>
       </c>
     </row>
@@ -2353,17 +2353,17 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>1317.0</t>
+          <t>1414.0</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>107420.3</t>
+          <t>117862.5</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>17518</t>
+          <t>17793</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -2403,7 +2403,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>19:51:23</t>
+          <t>19:51:45</t>
         </is>
       </c>
     </row>

--- a/report-2026-06-04.xlsx
+++ b/report-2026-06-04.xlsx
@@ -21,7 +21,7 @@
     <t>PunMonitor Leader Election — Current State</t>
   </si>
   <si>
-    <t>Generated 2026-06-04T19:51:45+05:30</t>
+    <t>Generated 2026-06-04T19:52:10+05:30</t>
   </si>
   <si>
     <t>Election method</t>
@@ -72,7 +72,7 @@
     <t>Leader last update</t>
   </si>
   <si>
-    <t>2026-06-04T19:50:33+05:30 (1m12s ago)</t>
+    <t>2026-06-04T19:50:33+05:30 (1m37s ago)</t>
   </si>
   <si>
     <t>Leader stale?</t>
@@ -1564,7 +1564,7 @@
     <t>Generated</t>
   </si>
   <si>
-    <t>2026-06-04T19:51:45+05:30</t>
+    <t>2026-06-04T19:52:10+05:30</t>
   </si>
   <si>
     <t>Total events</t>
@@ -2159,7 +2159,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>0h 27m 57s</t>
+          <t>0h 28m 22s</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -2189,7 +2189,7 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>19:51:45</t>
+          <t>19:52:10</t>
         </is>
       </c>
     </row>
@@ -2241,7 +2241,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>degraded</t>
+          <t>stale</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -2296,7 +2296,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>19:51:45</t>
+          <t>19:52:10</t>
         </is>
       </c>
     </row>
@@ -2353,17 +2353,17 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>1414.0</t>
+          <t>706.0</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>117862.5</t>
+          <t>118276.3</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>17793</t>
+          <t>18304</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -2403,7 +2403,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>19:51:45</t>
+          <t>19:52:10</t>
         </is>
       </c>
     </row>

--- a/report-2026-06-04.xlsx
+++ b/report-2026-06-04.xlsx
@@ -21,7 +21,7 @@
     <t>PunMonitor Leader Election — Current State</t>
   </si>
   <si>
-    <t>Generated 2026-06-04T19:52:10+05:30</t>
+    <t>Generated 2026-06-04T19:52:33+05:30</t>
   </si>
   <si>
     <t>Election method</t>
@@ -72,7 +72,7 @@
     <t>Leader last update</t>
   </si>
   <si>
-    <t>2026-06-04T19:50:33+05:30 (1m37s ago)</t>
+    <t>2026-06-04T19:50:33+05:30 (2m0s ago)</t>
   </si>
   <si>
     <t>Leader stale?</t>
@@ -1564,7 +1564,7 @@
     <t>Generated</t>
   </si>
   <si>
-    <t>2026-06-04T19:52:10+05:30</t>
+    <t>2026-06-04T19:52:33+05:30</t>
   </si>
   <si>
     <t>Total events</t>
@@ -2159,7 +2159,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>0h 28m 22s</t>
+          <t>0h 28m 45s</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -2189,7 +2189,7 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>19:52:10</t>
+          <t>19:52:33</t>
         </is>
       </c>
     </row>
@@ -2296,7 +2296,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>19:52:10</t>
+          <t>19:52:33</t>
         </is>
       </c>
     </row>
@@ -2353,17 +2353,17 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>706.0</t>
+          <t>724.0</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>118276.3</t>
+          <t>121553.9</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>18304</t>
+          <t>18797</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -2403,7 +2403,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>19:52:10</t>
+          <t>19:52:33</t>
         </is>
       </c>
     </row>

--- a/report-2026-06-04.xlsx
+++ b/report-2026-06-04.xlsx
@@ -16,12 +16,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="517" uniqueCount="517">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="523" uniqueCount="523">
   <si>
     <t>PunMonitor Leader Election — Current State</t>
   </si>
   <si>
-    <t>Generated 2026-06-04T19:52:33+05:30</t>
+    <t>Generated 2026-06-04T19:56:17+05:30</t>
   </si>
   <si>
     <t>Election method</t>
@@ -72,7 +72,7 @@
     <t>Leader last update</t>
   </si>
   <si>
-    <t>2026-06-04T19:50:33+05:30 (2m0s ago)</t>
+    <t>2026-06-04T19:55:54+05:30 (23s ago)</t>
   </si>
   <si>
     <t>Leader stale?</t>
@@ -87,7 +87,7 @@
     <t>Check count</t>
   </si>
   <si>
-    <t>24</t>
+    <t>30</t>
   </si>
   <si>
     <t>Last error</t>
@@ -1561,10 +1561,28 @@
     <t>19:50:33.013</t>
   </si>
   <si>
+    <t>2026-06-04T19:53:04.9083127+05:30</t>
+  </si>
+  <si>
+    <t>19:53:04.908</t>
+  </si>
+  <si>
+    <t>2026-06-04T19:54:17.8622383+05:30</t>
+  </si>
+  <si>
+    <t>19:54:17.862</t>
+  </si>
+  <si>
+    <t>2026-06-04T19:55:27.5510581+05:30</t>
+  </si>
+  <si>
+    <t>19:55:27.551</t>
+  </si>
+  <si>
     <t>Generated</t>
   </si>
   <si>
-    <t>2026-06-04T19:52:33+05:30</t>
+    <t>2026-06-04T19:56:17+05:30</t>
   </si>
   <si>
     <t>Total events</t>
@@ -2159,7 +2177,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>0h 28m 45s</t>
+          <t>0h 32m 29s</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -2179,7 +2197,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>10h 52m 40s</t>
+          <t>10h 55m 35s</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -2189,7 +2207,7 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>19:52:33</t>
+          <t>19:56:17</t>
         </is>
       </c>
     </row>
@@ -2241,7 +2259,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>stale</t>
+          <t>degraded</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -2296,7 +2314,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>19:52:33</t>
+          <t>19:56:17</t>
         </is>
       </c>
     </row>
@@ -2353,17 +2371,17 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>724.0</t>
+          <t>1496.0</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>121553.9</t>
+          <t>129972.3</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>18797</t>
+          <t>22498</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -2373,7 +2391,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>1605</t>
+          <t>1926</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -2393,7 +2411,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>10h 52m 35s</t>
+          <t>10h 55m 15s</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -2403,7 +2421,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>19:52:33</t>
+          <t>19:56:17</t>
         </is>
       </c>
     </row>
@@ -2522,7 +2540,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-06-04T19:50:33.0134877+05:30</t>
+          <t>2026-06-04T19:55:27.5510581+05:30</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -2532,7 +2550,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>19:50:33.013</t>
+          <t>19:55:27.551</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -13344,18 +13362,132 @@
         <v>43</v>
       </c>
     </row>
+    <row r="250">
+      <c r="A250" s="4">
+        <v>233</v>
+      </c>
+      <c r="B250" s="4" t="s">
+        <v>514</v>
+      </c>
+      <c r="C250" s="4" t="s">
+        <v>395</v>
+      </c>
+      <c r="D250" s="4" t="s">
+        <v>515</v>
+      </c>
+      <c r="E250" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F250" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G250" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H250" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I250" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J250" s="4">
+        <v>0</v>
+      </c>
+      <c r="K250" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L250" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
     <row r="251">
-      <c r="A251" t="s">
-        <v>514</v>
-      </c>
-      <c r="B251" t="s">
-        <v>515</v>
-      </c>
-      <c r="D251" t="s">
+      <c r="A251" s="4">
+        <v>234</v>
+      </c>
+      <c r="B251" s="4" t="s">
         <v>516</v>
       </c>
-      <c r="E251">
-        <v>232</v>
+      <c r="C251" s="4" t="s">
+        <v>395</v>
+      </c>
+      <c r="D251" s="4" t="s">
+        <v>517</v>
+      </c>
+      <c r="E251" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F251" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G251" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H251" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I251" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J251" s="4">
+        <v>0</v>
+      </c>
+      <c r="K251" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L251" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" s="4">
+        <v>235</v>
+      </c>
+      <c r="B252" s="4" t="s">
+        <v>518</v>
+      </c>
+      <c r="C252" s="4" t="s">
+        <v>395</v>
+      </c>
+      <c r="D252" s="4" t="s">
+        <v>519</v>
+      </c>
+      <c r="E252" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F252" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G252" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H252" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I252" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J252" s="4">
+        <v>0</v>
+      </c>
+      <c r="K252" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L252" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="s">
+        <v>520</v>
+      </c>
+      <c r="B254" t="s">
+        <v>521</v>
+      </c>
+      <c r="D254" t="s">
+        <v>522</v>
+      </c>
+      <c r="E254">
+        <v>235</v>
       </c>
     </row>
   </sheetData>

--- a/report-2026-06-04.xlsx
+++ b/report-2026-06-04.xlsx
@@ -21,7 +21,7 @@
     <t>PunMonitor Leader Election — Current State</t>
   </si>
   <si>
-    <t>Generated 2026-06-04T19:56:17+05:30</t>
+    <t>Generated 2026-06-04T19:56:44+05:30</t>
   </si>
   <si>
     <t>Election method</t>
@@ -72,7 +72,7 @@
     <t>Leader last update</t>
   </si>
   <si>
-    <t>2026-06-04T19:55:54+05:30 (23s ago)</t>
+    <t>2026-06-04T19:55:54+05:30 (50s ago)</t>
   </si>
   <si>
     <t>Leader stale?</t>
@@ -1582,7 +1582,7 @@
     <t>Generated</t>
   </si>
   <si>
-    <t>2026-06-04T19:56:17+05:30</t>
+    <t>2026-06-04T19:56:44+05:30</t>
   </si>
   <si>
     <t>Total events</t>
@@ -2177,7 +2177,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>0h 32m 29s</t>
+          <t>0h 32m 56s</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -2197,7 +2197,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>10h 55m 35s</t>
+          <t>10h 56m 5s</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -2207,7 +2207,7 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>19:56:17</t>
+          <t>19:56:44</t>
         </is>
       </c>
     </row>
@@ -2314,7 +2314,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>19:56:17</t>
+          <t>19:56:44</t>
         </is>
       </c>
     </row>
@@ -2371,17 +2371,17 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>1496.0</t>
+          <t>1552.0</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>129972.3</t>
+          <t>112254.3</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>22498</t>
+          <t>22900</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>19:56:17</t>
+          <t>19:56:44</t>
         </is>
       </c>
     </row>

--- a/report-2026-06-04.xlsx
+++ b/report-2026-06-04.xlsx
@@ -21,7 +21,7 @@
     <t>PunMonitor Leader Election — Current State</t>
   </si>
   <si>
-    <t>Generated 2026-06-04T19:56:44+05:30</t>
+    <t>Generated 2026-06-04T19:57:00+05:30</t>
   </si>
   <si>
     <t>Election method</t>
@@ -72,7 +72,7 @@
     <t>Leader last update</t>
   </si>
   <si>
-    <t>2026-06-04T19:55:54+05:30 (50s ago)</t>
+    <t>2026-06-04T19:55:54+05:30 (1m5s ago)</t>
   </si>
   <si>
     <t>Leader stale?</t>
@@ -1582,7 +1582,7 @@
     <t>Generated</t>
   </si>
   <si>
-    <t>2026-06-04T19:56:44+05:30</t>
+    <t>2026-06-04T19:57:00+05:30</t>
   </si>
   <si>
     <t>Total events</t>
@@ -2177,7 +2177,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>0h 32m 56s</t>
+          <t>0h 33m 12s</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -2197,7 +2197,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>10h 56m 5s</t>
+          <t>10h 56m 20s</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -2207,7 +2207,7 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>19:56:44</t>
+          <t>19:57:00</t>
         </is>
       </c>
     </row>
@@ -2259,7 +2259,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>degraded</t>
+          <t>stale</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -2314,7 +2314,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>19:56:44</t>
+          <t>19:57:00</t>
         </is>
       </c>
     </row>
@@ -2371,17 +2371,17 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>1552.0</t>
+          <t>1010.0</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>112254.3</t>
+          <t>107225.7</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>22900</t>
+          <t>23156</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>19:56:44</t>
+          <t>19:57:00</t>
         </is>
       </c>
     </row>

--- a/report-2026-06-04.xlsx
+++ b/report-2026-06-04.xlsx
@@ -21,7 +21,7 @@
     <t>PunMonitor Leader Election — Current State</t>
   </si>
   <si>
-    <t>Generated 2026-06-04T19:57:00+05:30</t>
+    <t>Generated 2026-06-04T19:57:27+05:30</t>
   </si>
   <si>
     <t>Election method</t>
@@ -72,7 +72,7 @@
     <t>Leader last update</t>
   </si>
   <si>
-    <t>2026-06-04T19:55:54+05:30 (1m5s ago)</t>
+    <t>2026-06-04T19:55:54+05:30 (1m33s ago)</t>
   </si>
   <si>
     <t>Leader stale?</t>
@@ -1582,7 +1582,7 @@
     <t>Generated</t>
   </si>
   <si>
-    <t>2026-06-04T19:57:00+05:30</t>
+    <t>2026-06-04T19:57:27+05:30</t>
   </si>
   <si>
     <t>Total events</t>
@@ -2177,7 +2177,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>0h 33m 12s</t>
+          <t>0h 33m 39s</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -2207,7 +2207,7 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>19:57:00</t>
+          <t>19:57:27</t>
         </is>
       </c>
     </row>
@@ -2314,7 +2314,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>19:57:00</t>
+          <t>19:57:27</t>
         </is>
       </c>
     </row>
@@ -2371,17 +2371,17 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>1010.0</t>
+          <t>2019.0</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>107225.7</t>
+          <t>116824.7</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>23156</t>
+          <t>23604</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>19:57:00</t>
+          <t>19:57:27</t>
         </is>
       </c>
     </row>

--- a/report-2026-06-04.xlsx
+++ b/report-2026-06-04.xlsx
@@ -21,7 +21,7 @@
     <t>PunMonitor Leader Election — Current State</t>
   </si>
   <si>
-    <t>Generated 2026-06-04T19:57:27+05:30</t>
+    <t>Generated 2026-06-04T19:57:54+05:30</t>
   </si>
   <si>
     <t>Election method</t>
@@ -72,7 +72,7 @@
     <t>Leader last update</t>
   </si>
   <si>
-    <t>2026-06-04T19:55:54+05:30 (1m33s ago)</t>
+    <t>2026-06-04T19:55:54+05:30 (2m0s ago)</t>
   </si>
   <si>
     <t>Leader stale?</t>
@@ -1582,7 +1582,7 @@
     <t>Generated</t>
   </si>
   <si>
-    <t>2026-06-04T19:57:27+05:30</t>
+    <t>2026-06-04T19:57:54+05:30</t>
   </si>
   <si>
     <t>Total events</t>
@@ -2177,7 +2177,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>0h 33m 39s</t>
+          <t>0h 34m 6s</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -2207,7 +2207,7 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>19:57:27</t>
+          <t>19:57:54</t>
         </is>
       </c>
     </row>
@@ -2314,7 +2314,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>19:57:27</t>
+          <t>19:57:54</t>
         </is>
       </c>
     </row>
@@ -2371,17 +2371,17 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>2019.0</t>
+          <t>1366.0</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>116824.7</t>
+          <t>112598.3</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>23604</t>
+          <t>24004</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>19:57:27</t>
+          <t>19:57:54</t>
         </is>
       </c>
     </row>

--- a/report-2026-06-04.xlsx
+++ b/report-2026-06-04.xlsx
@@ -16,12 +16,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="523" uniqueCount="523">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="529" uniqueCount="529">
   <si>
     <t>PunMonitor Leader Election — Current State</t>
   </si>
   <si>
-    <t>Generated 2026-06-04T19:57:54+05:30</t>
+    <t>Generated 2026-06-04T20:01:34+05:30</t>
   </si>
   <si>
     <t>Election method</t>
@@ -72,7 +72,7 @@
     <t>Leader last update</t>
   </si>
   <si>
-    <t>2026-06-04T19:55:54+05:30 (2m0s ago)</t>
+    <t>2026-06-04T20:01:20+05:30 (13s ago)</t>
   </si>
   <si>
     <t>Leader stale?</t>
@@ -87,7 +87,7 @@
     <t>Check count</t>
   </si>
   <si>
-    <t>30</t>
+    <t>37</t>
   </si>
   <si>
     <t>Last error</t>
@@ -1579,10 +1579,28 @@
     <t>19:55:27.551</t>
   </si>
   <si>
+    <t>2026-06-04T19:58:26.1013244+05:30</t>
+  </si>
+  <si>
+    <t>19:58:26.101</t>
+  </si>
+  <si>
+    <t>2026-06-04T19:59:34.3698348+05:30</t>
+  </si>
+  <si>
+    <t>19:59:34.369</t>
+  </si>
+  <si>
+    <t>2026-06-04T20:00:42.9577523+05:30</t>
+  </si>
+  <si>
+    <t>20:00:42.957</t>
+  </si>
+  <si>
     <t>Generated</t>
   </si>
   <si>
-    <t>2026-06-04T19:57:54+05:30</t>
+    <t>2026-06-04T20:01:34+05:30</t>
   </si>
   <si>
     <t>Total events</t>
@@ -2117,7 +2135,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>192.168.0.128</t>
+          <t>10.217.2.182</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -2177,7 +2195,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>0h 34m 6s</t>
+          <t>0h 37m 46s</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -2197,7 +2215,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>10h 56m 20s</t>
+          <t>10h 57m 45s</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -2207,44 +2225,44 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>19:57:54</t>
+          <t>20:01:34</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Puneets-MacBook-Air.local-esHl</t>
+          <t>PuneetU-EB6LMJD-cf4a9ce5</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Puneets-MacBook-Air.local</t>
+          <t>PuneetU-EB6LMJD</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>192.168.0.156</t>
+          <t>10.217.2.182</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>43.247.40.101</t>
+          <t>103.117.15.39</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>darwin</t>
+          <t>windows</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>arm64</t>
+          <t>amd64</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>10.0.0</t>
+          <t>10.0.45</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -2254,27 +2272,27 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>websocket</t>
+          <t>self</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>stale</t>
+          <t>good</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>1304.0</t>
+          <t>1107.0</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>15150.5</t>
+          <t>103569.9</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>26940</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -2284,27 +2302,27 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>19065</t>
+          <t>2253</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>2026-06-03 10:39:05</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>Jun 2 05:41 PM</t>
+          <t>Jun 4 07:08 PM</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-06-03 10:39:05</t>
+          <t>2026-06-04 19:23:48</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>13h 47m 45s</t>
+          <t>10h 57m 35s</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -2314,84 +2332,84 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>19:57:54</t>
+          <t>20:01:34</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>PuneetU-EB6LMJD-cf4a9ce5</t>
+          <t>Puneets-MacBook-Air.local-esHl</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>PuneetU-EB6LMJD</t>
+          <t>Puneets-MacBook-Air.local</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>192.168.0.128</t>
+          <t>192.168.0.156</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>103.117.15.39</t>
+          <t>43.247.40.101</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>windows</t>
+          <t>darwin</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>amd64</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>10.0.45</t>
+          <t>10.0.0</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>agent</t>
+          <t>disconnected</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>self</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>good</t>
+          <t>offline</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>1366.0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>112598.3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>24004</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>1926</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -2401,17 +2419,17 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>Jun 4 07:08 PM</t>
+          <t>—</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>2026-06-04 19:23:48</t>
+          <t>—</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>10h 55m 15s</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -2421,7 +2439,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>19:57:54</t>
+          <t>20:01:34</t>
         </is>
       </c>
     </row>
@@ -2540,7 +2558,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-06-04T19:55:27.5510581+05:30</t>
+          <t>2026-06-04T20:00:42.9577523+05:30</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -2550,7 +2568,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>19:55:27.551</t>
+          <t>20:00:42.957</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -13476,18 +13494,132 @@
         <v>43</v>
       </c>
     </row>
+    <row r="253">
+      <c r="A253" s="4">
+        <v>236</v>
+      </c>
+      <c r="B253" s="4" t="s">
+        <v>520</v>
+      </c>
+      <c r="C253" s="4" t="s">
+        <v>395</v>
+      </c>
+      <c r="D253" s="4" t="s">
+        <v>521</v>
+      </c>
+      <c r="E253" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F253" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G253" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H253" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I253" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J253" s="4">
+        <v>0</v>
+      </c>
+      <c r="K253" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L253" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
     <row r="254">
-      <c r="A254" t="s">
-        <v>520</v>
-      </c>
-      <c r="B254" t="s">
-        <v>521</v>
-      </c>
-      <c r="D254" t="s">
+      <c r="A254" s="4">
+        <v>237</v>
+      </c>
+      <c r="B254" s="4" t="s">
         <v>522</v>
       </c>
-      <c r="E254">
-        <v>235</v>
+      <c r="C254" s="4" t="s">
+        <v>395</v>
+      </c>
+      <c r="D254" s="4" t="s">
+        <v>523</v>
+      </c>
+      <c r="E254" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F254" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G254" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H254" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I254" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J254" s="4">
+        <v>0</v>
+      </c>
+      <c r="K254" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L254" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" s="4">
+        <v>238</v>
+      </c>
+      <c r="B255" s="4" t="s">
+        <v>524</v>
+      </c>
+      <c r="C255" s="4" t="s">
+        <v>395</v>
+      </c>
+      <c r="D255" s="4" t="s">
+        <v>525</v>
+      </c>
+      <c r="E255" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F255" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G255" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H255" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I255" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J255" s="4">
+        <v>0</v>
+      </c>
+      <c r="K255" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L255" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="s">
+        <v>526</v>
+      </c>
+      <c r="B257" t="s">
+        <v>527</v>
+      </c>
+      <c r="D257" t="s">
+        <v>528</v>
+      </c>
+      <c r="E257">
+        <v>238</v>
       </c>
     </row>
   </sheetData>

--- a/report-2026-06-04.xlsx
+++ b/report-2026-06-04.xlsx
@@ -16,12 +16,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="529" uniqueCount="529">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="536" uniqueCount="536">
   <si>
     <t>PunMonitor Leader Election — Current State</t>
   </si>
   <si>
-    <t>Generated 2026-06-04T20:01:34+05:30</t>
+    <t>Generated 2026-06-04T20:07:31+05:30</t>
   </si>
   <si>
     <t>Election method</t>
@@ -72,7 +72,7 @@
     <t>Leader last update</t>
   </si>
   <si>
-    <t>2026-06-04T20:01:20+05:30 (13s ago)</t>
+    <t>2026-06-04T20:06:34+05:30 (56s ago)</t>
   </si>
   <si>
     <t>Leader stale?</t>
@@ -87,7 +87,7 @@
     <t>Check count</t>
   </si>
   <si>
-    <t>37</t>
+    <t>42</t>
   </si>
   <si>
     <t>Last error</t>
@@ -1597,10 +1597,31 @@
     <t>20:00:42.957</t>
   </si>
   <si>
+    <t>2026-06-04T20:04:00.9179473+05:30</t>
+  </si>
+  <si>
+    <t>20:04:00.917</t>
+  </si>
+  <si>
+    <t>Get "https://api.github.com/repos/puniteswra-spec/PU/contents/primary_server.json": context deadline exceeded (Client.Timeout exceeded while awaiting headers)</t>
+  </si>
+  <si>
+    <t>2026-06-04T20:05:31.3142054+05:30</t>
+  </si>
+  <si>
+    <t>20:05:31.314</t>
+  </si>
+  <si>
+    <t>2026-06-04T20:06:34.7450856+05:30</t>
+  </si>
+  <si>
+    <t>20:06:34.745</t>
+  </si>
+  <si>
     <t>Generated</t>
   </si>
   <si>
-    <t>2026-06-04T20:01:34+05:30</t>
+    <t>2026-06-04T20:07:31+05:30</t>
   </si>
   <si>
     <t>Total events</t>
@@ -2135,7 +2156,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>10.217.2.182</t>
+          <t>192.168.0.128</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -2195,7 +2216,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>0h 37m 46s</t>
+          <t>0h 43m 43s</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -2215,7 +2236,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>10h 57m 45s</t>
+          <t>11h 2m 0s</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -2225,7 +2246,7 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>20:01:34</t>
+          <t>20:07:31</t>
         </is>
       </c>
     </row>
@@ -2242,7 +2263,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>10.217.2.182</t>
+          <t>192.168.0.128</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -2282,17 +2303,17 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>1107.0</t>
+          <t>7644.0</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>103569.9</t>
+          <t>311097.5</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>26940</t>
+          <t>31352</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -2302,7 +2323,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>2253</t>
+          <t>2567</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -2322,7 +2343,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>10h 57m 35s</t>
+          <t>11h 1m 5s</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -2332,7 +2353,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>20:01:34</t>
+          <t>20:07:31</t>
         </is>
       </c>
     </row>
@@ -2439,7 +2460,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>20:01:34</t>
+          <t>20:07:31</t>
         </is>
       </c>
     </row>
@@ -2558,7 +2579,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-06-04T20:00:42.9577523+05:30</t>
+          <t>2026-06-04T20:06:34.7450856+05:30</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -2568,7 +2589,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>20:00:42.957</t>
+          <t>20:06:34.745</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -13608,18 +13629,132 @@
         <v>43</v>
       </c>
     </row>
+    <row r="256">
+      <c r="A256" s="3">
+        <v>239</v>
+      </c>
+      <c r="B256" s="3" t="s">
+        <v>526</v>
+      </c>
+      <c r="C256" s="3" t="s">
+        <v>395</v>
+      </c>
+      <c r="D256" s="3" t="s">
+        <v>527</v>
+      </c>
+      <c r="E256" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F256" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G256" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="H256" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="I256" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="J256" s="3">
+        <v>9223372036</v>
+      </c>
+      <c r="K256" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="L256" s="3" t="s">
+        <v>528</v>
+      </c>
+    </row>
     <row r="257">
-      <c r="A257" t="s">
-        <v>526</v>
-      </c>
-      <c r="B257" t="s">
-        <v>527</v>
-      </c>
-      <c r="D257" t="s">
-        <v>528</v>
-      </c>
-      <c r="E257">
-        <v>238</v>
+      <c r="A257" s="4">
+        <v>240</v>
+      </c>
+      <c r="B257" s="4" t="s">
+        <v>529</v>
+      </c>
+      <c r="C257" s="4" t="s">
+        <v>395</v>
+      </c>
+      <c r="D257" s="4" t="s">
+        <v>530</v>
+      </c>
+      <c r="E257" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F257" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G257" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H257" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I257" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J257" s="4">
+        <v>0</v>
+      </c>
+      <c r="K257" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L257" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" s="4">
+        <v>241</v>
+      </c>
+      <c r="B258" s="4" t="s">
+        <v>531</v>
+      </c>
+      <c r="C258" s="4" t="s">
+        <v>395</v>
+      </c>
+      <c r="D258" s="4" t="s">
+        <v>532</v>
+      </c>
+      <c r="E258" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F258" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G258" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H258" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I258" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J258" s="4">
+        <v>0</v>
+      </c>
+      <c r="K258" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L258" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="s">
+        <v>533</v>
+      </c>
+      <c r="B260" t="s">
+        <v>534</v>
+      </c>
+      <c r="D260" t="s">
+        <v>535</v>
+      </c>
+      <c r="E260">
+        <v>241</v>
       </c>
     </row>
   </sheetData>

--- a/report-2026-06-04.xlsx
+++ b/report-2026-06-04.xlsx
@@ -21,7 +21,7 @@
     <t>PunMonitor Leader Election — Current State</t>
   </si>
   <si>
-    <t>Generated 2026-06-04T20:07:31+05:30</t>
+    <t>Generated 2026-06-04T20:07:54+05:30</t>
   </si>
   <si>
     <t>Election method</t>
@@ -72,7 +72,7 @@
     <t>Leader last update</t>
   </si>
   <si>
-    <t>2026-06-04T20:06:34+05:30 (56s ago)</t>
+    <t>2026-06-04T20:06:34+05:30 (1m19s ago)</t>
   </si>
   <si>
     <t>Leader stale?</t>
@@ -1621,7 +1621,7 @@
     <t>Generated</t>
   </si>
   <si>
-    <t>2026-06-04T20:07:31+05:30</t>
+    <t>2026-06-04T20:07:54+05:30</t>
   </si>
   <si>
     <t>Total events</t>
@@ -2216,7 +2216,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>0h 43m 43s</t>
+          <t>0h 44m 6s</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>11h 2m 0s</t>
+          <t>11h 2m 25s</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>20:07:31</t>
+          <t>20:07:54</t>
         </is>
       </c>
     </row>
@@ -2303,7 +2303,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>7644.0</t>
+          <t>13108.0</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -2313,7 +2313,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>31352</t>
+          <t>31409</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -2353,7 +2353,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>20:07:31</t>
+          <t>20:07:54</t>
         </is>
       </c>
     </row>
@@ -2460,7 +2460,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>20:07:31</t>
+          <t>20:07:54</t>
         </is>
       </c>
     </row>

--- a/report-2026-06-04.xlsx
+++ b/report-2026-06-04.xlsx
@@ -16,12 +16,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="536" uniqueCount="536">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="538" uniqueCount="538">
   <si>
     <t>PunMonitor Leader Election — Current State</t>
   </si>
   <si>
-    <t>Generated 2026-06-04T20:07:54+05:30</t>
+    <t>Generated 2026-06-04T20:10:34+05:30</t>
   </si>
   <si>
     <t>Election method</t>
@@ -72,7 +72,7 @@
     <t>Leader last update</t>
   </si>
   <si>
-    <t>2026-06-04T20:06:34+05:30 (1m19s ago)</t>
+    <t>2026-06-04T20:08:34+05:30 (2m0s ago)</t>
   </si>
   <si>
     <t>Leader stale?</t>
@@ -87,7 +87,7 @@
     <t>Check count</t>
   </si>
   <si>
-    <t>42</t>
+    <t>1</t>
   </si>
   <si>
     <t>Last error</t>
@@ -1618,10 +1618,16 @@
     <t>20:06:34.745</t>
   </si>
   <si>
+    <t>2026-06-04T20:08:34.2096369+05:30</t>
+  </si>
+  <si>
+    <t>20:08:34.209</t>
+  </si>
+  <si>
     <t>Generated</t>
   </si>
   <si>
-    <t>2026-06-04T20:07:54+05:30</t>
+    <t>2026-06-04T20:10:34+05:30</t>
   </si>
   <si>
     <t>Total events</t>
@@ -2176,7 +2182,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>10.0.45</t>
+          <t>10.0.46</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -2216,12 +2222,12 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>0h 44m 6s</t>
+          <t>0h 2m 20s</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>2026-06-04 19:23:48</t>
+          <t>2026-06-04 20:08:14</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
@@ -2231,12 +2237,12 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2026-06-04 19:23:48</t>
+          <t>2026-06-04 20:08:14</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>11h 2m 25s</t>
+          <t>11h 4m 40s</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -2246,7 +2252,7 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>20:07:54</t>
+          <t>20:10:34</t>
         </is>
       </c>
     </row>
@@ -2283,7 +2289,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>10.0.45</t>
+          <t>10.0.46</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -2303,17 +2309,17 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>13108.0</t>
+          <t>1043.0</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>311097.5</t>
+          <t>311001.5</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>31409</t>
+          <t>415</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -2323,7 +2329,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>2567</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -2338,12 +2344,12 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-06-04 19:23:48</t>
+          <t>2026-06-04 20:08:14</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>11h 1m 5s</t>
+          <t>11h 2m 40s</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -2353,324 +2359,217 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>20:07:54</t>
+          <t>20:10:34</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Puneets-MacBook-Air.local-esHl</t>
+          <t>── LATEST GITHUB ELECTION EVENT ──</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Puneets-MacBook-Air.local</t>
+          <t/>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>192.168.0.156</t>
+          <t/>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>43.247.40.101</t>
+          <t/>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>darwin</t>
+          <t/>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t/>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>10.0.0</t>
+          <t/>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>disconnected</t>
+          <t/>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t/>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>offline</t>
+          <t/>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t/>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t/>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t/>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t/>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t/>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t/>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t/>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t/>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t/>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t/>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>20:07:54</t>
+          <t/>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>── LATEST GITHUB ELECTION EVENT ──</t>
+          <t>[renewed]</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
+          <t>2026-06-04T20:08:34.2096369+05:30</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>20:08:34.209</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>renewed</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>PuneetU-EB6LMJD-cf4a9ce5</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>PuneetU-EB6LMJD</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>PuneetU-EB6LMJD-cf4a9ce5</t>
+        </is>
+      </c>
+      <c r="J5">
+        <v>0</v>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>renewed</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
           <t/>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="N5" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="O5" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="P5" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="Q5" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="R5" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="R5" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
       <c r="U5" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>[renewed]</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>2026-06-04T20:06:34.7450856+05:30</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>2026-06-04</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>20:06:34.745</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>renewed</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>github</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>PuneetU-EB6LMJD-cf4a9ce5</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>PuneetU-EB6LMJD</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>PuneetU-EB6LMJD-cf4a9ce5</t>
-        </is>
-      </c>
-      <c r="J6">
-        <v>0</v>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>renewed</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="R6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -13743,18 +13642,56 @@
         <v>43</v>
       </c>
     </row>
-    <row r="260">
-      <c r="A260" t="s">
+    <row r="259">
+      <c r="A259" s="4">
+        <v>242</v>
+      </c>
+      <c r="B259" s="4" t="s">
         <v>533</v>
       </c>
-      <c r="B260" t="s">
+      <c r="C259" s="4" t="s">
+        <v>395</v>
+      </c>
+      <c r="D259" s="4" t="s">
         <v>534</v>
       </c>
-      <c r="D260" t="s">
+      <c r="E259" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F259" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G259" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H259" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I259" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J259" s="4">
+        <v>0</v>
+      </c>
+      <c r="K259" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L259" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="s">
         <v>535</v>
       </c>
-      <c r="E260">
-        <v>241</v>
+      <c r="B261" t="s">
+        <v>536</v>
+      </c>
+      <c r="D261" t="s">
+        <v>537</v>
+      </c>
+      <c r="E261">
+        <v>242</v>
       </c>
     </row>
   </sheetData>

--- a/report-2026-06-04.xlsx
+++ b/report-2026-06-04.xlsx
@@ -16,12 +16,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="538" uniqueCount="538">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="540" uniqueCount="540">
   <si>
     <t>PunMonitor Leader Election — Current State</t>
   </si>
   <si>
-    <t>Generated 2026-06-04T20:10:34+05:30</t>
+    <t>Generated 2026-06-04T20:13:09+05:30</t>
   </si>
   <si>
     <t>Election method</t>
@@ -72,7 +72,7 @@
     <t>Leader last update</t>
   </si>
   <si>
-    <t>2026-06-04T20:08:34+05:30 (2m0s ago)</t>
+    <t>2026-06-04T20:11:09+05:30 (2m0s ago)</t>
   </si>
   <si>
     <t>Leader stale?</t>
@@ -1624,10 +1624,16 @@
     <t>20:08:34.209</t>
   </si>
   <si>
+    <t>2026-06-04T20:11:09.3612131+05:30</t>
+  </si>
+  <si>
+    <t>20:11:09.361</t>
+  </si>
+  <si>
     <t>Generated</t>
   </si>
   <si>
-    <t>2026-06-04T20:10:34+05:30</t>
+    <t>2026-06-04T20:13:09+05:30</t>
   </si>
   <si>
     <t>Total events</t>
@@ -2227,7 +2233,7 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>2026-06-04 20:08:14</t>
+          <t>2026-06-04 20:10:48</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
@@ -2237,12 +2243,12 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2026-06-04 20:08:14</t>
+          <t>2026-06-04 20:10:48</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>11h 4m 40s</t>
+          <t>11h 7m 5s</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -2252,7 +2258,7 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>20:10:34</t>
+          <t>20:13:09</t>
         </is>
       </c>
     </row>
@@ -2309,17 +2315,17 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>1043.0</t>
+          <t>364.0</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>311001.5</t>
+          <t>311009.5</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>415</t>
+          <t>588</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -2329,7 +2335,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>21</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -2344,12 +2350,12 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-06-04 20:08:14</t>
+          <t>2026-06-04 20:10:48</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>11h 2m 40s</t>
+          <t>11h 5m 5s</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -2359,7 +2365,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>20:10:34</t>
+          <t>20:13:09</t>
         </is>
       </c>
     </row>
@@ -2478,7 +2484,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-06-04T20:08:34.2096369+05:30</t>
+          <t>2026-06-04T20:11:09.3612131+05:30</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -2488,7 +2494,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>20:08:34.209</t>
+          <t>20:11:09.361</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -13680,18 +13686,56 @@
         <v>43</v>
       </c>
     </row>
-    <row r="261">
-      <c r="A261" t="s">
+    <row r="260">
+      <c r="A260" s="4">
+        <v>243</v>
+      </c>
+      <c r="B260" s="4" t="s">
         <v>535</v>
       </c>
-      <c r="B261" t="s">
+      <c r="C260" s="4" t="s">
+        <v>395</v>
+      </c>
+      <c r="D260" s="4" t="s">
         <v>536</v>
       </c>
-      <c r="D261" t="s">
+      <c r="E260" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F260" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G260" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H260" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I260" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J260" s="4">
+        <v>0</v>
+      </c>
+      <c r="K260" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L260" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="s">
         <v>537</v>
       </c>
-      <c r="E261">
-        <v>242</v>
+      <c r="B262" t="s">
+        <v>538</v>
+      </c>
+      <c r="D262" t="s">
+        <v>539</v>
+      </c>
+      <c r="E262">
+        <v>243</v>
       </c>
     </row>
   </sheetData>

--- a/report-2026-06-04.xlsx
+++ b/report-2026-06-04.xlsx
@@ -16,12 +16,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="540" uniqueCount="540">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="544" uniqueCount="544">
   <si>
     <t>PunMonitor Leader Election — Current State</t>
   </si>
   <si>
-    <t>Generated 2026-06-04T20:13:09+05:30</t>
+    <t>Generated 2026-06-04T20:18:24+05:30</t>
   </si>
   <si>
     <t>Election method</t>
@@ -72,7 +72,7 @@
     <t>Leader last update</t>
   </si>
   <si>
-    <t>2026-06-04T20:11:09+05:30 (2m0s ago)</t>
+    <t>2026-06-04T20:16:24+05:30 (2m0s ago)</t>
   </si>
   <si>
     <t>Leader stale?</t>
@@ -87,7 +87,7 @@
     <t>Check count</t>
   </si>
   <si>
-    <t>1</t>
+    <t>4</t>
   </si>
   <si>
     <t>Last error</t>
@@ -1630,10 +1630,22 @@
     <t>20:11:09.361</t>
   </si>
   <si>
+    <t>2026-06-04T20:13:40.9688703+05:30</t>
+  </si>
+  <si>
+    <t>20:13:40.968</t>
+  </si>
+  <si>
+    <t>2026-06-04T20:16:11.2180904+05:30</t>
+  </si>
+  <si>
+    <t>20:16:11.218</t>
+  </si>
+  <si>
     <t>Generated</t>
   </si>
   <si>
-    <t>2026-06-04T20:13:09+05:30</t>
+    <t>2026-06-04T20:18:24+05:30</t>
   </si>
   <si>
     <t>Total events</t>
@@ -2228,7 +2240,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>0h 2m 20s</t>
+          <t>0h 7m 36s</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -2248,7 +2260,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>11h 7m 5s</t>
+          <t>11h 10m 15s</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -2258,7 +2270,7 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>20:13:09</t>
+          <t>20:18:24</t>
         </is>
       </c>
     </row>
@@ -2315,17 +2327,17 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>364.0</t>
+          <t>151.0</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>311009.5</t>
+          <t>134051.3</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>588</t>
+          <t>3907</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -2335,7 +2347,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>336</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -2355,7 +2367,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>11h 5m 5s</t>
+          <t>11h 10m 10s</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -2365,7 +2377,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>20:13:09</t>
+          <t>20:18:24</t>
         </is>
       </c>
     </row>
@@ -2484,7 +2496,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-06-04T20:11:09.3612131+05:30</t>
+          <t>2026-06-04T20:16:11.2180904+05:30</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -2494,7 +2506,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>20:11:09.361</t>
+          <t>20:16:11.218</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -13724,18 +13736,94 @@
         <v>43</v>
       </c>
     </row>
+    <row r="261">
+      <c r="A261" s="4">
+        <v>244</v>
+      </c>
+      <c r="B261" s="4" t="s">
+        <v>537</v>
+      </c>
+      <c r="C261" s="4" t="s">
+        <v>395</v>
+      </c>
+      <c r="D261" s="4" t="s">
+        <v>538</v>
+      </c>
+      <c r="E261" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F261" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G261" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H261" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I261" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J261" s="4">
+        <v>0</v>
+      </c>
+      <c r="K261" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L261" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
     <row r="262">
-      <c r="A262" t="s">
-        <v>537</v>
-      </c>
-      <c r="B262" t="s">
-        <v>538</v>
-      </c>
-      <c r="D262" t="s">
+      <c r="A262" s="4">
+        <v>245</v>
+      </c>
+      <c r="B262" s="4" t="s">
         <v>539</v>
       </c>
-      <c r="E262">
-        <v>243</v>
+      <c r="C262" s="4" t="s">
+        <v>395</v>
+      </c>
+      <c r="D262" s="4" t="s">
+        <v>540</v>
+      </c>
+      <c r="E262" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F262" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G262" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H262" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I262" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J262" s="4">
+        <v>0</v>
+      </c>
+      <c r="K262" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L262" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="s">
+        <v>541</v>
+      </c>
+      <c r="B264" t="s">
+        <v>542</v>
+      </c>
+      <c r="D264" t="s">
+        <v>543</v>
+      </c>
+      <c r="E264">
+        <v>245</v>
       </c>
     </row>
   </sheetData>

--- a/report-2026-06-04.xlsx
+++ b/report-2026-06-04.xlsx
@@ -16,12 +16,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="544" uniqueCount="544">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="548" uniqueCount="548">
   <si>
     <t>PunMonitor Leader Election — Current State</t>
   </si>
   <si>
-    <t>Generated 2026-06-04T20:18:24+05:30</t>
+    <t>Generated 2026-06-04T20:23:25+05:30</t>
   </si>
   <si>
     <t>Election method</t>
@@ -72,7 +72,7 @@
     <t>Leader last update</t>
   </si>
   <si>
-    <t>2026-06-04T20:16:24+05:30 (2m0s ago)</t>
+    <t>2026-06-04T20:21:38+05:30 (1m46s ago)</t>
   </si>
   <si>
     <t>Leader stale?</t>
@@ -87,7 +87,7 @@
     <t>Check count</t>
   </si>
   <si>
-    <t>4</t>
+    <t>9</t>
   </si>
   <si>
     <t>Last error</t>
@@ -1642,10 +1642,22 @@
     <t>20:16:11.218</t>
   </si>
   <si>
+    <t>2026-06-04T20:18:40.9630746+05:30</t>
+  </si>
+  <si>
+    <t>20:18:40.963</t>
+  </si>
+  <si>
+    <t>2026-06-04T20:21:11.1612413+05:30</t>
+  </si>
+  <si>
+    <t>20:21:11.161</t>
+  </si>
+  <si>
     <t>Generated</t>
   </si>
   <si>
-    <t>2026-06-04T20:18:24+05:30</t>
+    <t>2026-06-04T20:23:25+05:30</t>
   </si>
   <si>
     <t>Total events</t>
@@ -2240,7 +2252,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>0h 7m 36s</t>
+          <t>0h 12m 36s</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -2260,7 +2272,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>11h 10m 15s</t>
+          <t>11h 11m 20s</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -2270,7 +2282,7 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>20:18:24</t>
+          <t>20:23:25</t>
         </is>
       </c>
     </row>
@@ -2327,17 +2339,17 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>151.0</t>
+          <t>506.0</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>134051.3</t>
+          <t>194824.9</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>3907</t>
+          <t>8575</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -2347,7 +2359,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>336</t>
+          <t>650</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -2367,7 +2379,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>11h 10m 10s</t>
+          <t>11h 11m 5s</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -2377,7 +2389,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>20:18:24</t>
+          <t>20:23:25</t>
         </is>
       </c>
     </row>
@@ -2496,7 +2508,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-06-04T20:16:11.2180904+05:30</t>
+          <t>2026-06-04T20:21:11.1612413+05:30</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -2506,7 +2518,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>20:16:11.218</t>
+          <t>20:21:11.161</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -13812,18 +13824,94 @@
         <v>43</v>
       </c>
     </row>
+    <row r="263">
+      <c r="A263" s="4">
+        <v>246</v>
+      </c>
+      <c r="B263" s="4" t="s">
+        <v>541</v>
+      </c>
+      <c r="C263" s="4" t="s">
+        <v>395</v>
+      </c>
+      <c r="D263" s="4" t="s">
+        <v>542</v>
+      </c>
+      <c r="E263" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F263" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G263" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H263" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I263" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J263" s="4">
+        <v>0</v>
+      </c>
+      <c r="K263" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L263" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
     <row r="264">
-      <c r="A264" t="s">
-        <v>541</v>
-      </c>
-      <c r="B264" t="s">
-        <v>542</v>
-      </c>
-      <c r="D264" t="s">
+      <c r="A264" s="4">
+        <v>247</v>
+      </c>
+      <c r="B264" s="4" t="s">
         <v>543</v>
       </c>
-      <c r="E264">
-        <v>245</v>
+      <c r="C264" s="4" t="s">
+        <v>395</v>
+      </c>
+      <c r="D264" s="4" t="s">
+        <v>544</v>
+      </c>
+      <c r="E264" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F264" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G264" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H264" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I264" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J264" s="4">
+        <v>0</v>
+      </c>
+      <c r="K264" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L264" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="s">
+        <v>545</v>
+      </c>
+      <c r="B266" t="s">
+        <v>546</v>
+      </c>
+      <c r="D266" t="s">
+        <v>547</v>
+      </c>
+      <c r="E266">
+        <v>247</v>
       </c>
     </row>
   </sheetData>

--- a/report-2026-06-04.xlsx
+++ b/report-2026-06-04.xlsx
@@ -21,7 +21,7 @@
     <t>PunMonitor Leader Election — Current State</t>
   </si>
   <si>
-    <t>Generated 2026-06-04T20:23:25+05:30</t>
+    <t>Generated 2026-06-04T20:23:38+05:30</t>
   </si>
   <si>
     <t>Election method</t>
@@ -72,7 +72,7 @@
     <t>Leader last update</t>
   </si>
   <si>
-    <t>2026-06-04T20:21:38+05:30 (1m46s ago)</t>
+    <t>2026-06-04T20:21:38+05:30 (2m0s ago)</t>
   </si>
   <si>
     <t>Leader stale?</t>
@@ -1657,7 +1657,7 @@
     <t>Generated</t>
   </si>
   <si>
-    <t>2026-06-04T20:23:25+05:30</t>
+    <t>2026-06-04T20:23:38+05:30</t>
   </si>
   <si>
     <t>Total events</t>
@@ -2252,7 +2252,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>0h 12m 36s</t>
+          <t>0h 12m 50s</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -2282,7 +2282,7 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>20:23:25</t>
+          <t>20:23:38</t>
         </is>
       </c>
     </row>
@@ -2339,17 +2339,17 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>506.0</t>
+          <t>376.0</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>194824.9</t>
+          <t>161861.3</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>8575</t>
+          <t>8719</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -2389,7 +2389,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>20:23:25</t>
+          <t>20:23:38</t>
         </is>
       </c>
     </row>

--- a/report-2026-06-04.xlsx
+++ b/report-2026-06-04.xlsx
@@ -16,12 +16,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="548" uniqueCount="548">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="554" uniqueCount="554">
   <si>
     <t>PunMonitor Leader Election — Current State</t>
   </si>
   <si>
-    <t>Generated 2026-06-04T20:23:38+05:30</t>
+    <t>Generated 2026-06-04T20:29:35+05:30</t>
   </si>
   <si>
     <t>Election method</t>
@@ -72,7 +72,7 @@
     <t>Leader last update</t>
   </si>
   <si>
-    <t>2026-06-04T20:21:38+05:30 (2m0s ago)</t>
+    <t>2026-06-04T20:27:35+05:30 (2m0s ago)</t>
   </si>
   <si>
     <t>Leader stale?</t>
@@ -87,7 +87,7 @@
     <t>Check count</t>
   </si>
   <si>
-    <t>9</t>
+    <t>1</t>
   </si>
   <si>
     <t>Last error</t>
@@ -1654,10 +1654,28 @@
     <t>20:21:11.161</t>
   </si>
   <si>
+    <t>2026-06-04T20:23:41.0058288+05:30</t>
+  </si>
+  <si>
+    <t>20:23:41.005</t>
+  </si>
+  <si>
+    <t>2026-06-04T20:26:11.108604+05:30</t>
+  </si>
+  <si>
+    <t>20:26:11.108</t>
+  </si>
+  <si>
+    <t>2026-06-04T20:27:35.5376596+05:30</t>
+  </si>
+  <si>
+    <t>20:27:35.537</t>
+  </si>
+  <si>
     <t>Generated</t>
   </si>
   <si>
-    <t>2026-06-04T20:23:38+05:30</t>
+    <t>2026-06-04T20:29:35+05:30</t>
   </si>
   <si>
     <t>Total events</t>
@@ -2212,7 +2230,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>10.0.46</t>
+          <t>10.0.47</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -2252,12 +2270,12 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>0h 12m 50s</t>
+          <t>0h 2m 19s</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>2026-06-04 20:10:48</t>
+          <t>2026-06-04 20:27:15</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
@@ -2267,12 +2285,12 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2026-06-04 20:10:48</t>
+          <t>2026-06-04 20:27:15</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>11h 11m 20s</t>
+          <t>11h 12m 45s</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -2282,7 +2300,7 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>20:23:38</t>
+          <t>20:29:35</t>
         </is>
       </c>
     </row>
@@ -2319,7 +2337,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>10.0.46</t>
+          <t>10.0.47</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -2339,17 +2357,17 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>376.0</t>
+          <t>119.0</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>161861.3</t>
+          <t>205349.5</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>8719</t>
+          <t>1716</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -2359,7 +2377,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>650</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -2374,12 +2392,12 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-06-04 20:10:48</t>
+          <t>2026-06-04 20:27:15</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>11h 11m 5s</t>
+          <t>11h 12m 0s</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -2389,7 +2407,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>20:23:38</t>
+          <t>20:29:35</t>
         </is>
       </c>
     </row>
@@ -2508,7 +2526,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-06-04T20:21:11.1612413+05:30</t>
+          <t>2026-06-04T20:27:35.5376596+05:30</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -2518,7 +2536,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>20:21:11.161</t>
+          <t>20:27:35.537</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -13900,18 +13918,132 @@
         <v>43</v>
       </c>
     </row>
+    <row r="265">
+      <c r="A265" s="4">
+        <v>248</v>
+      </c>
+      <c r="B265" s="4" t="s">
+        <v>545</v>
+      </c>
+      <c r="C265" s="4" t="s">
+        <v>395</v>
+      </c>
+      <c r="D265" s="4" t="s">
+        <v>546</v>
+      </c>
+      <c r="E265" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F265" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G265" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H265" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I265" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J265" s="4">
+        <v>0</v>
+      </c>
+      <c r="K265" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L265" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
     <row r="266">
-      <c r="A266" t="s">
-        <v>545</v>
-      </c>
-      <c r="B266" t="s">
-        <v>546</v>
-      </c>
-      <c r="D266" t="s">
+      <c r="A266" s="4">
+        <v>249</v>
+      </c>
+      <c r="B266" s="4" t="s">
         <v>547</v>
       </c>
-      <c r="E266">
-        <v>247</v>
+      <c r="C266" s="4" t="s">
+        <v>395</v>
+      </c>
+      <c r="D266" s="4" t="s">
+        <v>548</v>
+      </c>
+      <c r="E266" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F266" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G266" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H266" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I266" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J266" s="4">
+        <v>0</v>
+      </c>
+      <c r="K266" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L266" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" s="4">
+        <v>250</v>
+      </c>
+      <c r="B267" s="4" t="s">
+        <v>549</v>
+      </c>
+      <c r="C267" s="4" t="s">
+        <v>395</v>
+      </c>
+      <c r="D267" s="4" t="s">
+        <v>550</v>
+      </c>
+      <c r="E267" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F267" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G267" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H267" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I267" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J267" s="4">
+        <v>0</v>
+      </c>
+      <c r="K267" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L267" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="s">
+        <v>551</v>
+      </c>
+      <c r="B269" t="s">
+        <v>552</v>
+      </c>
+      <c r="D269" t="s">
+        <v>553</v>
+      </c>
+      <c r="E269">
+        <v>250</v>
       </c>
     </row>
   </sheetData>

--- a/report-2026-06-04.xlsx
+++ b/report-2026-06-04.xlsx
@@ -16,12 +16,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="554" uniqueCount="554">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="558" uniqueCount="558">
   <si>
     <t>PunMonitor Leader Election — Current State</t>
   </si>
   <si>
-    <t>Generated 2026-06-04T20:29:35+05:30</t>
+    <t>Generated 2026-06-04T20:35:22+05:30</t>
   </si>
   <si>
     <t>Election method</t>
@@ -72,7 +72,7 @@
     <t>Leader last update</t>
   </si>
   <si>
-    <t>2026-06-04T20:27:35+05:30 (2m0s ago)</t>
+    <t>2026-06-04T20:33:22+05:30 (2m0s ago)</t>
   </si>
   <si>
     <t>Leader stale?</t>
@@ -1672,10 +1672,22 @@
     <t>20:27:35.537</t>
   </si>
   <si>
+    <t>2026-06-04T20:30:06.9029531+05:30</t>
+  </si>
+  <si>
+    <t>20:30:06.902</t>
+  </si>
+  <si>
+    <t>2026-06-04T20:32:37.2564887+05:30</t>
+  </si>
+  <si>
+    <t>20:32:37.256</t>
+  </si>
+  <si>
     <t>Generated</t>
   </si>
   <si>
-    <t>2026-06-04T20:29:35+05:30</t>
+    <t>2026-06-04T20:35:22+05:30</t>
   </si>
   <si>
     <t>Total events</t>
@@ -2230,7 +2242,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>10.0.47</t>
+          <t>10.0.48</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -2270,12 +2282,12 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>0h 2m 19s</t>
+          <t>0h 2m 17s</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>2026-06-04 20:27:15</t>
+          <t>2026-06-04 20:33:04</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
@@ -2285,12 +2297,12 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2026-06-04 20:27:15</t>
+          <t>2026-06-04 20:33:04</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>11h 12m 45s</t>
+          <t>11h 13m 10s</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -2300,7 +2312,7 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>20:29:35</t>
+          <t>20:35:22</t>
         </is>
       </c>
     </row>
@@ -2337,7 +2349,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>10.0.47</t>
+          <t>10.0.48</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -2357,17 +2369,17 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>119.0</t>
+          <t>128.0</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>205349.5</t>
+          <t>249167.5</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>1716</t>
+          <t>1807</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -2377,7 +2389,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>18</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -2392,12 +2404,12 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-06-04 20:27:15</t>
+          <t>2026-06-04 20:33:04</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>11h 12m 0s</t>
+          <t>11h 12m 50s</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -2407,7 +2419,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>20:29:35</t>
+          <t>20:35:22</t>
         </is>
       </c>
     </row>
@@ -2526,7 +2538,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-06-04T20:27:35.5376596+05:30</t>
+          <t>2026-06-04T20:32:37.2564887+05:30</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -2536,7 +2548,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>20:27:35.537</t>
+          <t>20:32:37.256</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -14032,18 +14044,94 @@
         <v>43</v>
       </c>
     </row>
+    <row r="268">
+      <c r="A268" s="4">
+        <v>251</v>
+      </c>
+      <c r="B268" s="4" t="s">
+        <v>551</v>
+      </c>
+      <c r="C268" s="4" t="s">
+        <v>395</v>
+      </c>
+      <c r="D268" s="4" t="s">
+        <v>552</v>
+      </c>
+      <c r="E268" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F268" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G268" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H268" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I268" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J268" s="4">
+        <v>0</v>
+      </c>
+      <c r="K268" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L268" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
     <row r="269">
-      <c r="A269" t="s">
-        <v>551</v>
-      </c>
-      <c r="B269" t="s">
-        <v>552</v>
-      </c>
-      <c r="D269" t="s">
+      <c r="A269" s="4">
+        <v>252</v>
+      </c>
+      <c r="B269" s="4" t="s">
         <v>553</v>
       </c>
-      <c r="E269">
-        <v>250</v>
+      <c r="C269" s="4" t="s">
+        <v>395</v>
+      </c>
+      <c r="D269" s="4" t="s">
+        <v>554</v>
+      </c>
+      <c r="E269" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F269" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G269" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H269" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I269" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J269" s="4">
+        <v>0</v>
+      </c>
+      <c r="K269" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L269" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="s">
+        <v>555</v>
+      </c>
+      <c r="B271" t="s">
+        <v>556</v>
+      </c>
+      <c r="D271" t="s">
+        <v>557</v>
+      </c>
+      <c r="E271">
+        <v>252</v>
       </c>
     </row>
   </sheetData>

--- a/report-2026-06-04.xlsx
+++ b/report-2026-06-04.xlsx
@@ -16,12 +16,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="558" uniqueCount="558">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="562" uniqueCount="562">
   <si>
     <t>PunMonitor Leader Election — Current State</t>
   </si>
   <si>
-    <t>Generated 2026-06-04T20:35:22+05:30</t>
+    <t>Generated 2026-06-04T20:40:35+05:30</t>
   </si>
   <si>
     <t>Election method</t>
@@ -72,7 +72,7 @@
     <t>Leader last update</t>
   </si>
   <si>
-    <t>2026-06-04T20:33:22+05:30 (2m0s ago)</t>
+    <t>2026-06-04T20:38:35+05:30 (2m0s ago)</t>
   </si>
   <si>
     <t>Leader stale?</t>
@@ -87,7 +87,7 @@
     <t>Check count</t>
   </si>
   <si>
-    <t>1</t>
+    <t>4</t>
   </si>
   <si>
     <t>Last error</t>
@@ -1684,10 +1684,22 @@
     <t>20:32:37.256</t>
   </si>
   <si>
+    <t>2026-06-04T20:35:53.4386025+05:30</t>
+  </si>
+  <si>
+    <t>20:35:53.438</t>
+  </si>
+  <si>
+    <t>2026-06-04T20:38:23.6122987+05:30</t>
+  </si>
+  <si>
+    <t>20:38:23.612</t>
+  </si>
+  <si>
     <t>Generated</t>
   </si>
   <si>
-    <t>2026-06-04T20:35:22+05:30</t>
+    <t>2026-06-04T20:40:35+05:30</t>
   </si>
   <si>
     <t>Total events</t>
@@ -2282,7 +2294,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>0h 2m 17s</t>
+          <t>0h 7m 31s</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -2302,7 +2314,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>11h 13m 10s</t>
+          <t>11h 13m 15s</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -2312,7 +2324,7 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>20:35:22</t>
+          <t>20:40:35</t>
         </is>
       </c>
     </row>
@@ -2369,17 +2381,17 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>194.0</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>249167.5</t>
+          <t>181294.7</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>1807</t>
+          <t>6528</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -2389,7 +2401,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>331</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -2409,7 +2421,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>11h 12m 50s</t>
+          <t>11h 13m 10s</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -2419,7 +2431,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>20:35:22</t>
+          <t>20:40:35</t>
         </is>
       </c>
     </row>
@@ -2538,7 +2550,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-06-04T20:32:37.2564887+05:30</t>
+          <t>2026-06-04T20:38:23.6122987+05:30</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -2548,7 +2560,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>20:32:37.256</t>
+          <t>20:38:23.612</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -14120,18 +14132,94 @@
         <v>43</v>
       </c>
     </row>
+    <row r="270">
+      <c r="A270" s="4">
+        <v>253</v>
+      </c>
+      <c r="B270" s="4" t="s">
+        <v>555</v>
+      </c>
+      <c r="C270" s="4" t="s">
+        <v>395</v>
+      </c>
+      <c r="D270" s="4" t="s">
+        <v>556</v>
+      </c>
+      <c r="E270" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F270" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G270" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H270" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I270" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J270" s="4">
+        <v>0</v>
+      </c>
+      <c r="K270" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L270" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
     <row r="271">
-      <c r="A271" t="s">
-        <v>555</v>
-      </c>
-      <c r="B271" t="s">
-        <v>556</v>
-      </c>
-      <c r="D271" t="s">
+      <c r="A271" s="4">
+        <v>254</v>
+      </c>
+      <c r="B271" s="4" t="s">
         <v>557</v>
       </c>
-      <c r="E271">
-        <v>252</v>
+      <c r="C271" s="4" t="s">
+        <v>395</v>
+      </c>
+      <c r="D271" s="4" t="s">
+        <v>558</v>
+      </c>
+      <c r="E271" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F271" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G271" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H271" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I271" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J271" s="4">
+        <v>0</v>
+      </c>
+      <c r="K271" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L271" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="s">
+        <v>559</v>
+      </c>
+      <c r="B273" t="s">
+        <v>560</v>
+      </c>
+      <c r="D273" t="s">
+        <v>561</v>
+      </c>
+      <c r="E273">
+        <v>254</v>
       </c>
     </row>
   </sheetData>

--- a/report-2026-06-04.xlsx
+++ b/report-2026-06-04.xlsx
@@ -16,12 +16,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="562" uniqueCount="562">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="566" uniqueCount="566">
   <si>
     <t>PunMonitor Leader Election — Current State</t>
   </si>
   <si>
-    <t>Generated 2026-06-04T20:40:35+05:30</t>
+    <t>Generated 2026-06-04T20:46:05+05:30</t>
   </si>
   <si>
     <t>Election method</t>
@@ -72,7 +72,7 @@
     <t>Leader last update</t>
   </si>
   <si>
-    <t>2026-06-04T20:38:35+05:30 (2m0s ago)</t>
+    <t>2026-06-04T20:44:05+05:30 (2m0s ago)</t>
   </si>
   <si>
     <t>Leader stale?</t>
@@ -87,7 +87,7 @@
     <t>Check count</t>
   </si>
   <si>
-    <t>4</t>
+    <t>1</t>
   </si>
   <si>
     <t>Last error</t>
@@ -1696,10 +1696,22 @@
     <t>20:38:23.612</t>
   </si>
   <si>
+    <t>2026-06-04T20:40:53.4304118+05:30</t>
+  </si>
+  <si>
+    <t>20:40:53.430</t>
+  </si>
+  <si>
+    <t>2026-06-04T20:43:23.8741767+05:30</t>
+  </si>
+  <si>
+    <t>20:43:23.874</t>
+  </si>
+  <si>
     <t>Generated</t>
   </si>
   <si>
-    <t>2026-06-04T20:40:35+05:30</t>
+    <t>2026-06-04T20:46:05+05:30</t>
   </si>
   <si>
     <t>Total events</t>
@@ -2254,7 +2266,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>10.0.48</t>
+          <t>10.0.49</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -2294,12 +2306,12 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>0h 7m 31s</t>
+          <t>0h 2m 17s</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>2026-06-04 20:33:04</t>
+          <t>2026-06-04 20:43:48</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
@@ -2309,12 +2321,12 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2026-06-04 20:33:04</t>
+          <t>2026-06-04 20:43:48</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>11h 13m 15s</t>
+          <t>11h 16m 10s</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -2324,7 +2336,7 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>20:40:35</t>
+          <t>20:46:05</t>
         </is>
       </c>
     </row>
@@ -2361,7 +2373,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>10.0.48</t>
+          <t>10.0.49</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -2381,17 +2393,17 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>194.0</t>
+          <t>150.0</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>181294.7</t>
+          <t>121788.7</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>6528</t>
+          <t>1843</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -2401,7 +2413,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>331</t>
+          <t>18</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -2416,12 +2428,12 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-06-04 20:33:04</t>
+          <t>2026-06-04 20:43:48</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>11h 13m 10s</t>
+          <t>11h 15m 0s</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -2431,7 +2443,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>20:40:35</t>
+          <t>20:46:05</t>
         </is>
       </c>
     </row>
@@ -2550,7 +2562,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-06-04T20:38:23.6122987+05:30</t>
+          <t>2026-06-04T20:43:23.8741767+05:30</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -2560,7 +2572,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>20:38:23.612</t>
+          <t>20:43:23.874</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -14208,18 +14220,94 @@
         <v>43</v>
       </c>
     </row>
+    <row r="272">
+      <c r="A272" s="4">
+        <v>255</v>
+      </c>
+      <c r="B272" s="4" t="s">
+        <v>559</v>
+      </c>
+      <c r="C272" s="4" t="s">
+        <v>395</v>
+      </c>
+      <c r="D272" s="4" t="s">
+        <v>560</v>
+      </c>
+      <c r="E272" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F272" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G272" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H272" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I272" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J272" s="4">
+        <v>0</v>
+      </c>
+      <c r="K272" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L272" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
     <row r="273">
-      <c r="A273" t="s">
-        <v>559</v>
-      </c>
-      <c r="B273" t="s">
-        <v>560</v>
-      </c>
-      <c r="D273" t="s">
+      <c r="A273" s="4">
+        <v>256</v>
+      </c>
+      <c r="B273" s="4" t="s">
         <v>561</v>
       </c>
-      <c r="E273">
-        <v>254</v>
+      <c r="C273" s="4" t="s">
+        <v>395</v>
+      </c>
+      <c r="D273" s="4" t="s">
+        <v>562</v>
+      </c>
+      <c r="E273" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F273" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G273" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H273" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I273" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J273" s="4">
+        <v>0</v>
+      </c>
+      <c r="K273" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L273" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="s">
+        <v>563</v>
+      </c>
+      <c r="B275" t="s">
+        <v>564</v>
+      </c>
+      <c r="D275" t="s">
+        <v>565</v>
+      </c>
+      <c r="E275">
+        <v>256</v>
       </c>
     </row>
   </sheetData>

--- a/report-2026-06-04.xlsx
+++ b/report-2026-06-04.xlsx
@@ -16,12 +16,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="566" uniqueCount="566">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="570" uniqueCount="570">
   <si>
     <t>PunMonitor Leader Election — Current State</t>
   </si>
   <si>
-    <t>Generated 2026-06-04T20:46:05+05:30</t>
+    <t>Generated 2026-06-04T20:51:23+05:30</t>
   </si>
   <si>
     <t>Election method</t>
@@ -72,7 +72,7 @@
     <t>Leader last update</t>
   </si>
   <si>
-    <t>2026-06-04T20:44:05+05:30 (2m0s ago)</t>
+    <t>2026-06-04T20:49:23+05:30 (2m0s ago)</t>
   </si>
   <si>
     <t>Leader stale?</t>
@@ -87,7 +87,7 @@
     <t>Check count</t>
   </si>
   <si>
-    <t>1</t>
+    <t>4</t>
   </si>
   <si>
     <t>Last error</t>
@@ -1708,10 +1708,22 @@
     <t>20:43:23.874</t>
   </si>
   <si>
+    <t>2026-06-04T20:46:37.1046834+05:30</t>
+  </si>
+  <si>
+    <t>20:46:37.104</t>
+  </si>
+  <si>
+    <t>2026-06-04T20:49:07.227584+05:30</t>
+  </si>
+  <si>
+    <t>20:49:07.227</t>
+  </si>
+  <si>
     <t>Generated</t>
   </si>
   <si>
-    <t>2026-06-04T20:46:05+05:30</t>
+    <t>2026-06-04T20:51:23+05:30</t>
   </si>
   <si>
     <t>Total events</t>
@@ -2306,7 +2318,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>0h 2m 17s</t>
+          <t>0h 7m 35s</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -2326,7 +2338,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>11h 16m 10s</t>
+          <t>11h 16m 35s</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -2336,7 +2348,7 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>20:46:05</t>
+          <t>20:51:23</t>
         </is>
       </c>
     </row>
@@ -2393,17 +2405,17 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>150.0</t>
+          <t>322.0</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>121788.7</t>
+          <t>137608.7</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>1843</t>
+          <t>6380</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -2413,7 +2425,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>335</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -2433,7 +2445,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>11h 15m 0s</t>
+          <t>11h 16m 15s</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -2443,7 +2455,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>20:46:05</t>
+          <t>20:51:23</t>
         </is>
       </c>
     </row>
@@ -2562,7 +2574,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-06-04T20:43:23.8741767+05:30</t>
+          <t>2026-06-04T20:49:07.227584+05:30</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -2572,7 +2584,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>20:43:23.874</t>
+          <t>20:49:07.227</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -14296,18 +14308,94 @@
         <v>43</v>
       </c>
     </row>
+    <row r="274">
+      <c r="A274" s="4">
+        <v>257</v>
+      </c>
+      <c r="B274" s="4" t="s">
+        <v>563</v>
+      </c>
+      <c r="C274" s="4" t="s">
+        <v>395</v>
+      </c>
+      <c r="D274" s="4" t="s">
+        <v>564</v>
+      </c>
+      <c r="E274" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F274" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G274" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H274" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I274" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J274" s="4">
+        <v>0</v>
+      </c>
+      <c r="K274" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L274" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
     <row r="275">
-      <c r="A275" t="s">
-        <v>563</v>
-      </c>
-      <c r="B275" t="s">
-        <v>564</v>
-      </c>
-      <c r="D275" t="s">
+      <c r="A275" s="4">
+        <v>258</v>
+      </c>
+      <c r="B275" s="4" t="s">
         <v>565</v>
       </c>
-      <c r="E275">
-        <v>256</v>
+      <c r="C275" s="4" t="s">
+        <v>395</v>
+      </c>
+      <c r="D275" s="4" t="s">
+        <v>566</v>
+      </c>
+      <c r="E275" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F275" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G275" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H275" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I275" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J275" s="4">
+        <v>0</v>
+      </c>
+      <c r="K275" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L275" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="s">
+        <v>567</v>
+      </c>
+      <c r="B277" t="s">
+        <v>568</v>
+      </c>
+      <c r="D277" t="s">
+        <v>569</v>
+      </c>
+      <c r="E277">
+        <v>258</v>
       </c>
     </row>
   </sheetData>

--- a/report-2026-06-04.xlsx
+++ b/report-2026-06-04.xlsx
@@ -16,12 +16,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="570" uniqueCount="570">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="574" uniqueCount="574">
   <si>
     <t>PunMonitor Leader Election — Current State</t>
   </si>
   <si>
-    <t>Generated 2026-06-04T20:51:23+05:30</t>
+    <t>Generated 2026-06-04T20:56:17+05:30</t>
   </si>
   <si>
     <t>Election method</t>
@@ -72,7 +72,7 @@
     <t>Leader last update</t>
   </si>
   <si>
-    <t>2026-06-04T20:49:23+05:30 (2m0s ago)</t>
+    <t>2026-06-04T20:54:39+05:30 (1m38s ago)</t>
   </si>
   <si>
     <t>Leader stale?</t>
@@ -87,7 +87,7 @@
     <t>Check count</t>
   </si>
   <si>
-    <t>4</t>
+    <t>9</t>
   </si>
   <si>
     <t>Last error</t>
@@ -1720,10 +1720,22 @@
     <t>20:49:07.227</t>
   </si>
   <si>
+    <t>2026-06-04T20:51:37.1592094+05:30</t>
+  </si>
+  <si>
+    <t>20:51:37.159</t>
+  </si>
+  <si>
+    <t>2026-06-04T20:54:07.3900752+05:30</t>
+  </si>
+  <si>
+    <t>20:54:07.390</t>
+  </si>
+  <si>
     <t>Generated</t>
   </si>
   <si>
-    <t>2026-06-04T20:51:23+05:30</t>
+    <t>2026-06-04T20:56:17+05:30</t>
   </si>
   <si>
     <t>Total events</t>
@@ -2318,7 +2330,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>0h 7m 35s</t>
+          <t>0h 12m 29s</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -2338,7 +2350,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>11h 16m 35s</t>
+          <t>11h 18m 25s</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -2348,7 +2360,7 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>20:51:23</t>
+          <t>20:56:17</t>
         </is>
       </c>
     </row>
@@ -2405,17 +2417,17 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>322.0</t>
+          <t>517.0</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>137608.7</t>
+          <t>113561.1</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>6380</t>
+          <t>9523</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -2425,7 +2437,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>335</t>
+          <t>651</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -2445,7 +2457,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>11h 16m 15s</t>
+          <t>11h 18m 5s</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -2455,7 +2467,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>20:51:23</t>
+          <t>20:56:17</t>
         </is>
       </c>
     </row>
@@ -2574,7 +2586,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-06-04T20:49:07.227584+05:30</t>
+          <t>2026-06-04T20:54:07.3900752+05:30</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -2584,7 +2596,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>20:49:07.227</t>
+          <t>20:54:07.390</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -14384,18 +14396,94 @@
         <v>43</v>
       </c>
     </row>
+    <row r="276">
+      <c r="A276" s="4">
+        <v>259</v>
+      </c>
+      <c r="B276" s="4" t="s">
+        <v>567</v>
+      </c>
+      <c r="C276" s="4" t="s">
+        <v>395</v>
+      </c>
+      <c r="D276" s="4" t="s">
+        <v>568</v>
+      </c>
+      <c r="E276" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F276" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G276" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H276" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I276" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J276" s="4">
+        <v>0</v>
+      </c>
+      <c r="K276" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L276" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
     <row r="277">
-      <c r="A277" t="s">
-        <v>567</v>
-      </c>
-      <c r="B277" t="s">
-        <v>568</v>
-      </c>
-      <c r="D277" t="s">
+      <c r="A277" s="4">
+        <v>260</v>
+      </c>
+      <c r="B277" s="4" t="s">
         <v>569</v>
       </c>
-      <c r="E277">
-        <v>258</v>
+      <c r="C277" s="4" t="s">
+        <v>395</v>
+      </c>
+      <c r="D277" s="4" t="s">
+        <v>570</v>
+      </c>
+      <c r="E277" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F277" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G277" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H277" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I277" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J277" s="4">
+        <v>0</v>
+      </c>
+      <c r="K277" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L277" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="s">
+        <v>571</v>
+      </c>
+      <c r="B279" t="s">
+        <v>572</v>
+      </c>
+      <c r="D279" t="s">
+        <v>573</v>
+      </c>
+      <c r="E279">
+        <v>260</v>
       </c>
     </row>
   </sheetData>

--- a/report-2026-06-04.xlsx
+++ b/report-2026-06-04.xlsx
@@ -16,12 +16,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="574" uniqueCount="574">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="576" uniqueCount="576">
   <si>
     <t>PunMonitor Leader Election — Current State</t>
   </si>
   <si>
-    <t>Generated 2026-06-04T20:56:17+05:30</t>
+    <t>Generated 2026-06-04T20:56:39+05:30</t>
   </si>
   <si>
     <t>Election method</t>
@@ -72,7 +72,7 @@
     <t>Leader last update</t>
   </si>
   <si>
-    <t>2026-06-04T20:54:39+05:30 (1m38s ago)</t>
+    <t>2026-06-04T20:56:37+05:30 (1s ago)</t>
   </si>
   <si>
     <t>Leader stale?</t>
@@ -87,7 +87,7 @@
     <t>Check count</t>
   </si>
   <si>
-    <t>9</t>
+    <t>10</t>
   </si>
   <si>
     <t>Last error</t>
@@ -1732,10 +1732,16 @@
     <t>20:54:07.390</t>
   </si>
   <si>
+    <t>2026-06-04T20:56:37.2053098+05:30</t>
+  </si>
+  <si>
+    <t>20:56:37.205</t>
+  </si>
+  <si>
     <t>Generated</t>
   </si>
   <si>
-    <t>2026-06-04T20:56:17+05:30</t>
+    <t>2026-06-04T20:56:39+05:30</t>
   </si>
   <si>
     <t>Total events</t>
@@ -2330,7 +2336,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>0h 12m 29s</t>
+          <t>0h 12m 51s</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -2350,7 +2356,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>11h 18m 25s</t>
+          <t>11h 18m 30s</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -2360,7 +2366,7 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>20:56:17</t>
+          <t>20:56:39</t>
         </is>
       </c>
     </row>
@@ -2417,17 +2423,17 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>517.0</t>
+          <t>536.0</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>113561.1</t>
+          <t>108714.5</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>9523</t>
+          <t>9606</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -2467,7 +2473,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>20:56:17</t>
+          <t>20:56:39</t>
         </is>
       </c>
     </row>
@@ -2586,7 +2592,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-06-04T20:54:07.3900752+05:30</t>
+          <t>2026-06-04T20:56:37.2053098+05:30</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -2596,7 +2602,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>20:54:07.390</t>
+          <t>20:56:37.205</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -14472,18 +14478,56 @@
         <v>43</v>
       </c>
     </row>
-    <row r="279">
-      <c r="A279" t="s">
+    <row r="278">
+      <c r="A278" s="4">
+        <v>261</v>
+      </c>
+      <c r="B278" s="4" t="s">
         <v>571</v>
       </c>
-      <c r="B279" t="s">
+      <c r="C278" s="4" t="s">
+        <v>395</v>
+      </c>
+      <c r="D278" s="4" t="s">
         <v>572</v>
       </c>
-      <c r="D279" t="s">
+      <c r="E278" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F278" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G278" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H278" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I278" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J278" s="4">
+        <v>0</v>
+      </c>
+      <c r="K278" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L278" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="s">
         <v>573</v>
       </c>
-      <c r="E279">
-        <v>260</v>
+      <c r="B280" t="s">
+        <v>574</v>
+      </c>
+      <c r="D280" t="s">
+        <v>575</v>
+      </c>
+      <c r="E280">
+        <v>261</v>
       </c>
     </row>
   </sheetData>

--- a/report-2026-06-04.xlsx
+++ b/report-2026-06-04.xlsx
@@ -16,12 +16,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="576" uniqueCount="576">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="578" uniqueCount="578">
   <si>
     <t>PunMonitor Leader Election — Current State</t>
   </si>
   <si>
-    <t>Generated 2026-06-04T20:56:39+05:30</t>
+    <t>Generated 2026-06-04T21:01:22+05:30</t>
   </si>
   <si>
     <t>Election method</t>
@@ -72,7 +72,7 @@
     <t>Leader last update</t>
   </si>
   <si>
-    <t>2026-06-04T20:56:37+05:30 (1s ago)</t>
+    <t>2026-06-04T20:59:44+05:30 (1m38s ago)</t>
   </si>
   <si>
     <t>Leader stale?</t>
@@ -87,7 +87,7 @@
     <t>Check count</t>
   </si>
   <si>
-    <t>10</t>
+    <t>14</t>
   </si>
   <si>
     <t>Last error</t>
@@ -1738,10 +1738,16 @@
     <t>20:56:37.205</t>
   </si>
   <si>
+    <t>2026-06-04T20:59:07.3354306+05:30</t>
+  </si>
+  <si>
+    <t>20:59:07.335</t>
+  </si>
+  <si>
     <t>Generated</t>
   </si>
   <si>
-    <t>2026-06-04T20:56:39+05:30</t>
+    <t>2026-06-04T21:01:22+05:30</t>
   </si>
   <si>
     <t>Total events</t>
@@ -2336,7 +2342,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>0h 12m 51s</t>
+          <t>0h 17m 34s</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -2356,7 +2362,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>11h 18m 30s</t>
+          <t>11h 20m 15s</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -2366,7 +2372,7 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>20:56:39</t>
+          <t>21:01:22</t>
         </is>
       </c>
     </row>
@@ -2423,17 +2429,17 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>536.0</t>
+          <t>650.0</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>108714.5</t>
+          <t>126246.7</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>9606</t>
+          <t>11095</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -2443,7 +2449,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>651</t>
+          <t>956</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -2463,7 +2469,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>11h 18m 5s</t>
+          <t>11h 19m 35s</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -2473,7 +2479,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>20:56:39</t>
+          <t>21:01:22</t>
         </is>
       </c>
     </row>
@@ -2592,7 +2598,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-06-04T20:56:37.2053098+05:30</t>
+          <t>2026-06-04T20:59:07.3354306+05:30</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -2602,7 +2608,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>20:56:37.205</t>
+          <t>20:59:07.335</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -14516,18 +14522,56 @@
         <v>43</v>
       </c>
     </row>
-    <row r="280">
-      <c r="A280" t="s">
+    <row r="279">
+      <c r="A279" s="4">
+        <v>262</v>
+      </c>
+      <c r="B279" s="4" t="s">
         <v>573</v>
       </c>
-      <c r="B280" t="s">
+      <c r="C279" s="4" t="s">
+        <v>395</v>
+      </c>
+      <c r="D279" s="4" t="s">
         <v>574</v>
       </c>
-      <c r="D280" t="s">
+      <c r="E279" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F279" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G279" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H279" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I279" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J279" s="4">
+        <v>0</v>
+      </c>
+      <c r="K279" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L279" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="s">
         <v>575</v>
       </c>
-      <c r="E280">
-        <v>261</v>
+      <c r="B281" t="s">
+        <v>576</v>
+      </c>
+      <c r="D281" t="s">
+        <v>577</v>
+      </c>
+      <c r="E281">
+        <v>262</v>
       </c>
     </row>
   </sheetData>

--- a/report-2026-06-04.xlsx
+++ b/report-2026-06-04.xlsx
@@ -21,7 +21,7 @@
     <t>PunMonitor Leader Election — Current State</t>
   </si>
   <si>
-    <t>Generated 2026-06-04T21:01:22+05:30</t>
+    <t>Generated 2026-06-04T21:01:44+05:30</t>
   </si>
   <si>
     <t>Election method</t>
@@ -72,7 +72,7 @@
     <t>Leader last update</t>
   </si>
   <si>
-    <t>2026-06-04T20:59:44+05:30 (1m38s ago)</t>
+    <t>2026-06-04T20:59:44+05:30 (2m0s ago)</t>
   </si>
   <si>
     <t>Leader stale?</t>
@@ -1747,7 +1747,7 @@
     <t>Generated</t>
   </si>
   <si>
-    <t>2026-06-04T21:01:22+05:30</t>
+    <t>2026-06-04T21:01:44+05:30</t>
   </si>
   <si>
     <t>Total events</t>
@@ -2342,7 +2342,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>0h 17m 34s</t>
+          <t>0h 17m 56s</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -2362,7 +2362,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>11h 20m 15s</t>
+          <t>11h 20m 25s</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -2372,7 +2372,7 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>21:01:22</t>
+          <t>21:01:44</t>
         </is>
       </c>
     </row>
@@ -2429,17 +2429,17 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>650.0</t>
+          <t>495.0</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>126246.7</t>
+          <t>139236.3</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>11095</t>
+          <t>11308</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -2479,7 +2479,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>21:01:22</t>
+          <t>21:01:44</t>
         </is>
       </c>
     </row>

--- a/report-2026-06-04.xlsx
+++ b/report-2026-06-04.xlsx
@@ -16,12 +16,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="578" uniqueCount="578">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="582" uniqueCount="582">
   <si>
     <t>PunMonitor Leader Election — Current State</t>
   </si>
   <si>
-    <t>Generated 2026-06-04T21:01:44+05:30</t>
+    <t>Generated 2026-06-04T21:06:23+05:30</t>
   </si>
   <si>
     <t>Election method</t>
@@ -72,7 +72,7 @@
     <t>Leader last update</t>
   </si>
   <si>
-    <t>2026-06-04T20:59:44+05:30 (2m0s ago)</t>
+    <t>2026-06-04T21:05:00+05:30 (1m22s ago)</t>
   </si>
   <si>
     <t>Leader stale?</t>
@@ -87,7 +87,7 @@
     <t>Check count</t>
   </si>
   <si>
-    <t>14</t>
+    <t>17</t>
   </si>
   <si>
     <t>Last error</t>
@@ -1744,10 +1744,22 @@
     <t>20:59:07.335</t>
   </si>
   <si>
+    <t>2026-06-04T21:02:15.6092934+05:30</t>
+  </si>
+  <si>
+    <t>21:02:15.609</t>
+  </si>
+  <si>
+    <t>2026-06-04T21:04:23.2658692+05:30</t>
+  </si>
+  <si>
+    <t>21:04:23.265</t>
+  </si>
+  <si>
     <t>Generated</t>
   </si>
   <si>
-    <t>2026-06-04T21:01:44+05:30</t>
+    <t>2026-06-04T21:06:23+05:30</t>
   </si>
   <si>
     <t>Total events</t>
@@ -2342,7 +2354,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>0h 17m 56s</t>
+          <t>0h 22m 35s</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -2362,7 +2374,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>11h 20m 25s</t>
+          <t>11h 23m 0s</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -2372,7 +2384,7 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>21:01:44</t>
+          <t>21:06:23</t>
         </is>
       </c>
     </row>
@@ -2429,17 +2441,17 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>495.0</t>
+          <t>1270.0</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>139236.3</t>
+          <t>144735.5</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>11308</t>
+          <t>14185</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -2449,7 +2461,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>956</t>
+          <t>1272</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -2469,7 +2481,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>11h 19m 35s</t>
+          <t>11h 21m 40s</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -2479,7 +2491,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>21:01:44</t>
+          <t>21:06:23</t>
         </is>
       </c>
     </row>
@@ -2598,7 +2610,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-06-04T20:59:07.3354306+05:30</t>
+          <t>2026-06-04T21:04:23.2658692+05:30</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -2608,7 +2620,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>20:59:07.335</t>
+          <t>21:04:23.265</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -14560,18 +14572,94 @@
         <v>43</v>
       </c>
     </row>
+    <row r="280">
+      <c r="A280" s="4">
+        <v>263</v>
+      </c>
+      <c r="B280" s="4" t="s">
+        <v>575</v>
+      </c>
+      <c r="C280" s="4" t="s">
+        <v>395</v>
+      </c>
+      <c r="D280" s="4" t="s">
+        <v>576</v>
+      </c>
+      <c r="E280" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F280" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G280" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H280" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I280" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J280" s="4">
+        <v>0</v>
+      </c>
+      <c r="K280" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L280" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
     <row r="281">
-      <c r="A281" t="s">
-        <v>575</v>
-      </c>
-      <c r="B281" t="s">
-        <v>576</v>
-      </c>
-      <c r="D281" t="s">
+      <c r="A281" s="4">
+        <v>264</v>
+      </c>
+      <c r="B281" s="4" t="s">
         <v>577</v>
       </c>
-      <c r="E281">
-        <v>262</v>
+      <c r="C281" s="4" t="s">
+        <v>395</v>
+      </c>
+      <c r="D281" s="4" t="s">
+        <v>578</v>
+      </c>
+      <c r="E281" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F281" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G281" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H281" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I281" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J281" s="4">
+        <v>0</v>
+      </c>
+      <c r="K281" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L281" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="s">
+        <v>579</v>
+      </c>
+      <c r="B283" t="s">
+        <v>580</v>
+      </c>
+      <c r="D283" t="s">
+        <v>581</v>
+      </c>
+      <c r="E283">
+        <v>264</v>
       </c>
     </row>
   </sheetData>

--- a/report-2026-06-04.xlsx
+++ b/report-2026-06-04.xlsx
@@ -16,12 +16,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="582" uniqueCount="582">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="584" uniqueCount="584">
   <si>
     <t>PunMonitor Leader Election — Current State</t>
   </si>
   <si>
-    <t>Generated 2026-06-04T21:06:23+05:30</t>
+    <t>Generated 2026-06-04T21:08:53+05:30</t>
   </si>
   <si>
     <t>Election method</t>
@@ -72,7 +72,7 @@
     <t>Leader last update</t>
   </si>
   <si>
-    <t>2026-06-04T21:05:00+05:30 (1m22s ago)</t>
+    <t>2026-06-04T21:06:53+05:30 (2m0s ago)</t>
   </si>
   <si>
     <t>Leader stale?</t>
@@ -87,7 +87,7 @@
     <t>Check count</t>
   </si>
   <si>
-    <t>17</t>
+    <t>1</t>
   </si>
   <si>
     <t>Last error</t>
@@ -1756,10 +1756,16 @@
     <t>21:04:23.265</t>
   </si>
   <si>
+    <t>2026-06-04T21:06:53.4672925+05:30</t>
+  </si>
+  <si>
+    <t>21:06:53.467</t>
+  </si>
+  <si>
     <t>Generated</t>
   </si>
   <si>
-    <t>2026-06-04T21:06:23+05:30</t>
+    <t>2026-06-04T21:08:53+05:30</t>
   </si>
   <si>
     <t>Total events</t>
@@ -2314,7 +2320,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>10.0.49</t>
+          <t>10.0.50</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -2354,12 +2360,12 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>0h 22m 35s</t>
+          <t>0h 2m 16s</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>2026-06-04 20:43:48</t>
+          <t>2026-06-04 21:06:36</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
@@ -2369,12 +2375,12 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2026-06-04 20:43:48</t>
+          <t>2026-06-04 21:06:36</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>11h 23m 0s</t>
+          <t>11h 25m 15s</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -2384,7 +2390,7 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>21:06:23</t>
+          <t>21:08:53</t>
         </is>
       </c>
     </row>
@@ -2421,7 +2427,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>10.0.49</t>
+          <t>10.0.50</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -2441,17 +2447,17 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>1270.0</t>
+          <t>235.0</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>144735.5</t>
+          <t>125989.5</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>14185</t>
+          <t>1004</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -2461,7 +2467,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>1272</t>
+          <t>17</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -2476,12 +2482,12 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-06-04 20:43:48</t>
+          <t>2026-06-04 21:06:36</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>11h 21m 40s</t>
+          <t>11h 23m 20s</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -2491,7 +2497,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>21:06:23</t>
+          <t>21:08:53</t>
         </is>
       </c>
     </row>
@@ -2610,7 +2616,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-06-04T21:04:23.2658692+05:30</t>
+          <t>2026-06-04T21:06:53.4672925+05:30</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -2620,7 +2626,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>21:04:23.265</t>
+          <t>21:06:53.467</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -14648,18 +14654,56 @@
         <v>43</v>
       </c>
     </row>
-    <row r="283">
-      <c r="A283" t="s">
+    <row r="282">
+      <c r="A282" s="4">
+        <v>265</v>
+      </c>
+      <c r="B282" s="4" t="s">
         <v>579</v>
       </c>
-      <c r="B283" t="s">
+      <c r="C282" s="4" t="s">
+        <v>395</v>
+      </c>
+      <c r="D282" s="4" t="s">
         <v>580</v>
       </c>
-      <c r="D283" t="s">
+      <c r="E282" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F282" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G282" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H282" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I282" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J282" s="4">
+        <v>0</v>
+      </c>
+      <c r="K282" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L282" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="s">
         <v>581</v>
       </c>
-      <c r="E283">
-        <v>264</v>
+      <c r="B284" t="s">
+        <v>582</v>
+      </c>
+      <c r="D284" t="s">
+        <v>583</v>
+      </c>
+      <c r="E284">
+        <v>265</v>
       </c>
     </row>
   </sheetData>

--- a/report-2026-06-04.xlsx
+++ b/report-2026-06-04.xlsx
@@ -16,12 +16,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="584" uniqueCount="584">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="588" uniqueCount="588">
   <si>
     <t>PunMonitor Leader Election — Current State</t>
   </si>
   <si>
-    <t>Generated 2026-06-04T21:08:53+05:30</t>
+    <t>Generated 2026-06-04T21:14:08+05:30</t>
   </si>
   <si>
     <t>Election method</t>
@@ -72,7 +72,7 @@
     <t>Leader last update</t>
   </si>
   <si>
-    <t>2026-06-04T21:06:53+05:30 (2m0s ago)</t>
+    <t>2026-06-04T21:12:08+05:30 (2m0s ago)</t>
   </si>
   <si>
     <t>Leader stale?</t>
@@ -87,7 +87,7 @@
     <t>Check count</t>
   </si>
   <si>
-    <t>1</t>
+    <t>4</t>
   </si>
   <si>
     <t>Last error</t>
@@ -1762,10 +1762,22 @@
     <t>21:06:53.467</t>
   </si>
   <si>
+    <t>2026-06-04T21:09:25.0394416+05:30</t>
+  </si>
+  <si>
+    <t>21:09:25.039</t>
+  </si>
+  <si>
+    <t>2026-06-04T21:11:55.2220815+05:30</t>
+  </si>
+  <si>
+    <t>21:11:55.222</t>
+  </si>
+  <si>
     <t>Generated</t>
   </si>
   <si>
-    <t>2026-06-04T21:08:53+05:30</t>
+    <t>2026-06-04T21:14:08+05:30</t>
   </si>
   <si>
     <t>Total events</t>
@@ -2360,7 +2372,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>0h 2m 16s</t>
+          <t>0h 7m 31s</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -2380,7 +2392,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>11h 25m 15s</t>
+          <t>11h 26m 25s</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -2390,7 +2402,7 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>21:08:53</t>
+          <t>21:14:08</t>
         </is>
       </c>
     </row>
@@ -2447,17 +2459,17 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>235.0</t>
+          <t>195.0</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>125989.5</t>
+          <t>138561.7</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>1004</t>
+          <t>4841</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -2467,7 +2479,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>332</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -2487,7 +2499,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>11h 23m 20s</t>
+          <t>11h 26m 5s</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -2497,7 +2509,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>21:08:53</t>
+          <t>21:14:08</t>
         </is>
       </c>
     </row>
@@ -2616,7 +2628,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-06-04T21:06:53.4672925+05:30</t>
+          <t>2026-06-04T21:11:55.2220815+05:30</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -2626,7 +2638,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>21:06:53.467</t>
+          <t>21:11:55.222</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -14692,18 +14704,94 @@
         <v>43</v>
       </c>
     </row>
+    <row r="283">
+      <c r="A283" s="4">
+        <v>266</v>
+      </c>
+      <c r="B283" s="4" t="s">
+        <v>581</v>
+      </c>
+      <c r="C283" s="4" t="s">
+        <v>395</v>
+      </c>
+      <c r="D283" s="4" t="s">
+        <v>582</v>
+      </c>
+      <c r="E283" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F283" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G283" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H283" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I283" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J283" s="4">
+        <v>0</v>
+      </c>
+      <c r="K283" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L283" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
     <row r="284">
-      <c r="A284" t="s">
-        <v>581</v>
-      </c>
-      <c r="B284" t="s">
-        <v>582</v>
-      </c>
-      <c r="D284" t="s">
+      <c r="A284" s="4">
+        <v>267</v>
+      </c>
+      <c r="B284" s="4" t="s">
         <v>583</v>
       </c>
-      <c r="E284">
-        <v>265</v>
+      <c r="C284" s="4" t="s">
+        <v>395</v>
+      </c>
+      <c r="D284" s="4" t="s">
+        <v>584</v>
+      </c>
+      <c r="E284" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F284" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G284" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H284" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I284" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J284" s="4">
+        <v>0</v>
+      </c>
+      <c r="K284" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L284" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="s">
+        <v>585</v>
+      </c>
+      <c r="B286" t="s">
+        <v>586</v>
+      </c>
+      <c r="D286" t="s">
+        <v>587</v>
+      </c>
+      <c r="E286">
+        <v>267</v>
       </c>
     </row>
   </sheetData>

--- a/report-2026-06-04.xlsx
+++ b/report-2026-06-04.xlsx
@@ -16,12 +16,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="588" uniqueCount="588">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="592" uniqueCount="592">
   <si>
     <t>PunMonitor Leader Election — Current State</t>
   </si>
   <si>
-    <t>Generated 2026-06-04T21:14:08+05:30</t>
+    <t>Generated 2026-06-04T21:19:16+05:30</t>
   </si>
   <si>
     <t>Election method</t>
@@ -72,7 +72,7 @@
     <t>Leader last update</t>
   </si>
   <si>
-    <t>2026-06-04T21:12:08+05:30 (2m0s ago)</t>
+    <t>2026-06-04T21:17:16+05:30 (2m0s ago)</t>
   </si>
   <si>
     <t>Leader stale?</t>
@@ -87,7 +87,7 @@
     <t>Check count</t>
   </si>
   <si>
-    <t>4</t>
+    <t>8</t>
   </si>
   <si>
     <t>Last error</t>
@@ -1774,10 +1774,22 @@
     <t>21:11:55.222</t>
   </si>
   <si>
+    <t>2026-06-04T21:14:25.1198258+05:30</t>
+  </si>
+  <si>
+    <t>21:14:25.119</t>
+  </si>
+  <si>
+    <t>2026-06-04T21:16:55.4825957+05:30</t>
+  </si>
+  <si>
+    <t>21:16:55.482</t>
+  </si>
+  <si>
     <t>Generated</t>
   </si>
   <si>
-    <t>2026-06-04T21:14:08+05:30</t>
+    <t>2026-06-04T21:19:16+05:30</t>
   </si>
   <si>
     <t>Total events</t>
@@ -2372,7 +2384,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>0h 7m 31s</t>
+          <t>0h 12m 39s</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -2392,7 +2404,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>11h 26m 25s</t>
+          <t>11h 27m 55s</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -2402,7 +2414,7 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>21:14:08</t>
+          <t>21:19:16</t>
         </is>
       </c>
     </row>
@@ -2459,17 +2471,17 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>195.0</t>
+          <t>385.0</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>138561.7</t>
+          <t>99155.5</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>4841</t>
+          <t>9091</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -2479,7 +2491,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>332</t>
+          <t>639</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -2499,7 +2511,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>11h 26m 5s</t>
+          <t>11h 27m 25s</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -2509,7 +2521,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>21:14:08</t>
+          <t>21:19:16</t>
         </is>
       </c>
     </row>
@@ -2628,7 +2640,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-06-04T21:11:55.2220815+05:30</t>
+          <t>2026-06-04T21:16:55.4825957+05:30</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -2638,7 +2650,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>21:11:55.222</t>
+          <t>21:16:55.482</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -14780,18 +14792,94 @@
         <v>43</v>
       </c>
     </row>
+    <row r="285">
+      <c r="A285" s="4">
+        <v>268</v>
+      </c>
+      <c r="B285" s="4" t="s">
+        <v>585</v>
+      </c>
+      <c r="C285" s="4" t="s">
+        <v>395</v>
+      </c>
+      <c r="D285" s="4" t="s">
+        <v>586</v>
+      </c>
+      <c r="E285" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F285" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G285" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H285" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I285" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J285" s="4">
+        <v>0</v>
+      </c>
+      <c r="K285" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L285" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
     <row r="286">
-      <c r="A286" t="s">
-        <v>585</v>
-      </c>
-      <c r="B286" t="s">
-        <v>586</v>
-      </c>
-      <c r="D286" t="s">
+      <c r="A286" s="4">
+        <v>269</v>
+      </c>
+      <c r="B286" s="4" t="s">
         <v>587</v>
       </c>
-      <c r="E286">
-        <v>267</v>
+      <c r="C286" s="4" t="s">
+        <v>395</v>
+      </c>
+      <c r="D286" s="4" t="s">
+        <v>588</v>
+      </c>
+      <c r="E286" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F286" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G286" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H286" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I286" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J286" s="4">
+        <v>0</v>
+      </c>
+      <c r="K286" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L286" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="s">
+        <v>589</v>
+      </c>
+      <c r="B288" t="s">
+        <v>590</v>
+      </c>
+      <c r="D288" t="s">
+        <v>591</v>
+      </c>
+      <c r="E288">
+        <v>269</v>
       </c>
     </row>
   </sheetData>

--- a/report-2026-06-04.xlsx
+++ b/report-2026-06-04.xlsx
@@ -16,12 +16,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="592" uniqueCount="592">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="596" uniqueCount="596">
   <si>
     <t>PunMonitor Leader Election — Current State</t>
   </si>
   <si>
-    <t>Generated 2026-06-04T21:19:16+05:30</t>
+    <t>Generated 2026-06-04T21:24:13+05:30</t>
   </si>
   <si>
     <t>Election method</t>
@@ -72,7 +72,7 @@
     <t>Leader last update</t>
   </si>
   <si>
-    <t>2026-06-04T21:17:16+05:30 (2m0s ago)</t>
+    <t>2026-06-04T21:22:13+05:30 (2m0s ago)</t>
   </si>
   <si>
     <t>Leader stale?</t>
@@ -87,7 +87,7 @@
     <t>Check count</t>
   </si>
   <si>
-    <t>8</t>
+    <t>10</t>
   </si>
   <si>
     <t>Last error</t>
@@ -1786,10 +1786,22 @@
     <t>21:16:55.482</t>
   </si>
   <si>
+    <t>2026-06-04T21:19:47.3805285+05:30</t>
+  </si>
+  <si>
+    <t>21:19:47.380</t>
+  </si>
+  <si>
+    <t>2026-06-04T21:22:13.0559925+05:30</t>
+  </si>
+  <si>
+    <t>21:22:13.055</t>
+  </si>
+  <si>
     <t>Generated</t>
   </si>
   <si>
-    <t>2026-06-04T21:19:16+05:30</t>
+    <t>2026-06-04T21:24:13+05:30</t>
   </si>
   <si>
     <t>Total events</t>
@@ -2384,7 +2396,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>0h 12m 39s</t>
+          <t>0h 17m 36s</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -2404,7 +2416,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>11h 27m 55s</t>
+          <t>11h 30m 15s</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -2414,7 +2426,7 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>21:19:16</t>
+          <t>21:24:13</t>
         </is>
       </c>
     </row>
@@ -2471,17 +2483,17 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>385.0</t>
+          <t>584.0</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>99155.5</t>
+          <t>208725.1</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>9091</t>
+          <t>12968</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -2491,7 +2503,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>639</t>
+          <t>936</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -2511,7 +2523,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>11h 27m 25s</t>
+          <t>11h 29m 45s</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -2521,7 +2533,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>21:19:16</t>
+          <t>21:24:13</t>
         </is>
       </c>
     </row>
@@ -2640,7 +2652,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-06-04T21:16:55.4825957+05:30</t>
+          <t>2026-06-04T21:22:13.0559925+05:30</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -2650,7 +2662,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>21:16:55.482</t>
+          <t>21:22:13.055</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -14868,18 +14880,94 @@
         <v>43</v>
       </c>
     </row>
+    <row r="287">
+      <c r="A287" s="4">
+        <v>270</v>
+      </c>
+      <c r="B287" s="4" t="s">
+        <v>589</v>
+      </c>
+      <c r="C287" s="4" t="s">
+        <v>395</v>
+      </c>
+      <c r="D287" s="4" t="s">
+        <v>590</v>
+      </c>
+      <c r="E287" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F287" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G287" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H287" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I287" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J287" s="4">
+        <v>0</v>
+      </c>
+      <c r="K287" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L287" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
     <row r="288">
-      <c r="A288" t="s">
-        <v>589</v>
-      </c>
-      <c r="B288" t="s">
-        <v>590</v>
-      </c>
-      <c r="D288" t="s">
+      <c r="A288" s="4">
+        <v>271</v>
+      </c>
+      <c r="B288" s="4" t="s">
         <v>591</v>
       </c>
-      <c r="E288">
-        <v>269</v>
+      <c r="C288" s="4" t="s">
+        <v>395</v>
+      </c>
+      <c r="D288" s="4" t="s">
+        <v>592</v>
+      </c>
+      <c r="E288" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F288" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G288" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H288" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I288" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J288" s="4">
+        <v>0</v>
+      </c>
+      <c r="K288" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L288" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="s">
+        <v>593</v>
+      </c>
+      <c r="B290" t="s">
+        <v>594</v>
+      </c>
+      <c r="D290" t="s">
+        <v>595</v>
+      </c>
+      <c r="E290">
+        <v>271</v>
       </c>
     </row>
   </sheetData>

--- a/report-2026-06-04.xlsx
+++ b/report-2026-06-04.xlsx
@@ -16,12 +16,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="596" uniqueCount="596">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="616" uniqueCount="616">
   <si>
     <t>PunMonitor Leader Election — Current State</t>
   </si>
   <si>
-    <t>Generated 2026-06-04T21:24:13+05:30</t>
+    <t>Generated 2026-06-04T21:49:36+05:30</t>
   </si>
   <si>
     <t>Election method</t>
@@ -72,7 +72,7 @@
     <t>Leader last update</t>
   </si>
   <si>
-    <t>2026-06-04T21:22:13+05:30 (2m0s ago)</t>
+    <t>2026-06-04T21:47:36+05:30 (2m0s ago)</t>
   </si>
   <si>
     <t>Leader stale?</t>
@@ -87,7 +87,7 @@
     <t>Check count</t>
   </si>
   <si>
-    <t>10</t>
+    <t>1</t>
   </si>
   <si>
     <t>Last error</t>
@@ -1798,10 +1798,70 @@
     <t>21:22:13.055</t>
   </si>
   <si>
+    <t>2026-06-04T21:24:44.2962887+05:30</t>
+  </si>
+  <si>
+    <t>21:24:44.296</t>
+  </si>
+  <si>
+    <t>2026-06-04T21:27:14.2311071+05:30</t>
+  </si>
+  <si>
+    <t>21:27:14.231</t>
+  </si>
+  <si>
+    <t>2026-06-04T21:29:44.3855447+05:30</t>
+  </si>
+  <si>
+    <t>21:29:44.385</t>
+  </si>
+  <si>
+    <t>2026-06-04T21:32:14.3598146+05:30</t>
+  </si>
+  <si>
+    <t>21:32:14.359</t>
+  </si>
+  <si>
+    <t>2026-06-04T21:34:44.5075142+05:30</t>
+  </si>
+  <si>
+    <t>21:34:44.507</t>
+  </si>
+  <si>
+    <t>2026-06-04T21:37:14.3841481+05:30</t>
+  </si>
+  <si>
+    <t>21:37:14.384</t>
+  </si>
+  <si>
+    <t>2026-06-04T21:39:44.4743208+05:30</t>
+  </si>
+  <si>
+    <t>21:39:44.474</t>
+  </si>
+  <si>
+    <t>2026-06-04T21:42:14.2316611+05:30</t>
+  </si>
+  <si>
+    <t>21:42:14.231</t>
+  </si>
+  <si>
+    <t>2026-06-04T21:44:44.3156892+05:30</t>
+  </si>
+  <si>
+    <t>21:44:44.315</t>
+  </si>
+  <si>
+    <t>2026-06-04T21:47:04.12608+05:30</t>
+  </si>
+  <si>
+    <t>21:47:04.126</t>
+  </si>
+  <si>
     <t>Generated</t>
   </si>
   <si>
-    <t>2026-06-04T21:24:13+05:30</t>
+    <t>2026-06-04T21:49:36+05:30</t>
   </si>
   <si>
     <t>Total events</t>
@@ -2356,7 +2416,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>10.0.50</t>
+          <t>10.0.37</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -2396,12 +2456,12 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>0h 17m 36s</t>
+          <t>0h 2m 12s</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>2026-06-04 21:06:36</t>
+          <t>2026-06-04 21:47:23</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
@@ -2411,12 +2471,12 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2026-06-04 21:06:36</t>
+          <t>2026-06-04 21:47:23</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>11h 30m 15s</t>
+          <t>11h 46m 30s</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -2426,7 +2486,7 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>21:24:13</t>
+          <t>21:49:36</t>
         </is>
       </c>
     </row>
@@ -2463,7 +2523,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>10.0.50</t>
+          <t>10.0.37</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -2483,17 +2543,17 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>584.0</t>
+          <t>109.0</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>208725.1</t>
+          <t>189507.5</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>12968</t>
+          <t>820</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -2503,7 +2563,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>936</t>
+          <t>13</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -2518,12 +2578,12 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-06-04 21:06:36</t>
+          <t>2026-06-04 21:47:23</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>11h 29m 45s</t>
+          <t>11h 46m 10s</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -2533,7 +2593,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>21:24:13</t>
+          <t>21:49:36</t>
         </is>
       </c>
     </row>
@@ -2652,7 +2712,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-06-04T21:22:13.0559925+05:30</t>
+          <t>2026-06-04T21:47:04.12608+05:30</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -2662,7 +2722,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>21:22:13.055</t>
+          <t>21:47:04.126</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -14956,18 +15016,398 @@
         <v>43</v>
       </c>
     </row>
+    <row r="289">
+      <c r="A289" s="4">
+        <v>272</v>
+      </c>
+      <c r="B289" s="4" t="s">
+        <v>593</v>
+      </c>
+      <c r="C289" s="4" t="s">
+        <v>395</v>
+      </c>
+      <c r="D289" s="4" t="s">
+        <v>594</v>
+      </c>
+      <c r="E289" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F289" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G289" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H289" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I289" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J289" s="4">
+        <v>0</v>
+      </c>
+      <c r="K289" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L289" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
     <row r="290">
-      <c r="A290" t="s">
-        <v>593</v>
-      </c>
-      <c r="B290" t="s">
-        <v>594</v>
-      </c>
-      <c r="D290" t="s">
+      <c r="A290" s="4">
+        <v>273</v>
+      </c>
+      <c r="B290" s="4" t="s">
         <v>595</v>
       </c>
-      <c r="E290">
-        <v>271</v>
+      <c r="C290" s="4" t="s">
+        <v>395</v>
+      </c>
+      <c r="D290" s="4" t="s">
+        <v>596</v>
+      </c>
+      <c r="E290" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F290" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G290" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H290" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I290" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J290" s="4">
+        <v>0</v>
+      </c>
+      <c r="K290" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L290" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" s="4">
+        <v>274</v>
+      </c>
+      <c r="B291" s="4" t="s">
+        <v>597</v>
+      </c>
+      <c r="C291" s="4" t="s">
+        <v>395</v>
+      </c>
+      <c r="D291" s="4" t="s">
+        <v>598</v>
+      </c>
+      <c r="E291" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F291" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G291" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H291" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I291" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J291" s="4">
+        <v>0</v>
+      </c>
+      <c r="K291" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L291" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" s="4">
+        <v>275</v>
+      </c>
+      <c r="B292" s="4" t="s">
+        <v>599</v>
+      </c>
+      <c r="C292" s="4" t="s">
+        <v>395</v>
+      </c>
+      <c r="D292" s="4" t="s">
+        <v>600</v>
+      </c>
+      <c r="E292" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F292" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G292" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H292" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I292" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J292" s="4">
+        <v>0</v>
+      </c>
+      <c r="K292" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L292" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" s="4">
+        <v>276</v>
+      </c>
+      <c r="B293" s="4" t="s">
+        <v>601</v>
+      </c>
+      <c r="C293" s="4" t="s">
+        <v>395</v>
+      </c>
+      <c r="D293" s="4" t="s">
+        <v>602</v>
+      </c>
+      <c r="E293" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F293" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G293" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H293" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I293" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J293" s="4">
+        <v>0</v>
+      </c>
+      <c r="K293" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L293" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" s="4">
+        <v>277</v>
+      </c>
+      <c r="B294" s="4" t="s">
+        <v>603</v>
+      </c>
+      <c r="C294" s="4" t="s">
+        <v>395</v>
+      </c>
+      <c r="D294" s="4" t="s">
+        <v>604</v>
+      </c>
+      <c r="E294" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F294" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G294" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H294" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I294" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J294" s="4">
+        <v>0</v>
+      </c>
+      <c r="K294" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L294" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" s="4">
+        <v>278</v>
+      </c>
+      <c r="B295" s="4" t="s">
+        <v>605</v>
+      </c>
+      <c r="C295" s="4" t="s">
+        <v>395</v>
+      </c>
+      <c r="D295" s="4" t="s">
+        <v>606</v>
+      </c>
+      <c r="E295" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F295" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G295" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H295" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I295" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J295" s="4">
+        <v>0</v>
+      </c>
+      <c r="K295" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L295" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" s="4">
+        <v>279</v>
+      </c>
+      <c r="B296" s="4" t="s">
+        <v>607</v>
+      </c>
+      <c r="C296" s="4" t="s">
+        <v>395</v>
+      </c>
+      <c r="D296" s="4" t="s">
+        <v>608</v>
+      </c>
+      <c r="E296" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F296" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G296" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H296" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I296" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J296" s="4">
+        <v>0</v>
+      </c>
+      <c r="K296" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L296" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" s="4">
+        <v>280</v>
+      </c>
+      <c r="B297" s="4" t="s">
+        <v>609</v>
+      </c>
+      <c r="C297" s="4" t="s">
+        <v>395</v>
+      </c>
+      <c r="D297" s="4" t="s">
+        <v>610</v>
+      </c>
+      <c r="E297" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F297" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G297" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H297" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I297" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J297" s="4">
+        <v>0</v>
+      </c>
+      <c r="K297" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L297" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" s="4">
+        <v>281</v>
+      </c>
+      <c r="B298" s="4" t="s">
+        <v>611</v>
+      </c>
+      <c r="C298" s="4" t="s">
+        <v>395</v>
+      </c>
+      <c r="D298" s="4" t="s">
+        <v>612</v>
+      </c>
+      <c r="E298" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F298" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G298" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H298" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I298" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J298" s="4">
+        <v>0</v>
+      </c>
+      <c r="K298" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L298" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="s">
+        <v>613</v>
+      </c>
+      <c r="B300" t="s">
+        <v>614</v>
+      </c>
+      <c r="D300" t="s">
+        <v>615</v>
+      </c>
+      <c r="E300">
+        <v>281</v>
       </c>
     </row>
   </sheetData>

--- a/report-2026-06-04.xlsx
+++ b/report-2026-06-04.xlsx
@@ -16,12 +16,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="616" uniqueCount="616">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="626" uniqueCount="626">
   <si>
     <t>PunMonitor Leader Election — Current State</t>
   </si>
   <si>
-    <t>Generated 2026-06-04T21:49:36+05:30</t>
+    <t>Generated 2026-06-04T22:01:05+05:30</t>
   </si>
   <si>
     <t>Election method</t>
@@ -72,7 +72,7 @@
     <t>Leader last update</t>
   </si>
   <si>
-    <t>2026-06-04T21:47:36+05:30 (2m0s ago)</t>
+    <t>2026-06-04T21:59:05+05:30 (2m0s ago)</t>
   </si>
   <si>
     <t>Leader stale?</t>
@@ -1858,10 +1858,40 @@
     <t>21:47:04.126</t>
   </si>
   <si>
+    <t>2026-06-04T21:50:07.8333054+05:30</t>
+  </si>
+  <si>
+    <t>21:50:07.833</t>
+  </si>
+  <si>
+    <t>2026-06-04T21:52:37.7648135+05:30</t>
+  </si>
+  <si>
+    <t>21:52:37.764</t>
+  </si>
+  <si>
+    <t>2026-06-04T21:55:07.9401045+05:30</t>
+  </si>
+  <si>
+    <t>21:55:07.940</t>
+  </si>
+  <si>
+    <t>2026-06-04T21:57:28.1352897+05:30</t>
+  </si>
+  <si>
+    <t>21:57:28.135</t>
+  </si>
+  <si>
+    <t>2026-06-04T21:59:05.4216426+05:30</t>
+  </si>
+  <si>
+    <t>21:59:05.421</t>
+  </si>
+  <si>
     <t>Generated</t>
   </si>
   <si>
-    <t>2026-06-04T21:49:36+05:30</t>
+    <t>2026-06-04T22:01:05+05:30</t>
   </si>
   <si>
     <t>Total events</t>
@@ -2416,7 +2446,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>10.0.37</t>
+          <t>10.0.51</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -2456,12 +2486,12 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>0h 2m 12s</t>
+          <t>0h 2m 16s</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>2026-06-04 21:47:23</t>
+          <t>2026-06-04 21:58:49</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
@@ -2471,12 +2501,12 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2026-06-04 21:47:23</t>
+          <t>2026-06-04 21:58:49</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>11h 46m 30s</t>
+          <t>11h 48m 30s</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -2486,7 +2516,7 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>21:49:36</t>
+          <t>22:01:05</t>
         </is>
       </c>
     </row>
@@ -2523,7 +2553,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>10.0.37</t>
+          <t>10.0.51</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -2538,22 +2568,22 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>good</t>
+          <t>stale</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>109.0</t>
+          <t>2945.0</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>189507.5</t>
+          <t>209709.1</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>820</t>
+          <t>317</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -2563,7 +2593,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>16</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -2578,12 +2608,12 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-06-04 21:47:23</t>
+          <t>2026-06-04 21:58:49</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>11h 46m 10s</t>
+          <t>11h 48m 30s</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -2593,7 +2623,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>21:49:36</t>
+          <t>22:01:05</t>
         </is>
       </c>
     </row>
@@ -2712,7 +2742,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-06-04T21:47:04.12608+05:30</t>
+          <t>2026-06-04T21:59:05.4216426+05:30</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -2722,7 +2752,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>21:47:04.126</t>
+          <t>21:59:05.421</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -15396,18 +15426,208 @@
         <v>43</v>
       </c>
     </row>
+    <row r="299">
+      <c r="A299" s="4">
+        <v>282</v>
+      </c>
+      <c r="B299" s="4" t="s">
+        <v>613</v>
+      </c>
+      <c r="C299" s="4" t="s">
+        <v>395</v>
+      </c>
+      <c r="D299" s="4" t="s">
+        <v>614</v>
+      </c>
+      <c r="E299" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F299" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G299" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H299" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I299" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J299" s="4">
+        <v>0</v>
+      </c>
+      <c r="K299" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L299" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
     <row r="300">
-      <c r="A300" t="s">
-        <v>613</v>
-      </c>
-      <c r="B300" t="s">
-        <v>614</v>
-      </c>
-      <c r="D300" t="s">
+      <c r="A300" s="4">
+        <v>283</v>
+      </c>
+      <c r="B300" s="4" t="s">
         <v>615</v>
       </c>
-      <c r="E300">
-        <v>281</v>
+      <c r="C300" s="4" t="s">
+        <v>395</v>
+      </c>
+      <c r="D300" s="4" t="s">
+        <v>616</v>
+      </c>
+      <c r="E300" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F300" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G300" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H300" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I300" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J300" s="4">
+        <v>0</v>
+      </c>
+      <c r="K300" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L300" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" s="4">
+        <v>284</v>
+      </c>
+      <c r="B301" s="4" t="s">
+        <v>617</v>
+      </c>
+      <c r="C301" s="4" t="s">
+        <v>395</v>
+      </c>
+      <c r="D301" s="4" t="s">
+        <v>618</v>
+      </c>
+      <c r="E301" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F301" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G301" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H301" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I301" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J301" s="4">
+        <v>0</v>
+      </c>
+      <c r="K301" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L301" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" s="4">
+        <v>285</v>
+      </c>
+      <c r="B302" s="4" t="s">
+        <v>619</v>
+      </c>
+      <c r="C302" s="4" t="s">
+        <v>395</v>
+      </c>
+      <c r="D302" s="4" t="s">
+        <v>620</v>
+      </c>
+      <c r="E302" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F302" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G302" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H302" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I302" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J302" s="4">
+        <v>0</v>
+      </c>
+      <c r="K302" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L302" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" s="4">
+        <v>286</v>
+      </c>
+      <c r="B303" s="4" t="s">
+        <v>621</v>
+      </c>
+      <c r="C303" s="4" t="s">
+        <v>395</v>
+      </c>
+      <c r="D303" s="4" t="s">
+        <v>622</v>
+      </c>
+      <c r="E303" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F303" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G303" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H303" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I303" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J303" s="4">
+        <v>0</v>
+      </c>
+      <c r="K303" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L303" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="s">
+        <v>623</v>
+      </c>
+      <c r="B305" t="s">
+        <v>624</v>
+      </c>
+      <c r="D305" t="s">
+        <v>625</v>
+      </c>
+      <c r="E305">
+        <v>286</v>
       </c>
     </row>
   </sheetData>

--- a/report-2026-06-04.xlsx
+++ b/report-2026-06-04.xlsx
@@ -16,12 +16,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="626" uniqueCount="626">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="636" uniqueCount="636">
   <si>
     <t>PunMonitor Leader Election — Current State</t>
   </si>
   <si>
-    <t>Generated 2026-06-04T22:01:05+05:30</t>
+    <t>Generated 2026-06-04T22:13:19+05:30</t>
   </si>
   <si>
     <t>Election method</t>
@@ -72,7 +72,7 @@
     <t>Leader last update</t>
   </si>
   <si>
-    <t>2026-06-04T21:59:05+05:30 (2m0s ago)</t>
+    <t>2026-06-04T22:11:19+05:30 (2m0s ago)</t>
   </si>
   <si>
     <t>Leader stale?</t>
@@ -1888,10 +1888,40 @@
     <t>21:59:05.421</t>
   </si>
   <si>
+    <t>2026-06-04T22:01:36.9458187+05:30</t>
+  </si>
+  <si>
+    <t>22:01:36.945</t>
+  </si>
+  <si>
+    <t>2026-06-04T22:04:07.0640102+05:30</t>
+  </si>
+  <si>
+    <t>22:04:07.064</t>
+  </si>
+  <si>
+    <t>2026-06-04T22:06:36.9430895+05:30</t>
+  </si>
+  <si>
+    <t>22:06:36.943</t>
+  </si>
+  <si>
+    <t>2026-06-04T22:09:07.0426445+05:30</t>
+  </si>
+  <si>
+    <t>22:09:07.042</t>
+  </si>
+  <si>
+    <t>2026-06-04T22:11:19.6060718+05:30</t>
+  </si>
+  <si>
+    <t>22:11:19.606</t>
+  </si>
+  <si>
     <t>Generated</t>
   </si>
   <si>
-    <t>2026-06-04T22:01:05+05:30</t>
+    <t>2026-06-04T22:13:19+05:30</t>
   </si>
   <si>
     <t>Total events</t>
@@ -2446,7 +2476,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>10.0.51</t>
+          <t>10.0.52</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -2491,7 +2521,7 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>2026-06-04 21:58:49</t>
+          <t>2026-06-04 22:11:03</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
@@ -2501,12 +2531,12 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2026-06-04 21:58:49</t>
+          <t>2026-06-04 22:11:03</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>11h 48m 30s</t>
+          <t>11h 55m 25s</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -2516,7 +2546,7 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>22:01:05</t>
+          <t>22:13:19</t>
         </is>
       </c>
     </row>
@@ -2553,7 +2583,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>10.0.51</t>
+          <t>10.0.52</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -2568,22 +2598,22 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>stale</t>
+          <t>good</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2945.0</t>
+          <t>162.0</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>209709.1</t>
+          <t>310435.5</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>317</t>
+          <t>853</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -2608,12 +2638,12 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-06-04 21:58:49</t>
+          <t>2026-06-04 22:11:03</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>11h 48m 30s</t>
+          <t>11h 53m 25s</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -2623,7 +2653,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>22:01:05</t>
+          <t>22:13:19</t>
         </is>
       </c>
     </row>
@@ -2742,7 +2772,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-06-04T21:59:05.4216426+05:30</t>
+          <t>2026-06-04T22:11:19.6060718+05:30</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -2752,7 +2782,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>21:59:05.421</t>
+          <t>22:11:19.606</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -15616,18 +15646,208 @@
         <v>43</v>
       </c>
     </row>
+    <row r="304">
+      <c r="A304" s="4">
+        <v>287</v>
+      </c>
+      <c r="B304" s="4" t="s">
+        <v>623</v>
+      </c>
+      <c r="C304" s="4" t="s">
+        <v>395</v>
+      </c>
+      <c r="D304" s="4" t="s">
+        <v>624</v>
+      </c>
+      <c r="E304" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F304" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G304" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H304" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I304" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J304" s="4">
+        <v>0</v>
+      </c>
+      <c r="K304" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L304" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
     <row r="305">
-      <c r="A305" t="s">
-        <v>623</v>
-      </c>
-      <c r="B305" t="s">
-        <v>624</v>
-      </c>
-      <c r="D305" t="s">
+      <c r="A305" s="4">
+        <v>288</v>
+      </c>
+      <c r="B305" s="4" t="s">
         <v>625</v>
       </c>
-      <c r="E305">
-        <v>286</v>
+      <c r="C305" s="4" t="s">
+        <v>395</v>
+      </c>
+      <c r="D305" s="4" t="s">
+        <v>626</v>
+      </c>
+      <c r="E305" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F305" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G305" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H305" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I305" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J305" s="4">
+        <v>0</v>
+      </c>
+      <c r="K305" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L305" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" s="4">
+        <v>289</v>
+      </c>
+      <c r="B306" s="4" t="s">
+        <v>627</v>
+      </c>
+      <c r="C306" s="4" t="s">
+        <v>395</v>
+      </c>
+      <c r="D306" s="4" t="s">
+        <v>628</v>
+      </c>
+      <c r="E306" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F306" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G306" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H306" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I306" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J306" s="4">
+        <v>0</v>
+      </c>
+      <c r="K306" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L306" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" s="4">
+        <v>290</v>
+      </c>
+      <c r="B307" s="4" t="s">
+        <v>629</v>
+      </c>
+      <c r="C307" s="4" t="s">
+        <v>395</v>
+      </c>
+      <c r="D307" s="4" t="s">
+        <v>630</v>
+      </c>
+      <c r="E307" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F307" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G307" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H307" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I307" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J307" s="4">
+        <v>0</v>
+      </c>
+      <c r="K307" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L307" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" s="4">
+        <v>291</v>
+      </c>
+      <c r="B308" s="4" t="s">
+        <v>631</v>
+      </c>
+      <c r="C308" s="4" t="s">
+        <v>395</v>
+      </c>
+      <c r="D308" s="4" t="s">
+        <v>632</v>
+      </c>
+      <c r="E308" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F308" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G308" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H308" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I308" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J308" s="4">
+        <v>0</v>
+      </c>
+      <c r="K308" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L308" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="s">
+        <v>633</v>
+      </c>
+      <c r="B310" t="s">
+        <v>634</v>
+      </c>
+      <c r="D310" t="s">
+        <v>635</v>
+      </c>
+      <c r="E310">
+        <v>291</v>
       </c>
     </row>
   </sheetData>

--- a/report-2026-06-04.xlsx
+++ b/report-2026-06-04.xlsx
@@ -16,12 +16,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="636" uniqueCount="636">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="640" uniqueCount="640">
   <si>
     <t>PunMonitor Leader Election — Current State</t>
   </si>
   <si>
-    <t>Generated 2026-06-04T22:13:19+05:30</t>
+    <t>Generated 2026-06-04T22:17:56+05:30</t>
   </si>
   <si>
     <t>Election method</t>
@@ -72,7 +72,7 @@
     <t>Leader last update</t>
   </si>
   <si>
-    <t>2026-06-04T22:11:19+05:30 (2m0s ago)</t>
+    <t>2026-06-04T22:15:55+05:30 (2m0s ago)</t>
   </si>
   <si>
     <t>Leader stale?</t>
@@ -1918,10 +1918,22 @@
     <t>22:11:19.606</t>
   </si>
   <si>
+    <t>2026-06-04T22:13:51.3073971+05:30</t>
+  </si>
+  <si>
+    <t>22:13:51.307</t>
+  </si>
+  <si>
+    <t>2026-06-04T22:15:55.3079261+05:30</t>
+  </si>
+  <si>
+    <t>22:15:55.307</t>
+  </si>
+  <si>
     <t>Generated</t>
   </si>
   <si>
-    <t>2026-06-04T22:13:19+05:30</t>
+    <t>2026-06-04T22:17:56+05:30</t>
   </si>
   <si>
     <t>Total events</t>
@@ -2521,7 +2533,7 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>2026-06-04 22:11:03</t>
+          <t>2026-06-04 22:15:39</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
@@ -2531,12 +2543,12 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2026-06-04 22:11:03</t>
+          <t>2026-06-04 22:15:39</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>11h 55m 25s</t>
+          <t>11h 59m 50s</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -2546,7 +2558,7 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>22:13:19</t>
+          <t>22:17:56</t>
         </is>
       </c>
     </row>
@@ -2603,17 +2615,17 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>162.0</t>
+          <t>292.0</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>310435.5</t>
+          <t>310067.5</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>853</t>
+          <t>512</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -2623,7 +2635,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>17</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -2638,12 +2650,12 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-06-04 22:11:03</t>
+          <t>2026-06-04 22:15:39</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>11h 53m 25s</t>
+          <t>11h 57m 50s</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -2653,7 +2665,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>22:13:19</t>
+          <t>22:17:56</t>
         </is>
       </c>
     </row>
@@ -2772,7 +2784,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-06-04T22:11:19.6060718+05:30</t>
+          <t>2026-06-04T22:15:55.3079261+05:30</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -2782,7 +2794,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>22:11:19.606</t>
+          <t>22:15:55.307</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -15836,18 +15848,94 @@
         <v>43</v>
       </c>
     </row>
+    <row r="309">
+      <c r="A309" s="4">
+        <v>292</v>
+      </c>
+      <c r="B309" s="4" t="s">
+        <v>633</v>
+      </c>
+      <c r="C309" s="4" t="s">
+        <v>395</v>
+      </c>
+      <c r="D309" s="4" t="s">
+        <v>634</v>
+      </c>
+      <c r="E309" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F309" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G309" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H309" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I309" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J309" s="4">
+        <v>0</v>
+      </c>
+      <c r="K309" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L309" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
     <row r="310">
-      <c r="A310" t="s">
-        <v>633</v>
-      </c>
-      <c r="B310" t="s">
-        <v>634</v>
-      </c>
-      <c r="D310" t="s">
+      <c r="A310" s="4">
+        <v>293</v>
+      </c>
+      <c r="B310" s="4" t="s">
         <v>635</v>
       </c>
-      <c r="E310">
-        <v>291</v>
+      <c r="C310" s="4" t="s">
+        <v>395</v>
+      </c>
+      <c r="D310" s="4" t="s">
+        <v>636</v>
+      </c>
+      <c r="E310" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F310" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G310" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H310" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I310" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J310" s="4">
+        <v>0</v>
+      </c>
+      <c r="K310" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L310" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="s">
+        <v>637</v>
+      </c>
+      <c r="B312" t="s">
+        <v>638</v>
+      </c>
+      <c r="D312" t="s">
+        <v>639</v>
+      </c>
+      <c r="E312">
+        <v>293</v>
       </c>
     </row>
   </sheetData>

--- a/report-2026-06-04.xlsx
+++ b/report-2026-06-04.xlsx
@@ -16,12 +16,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="640" uniqueCount="640">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="644" uniqueCount="644">
   <si>
     <t>PunMonitor Leader Election — Current State</t>
   </si>
   <si>
-    <t>Generated 2026-06-04T22:17:56+05:30</t>
+    <t>Generated 2026-06-04T22:22:10+05:30</t>
   </si>
   <si>
     <t>Election method</t>
@@ -72,7 +72,7 @@
     <t>Leader last update</t>
   </si>
   <si>
-    <t>2026-06-04T22:15:55+05:30 (2m0s ago)</t>
+    <t>2026-06-04T22:20:10+05:30 (2m0s ago)</t>
   </si>
   <si>
     <t>Leader stale?</t>
@@ -1930,10 +1930,22 @@
     <t>22:15:55.307</t>
   </si>
   <si>
+    <t>2026-06-04T22:18:27.2919849+05:30</t>
+  </si>
+  <si>
+    <t>22:18:27.291</t>
+  </si>
+  <si>
+    <t>2026-06-04T22:20:10.0260388+05:30</t>
+  </si>
+  <si>
+    <t>22:20:10.026</t>
+  </si>
+  <si>
     <t>Generated</t>
   </si>
   <si>
-    <t>2026-06-04T22:17:56+05:30</t>
+    <t>2026-06-04T22:22:10+05:30</t>
   </si>
   <si>
     <t>Total events</t>
@@ -2488,7 +2500,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>10.0.52</t>
+          <t>10.0.53</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -2528,12 +2540,12 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>0h 2m 16s</t>
+          <t>0h 2m 15s</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>2026-06-04 22:15:39</t>
+          <t>2026-06-04 22:19:55</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
@@ -2543,12 +2555,12 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2026-06-04 22:15:39</t>
+          <t>2026-06-04 22:19:55</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>11h 59m 50s</t>
+          <t>12h 3m 50s</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -2558,7 +2570,7 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>22:17:56</t>
+          <t>22:22:10</t>
         </is>
       </c>
     </row>
@@ -2595,7 +2607,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>10.0.52</t>
+          <t>10.0.53</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -2615,17 +2627,17 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>292.0</t>
+          <t>215.0</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>310067.5</t>
+          <t>310621.5</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>512</t>
+          <t>590</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -2635,7 +2647,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>15</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -2650,12 +2662,12 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-06-04 22:15:39</t>
+          <t>2026-06-04 22:19:55</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>11h 57m 50s</t>
+          <t>12h 1m 50s</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -2665,7 +2677,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>22:17:56</t>
+          <t>22:22:10</t>
         </is>
       </c>
     </row>
@@ -2784,7 +2796,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-06-04T22:15:55.3079261+05:30</t>
+          <t>2026-06-04T22:20:10.0260388+05:30</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -2794,7 +2806,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>22:15:55.307</t>
+          <t>22:20:10.026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -15924,18 +15936,94 @@
         <v>43</v>
       </c>
     </row>
+    <row r="311">
+      <c r="A311" s="4">
+        <v>294</v>
+      </c>
+      <c r="B311" s="4" t="s">
+        <v>637</v>
+      </c>
+      <c r="C311" s="4" t="s">
+        <v>395</v>
+      </c>
+      <c r="D311" s="4" t="s">
+        <v>638</v>
+      </c>
+      <c r="E311" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F311" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G311" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H311" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I311" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J311" s="4">
+        <v>0</v>
+      </c>
+      <c r="K311" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L311" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
     <row r="312">
-      <c r="A312" t="s">
-        <v>637</v>
-      </c>
-      <c r="B312" t="s">
-        <v>638</v>
-      </c>
-      <c r="D312" t="s">
+      <c r="A312" s="4">
+        <v>295</v>
+      </c>
+      <c r="B312" s="4" t="s">
         <v>639</v>
       </c>
-      <c r="E312">
-        <v>293</v>
+      <c r="C312" s="4" t="s">
+        <v>395</v>
+      </c>
+      <c r="D312" s="4" t="s">
+        <v>640</v>
+      </c>
+      <c r="E312" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F312" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G312" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H312" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I312" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J312" s="4">
+        <v>0</v>
+      </c>
+      <c r="K312" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L312" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="s">
+        <v>641</v>
+      </c>
+      <c r="B314" t="s">
+        <v>642</v>
+      </c>
+      <c r="D314" t="s">
+        <v>643</v>
+      </c>
+      <c r="E314">
+        <v>295</v>
       </c>
     </row>
   </sheetData>

--- a/report-2026-06-04.xlsx
+++ b/report-2026-06-04.xlsx
@@ -16,12 +16,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="644" uniqueCount="644">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="682" uniqueCount="682">
   <si>
     <t>PunMonitor Leader Election — Current State</t>
   </si>
   <si>
-    <t>Generated 2026-06-04T22:22:10+05:30</t>
+    <t>Generated 2026-06-04T23:14:01+05:30</t>
   </si>
   <si>
     <t>Election method</t>
@@ -72,7 +72,7 @@
     <t>Leader last update</t>
   </si>
   <si>
-    <t>2026-06-04T22:20:10+05:30 (2m0s ago)</t>
+    <t>2026-06-04T23:12:01+05:30 (2m0s ago)</t>
   </si>
   <si>
     <t>Leader stale?</t>
@@ -1942,10 +1942,124 @@
     <t>22:20:10.026</t>
   </si>
   <si>
+    <t>2026-06-04T22:22:41.4491888+05:30</t>
+  </si>
+  <si>
+    <t>22:22:41.449</t>
+  </si>
+  <si>
+    <t>2026-06-04T22:25:11.7219628+05:30</t>
+  </si>
+  <si>
+    <t>22:25:11.721</t>
+  </si>
+  <si>
+    <t>2026-06-04T22:27:41.4915352+05:30</t>
+  </si>
+  <si>
+    <t>22:27:41.491</t>
+  </si>
+  <si>
+    <t>2026-06-04T22:30:11.8675445+05:30</t>
+  </si>
+  <si>
+    <t>22:30:11.867</t>
+  </si>
+  <si>
+    <t>2026-06-04T22:32:41.7629578+05:30</t>
+  </si>
+  <si>
+    <t>22:32:41.762</t>
+  </si>
+  <si>
+    <t>2026-06-04T22:35:11.5176423+05:30</t>
+  </si>
+  <si>
+    <t>22:35:11.517</t>
+  </si>
+  <si>
+    <t>2026-06-04T22:37:41.6876879+05:30</t>
+  </si>
+  <si>
+    <t>22:37:41.687</t>
+  </si>
+  <si>
+    <t>2026-06-04T22:40:11.5009214+05:30</t>
+  </si>
+  <si>
+    <t>22:40:11.500</t>
+  </si>
+  <si>
+    <t>2026-06-04T22:42:41.8167422+05:30</t>
+  </si>
+  <si>
+    <t>22:42:41.816</t>
+  </si>
+  <si>
+    <t>2026-06-04T22:45:11.7301221+05:30</t>
+  </si>
+  <si>
+    <t>22:45:11.730</t>
+  </si>
+  <si>
+    <t>2026-06-04T22:47:41.621485+05:30</t>
+  </si>
+  <si>
+    <t>22:47:41.621</t>
+  </si>
+  <si>
+    <t>2026-06-04T22:50:11.5957599+05:30</t>
+  </si>
+  <si>
+    <t>22:50:11.595</t>
+  </si>
+  <si>
+    <t>2026-06-04T22:52:41.6193318+05:30</t>
+  </si>
+  <si>
+    <t>22:52:41.619</t>
+  </si>
+  <si>
+    <t>2026-06-04T22:55:11.459619+05:30</t>
+  </si>
+  <si>
+    <t>22:55:11.459</t>
+  </si>
+  <si>
+    <t>2026-06-04T22:57:41.5635643+05:30</t>
+  </si>
+  <si>
+    <t>22:57:41.563</t>
+  </si>
+  <si>
+    <t>2026-06-04T23:00:11.5520351+05:30</t>
+  </si>
+  <si>
+    <t>23:00:11.552</t>
+  </si>
+  <si>
+    <t>2026-06-04T23:02:41.6187355+05:30</t>
+  </si>
+  <si>
+    <t>23:02:41.618</t>
+  </si>
+  <si>
+    <t>2026-06-04T23:05:11.6612849+05:30</t>
+  </si>
+  <si>
+    <t>23:05:11.661</t>
+  </si>
+  <si>
+    <t>2026-06-04T23:12:01.1735119+05:30</t>
+  </si>
+  <si>
+    <t>23:12:01.173</t>
+  </si>
+  <si>
     <t>Generated</t>
   </si>
   <si>
-    <t>2026-06-04T22:22:10+05:30</t>
+    <t>2026-06-04T23:14:01+05:30</t>
   </si>
   <si>
     <t>Total events</t>
@@ -2500,7 +2614,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>10.0.53</t>
+          <t>10.0.54</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -2545,7 +2659,7 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>2026-06-04 22:19:55</t>
+          <t>2026-06-04 23:11:46</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
@@ -2555,12 +2669,12 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2026-06-04 22:19:55</t>
+          <t>2026-06-04 23:11:46</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>12h 3m 50s</t>
+          <t>12h 31m 40s</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -2570,7 +2684,7 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>22:22:10</t>
+          <t>23:14:01</t>
         </is>
       </c>
     </row>
@@ -2607,7 +2721,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>10.0.53</t>
+          <t>10.0.54</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -2627,17 +2741,17 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>215.0</t>
+          <t>249.0</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>310621.5</t>
+          <t>485008.3</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>590</t>
+          <t>792</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -2662,12 +2776,12 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-06-04 22:19:55</t>
+          <t>2026-06-04 23:11:46</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>12h 1m 50s</t>
+          <t>12h 29m 40s</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -2677,7 +2791,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>22:22:10</t>
+          <t>23:14:01</t>
         </is>
       </c>
     </row>
@@ -2796,7 +2910,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-06-04T22:20:10.0260388+05:30</t>
+          <t>2026-06-04T23:12:01.1735119+05:30</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -2806,7 +2920,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>22:20:10.026</t>
+          <t>23:12:01.173</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -16012,18 +16126,740 @@
         <v>43</v>
       </c>
     </row>
+    <row r="313">
+      <c r="A313" s="4">
+        <v>296</v>
+      </c>
+      <c r="B313" s="4" t="s">
+        <v>641</v>
+      </c>
+      <c r="C313" s="4" t="s">
+        <v>395</v>
+      </c>
+      <c r="D313" s="4" t="s">
+        <v>642</v>
+      </c>
+      <c r="E313" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F313" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G313" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H313" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I313" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J313" s="4">
+        <v>0</v>
+      </c>
+      <c r="K313" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L313" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
     <row r="314">
-      <c r="A314" t="s">
-        <v>641</v>
-      </c>
-      <c r="B314" t="s">
-        <v>642</v>
-      </c>
-      <c r="D314" t="s">
+      <c r="A314" s="4">
+        <v>297</v>
+      </c>
+      <c r="B314" s="4" t="s">
         <v>643</v>
       </c>
-      <c r="E314">
-        <v>295</v>
+      <c r="C314" s="4" t="s">
+        <v>395</v>
+      </c>
+      <c r="D314" s="4" t="s">
+        <v>644</v>
+      </c>
+      <c r="E314" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F314" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G314" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H314" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I314" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J314" s="4">
+        <v>0</v>
+      </c>
+      <c r="K314" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L314" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" s="4">
+        <v>298</v>
+      </c>
+      <c r="B315" s="4" t="s">
+        <v>645</v>
+      </c>
+      <c r="C315" s="4" t="s">
+        <v>395</v>
+      </c>
+      <c r="D315" s="4" t="s">
+        <v>646</v>
+      </c>
+      <c r="E315" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F315" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G315" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H315" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I315" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J315" s="4">
+        <v>0</v>
+      </c>
+      <c r="K315" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L315" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" s="4">
+        <v>299</v>
+      </c>
+      <c r="B316" s="4" t="s">
+        <v>647</v>
+      </c>
+      <c r="C316" s="4" t="s">
+        <v>395</v>
+      </c>
+      <c r="D316" s="4" t="s">
+        <v>648</v>
+      </c>
+      <c r="E316" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F316" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G316" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H316" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I316" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J316" s="4">
+        <v>0</v>
+      </c>
+      <c r="K316" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L316" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" s="4">
+        <v>300</v>
+      </c>
+      <c r="B317" s="4" t="s">
+        <v>649</v>
+      </c>
+      <c r="C317" s="4" t="s">
+        <v>395</v>
+      </c>
+      <c r="D317" s="4" t="s">
+        <v>650</v>
+      </c>
+      <c r="E317" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F317" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G317" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H317" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I317" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J317" s="4">
+        <v>0</v>
+      </c>
+      <c r="K317" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L317" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" s="4">
+        <v>301</v>
+      </c>
+      <c r="B318" s="4" t="s">
+        <v>651</v>
+      </c>
+      <c r="C318" s="4" t="s">
+        <v>395</v>
+      </c>
+      <c r="D318" s="4" t="s">
+        <v>652</v>
+      </c>
+      <c r="E318" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F318" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G318" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H318" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I318" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J318" s="4">
+        <v>0</v>
+      </c>
+      <c r="K318" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L318" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" s="4">
+        <v>302</v>
+      </c>
+      <c r="B319" s="4" t="s">
+        <v>653</v>
+      </c>
+      <c r="C319" s="4" t="s">
+        <v>395</v>
+      </c>
+      <c r="D319" s="4" t="s">
+        <v>654</v>
+      </c>
+      <c r="E319" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F319" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G319" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H319" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I319" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J319" s="4">
+        <v>0</v>
+      </c>
+      <c r="K319" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L319" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" s="4">
+        <v>303</v>
+      </c>
+      <c r="B320" s="4" t="s">
+        <v>655</v>
+      </c>
+      <c r="C320" s="4" t="s">
+        <v>395</v>
+      </c>
+      <c r="D320" s="4" t="s">
+        <v>656</v>
+      </c>
+      <c r="E320" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F320" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G320" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H320" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I320" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J320" s="4">
+        <v>0</v>
+      </c>
+      <c r="K320" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L320" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" s="4">
+        <v>304</v>
+      </c>
+      <c r="B321" s="4" t="s">
+        <v>657</v>
+      </c>
+      <c r="C321" s="4" t="s">
+        <v>395</v>
+      </c>
+      <c r="D321" s="4" t="s">
+        <v>658</v>
+      </c>
+      <c r="E321" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F321" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G321" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H321" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I321" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J321" s="4">
+        <v>0</v>
+      </c>
+      <c r="K321" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L321" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" s="4">
+        <v>305</v>
+      </c>
+      <c r="B322" s="4" t="s">
+        <v>659</v>
+      </c>
+      <c r="C322" s="4" t="s">
+        <v>395</v>
+      </c>
+      <c r="D322" s="4" t="s">
+        <v>660</v>
+      </c>
+      <c r="E322" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F322" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G322" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H322" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I322" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J322" s="4">
+        <v>0</v>
+      </c>
+      <c r="K322" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L322" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" s="4">
+        <v>306</v>
+      </c>
+      <c r="B323" s="4" t="s">
+        <v>661</v>
+      </c>
+      <c r="C323" s="4" t="s">
+        <v>395</v>
+      </c>
+      <c r="D323" s="4" t="s">
+        <v>662</v>
+      </c>
+      <c r="E323" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F323" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G323" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H323" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I323" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J323" s="4">
+        <v>0</v>
+      </c>
+      <c r="K323" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L323" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" s="4">
+        <v>307</v>
+      </c>
+      <c r="B324" s="4" t="s">
+        <v>663</v>
+      </c>
+      <c r="C324" s="4" t="s">
+        <v>395</v>
+      </c>
+      <c r="D324" s="4" t="s">
+        <v>664</v>
+      </c>
+      <c r="E324" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F324" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G324" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H324" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I324" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J324" s="4">
+        <v>0</v>
+      </c>
+      <c r="K324" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L324" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" s="4">
+        <v>308</v>
+      </c>
+      <c r="B325" s="4" t="s">
+        <v>665</v>
+      </c>
+      <c r="C325" s="4" t="s">
+        <v>395</v>
+      </c>
+      <c r="D325" s="4" t="s">
+        <v>666</v>
+      </c>
+      <c r="E325" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F325" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G325" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H325" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I325" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J325" s="4">
+        <v>0</v>
+      </c>
+      <c r="K325" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L325" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" s="4">
+        <v>309</v>
+      </c>
+      <c r="B326" s="4" t="s">
+        <v>667</v>
+      </c>
+      <c r="C326" s="4" t="s">
+        <v>395</v>
+      </c>
+      <c r="D326" s="4" t="s">
+        <v>668</v>
+      </c>
+      <c r="E326" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F326" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G326" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H326" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I326" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J326" s="4">
+        <v>0</v>
+      </c>
+      <c r="K326" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L326" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" s="4">
+        <v>310</v>
+      </c>
+      <c r="B327" s="4" t="s">
+        <v>669</v>
+      </c>
+      <c r="C327" s="4" t="s">
+        <v>395</v>
+      </c>
+      <c r="D327" s="4" t="s">
+        <v>670</v>
+      </c>
+      <c r="E327" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F327" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G327" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H327" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I327" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J327" s="4">
+        <v>0</v>
+      </c>
+      <c r="K327" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L327" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" s="4">
+        <v>311</v>
+      </c>
+      <c r="B328" s="4" t="s">
+        <v>671</v>
+      </c>
+      <c r="C328" s="4" t="s">
+        <v>395</v>
+      </c>
+      <c r="D328" s="4" t="s">
+        <v>672</v>
+      </c>
+      <c r="E328" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F328" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G328" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H328" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I328" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J328" s="4">
+        <v>0</v>
+      </c>
+      <c r="K328" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L328" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" s="4">
+        <v>312</v>
+      </c>
+      <c r="B329" s="4" t="s">
+        <v>673</v>
+      </c>
+      <c r="C329" s="4" t="s">
+        <v>395</v>
+      </c>
+      <c r="D329" s="4" t="s">
+        <v>674</v>
+      </c>
+      <c r="E329" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F329" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G329" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H329" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I329" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J329" s="4">
+        <v>0</v>
+      </c>
+      <c r="K329" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L329" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" s="4">
+        <v>313</v>
+      </c>
+      <c r="B330" s="4" t="s">
+        <v>675</v>
+      </c>
+      <c r="C330" s="4" t="s">
+        <v>395</v>
+      </c>
+      <c r="D330" s="4" t="s">
+        <v>676</v>
+      </c>
+      <c r="E330" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F330" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G330" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H330" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I330" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J330" s="4">
+        <v>0</v>
+      </c>
+      <c r="K330" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L330" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" s="4">
+        <v>314</v>
+      </c>
+      <c r="B331" s="4" t="s">
+        <v>677</v>
+      </c>
+      <c r="C331" s="4" t="s">
+        <v>395</v>
+      </c>
+      <c r="D331" s="4" t="s">
+        <v>678</v>
+      </c>
+      <c r="E331" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F331" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G331" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H331" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I331" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J331" s="4">
+        <v>0</v>
+      </c>
+      <c r="K331" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L331" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="s">
+        <v>679</v>
+      </c>
+      <c r="B333" t="s">
+        <v>680</v>
+      </c>
+      <c r="D333" t="s">
+        <v>681</v>
+      </c>
+      <c r="E333">
+        <v>314</v>
       </c>
     </row>
   </sheetData>
